--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0006990F-52A0-41CB-8028-D9CB1F593CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2662045-31D1-41B7-8B4D-8DCDE9591D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2187,31 +2187,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2257,6 +2237,30 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
@@ -2285,19 +2289,15 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -7962,28 +7962,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="146" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="153"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="154">
+      <c r="H1" s="149">
         <v>45076</v>
       </c>
-      <c r="I1" s="155"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="156">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="157"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -7992,8 +7992,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8005,10 +8005,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="160" t="s">
+      <c r="H2" s="155" t="s">
         <v>329</v>
       </c>
-      <c r="I2" s="161"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8021,25 +8021,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="146"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="149" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="145" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="146"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="147"/>
-      <c r="N3" s="148"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8332,11 +8332,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="163" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="164"/>
-      <c r="I12" s="165"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8397,10 +8397,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="160" t="s">
+      <c r="H14" s="155" t="s">
         <v>330</v>
       </c>
-      <c r="I14" s="161"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8426,11 +8426,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="149" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="150"/>
-      <c r="I15" s="150"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -10759,34 +10759,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="146" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="153"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="154">
+      <c r="G1" s="149">
         <v>45918</v>
       </c>
-      <c r="H1" s="155"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="156">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="157"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="158"/>
-      <c r="B2" s="159"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10798,10 +10798,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="160" t="s">
+      <c r="G2" s="155" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="161"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10814,25 +10814,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="145" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="146"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="149" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="150"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="145" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="146"/>
-      <c r="K3" s="147"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="148"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11195,11 +11195,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="163" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="164"/>
-      <c r="H14" s="165"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11219,10 +11219,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="154">
+      <c r="G15" s="149">
         <v>45918</v>
       </c>
-      <c r="H15" s="155"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11242,10 +11242,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="160" t="s">
+      <c r="G16" s="155" t="s">
         <v>349</v>
       </c>
-      <c r="H16" s="166"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11262,11 +11262,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="149" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="150"/>
-      <c r="H17" s="167"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11606,14 +11606,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="168" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="168"/>
-      <c r="K32" s="169" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="L32" s="170"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11633,11 +11633,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="162">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="162"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>322</v>
       </c>
@@ -11663,11 +11663,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="162">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="162"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11694,11 +11694,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="162">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="162"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85" t="s">
         <v>332</v>
       </c>
@@ -11726,11 +11726,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="162">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="162"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="85" t="s">
         <v>333</v>
       </c>
@@ -11756,11 +11756,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="162">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="162"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85" t="s">
         <v>335</v>
       </c>
@@ -11786,11 +11786,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="162">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="162"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85" t="s">
         <v>322</v>
       </c>
@@ -11808,11 +11808,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="162">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="162"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11835,11 +11835,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="171">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="171"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>176</v>
       </c>
@@ -11860,8 +11860,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="172"/>
-      <c r="J41" s="172"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>177</v>
       </c>
@@ -11877,10 +11877,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="144" t="s">
+      <c r="A43" s="172" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="144"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11900,10 +11900,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="144" t="s">
+      <c r="A44" s="172" t="s">
         <v>290</v>
       </c>
-      <c r="B44" s="144"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -11941,15 +11941,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -11966,6 +11957,15 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
@@ -12015,34 +12015,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="146" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="153"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="154">
+      <c r="G1" s="149">
         <v>46016</v>
       </c>
-      <c r="H1" s="155"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="156">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="157"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="158"/>
-      <c r="B2" s="159"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12054,10 +12054,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="160" t="s">
+      <c r="G2" s="155" t="s">
         <v>352</v>
       </c>
-      <c r="H2" s="161"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12070,25 +12070,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="145" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="146"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="149" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="150"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="145" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="146"/>
-      <c r="K3" s="147"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="148"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12382,11 +12382,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="163" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="164"/>
-      <c r="H14" s="165"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12406,10 +12406,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="154">
+      <c r="G15" s="149">
         <v>46016</v>
       </c>
-      <c r="H15" s="155"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12429,10 +12429,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="160" t="s">
+      <c r="G16" s="155" t="s">
         <v>353</v>
       </c>
-      <c r="H16" s="166"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12449,11 +12449,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="149" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="150"/>
-      <c r="H17" s="167"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12775,14 +12775,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="168" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="168"/>
-      <c r="K32" s="169" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="L32" s="170"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12802,11 +12802,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="162">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="162"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12824,11 +12824,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="162">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="162"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12843,11 +12843,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="162">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="162"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -12863,11 +12863,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="162">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="162"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12881,11 +12881,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="162">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="162"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12899,11 +12899,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="162">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="162"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12917,11 +12917,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="162">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="162"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12940,11 +12940,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="171">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="171"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>176</v>
       </c>
@@ -12965,8 +12965,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="172"/>
-      <c r="J41" s="172"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>177</v>
       </c>
@@ -12982,10 +12982,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="144" t="s">
+      <c r="A43" s="172" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="144"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13005,10 +13005,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="144" t="s">
+      <c r="A44" s="172" t="s">
         <v>290</v>
       </c>
-      <c r="B44" s="144"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13046,15 +13046,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13066,11 +13062,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
@@ -13120,34 +13120,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="146" t="s">
         <v>339</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="153"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="154">
+      <c r="G1" s="149">
         <v>46068</v>
       </c>
-      <c r="H1" s="155"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="156">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>-327672</v>
       </c>
-      <c r="K1" s="157"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="158"/>
-      <c r="B2" s="159"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -13159,11 +13159,11 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="160" t="str">
+      <c r="G2" s="155" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>7 days</v>
-      </c>
-      <c r="H2" s="161"/>
+        <v>10 days</v>
+      </c>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13176,25 +13176,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="145" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="146"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="149" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="150"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="145" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="146"/>
-      <c r="K3" s="147"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="148"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13460,11 +13460,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="163" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="164"/>
-      <c r="H14" s="165"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13484,10 +13484,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="154">
+      <c r="G15" s="149">
         <v>46068</v>
       </c>
-      <c r="H15" s="155"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13507,11 +13507,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="160" t="str">
+      <c r="G16" s="155" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>7 days</v>
-      </c>
-      <c r="H16" s="166"/>
+        <v>10 days</v>
+      </c>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13528,11 +13528,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="149" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="150"/>
-      <c r="H17" s="167"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13855,14 +13855,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="168" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="168"/>
-      <c r="K32" s="169" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="L32" s="170"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -13874,11 +13874,11 @@
       <c r="F33" s="59"/>
       <c r="G33" s="67"/>
       <c r="H33" s="62"/>
-      <c r="I33" s="162">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="162"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85"/>
       <c r="L33" s="136"/>
       <c r="M33" s="15"/>
@@ -13892,11 +13892,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="162">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="162"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -13911,11 +13911,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="162">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="162"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -13931,11 +13931,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="162">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="162"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -13949,11 +13949,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="162">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="162"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -13967,11 +13967,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="162">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="162"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -13985,11 +13985,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="162">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="162"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14008,11 +14008,11 @@
         <v>0</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="171">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="171"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>176</v>
       </c>
@@ -14033,8 +14033,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="172"/>
-      <c r="J41" s="172"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>177</v>
       </c>
@@ -14050,10 +14050,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="144" t="s">
+      <c r="A43" s="172" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="144"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -14073,10 +14073,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="144" t="s">
+      <c r="A44" s="172" t="s">
         <v>290</v>
       </c>
-      <c r="B44" s="144"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -14111,15 +14111,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14131,11 +14127,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
@@ -14218,7 +14218,7 @@
       <c r="M1" s="186"/>
       <c r="N1" s="182" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>2 year, 10 months, 20 days</v>
+        <v>2 year, 10 months, 23 days</v>
       </c>
       <c r="O1" s="183"/>
       <c r="P1" s="183"/>
@@ -15166,28 +15166,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="146" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="153"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="154">
+      <c r="H1" s="149">
         <v>45163</v>
       </c>
-      <c r="I1" s="155"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="156">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="157"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -15196,8 +15196,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -15209,10 +15209,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="160" t="s">
+      <c r="H2" s="155" t="s">
         <v>169</v>
       </c>
-      <c r="I2" s="161"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15225,25 +15225,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="146"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="149" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="145" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="146"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="147"/>
-      <c r="N3" s="148"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -15490,11 +15490,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="163" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="164"/>
-      <c r="I12" s="165"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15515,10 +15515,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="154">
+      <c r="H13" s="149">
         <v>45163</v>
       </c>
-      <c r="I13" s="155"/>
+      <c r="I13" s="150"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15539,10 +15539,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="160" t="s">
+      <c r="H14" s="155" t="s">
         <v>169</v>
       </c>
-      <c r="I14" s="161"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15560,11 +15560,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="149" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="150"/>
-      <c r="I15" s="150"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17328,12 +17328,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17342,6 +17336,12 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
     <cfRule type="duplicateValues" dxfId="55" priority="6"/>
@@ -17398,28 +17398,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="146" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="153"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="154">
+      <c r="H1" s="149">
         <v>45163</v>
       </c>
-      <c r="I1" s="155"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="156">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="157"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17428,8 +17428,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17441,10 +17441,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="160" t="s">
+      <c r="H2" s="155" t="s">
         <v>170</v>
       </c>
-      <c r="I2" s="161"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17457,25 +17457,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="146"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="149" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="145" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="146"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="147"/>
-      <c r="N3" s="148"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17718,11 +17718,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="163" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="164"/>
-      <c r="I12" s="165"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17743,10 +17743,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="154">
+      <c r="H13" s="149">
         <v>45163</v>
       </c>
-      <c r="I13" s="155"/>
+      <c r="I13" s="150"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17767,10 +17767,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="160" t="s">
+      <c r="H14" s="155" t="s">
         <v>170</v>
       </c>
-      <c r="I14" s="161"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17788,11 +17788,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="149" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="150"/>
-      <c r="I15" s="150"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -19626,28 +19626,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="146" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="153"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="154">
+      <c r="H1" s="149">
         <v>45345</v>
       </c>
-      <c r="I1" s="155"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="156">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="157"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -19656,8 +19656,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19669,10 +19669,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="160" t="s">
+      <c r="H2" s="155" t="s">
         <v>344</v>
       </c>
-      <c r="I2" s="161"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19685,25 +19685,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="146"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="149" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="145" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="146"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="147"/>
-      <c r="N3" s="148"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -20045,11 +20045,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="163" t="s">
+      <c r="G14" s="164" t="s">
         <v>178</v>
       </c>
-      <c r="H14" s="164"/>
-      <c r="I14" s="165"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20070,10 +20070,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="154">
+      <c r="H15" s="149">
         <v>45345</v>
       </c>
-      <c r="I15" s="155"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20115,11 +20115,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="149" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="150"/>
-      <c r="I17" s="167"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20356,10 +20356,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="168" t="s">
+      <c r="J28" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="168"/>
+      <c r="K28" s="169"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20378,11 +20378,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="162">
+      <c r="J29" s="163">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="162"/>
+      <c r="K29" s="163"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20407,11 +20407,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="162">
+      <c r="J30" s="163">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="162"/>
+      <c r="K30" s="163"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20436,11 +20436,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="162">
+      <c r="J31" s="163">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="162"/>
+      <c r="K31" s="163"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20465,11 +20465,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="162">
+      <c r="J32" s="163">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="162"/>
+      <c r="K32" s="163"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20494,11 +20494,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="162">
+      <c r="J33" s="163">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="162"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20522,11 +20522,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="162">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="162"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20550,11 +20550,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="162">
+      <c r="J35" s="163">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="162"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20576,11 +20576,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="171">
+      <c r="J36" s="170">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="171"/>
+      <c r="K36" s="170"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20599,8 +20599,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="172"/>
-      <c r="K37" s="172"/>
+      <c r="J37" s="171"/>
+      <c r="K37" s="171"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20649,6 +20649,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J27:K27"/>
@@ -20658,20 +20672,6 @@
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="J35:K35"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="41" priority="4" operator="greaterThan">
@@ -20719,35 +20719,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="146" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="153"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="154">
+      <c r="H1" s="149">
         <v>45477</v>
       </c>
-      <c r="I1" s="155"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="156">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="157"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20759,10 +20759,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="160" t="s">
+      <c r="H2" s="155" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="161"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20775,25 +20775,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="146"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="149" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="145" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="146"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="147"/>
-      <c r="N3" s="148"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -21127,11 +21127,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="163" t="s">
+      <c r="G14" s="164" t="s">
         <v>178</v>
       </c>
-      <c r="H14" s="164"/>
-      <c r="I14" s="165"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21154,10 +21154,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="154">
+      <c r="H15" s="149">
         <v>45477</v>
       </c>
-      <c r="I15" s="155"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21203,11 +21203,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="149" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="150"/>
-      <c r="I17" s="167"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21573,14 +21573,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="168" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="168"/>
-      <c r="L32" s="169" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="M32" s="169"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -21605,11 +21605,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="162">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="162"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>174</v>
       </c>
@@ -21637,11 +21637,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="162">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="162"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>175</v>
       </c>
@@ -21673,11 +21673,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="162">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="162"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>175</v>
       </c>
@@ -21698,11 +21698,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="171">
+      <c r="J36" s="170">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="171"/>
+      <c r="K36" s="170"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21719,11 +21719,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="162">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="162"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>181</v>
       </c>
@@ -21740,11 +21740,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="162">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="162"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21761,11 +21761,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="162">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="162"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21783,11 +21783,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="171">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="171"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -21802,8 +21802,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="172"/>
-      <c r="K41" s="172"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="52" t="s">
         <v>176</v>
       </c>
@@ -21874,16 +21874,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -21900,6 +21890,16 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
@@ -21948,35 +21948,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="146" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="153"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="154">
+      <c r="H1" s="149">
         <v>45548</v>
       </c>
-      <c r="I1" s="155"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="156">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="157"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -21988,10 +21988,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="160" t="s">
+      <c r="H2" s="155" t="s">
         <v>293</v>
       </c>
-      <c r="I2" s="161"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22004,25 +22004,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="146"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="149" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="145" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="146"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="147"/>
-      <c r="N3" s="148"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22396,11 +22396,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="163" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="164"/>
-      <c r="I14" s="165"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22427,10 +22427,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="154">
+      <c r="H15" s="149">
         <v>45561</v>
       </c>
-      <c r="I15" s="155"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22457,10 +22457,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="160" t="s">
+      <c r="H16" s="155" t="s">
         <v>293</v>
       </c>
-      <c r="I16" s="166"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22484,11 +22484,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="149" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="150"/>
-      <c r="I17" s="167"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22853,14 +22853,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="168" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="168"/>
-      <c r="L32" s="169" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="M32" s="169"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -22879,11 +22879,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="162">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="162"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>217</v>
       </c>
@@ -22908,11 +22908,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="162">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="162"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -22937,11 +22937,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="162">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="162"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -22958,11 +22958,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="162">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="162"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>174</v>
       </c>
@@ -22979,11 +22979,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="162">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="162"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23000,11 +23000,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="162">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="162"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23024,11 +23024,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="162">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="162"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23080,11 +23080,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="171">
+      <c r="J42" s="170">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="171"/>
+      <c r="K42" s="170"/>
       <c r="L42" s="52" t="s">
         <v>176</v>
       </c>
@@ -23104,8 +23104,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="172"/>
-      <c r="K43" s="172"/>
+      <c r="J43" s="171"/>
+      <c r="K43" s="171"/>
       <c r="L43" s="83" t="s">
         <v>177</v>
       </c>
@@ -23120,11 +23120,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="144" t="s">
+      <c r="A45" s="172" t="s">
         <v>198</v>
       </c>
-      <c r="B45" s="144"/>
-      <c r="C45" s="144"/>
+      <c r="B45" s="172"/>
+      <c r="C45" s="172"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23241,19 +23241,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -23268,6 +23255,19 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="33" priority="1" operator="greaterThan">
@@ -23316,35 +23316,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="146" t="s">
         <v>273</v>
       </c>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="153"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="154">
+      <c r="H1" s="149">
         <v>45631</v>
       </c>
-      <c r="I1" s="155"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="156">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="157"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23356,10 +23356,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="160" t="s">
+      <c r="H2" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="161"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23372,25 +23372,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="146"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="149" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="145" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="146"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="147"/>
-      <c r="N3" s="148"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23730,11 +23730,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="163" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="164"/>
-      <c r="I14" s="165"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23755,10 +23755,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="154">
+      <c r="H15" s="149">
         <v>45653</v>
       </c>
-      <c r="I15" s="155"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23779,10 +23779,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="160" t="s">
+      <c r="H16" s="155" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="166"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23800,11 +23800,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="149" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="150"/>
-      <c r="I17" s="167"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24150,14 +24150,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="168" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="168"/>
-      <c r="L32" s="169" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="M32" s="169"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24176,11 +24176,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="162">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="162"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>217</v>
       </c>
@@ -24205,11 +24205,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="162">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="162"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>217</v>
       </c>
@@ -24234,11 +24234,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="162">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="162"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>217</v>
       </c>
@@ -24255,11 +24255,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="162">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="162"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24276,11 +24276,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="162">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="162"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24297,11 +24297,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="162">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="162"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24318,11 +24318,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="162">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="162"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24340,11 +24340,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="171">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="171"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="52" t="s">
         <v>176</v>
       </c>
@@ -24364,8 +24364,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="172"/>
-      <c r="K41" s="172"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="83" t="s">
         <v>177</v>
       </c>
@@ -24380,11 +24380,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="144" t="s">
+      <c r="A43" s="172" t="s">
         <v>198</v>
       </c>
-      <c r="B43" s="144"/>
-      <c r="C43" s="144"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24532,6 +24532,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24540,23 +24557,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="29" priority="2" operator="greaterThan">
@@ -24608,35 +24608,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="146" t="s">
         <v>274</v>
       </c>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="153"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="154">
+      <c r="H1" s="149">
         <v>45714</v>
       </c>
-      <c r="I1" s="155"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="156">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="157"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24648,10 +24648,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="160" t="s">
+      <c r="H2" s="155" t="s">
         <v>349</v>
       </c>
-      <c r="I2" s="161"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24664,25 +24664,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="146"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="149" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="145" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="146"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="147"/>
-      <c r="N3" s="148"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -25024,11 +25024,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="163" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="164"/>
-      <c r="I14" s="165"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25051,10 +25051,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="154">
+      <c r="H15" s="149">
         <v>45743</v>
       </c>
-      <c r="I15" s="155"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25077,10 +25077,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="160" t="s">
+      <c r="H16" s="155" t="s">
         <v>350</v>
       </c>
-      <c r="I16" s="166"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25100,11 +25100,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="149" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="150"/>
-      <c r="I17" s="167"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25444,14 +25444,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="168" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="168"/>
-      <c r="L32" s="169" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="M32" s="169"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25470,11 +25470,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="162">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="162"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>259</v>
       </c>
@@ -25499,11 +25499,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="162">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="162"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>264</v>
       </c>
@@ -25529,11 +25529,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="162">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="162"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>265</v>
       </c>
@@ -25558,11 +25558,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="162">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="162"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>266</v>
       </c>
@@ -25578,11 +25578,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="162">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="162"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25595,11 +25595,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="162">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="162"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25612,11 +25612,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="162">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="162"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25634,11 +25634,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="171">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="171"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="52" t="s">
         <v>176</v>
       </c>
@@ -25658,8 +25658,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="172"/>
-      <c r="K41" s="172"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="83" t="s">
         <v>177</v>
       </c>
@@ -25674,11 +25674,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="144" t="s">
+      <c r="A43" s="172" t="s">
         <v>198</v>
       </c>
-      <c r="B43" s="144"/>
-      <c r="C43" s="144"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25710,23 +25710,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25735,6 +25718,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
@@ -25784,34 +25784,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="146" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="153"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="154">
+      <c r="G1" s="149">
         <v>45840</v>
       </c>
-      <c r="H1" s="155"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="156">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="157"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="158"/>
-      <c r="B2" s="159"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -25823,10 +25823,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="160" t="s">
+      <c r="G2" s="155" t="s">
         <v>351</v>
       </c>
-      <c r="H2" s="161"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25839,25 +25839,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="145" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="146"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="149" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="150"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="145" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="146"/>
-      <c r="K3" s="147"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="148"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -26175,11 +26175,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="163" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="164"/>
-      <c r="H14" s="165"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26199,10 +26199,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="154">
+      <c r="G15" s="149">
         <v>45840</v>
       </c>
-      <c r="H15" s="155"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26222,10 +26222,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="160" t="s">
+      <c r="G16" s="155" t="s">
         <v>293</v>
       </c>
-      <c r="H16" s="166"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26242,11 +26242,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="149" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="150"/>
-      <c r="H17" s="167"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26602,14 +26602,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="168" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="168"/>
-      <c r="K32" s="169" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="L32" s="169"/>
+      <c r="L32" s="144"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -26628,11 +26628,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="162">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="162"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>289</v>
       </c>
@@ -26657,11 +26657,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="162">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="162"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>292</v>
       </c>
@@ -26687,11 +26687,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="162">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="162"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85" t="s">
         <v>296</v>
       </c>
@@ -26716,11 +26716,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="162">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="162"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26745,11 +26745,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="162">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="162"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85" t="s">
         <v>297</v>
       </c>
@@ -26774,11 +26774,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="162">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="162"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85" t="s">
         <v>299</v>
       </c>
@@ -26795,11 +26795,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="162">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="162"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26817,11 +26817,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="171">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="171"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>176</v>
       </c>
@@ -26841,8 +26841,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="172"/>
-      <c r="J41" s="172"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>177</v>
       </c>
@@ -26857,10 +26857,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="144" t="s">
+      <c r="A43" s="172" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="144"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -26900,23 +26900,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -26925,6 +26908,23 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2662045-31D1-41B7-8B4D-8DCDE9591D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9400BB6E-8706-4B4C-9CD4-B7F2EB11D766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="355">
   <si>
     <t>#</t>
   </si>
@@ -2187,6 +2187,64 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2207,12 +2265,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -2226,10 +2278,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2250,54 +2298,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -3166,7 +3166,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-327672</c:v>
+                  <c:v>-343242</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3698,7 +3698,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>3263545</c:v>
+                  <c:v>3247975</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4113,7 +4113,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-797394.5</c:v>
+                  <c:v>-812964.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7962,28 +7962,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45076</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -7992,8 +7992,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8005,10 +8005,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>329</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8021,25 +8021,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8332,11 +8332,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8397,10 +8397,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>330</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8426,11 +8426,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -10759,34 +10759,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>45918</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10798,10 +10798,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10814,25 +10814,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11195,11 +11195,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11219,10 +11219,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>45918</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11242,10 +11242,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>349</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11262,11 +11262,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11606,14 +11606,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>248</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11633,11 +11633,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>322</v>
       </c>
@@ -11663,11 +11663,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11694,11 +11694,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
         <v>332</v>
       </c>
@@ -11726,11 +11726,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="85" t="s">
         <v>333</v>
       </c>
@@ -11756,11 +11756,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85" t="s">
         <v>335</v>
       </c>
@@ -11786,11 +11786,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85" t="s">
         <v>322</v>
       </c>
@@ -11808,11 +11808,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11835,11 +11835,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>176</v>
       </c>
@@ -11860,8 +11860,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>177</v>
       </c>
@@ -11877,10 +11877,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11900,10 +11900,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>290</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -11941,6 +11941,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -11957,15 +11966,6 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
@@ -12015,34 +12015,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>46016</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12054,10 +12054,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>352</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12070,25 +12070,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12382,11 +12382,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12406,10 +12406,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>46016</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12429,10 +12429,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>353</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12449,11 +12449,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12775,14 +12775,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>248</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12802,11 +12802,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12824,11 +12824,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12843,11 +12843,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -12863,11 +12863,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12881,11 +12881,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12899,11 +12899,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12917,11 +12917,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12940,11 +12940,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>176</v>
       </c>
@@ -12965,8 +12965,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>177</v>
       </c>
@@ -12982,10 +12982,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13005,10 +13005,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>290</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13046,11 +13046,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13062,15 +13066,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
@@ -13120,50 +13120,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>339</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>46068</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
-        <v>-327672</v>
-      </c>
-      <c r="K1" s="152"/>
+        <v>-343242</v>
+      </c>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>327672</v>
+        <v>343242</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="str">
+      <c r="G2" s="153" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>10 days</v>
-      </c>
-      <c r="H2" s="156"/>
+        <v>27 days</v>
+      </c>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13176,25 +13176,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13325,9 +13325,15 @@
       <c r="A8" s="41">
         <v>4</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="5"/>
+      <c r="B8" s="7">
+        <v>46067</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="5">
+        <v>15570</v>
+      </c>
       <c r="E8" s="22"/>
       <c r="F8" s="45"/>
       <c r="G8" s="46"/>
@@ -13460,11 +13466,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13484,10 +13490,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>46068</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13507,11 +13513,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="str">
+      <c r="G16" s="153" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>10 days</v>
-      </c>
-      <c r="H16" s="167"/>
+        <v>27 days</v>
+      </c>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13528,11 +13534,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13855,14 +13861,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>248</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -13874,11 +13880,11 @@
       <c r="F33" s="59"/>
       <c r="G33" s="67"/>
       <c r="H33" s="62"/>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85"/>
       <c r="L33" s="136"/>
       <c r="M33" s="15"/>
@@ -13892,11 +13898,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -13911,11 +13917,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -13931,11 +13937,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -13949,11 +13955,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -13967,11 +13973,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -13985,11 +13991,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14008,11 +14014,11 @@
         <v>0</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>176</v>
       </c>
@@ -14033,8 +14039,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>177</v>
       </c>
@@ -14050,10 +14056,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -14073,10 +14079,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>290</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -14111,11 +14117,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14127,15 +14137,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
@@ -14218,7 +14224,7 @@
       <c r="M1" s="186"/>
       <c r="N1" s="182" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>2 year, 10 months, 23 days</v>
+        <v>2 year, 11 months, 12 days</v>
       </c>
       <c r="O1" s="183"/>
       <c r="P1" s="183"/>
@@ -14631,7 +14637,7 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>-327672</v>
+        <v>-343242</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
@@ -14639,7 +14645,7 @@
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
-        <v>327672</v>
+        <v>343242</v>
       </c>
       <c r="G13" s="143">
         <f>MIN('Term-12'!G6:G14)</f>
@@ -14793,7 +14799,7 @@
       <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>3263545</v>
+        <v>3247975</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
@@ -14801,7 +14807,7 @@
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
-        <v>14157249</v>
+        <v>14172819</v>
       </c>
       <c r="G25" s="143"/>
       <c r="H25" s="89"/>
@@ -14886,7 +14892,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>-797394.5</v>
+        <v>-812964.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -14917,7 +14923,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>3263545</v>
+        <v>3247975</v>
       </c>
     </row>
   </sheetData>
@@ -15166,28 +15172,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45163</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -15196,8 +15202,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -15209,10 +15215,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>169</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15225,25 +15231,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -15490,11 +15496,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15515,10 +15521,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="149">
+      <c r="H13" s="151">
         <v>45163</v>
       </c>
-      <c r="I13" s="150"/>
+      <c r="I13" s="152"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15539,10 +15545,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>169</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15560,11 +15566,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17328,6 +17334,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17336,12 +17348,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
     <cfRule type="duplicateValues" dxfId="55" priority="6"/>
@@ -17398,28 +17404,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45163</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17428,8 +17434,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17441,10 +17447,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>170</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17457,25 +17463,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17718,11 +17724,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17743,10 +17749,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="149">
+      <c r="H13" s="151">
         <v>45163</v>
       </c>
-      <c r="I13" s="150"/>
+      <c r="I13" s="152"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17767,10 +17773,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>170</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17788,11 +17794,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -19626,28 +19632,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45345</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -19656,8 +19662,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19669,10 +19675,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>344</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19685,25 +19691,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -20045,11 +20051,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>178</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20070,10 +20076,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45345</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20115,11 +20121,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20356,10 +20362,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="169" t="s">
+      <c r="J28" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="169"/>
+      <c r="K28" s="158"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20378,11 +20384,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="163">
+      <c r="J29" s="144">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="163"/>
+      <c r="K29" s="144"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20407,11 +20413,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="163">
+      <c r="J30" s="144">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="163"/>
+      <c r="K30" s="144"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20436,11 +20442,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="163">
+      <c r="J31" s="144">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="163"/>
+      <c r="K31" s="144"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20465,11 +20471,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="163">
+      <c r="J32" s="144">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="163"/>
+      <c r="K32" s="144"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20494,11 +20500,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20522,11 +20528,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20550,11 +20556,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20576,11 +20582,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="170">
+      <c r="J36" s="145">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="170"/>
+      <c r="K36" s="145"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20599,8 +20605,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="171"/>
-      <c r="K37" s="171"/>
+      <c r="J37" s="146"/>
+      <c r="K37" s="146"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20649,6 +20655,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="J29:K29"/>
@@ -20658,20 +20678,6 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="G17:I17"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="41" priority="4" operator="greaterThan">
@@ -20719,35 +20725,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45477</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20759,10 +20765,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20775,25 +20781,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -21127,11 +21133,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>178</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21154,10 +21160,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45477</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21203,11 +21209,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21573,14 +21579,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>248</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -21605,11 +21611,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>174</v>
       </c>
@@ -21637,11 +21643,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>175</v>
       </c>
@@ -21673,11 +21679,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>175</v>
       </c>
@@ -21698,11 +21704,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="170">
+      <c r="J36" s="145">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="170"/>
+      <c r="K36" s="145"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21719,11 +21725,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>181</v>
       </c>
@@ -21740,11 +21746,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21761,11 +21767,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21783,11 +21789,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -21802,8 +21808,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="52" t="s">
         <v>176</v>
       </c>
@@ -21874,6 +21880,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -21890,16 +21906,6 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
@@ -21948,35 +21954,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45548</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -21988,10 +21994,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>293</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22004,25 +22010,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22396,11 +22402,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22427,10 +22433,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45561</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22457,10 +22463,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>293</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22484,11 +22490,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22853,14 +22859,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>248</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -22879,11 +22885,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>217</v>
       </c>
@@ -22908,11 +22914,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -22937,11 +22943,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -22958,11 +22964,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>174</v>
       </c>
@@ -22979,11 +22985,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23000,11 +23006,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23024,11 +23030,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23080,11 +23086,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="170">
+      <c r="J42" s="145">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="170"/>
+      <c r="K42" s="145"/>
       <c r="L42" s="52" t="s">
         <v>176</v>
       </c>
@@ -23104,8 +23110,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="171"/>
-      <c r="K43" s="171"/>
+      <c r="J43" s="146"/>
+      <c r="K43" s="146"/>
       <c r="L43" s="83" t="s">
         <v>177</v>
       </c>
@@ -23120,11 +23126,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="172" t="s">
+      <c r="A45" s="147" t="s">
         <v>198</v>
       </c>
-      <c r="B45" s="172"/>
-      <c r="C45" s="172"/>
+      <c r="B45" s="147"/>
+      <c r="C45" s="147"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23241,6 +23247,19 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -23255,19 +23274,6 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="33" priority="1" operator="greaterThan">
@@ -23316,35 +23322,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>273</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45631</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23356,10 +23362,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23372,25 +23378,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23730,11 +23736,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23755,10 +23761,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45653</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23779,10 +23785,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23800,11 +23806,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24150,14 +24156,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>248</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24176,11 +24182,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>217</v>
       </c>
@@ -24205,11 +24211,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>217</v>
       </c>
@@ -24234,11 +24240,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>217</v>
       </c>
@@ -24255,11 +24261,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24276,11 +24282,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24297,11 +24303,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24318,11 +24324,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24340,11 +24346,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="52" t="s">
         <v>176</v>
       </c>
@@ -24364,8 +24370,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="83" t="s">
         <v>177</v>
       </c>
@@ -24380,11 +24386,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>198</v>
       </c>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="147"/>
+      <c r="C43" s="147"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24532,23 +24538,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24557,6 +24546,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="29" priority="2" operator="greaterThan">
@@ -24608,35 +24614,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>274</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45714</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24648,10 +24654,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>349</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24664,25 +24670,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -25024,11 +25030,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25051,10 +25057,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45743</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25077,10 +25083,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>350</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25100,11 +25106,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25444,14 +25450,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>248</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25470,11 +25476,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>259</v>
       </c>
@@ -25499,11 +25505,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>264</v>
       </c>
@@ -25529,11 +25535,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>265</v>
       </c>
@@ -25558,11 +25564,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>266</v>
       </c>
@@ -25578,11 +25584,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25595,11 +25601,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25612,11 +25618,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25634,11 +25640,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="52" t="s">
         <v>176</v>
       </c>
@@ -25658,8 +25664,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="83" t="s">
         <v>177</v>
       </c>
@@ -25674,11 +25680,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>198</v>
       </c>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="147"/>
+      <c r="C43" s="147"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25710,6 +25716,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25718,23 +25741,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
@@ -25784,34 +25790,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>45840</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -25823,10 +25829,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>351</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25839,25 +25845,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -26175,11 +26181,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26199,10 +26205,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>45840</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26222,10 +26228,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>293</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26242,11 +26248,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26602,14 +26608,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>248</v>
       </c>
-      <c r="L32" s="144"/>
+      <c r="L32" s="159"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -26628,11 +26634,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>289</v>
       </c>
@@ -26657,11 +26663,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>292</v>
       </c>
@@ -26687,11 +26693,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
         <v>296</v>
       </c>
@@ -26716,11 +26722,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26745,11 +26751,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85" t="s">
         <v>297</v>
       </c>
@@ -26774,11 +26780,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85" t="s">
         <v>299</v>
       </c>
@@ -26795,11 +26801,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26817,11 +26823,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>176</v>
       </c>
@@ -26841,8 +26847,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>177</v>
       </c>
@@ -26857,10 +26863,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -26900,6 +26906,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -26908,23 +26931,6 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9400BB6E-8706-4B4C-9CD4-B7F2EB11D766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D0EBA8-ABCB-4CA2-9834-988C8888501B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2187,64 +2187,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2265,6 +2207,12 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -2278,6 +2226,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2298,6 +2250,54 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -3166,7 +3166,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-343242</c:v>
+                  <c:v>-343485</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3698,7 +3698,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>3247975</c:v>
+                  <c:v>3247732</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4113,7 +4113,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-812964.5</c:v>
+                  <c:v>-813207.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7962,28 +7962,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45076</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -7992,8 +7992,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8005,10 +8005,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>329</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8021,25 +8021,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8332,11 +8332,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8397,10 +8397,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>330</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8426,11 +8426,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -10759,34 +10759,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>317</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>45918</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10798,10 +10798,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10814,25 +10814,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11195,11 +11195,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11219,10 +11219,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>45918</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11242,10 +11242,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>349</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11262,11 +11262,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11606,14 +11606,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11633,11 +11633,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>322</v>
       </c>
@@ -11663,11 +11663,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11694,11 +11694,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85" t="s">
         <v>332</v>
       </c>
@@ -11726,11 +11726,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="85" t="s">
         <v>333</v>
       </c>
@@ -11756,11 +11756,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85" t="s">
         <v>335</v>
       </c>
@@ -11786,11 +11786,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85" t="s">
         <v>322</v>
       </c>
@@ -11808,11 +11808,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11835,11 +11835,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>176</v>
       </c>
@@ -11860,8 +11860,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>177</v>
       </c>
@@ -11877,10 +11877,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11900,10 +11900,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>290</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -11941,15 +11941,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -11966,6 +11957,15 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
@@ -12015,34 +12015,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>46016</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12054,10 +12054,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>352</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12070,25 +12070,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12382,11 +12382,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12406,10 +12406,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>46016</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12429,10 +12429,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>353</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12449,11 +12449,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12775,14 +12775,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12802,11 +12802,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12824,11 +12824,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12843,11 +12843,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -12863,11 +12863,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12881,11 +12881,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12899,11 +12899,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12917,11 +12917,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12940,11 +12940,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>176</v>
       </c>
@@ -12965,8 +12965,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>177</v>
       </c>
@@ -12982,10 +12982,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13005,10 +13005,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>290</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13046,15 +13046,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13066,11 +13062,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
@@ -13120,50 +13120,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>339</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>46068</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
-        <v>-343242</v>
-      </c>
-      <c r="K1" s="165"/>
+        <v>-343485</v>
+      </c>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>343242</v>
+        <v>343485</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="str">
+      <c r="G2" s="155" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>27 days</v>
-      </c>
-      <c r="H2" s="168"/>
+        <v>28 days</v>
+      </c>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13176,25 +13176,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13332,7 +13332,7 @@
         <v>96</v>
       </c>
       <c r="D8" s="5">
-        <v>15570</v>
+        <v>15813</v>
       </c>
       <c r="E8" s="22"/>
       <c r="F8" s="45"/>
@@ -13466,11 +13466,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13490,10 +13490,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>46068</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13513,11 +13513,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="str">
+      <c r="G16" s="155" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>27 days</v>
-      </c>
-      <c r="H16" s="154"/>
+        <v>28 days</v>
+      </c>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13534,11 +13534,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13861,14 +13861,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -13880,11 +13880,11 @@
       <c r="F33" s="59"/>
       <c r="G33" s="67"/>
       <c r="H33" s="62"/>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85"/>
       <c r="L33" s="136"/>
       <c r="M33" s="15"/>
@@ -13898,11 +13898,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -13917,11 +13917,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -13937,11 +13937,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -13955,11 +13955,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -13973,11 +13973,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -13991,11 +13991,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14014,11 +14014,11 @@
         <v>0</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>176</v>
       </c>
@@ -14039,8 +14039,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>177</v>
       </c>
@@ -14056,10 +14056,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -14079,10 +14079,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>290</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -14117,15 +14117,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14137,11 +14133,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
@@ -14224,7 +14224,7 @@
       <c r="M1" s="186"/>
       <c r="N1" s="182" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>2 year, 11 months, 12 days</v>
+        <v>2 year, 11 months, 13 days</v>
       </c>
       <c r="O1" s="183"/>
       <c r="P1" s="183"/>
@@ -14637,7 +14637,7 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>-343242</v>
+        <v>-343485</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
@@ -14645,7 +14645,7 @@
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
-        <v>343242</v>
+        <v>343485</v>
       </c>
       <c r="G13" s="143">
         <f>MIN('Term-12'!G6:G14)</f>
@@ -14799,7 +14799,7 @@
       <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>3247975</v>
+        <v>3247732</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
-        <v>14172819</v>
+        <v>14173062</v>
       </c>
       <c r="G25" s="143"/>
       <c r="H25" s="89"/>
@@ -14892,7 +14892,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>-812964.5</v>
+        <v>-813207.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>3247975</v>
+        <v>3247732</v>
       </c>
     </row>
   </sheetData>
@@ -15172,28 +15172,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45163</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -15202,8 +15202,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -15215,10 +15215,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>169</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15231,25 +15231,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -15496,11 +15496,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15521,10 +15521,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="149">
         <v>45163</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="150"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15545,10 +15545,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>169</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15566,11 +15566,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17334,12 +17334,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17348,6 +17342,12 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
     <cfRule type="duplicateValues" dxfId="55" priority="6"/>
@@ -17404,28 +17404,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45163</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17434,8 +17434,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17447,10 +17447,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>170</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17463,25 +17463,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17724,11 +17724,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17749,10 +17749,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="149">
         <v>45163</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="150"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17773,10 +17773,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>170</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17794,11 +17794,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -19632,28 +19632,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45345</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -19662,8 +19662,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19675,10 +19675,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>344</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19691,25 +19691,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -20051,11 +20051,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>178</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20076,10 +20076,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45345</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20121,11 +20121,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20362,10 +20362,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="158" t="s">
+      <c r="J28" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="158"/>
+      <c r="K28" s="169"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20384,11 +20384,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="144">
+      <c r="J29" s="163">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="144"/>
+      <c r="K29" s="163"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20413,11 +20413,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="144">
+      <c r="J30" s="163">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="144"/>
+      <c r="K30" s="163"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20442,11 +20442,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="144">
+      <c r="J31" s="163">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="144"/>
+      <c r="K31" s="163"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20471,11 +20471,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="144">
+      <c r="J32" s="163">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="144"/>
+      <c r="K32" s="163"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20500,11 +20500,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20528,11 +20528,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20556,11 +20556,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20582,11 +20582,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="145">
+      <c r="J36" s="170">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="145"/>
+      <c r="K36" s="170"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20605,8 +20605,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="146"/>
-      <c r="K37" s="146"/>
+      <c r="J37" s="171"/>
+      <c r="K37" s="171"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20655,6 +20655,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J27:K27"/>
@@ -20664,20 +20678,6 @@
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="J35:K35"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="41" priority="4" operator="greaterThan">
@@ -20725,35 +20725,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45477</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20765,10 +20765,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20781,25 +20781,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -21133,11 +21133,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>178</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21160,10 +21160,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45477</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21209,11 +21209,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21579,14 +21579,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -21611,11 +21611,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>174</v>
       </c>
@@ -21643,11 +21643,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>175</v>
       </c>
@@ -21679,11 +21679,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>175</v>
       </c>
@@ -21704,11 +21704,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="145">
+      <c r="J36" s="170">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="145"/>
+      <c r="K36" s="170"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21725,11 +21725,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>181</v>
       </c>
@@ -21746,11 +21746,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21767,11 +21767,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21789,11 +21789,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -21808,8 +21808,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="52" t="s">
         <v>176</v>
       </c>
@@ -21880,16 +21880,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -21906,6 +21896,16 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
@@ -21954,35 +21954,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45548</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -21994,10 +21994,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>293</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22010,25 +22010,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22402,11 +22402,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22433,10 +22433,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45561</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22463,10 +22463,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>293</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22490,11 +22490,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22859,14 +22859,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -22885,11 +22885,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>217</v>
       </c>
@@ -22914,11 +22914,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -22943,11 +22943,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -22964,11 +22964,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>174</v>
       </c>
@@ -22985,11 +22985,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23006,11 +23006,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23030,11 +23030,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23086,11 +23086,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="145">
+      <c r="J42" s="170">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="145"/>
+      <c r="K42" s="170"/>
       <c r="L42" s="52" t="s">
         <v>176</v>
       </c>
@@ -23110,8 +23110,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="146"/>
-      <c r="K43" s="146"/>
+      <c r="J43" s="171"/>
+      <c r="K43" s="171"/>
       <c r="L43" s="83" t="s">
         <v>177</v>
       </c>
@@ -23126,11 +23126,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="147" t="s">
+      <c r="A45" s="172" t="s">
         <v>198</v>
       </c>
-      <c r="B45" s="147"/>
-      <c r="C45" s="147"/>
+      <c r="B45" s="172"/>
+      <c r="C45" s="172"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23247,19 +23247,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -23274,6 +23261,19 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="33" priority="1" operator="greaterThan">
@@ -23322,35 +23322,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>273</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45631</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23362,10 +23362,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23378,25 +23378,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23736,11 +23736,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23761,10 +23761,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45653</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23785,10 +23785,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23806,11 +23806,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24156,14 +24156,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24182,11 +24182,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>217</v>
       </c>
@@ -24211,11 +24211,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>217</v>
       </c>
@@ -24240,11 +24240,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>217</v>
       </c>
@@ -24261,11 +24261,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24282,11 +24282,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24303,11 +24303,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24324,11 +24324,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24346,11 +24346,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="52" t="s">
         <v>176</v>
       </c>
@@ -24370,8 +24370,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="83" t="s">
         <v>177</v>
       </c>
@@ -24386,11 +24386,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>198</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="147"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24538,6 +24538,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24546,23 +24563,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="29" priority="2" operator="greaterThan">
@@ -24614,35 +24614,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>274</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45714</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24654,10 +24654,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>349</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24670,25 +24670,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -25030,11 +25030,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25057,10 +25057,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45743</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25083,10 +25083,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>350</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25106,11 +25106,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25450,14 +25450,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25476,11 +25476,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>259</v>
       </c>
@@ -25505,11 +25505,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>264</v>
       </c>
@@ -25535,11 +25535,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>265</v>
       </c>
@@ -25564,11 +25564,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>266</v>
       </c>
@@ -25584,11 +25584,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25601,11 +25601,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25618,11 +25618,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25640,11 +25640,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="52" t="s">
         <v>176</v>
       </c>
@@ -25664,8 +25664,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="83" t="s">
         <v>177</v>
       </c>
@@ -25680,11 +25680,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>198</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="147"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25716,23 +25716,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25741,6 +25724,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
@@ -25790,34 +25790,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>45840</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -25829,10 +25829,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>351</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25845,25 +25845,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -26181,11 +26181,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26205,10 +26205,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>45840</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26228,10 +26228,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>293</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26248,11 +26248,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26608,14 +26608,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="L32" s="159"/>
+      <c r="L32" s="144"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -26634,11 +26634,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>289</v>
       </c>
@@ -26663,11 +26663,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>292</v>
       </c>
@@ -26693,11 +26693,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85" t="s">
         <v>296</v>
       </c>
@@ -26722,11 +26722,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26751,11 +26751,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85" t="s">
         <v>297</v>
       </c>
@@ -26780,11 +26780,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85" t="s">
         <v>299</v>
       </c>
@@ -26801,11 +26801,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26823,11 +26823,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>176</v>
       </c>
@@ -26847,8 +26847,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>177</v>
       </c>
@@ -26863,10 +26863,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -26906,23 +26906,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -26931,6 +26914,23 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D0EBA8-ABCB-4CA2-9834-988C8888501B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5226141-15A9-492F-9C24-8451B05E4E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Term-1" sheetId="4" r:id="rId1"/>
@@ -570,12 +570,6 @@
     <t>Big Tank - Soft</t>
   </si>
   <si>
-    <t>50 days</t>
-  </si>
-  <si>
-    <t>61 days</t>
-  </si>
-  <si>
     <t>Small Tank - Full</t>
   </si>
   <si>
@@ -1126,6 +1120,12 @@
   </si>
   <si>
     <t>Assam salary</t>
+  </si>
+  <si>
+    <t>27 days</t>
+  </si>
+  <si>
+    <t>37 days</t>
   </si>
 </sst>
 </file>
@@ -2187,6 +2187,64 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2207,12 +2265,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -2226,10 +2278,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2250,54 +2298,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -7962,28 +7962,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
-        <v>267</v>
-      </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="B1" s="161" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45076</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -7992,8 +7992,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8005,10 +8005,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
-        <v>329</v>
-      </c>
-      <c r="I2" s="156"/>
+      <c r="H2" s="153" t="s">
+        <v>327</v>
+      </c>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8021,25 +8021,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8332,11 +8332,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8397,10 +8397,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
-        <v>330</v>
-      </c>
-      <c r="I14" s="156"/>
+      <c r="H14" s="153" t="s">
+        <v>328</v>
+      </c>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8426,11 +8426,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -10759,34 +10759,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
-        <v>317</v>
-      </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="A1" s="161" t="s">
+        <v>315</v>
+      </c>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>45918</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10798,10 +10798,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
-        <v>349</v>
-      </c>
-      <c r="H2" s="156"/>
+      <c r="G2" s="153" t="s">
+        <v>347</v>
+      </c>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10814,25 +10814,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -10889,7 +10889,7 @@
         <v>288000</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F5" s="45">
         <v>45972</v>
@@ -10908,7 +10908,7 @@
         <v>45975</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L5" s="5">
         <v>496056</v>
@@ -10923,7 +10923,7 @@
         <v>45918</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D6" s="5">
         <v>17500</v>
@@ -10946,7 +10946,7 @@
         <v>45985</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L6" s="5">
         <v>644160</v>
@@ -10961,7 +10961,7 @@
         <v>45961</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D7" s="5">
         <v>996000</v>
@@ -10984,7 +10984,7 @@
         <v>45995</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L7" s="5">
         <v>1136588</v>
@@ -10999,7 +10999,7 @@
         <v>45956</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D8" s="5">
         <v>15000</v>
@@ -11022,7 +11022,7 @@
         <v>45995</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="L8" s="5">
         <v>244273.5</v>
@@ -11037,7 +11037,7 @@
         <v>45995</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D9" s="5">
         <v>100000</v>
@@ -11060,7 +11060,7 @@
         <v>46001</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="L9" s="5">
         <v>3182.5</v>
@@ -11098,7 +11098,7 @@
         <v>46003</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="L10" s="5">
         <v>6090</v>
@@ -11113,7 +11113,7 @@
         <v>45995</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D11" s="5">
         <v>34500</v>
@@ -11145,7 +11145,7 @@
         <v>45995</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D12" s="5">
         <v>30000</v>
@@ -11195,11 +11195,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11219,10 +11219,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>45918</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11242,10 +11242,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
-        <v>349</v>
-      </c>
-      <c r="H16" s="167"/>
+      <c r="G16" s="153" t="s">
+        <v>347</v>
+      </c>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11262,11 +11262,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11296,7 +11296,7 @@
         <v>14</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="5"/>
@@ -11574,13 +11574,13 @@
         <v>900000</v>
       </c>
       <c r="F31" s="93" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G31" s="86">
         <v>750000</v>
       </c>
       <c r="H31" s="61" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I31" s="86">
         <v>150000</v>
@@ -11601,24 +11601,24 @@
         <v>88</v>
       </c>
       <c r="G32" s="93" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
-        <v>248</v>
-      </c>
-      <c r="L32" s="145"/>
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
+        <v>246</v>
+      </c>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E33" s="59">
         <f>G33*F33</f>
@@ -11633,13 +11633,13 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="L33" s="136">
         <v>50000</v>
@@ -11648,7 +11648,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D34" s="15" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E34" s="59">
         <f t="shared" ref="E34:E39" si="2">G34*F34</f>
@@ -11663,11 +11663,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11679,7 +11679,7 @@
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B35" s="126"/>
       <c r="D35" s="15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E35" s="59">
         <f t="shared" si="2"/>
@@ -11694,24 +11694,24 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L35" s="136">
         <v>500000</v>
       </c>
       <c r="M35" s="15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D36" s="15" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E36" s="59">
         <f t="shared" si="2"/>
@@ -11726,13 +11726,13 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="85" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L36" s="136">
         <v>500000</v>
@@ -11741,7 +11741,7 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D37" s="15" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E37" s="59">
         <f t="shared" si="2"/>
@@ -11756,13 +11756,13 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L37" s="136">
         <v>300000</v>
@@ -11771,7 +11771,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D38" s="15" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E38" s="59">
         <f t="shared" si="2"/>
@@ -11786,13 +11786,13 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="L38" s="136">
         <v>50000</v>
@@ -11808,11 +11808,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11835,13 +11835,13 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L40" s="137">
         <f>SUM(L33:L39)</f>
@@ -11851,7 +11851,7 @@
     </row>
     <row r="41" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D41" s="52" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E41" s="109" t="str">
         <f>CONCATENATE(ROUND((E40/E31)*100,2),"%")</f>
@@ -11860,10 +11860,10 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L41" s="105">
         <f>I40-L40</f>
@@ -11877,10 +11877,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
-        <v>290</v>
-      </c>
-      <c r="B43" s="172"/>
+      <c r="A43" s="147" t="s">
+        <v>288</v>
+      </c>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11900,10 +11900,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
-        <v>290</v>
-      </c>
-      <c r="B44" s="172"/>
+      <c r="A44" s="147" t="s">
+        <v>288</v>
+      </c>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -11936,11 +11936,20 @@
     </row>
     <row r="56" spans="5:9" x14ac:dyDescent="0.3">
       <c r="I56" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -11957,15 +11966,6 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
@@ -12015,34 +12015,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
-        <v>338</v>
-      </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="A1" s="161" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>46016</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12054,10 +12054,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
-        <v>352</v>
-      </c>
-      <c r="H2" s="156"/>
+      <c r="G2" s="153" t="s">
+        <v>350</v>
+      </c>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12070,25 +12070,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12145,7 +12145,7 @@
         <v>288000</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F5" s="45">
         <v>46049</v>
@@ -12164,13 +12164,13 @@
         <v>46046</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
       </c>
       <c r="M5" s="22" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -12181,7 +12181,7 @@
         <v>46016</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D6" s="5">
         <v>13000</v>
@@ -12200,13 +12200,13 @@
         <v>46049</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="L6" s="5">
         <v>115277.5</v>
       </c>
       <c r="M6" s="22" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -12217,7 +12217,7 @@
         <v>46046</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D7" s="5">
         <v>250000</v>
@@ -12245,7 +12245,7 @@
         <v>46046</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D8" s="5">
         <v>34000</v>
@@ -12382,11 +12382,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12406,10 +12406,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>46016</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12429,10 +12429,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
-        <v>353</v>
-      </c>
-      <c r="H16" s="167"/>
+      <c r="G16" s="153" t="s">
+        <v>351</v>
+      </c>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12449,11 +12449,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12743,13 +12743,13 @@
         <v>990000</v>
       </c>
       <c r="F31" s="93" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G31" s="86">
         <v>830000</v>
       </c>
       <c r="H31" s="61" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I31" s="86">
         <v>160000</v>
@@ -12770,24 +12770,24 @@
         <v>88</v>
       </c>
       <c r="G32" s="93" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
-        <v>248</v>
-      </c>
-      <c r="L32" s="145"/>
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
+        <v>246</v>
+      </c>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E33" s="59">
         <f>G33*F33</f>
@@ -12802,11 +12802,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12824,11 +12824,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12843,15 +12843,15 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
@@ -12863,11 +12863,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12881,11 +12881,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12899,11 +12899,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12917,11 +12917,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12940,13 +12940,13 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L40" s="137">
         <f>SUM(L33:L39)</f>
@@ -12956,7 +12956,7 @@
     </row>
     <row r="41" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D41" s="52" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E41" s="109" t="str">
         <f>CONCATENATE(ROUND((E40/E31)*100,2),"%")</f>
@@ -12965,10 +12965,10 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L41" s="105">
         <f>I40-L40</f>
@@ -12982,10 +12982,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
-        <v>290</v>
-      </c>
-      <c r="B43" s="172"/>
+      <c r="A43" s="147" t="s">
+        <v>288</v>
+      </c>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13005,10 +13005,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
-        <v>290</v>
-      </c>
-      <c r="B44" s="172"/>
+      <c r="A44" s="147" t="s">
+        <v>288</v>
+      </c>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13041,16 +13041,20 @@
     </row>
     <row r="56" spans="5:9" x14ac:dyDescent="0.3">
       <c r="I56" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13062,15 +13066,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
@@ -13120,34 +13120,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
-        <v>339</v>
-      </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="A1" s="161" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>46068</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>-343485</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -13159,11 +13159,11 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="str">
+      <c r="G2" s="153" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>28 days</v>
-      </c>
-      <c r="H2" s="156"/>
+        <v>35 days</v>
+      </c>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13176,25 +13176,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13273,7 +13273,7 @@
         <v>46068</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D6" s="5">
         <v>33000</v>
@@ -13466,11 +13466,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13490,10 +13490,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>46068</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13513,11 +13513,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="str">
+      <c r="G16" s="153" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>28 days</v>
-      </c>
-      <c r="H16" s="167"/>
+        <v>35 days</v>
+      </c>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13534,11 +13534,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13829,13 +13829,13 @@
         <v>800000</v>
       </c>
       <c r="F31" s="93" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G31" s="86">
         <v>700000</v>
       </c>
       <c r="H31" s="61" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I31" s="86">
         <v>100000</v>
@@ -13856,19 +13856,19 @@
         <v>88</v>
       </c>
       <c r="G32" s="93" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
-        <v>248</v>
-      </c>
-      <c r="L32" s="145"/>
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
+        <v>246</v>
+      </c>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -13880,11 +13880,11 @@
       <c r="F33" s="59"/>
       <c r="G33" s="67"/>
       <c r="H33" s="62"/>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85"/>
       <c r="L33" s="136"/>
       <c r="M33" s="15"/>
@@ -13898,11 +13898,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -13917,15 +13917,15 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
@@ -13937,11 +13937,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -13955,11 +13955,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -13973,11 +13973,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -13991,11 +13991,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14014,13 +14014,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L40" s="137">
         <f>SUM(L33:L39)</f>
@@ -14030,7 +14030,7 @@
     </row>
     <row r="41" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D41" s="52" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E41" s="109" t="str">
         <f>CONCATENATE(ROUND((E40/E31)*100,2),"%")</f>
@@ -14039,10 +14039,10 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L41" s="105">
         <f>I40-L40</f>
@@ -14056,10 +14056,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
-        <v>290</v>
-      </c>
-      <c r="B43" s="172"/>
+      <c r="A43" s="147" t="s">
+        <v>288</v>
+      </c>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -14079,10 +14079,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
-        <v>290</v>
-      </c>
-      <c r="B44" s="172"/>
+      <c r="A44" s="147" t="s">
+        <v>288</v>
+      </c>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -14112,16 +14112,20 @@
     </row>
     <row r="56" spans="5:9" x14ac:dyDescent="0.3">
       <c r="I56" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14133,15 +14137,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
@@ -14195,10 +14195,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="127" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C1" s="91" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D1" s="95" t="s">
         <v>36</v>
@@ -14216,7 +14216,7 @@
         <v>100</v>
       </c>
       <c r="I1" s="185" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J1" s="185"/>
       <c r="K1" s="185"/>
@@ -14224,14 +14224,14 @@
       <c r="M1" s="186"/>
       <c r="N1" s="182" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>2 year, 11 months, 13 days</v>
+        <v>2 year, 11 months, 20 days</v>
       </c>
       <c r="O1" s="183"/>
       <c r="P1" s="183"/>
       <c r="Q1" s="183"/>
       <c r="R1" s="184"/>
       <c r="S1" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="T1" s="104">
         <v>45023</v>
@@ -14248,7 +14248,7 @@
         <v>May2023 - Sept2023</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D2" s="96">
         <f>IF(F2="","",E2-F2)</f>
@@ -14283,7 +14283,7 @@
         <v>Sept2023 - Nov2023</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D3" s="96">
         <f t="shared" ref="D3:D7" si="0">IF(F3="","",E3-F3)</f>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="H3" s="141" t="str" cm="1">
         <f t="array" ref="H3:I3">'Term-2'!H2:I2</f>
-        <v>50 days</v>
+        <v>27 days</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -14318,7 +14318,7 @@
         <v>Nov2023 - Jan2024</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D4" s="96">
         <f t="shared" si="0"/>
@@ -14338,7 +14338,7 @@
       </c>
       <c r="H4" s="141" t="str" cm="1">
         <f t="array" ref="H4:I4">'Term-3'!H2:I2</f>
-        <v>61 days</v>
+        <v>37 days</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -14353,7 +14353,7 @@
         <v>Feb2024 - May2024</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D5" s="96">
         <f t="shared" si="0"/>
@@ -14388,7 +14388,7 @@
         <v>July 2024 - Sept2024</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D6" s="96">
         <f t="shared" si="0"/>
@@ -14423,7 +14423,7 @@
         <v>Sep2024 - Nov2024</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D7" s="96">
         <f t="shared" si="0"/>
@@ -14458,7 +14458,7 @@
         <v>Dec2024 - Feb2025</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D8" s="96">
         <f t="shared" ref="D8:D10" si="1">IF(F8="","",E8-F8)</f>
@@ -14493,7 +14493,7 @@
         <v>Feb2025 - May2025</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D9" s="96">
         <f t="shared" si="1"/>
@@ -14528,7 +14528,7 @@
         <v>July2025 - Sept2025</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D10" s="96">
         <f t="shared" si="1"/>
@@ -14563,7 +14563,7 @@
         <v>Sept2025 - Dec2025</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D11" s="96">
         <f t="shared" ref="D11" si="2">IF(F11="","",E11-F11)</f>
@@ -14598,7 +14598,7 @@
         <v>Dec2025 - Jan2026</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D12" s="96">
         <f t="shared" ref="D12" si="3">IF(F12="","",E12-F12)</f>
@@ -14633,7 +14633,7 @@
         <v>Dec2025 - Jan2026</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
@@ -14793,7 +14793,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="179" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B25" s="180"/>
       <c r="C25" s="181"/>
@@ -14814,7 +14814,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B27" s="138" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -14822,10 +14822,10 @@
         <v>0</v>
       </c>
       <c r="B28" s="91" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C28" s="95" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D28" s="94" t="s">
         <v>36</v>
@@ -14955,13 +14955,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="107" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1" s="107" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1" s="107" t="s">
         <v>213</v>
-      </c>
-      <c r="C1" s="107" t="s">
-        <v>214</v>
-      </c>
-      <c r="D1" s="107" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -14969,28 +14969,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="108" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C2" s="108" t="s">
+        <v>208</v>
+      </c>
+      <c r="D2" s="108" t="s">
         <v>210</v>
-      </c>
-      <c r="D2" s="108" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="88"/>
       <c r="B3" s="108" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C3" s="108" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D3" s="108" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E3" s="134" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G3" s="117"/>
       <c r="H3" s="117"/>
@@ -15000,11 +15000,11 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="88"/>
       <c r="B4" s="108" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C4" s="108"/>
       <c r="D4" s="108" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G4" s="117"/>
       <c r="H4" s="117"/>
@@ -15014,11 +15014,11 @@
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="88"/>
       <c r="B5" s="108" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C5" s="108"/>
       <c r="D5" s="108" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G5" s="117"/>
       <c r="H5" s="117"/>
@@ -15172,28 +15172,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
-        <v>268</v>
-      </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="B1" s="161" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45163</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -15202,8 +15202,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -15215,10 +15215,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
-        <v>169</v>
-      </c>
-      <c r="I2" s="156"/>
+      <c r="H2" s="153" t="s">
+        <v>353</v>
+      </c>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15231,25 +15231,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -15496,11 +15496,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15521,10 +15521,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="149">
+      <c r="H13" s="151">
         <v>45163</v>
       </c>
-      <c r="I13" s="150"/>
+      <c r="I13" s="152"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15545,10 +15545,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
-        <v>169</v>
-      </c>
-      <c r="I14" s="156"/>
+      <c r="H14" s="153" t="s">
+        <v>353</v>
+      </c>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15566,11 +15566,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17334,6 +17334,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17342,12 +17348,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
     <cfRule type="duplicateValues" dxfId="55" priority="6"/>
@@ -17404,28 +17404,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
-        <v>269</v>
-      </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="B1" s="161" t="s">
+        <v>267</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45163</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17434,8 +17434,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17447,10 +17447,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
-        <v>170</v>
-      </c>
-      <c r="I2" s="156"/>
+      <c r="H2" s="153" t="s">
+        <v>354</v>
+      </c>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17463,25 +17463,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17541,14 +17541,14 @@
         <v>127</v>
       </c>
       <c r="G5" s="45">
-        <v>45189</v>
+        <v>45199</v>
       </c>
       <c r="H5" s="46">
         <v>325</v>
       </c>
       <c r="I5" s="49" t="str">
         <f>IF(ISBLANK(G5),"",CONCATENATE(G5-$H$1+1," days"))</f>
-        <v>27 days</v>
+        <v>37 days</v>
       </c>
       <c r="J5" s="21">
         <v>1</v>
@@ -17557,7 +17557,7 @@
         <v>45189</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M5" s="5">
         <v>120000</v>
@@ -17724,11 +17724,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17749,10 +17749,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="149">
+      <c r="H13" s="151">
         <v>45163</v>
       </c>
-      <c r="I13" s="150"/>
+      <c r="I13" s="152"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17773,10 +17773,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
-        <v>170</v>
-      </c>
-      <c r="I14" s="156"/>
+      <c r="H14" s="153" t="s">
+        <v>354</v>
+      </c>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17794,11 +17794,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17841,14 +17841,14 @@
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
       <c r="G17" s="45">
-        <v>45189</v>
+        <v>45199</v>
       </c>
       <c r="H17" s="46">
         <v>325</v>
       </c>
       <c r="I17" s="49" t="str">
         <f>IF(ISBLANK(G17),"",CONCATENATE(G17-$H$13+1," days"))</f>
-        <v>27 days</v>
+        <v>37 days</v>
       </c>
       <c r="J17" s="21">
         <v>13</v>
@@ -19632,28 +19632,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
-        <v>270</v>
-      </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="B1" s="161" t="s">
+        <v>268</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45345</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -19662,8 +19662,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19675,10 +19675,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
-        <v>344</v>
-      </c>
-      <c r="I2" s="156"/>
+      <c r="H2" s="153" t="s">
+        <v>342</v>
+      </c>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19691,25 +19691,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -19779,7 +19779,7 @@
         <v>45399</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M5" s="5">
         <v>432360</v>
@@ -19815,7 +19815,7 @@
         <v>45408</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M6" s="5">
         <v>454020</v>
@@ -19834,7 +19834,7 @@
         <v>436381</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G7" s="45">
         <v>45404</v>
@@ -19890,7 +19890,7 @@
         <v>45416</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M8" s="5">
         <v>535000</v>
@@ -20051,11 +20051,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
-        <v>178</v>
-      </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="G14" s="148" t="s">
+        <v>176</v>
+      </c>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20076,10 +20076,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45345</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20101,7 +20101,7 @@
         <v>100</v>
       </c>
       <c r="H16" s="55" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I16" s="56"/>
       <c r="J16" s="21">
@@ -20121,11 +20121,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20357,15 +20357,15 @@
         <v>88</v>
       </c>
       <c r="H28" s="93" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="169" t="s">
+      <c r="J28" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="169"/>
+      <c r="K28" s="158"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20384,11 +20384,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="163">
+      <c r="J29" s="144">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="163"/>
+      <c r="K29" s="144"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20413,11 +20413,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="163">
+      <c r="J30" s="144">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="163"/>
+      <c r="K30" s="144"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20442,11 +20442,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="163">
+      <c r="J31" s="144">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="163"/>
+      <c r="K31" s="144"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20471,11 +20471,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="163">
+      <c r="J32" s="144">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="163"/>
+      <c r="K32" s="144"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20500,11 +20500,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20528,11 +20528,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20556,11 +20556,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20582,11 +20582,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="170">
+      <c r="J36" s="145">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="170"/>
+      <c r="K36" s="145"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20596,7 +20596,7 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="E37" s="52" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F37" s="109" t="str">
         <f>CONCATENATE(ROUND((F36/F27)*100,2),"%")</f>
@@ -20605,8 +20605,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="171"/>
-      <c r="K37" s="171"/>
+      <c r="J37" s="146"/>
+      <c r="K37" s="146"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20655,6 +20655,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="J29:K29"/>
@@ -20664,20 +20678,6 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="G17:I17"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="41" priority="4" operator="greaterThan">
@@ -20725,35 +20725,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
-        <v>271</v>
-      </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="B1" s="161" t="s">
+        <v>269</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45477</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20765,10 +20765,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
-        <v>345</v>
-      </c>
-      <c r="I2" s="156"/>
+      <c r="H2" s="153" t="s">
+        <v>343</v>
+      </c>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20781,25 +20781,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -20895,7 +20895,7 @@
         <v>262500</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G6" s="45">
         <v>45534</v>
@@ -20914,7 +20914,7 @@
         <v>45543</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M6" s="5">
         <v>277732</v>
@@ -21048,7 +21048,7 @@
         <v>45534</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E11" s="5">
         <v>100000</v>
@@ -21077,7 +21077,7 @@
         <v>45550</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E12" s="5">
         <v>19643</v>
@@ -21104,7 +21104,7 @@
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="57"/>
@@ -21133,11 +21133,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
-        <v>178</v>
-      </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="G14" s="148" t="s">
+        <v>176</v>
+      </c>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21160,10 +21160,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45477</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21187,7 +21187,7 @@
         <v>100</v>
       </c>
       <c r="H16" s="55" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I16" s="56"/>
       <c r="J16" s="21">
@@ -21209,11 +21209,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21559,7 +21559,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C32" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D32" s="6">
         <v>133202</v>
@@ -21574,23 +21574,23 @@
         <v>88</v>
       </c>
       <c r="H32" s="93" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
-        <v>248</v>
-      </c>
-      <c r="M32" s="144"/>
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
+        <v>246</v>
+      </c>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D33" s="6">
         <v>30000</v>
@@ -21611,13 +21611,13 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M33" s="62">
         <v>600000</v>
@@ -21643,13 +21643,13 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="M34" s="62">
         <v>250000</v>
@@ -21664,7 +21664,7 @@
         <v>403043.19999999995</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F35" s="59">
         <f t="shared" si="2"/>
@@ -21679,13 +21679,13 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="M35" s="62">
         <v>50000</v>
@@ -21704,11 +21704,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="170">
+      <c r="J36" s="145">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="170"/>
+      <c r="K36" s="145"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21725,13 +21725,13 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M37" s="62">
         <v>133202</v>
@@ -21746,11 +21746,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21767,11 +21767,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21789,17 +21789,17 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E41" s="52" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F41" s="109" t="str">
         <f>CONCATENATE(ROUND((F40/F31)*100,2),"%")</f>
@@ -21808,10 +21808,10 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M41" s="5">
         <f>SUM(M33:M40)</f>
@@ -21831,7 +21831,7 @@
       <c r="J42" s="80"/>
       <c r="K42" s="80"/>
       <c r="L42" s="83" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M42" s="82">
         <f>J40-M41</f>
@@ -21880,6 +21880,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -21896,16 +21906,6 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
@@ -21954,35 +21954,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
-        <v>272</v>
-      </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="B1" s="161" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45548</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -21994,10 +21994,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
-        <v>293</v>
-      </c>
-      <c r="I2" s="156"/>
+      <c r="H2" s="153" t="s">
+        <v>291</v>
+      </c>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22010,25 +22010,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22087,7 +22087,7 @@
         <v>210000</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G5" s="45">
         <v>45599</v>
@@ -22106,7 +22106,7 @@
         <v>45609</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M5" s="5">
         <v>558927</v>
@@ -22145,7 +22145,7 @@
         <v>45620</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="M6" s="5">
         <v>1478368</v>
@@ -22161,13 +22161,13 @@
         <v>45561</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E7" s="9">
         <v>35000</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G7" s="102">
         <v>45606</v>
@@ -22186,7 +22186,7 @@
         <v>45633</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M7" s="5">
         <v>377808</v>
@@ -22202,7 +22202,7 @@
         <v>45561</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E8" s="9">
         <v>3500</v>
@@ -22301,7 +22301,7 @@
         <v>45599</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E11" s="5">
         <v>1200</v>
@@ -22334,7 +22334,7 @@
         <v>45609</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E12" s="5">
         <v>5600</v>
@@ -22367,7 +22367,7 @@
         <v>45620</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E13" s="5">
         <v>893146</v>
@@ -22396,17 +22396,17 @@
         <v>45620</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E14" s="5">
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22433,10 +22433,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45561</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22454,7 +22454,7 @@
         <v>45634</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E16" s="5">
         <v>27000</v>
@@ -22463,10 +22463,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
-        <v>293</v>
-      </c>
-      <c r="I16" s="167"/>
+      <c r="H16" s="153" t="s">
+        <v>291</v>
+      </c>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22484,17 +22484,17 @@
         <v>45634</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E17" s="5">
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22544,7 +22544,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="5"/>
       <c r="F19" s="22" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G19" s="45">
         <v>45602</v>
@@ -22854,19 +22854,19 @@
         <v>88</v>
       </c>
       <c r="H32" s="93" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
-        <v>248</v>
-      </c>
-      <c r="M32" s="144"/>
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
+        <v>246</v>
+      </c>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -22885,13 +22885,13 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M33" s="62">
         <v>200000</v>
@@ -22899,7 +22899,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E34" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F34" s="59">
         <f t="shared" ref="F34:F39" si="2">H34*G34</f>
@@ -22914,11 +22914,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -22943,11 +22943,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -22964,13 +22964,13 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M36" s="62">
         <v>900000</v>
@@ -22985,11 +22985,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23006,11 +23006,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23018,7 +23018,7 @@
         <v>300000</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -23030,11 +23030,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23086,13 +23086,13 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="170">
+      <c r="J42" s="145">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="170"/>
+      <c r="K42" s="145"/>
       <c r="L42" s="52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M42" s="5">
         <f>SUM(M33:M41)</f>
@@ -23101,7 +23101,7 @@
     </row>
     <row r="43" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E43" s="52" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F43" s="109" t="str">
         <f>CONCATENATE(ROUND((F42/F31)*100,2),"%")</f>
@@ -23110,10 +23110,10 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="171"/>
-      <c r="K43" s="171"/>
+      <c r="J43" s="146"/>
+      <c r="K43" s="146"/>
       <c r="L43" s="83" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M43" s="114">
         <f>J42-M42</f>
@@ -23126,11 +23126,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="172" t="s">
-        <v>198</v>
-      </c>
-      <c r="B45" s="172"/>
-      <c r="C45" s="172"/>
+      <c r="A45" s="147" t="s">
+        <v>196</v>
+      </c>
+      <c r="B45" s="147"/>
+      <c r="C45" s="147"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23154,10 +23154,10 @@
       </c>
       <c r="D46" s="40"/>
       <c r="F46" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
@@ -23181,7 +23181,7 @@
     <row r="50" spans="7:13" x14ac:dyDescent="0.3">
       <c r="H50" s="26"/>
       <c r="L50" s="58" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="M50" s="62">
         <v>400000</v>
@@ -23190,7 +23190,7 @@
     <row r="51" spans="7:13" x14ac:dyDescent="0.3">
       <c r="K51" s="40"/>
       <c r="L51" s="58" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="M51" s="62">
         <v>300000</v>
@@ -23198,7 +23198,7 @@
     </row>
     <row r="52" spans="7:13" x14ac:dyDescent="0.3">
       <c r="L52" s="58" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M52" s="62">
         <v>40000</v>
@@ -23206,7 +23206,7 @@
     </row>
     <row r="53" spans="7:13" x14ac:dyDescent="0.3">
       <c r="L53" s="58" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M53" s="62">
         <v>38000</v>
@@ -23214,7 +23214,7 @@
     </row>
     <row r="54" spans="7:13" x14ac:dyDescent="0.3">
       <c r="L54" s="58" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M54" s="62">
         <v>15000</v>
@@ -23247,6 +23247,19 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -23261,19 +23274,6 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="33" priority="1" operator="greaterThan">
@@ -23322,35 +23322,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
-        <v>273</v>
-      </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="B1" s="161" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45631</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23362,10 +23362,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
-        <v>347</v>
-      </c>
-      <c r="I2" s="156"/>
+      <c r="H2" s="153" t="s">
+        <v>345</v>
+      </c>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23378,25 +23378,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23449,13 +23449,13 @@
         <v>45631</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E5" s="9">
         <v>265000</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G5" s="45">
         <v>45692</v>
@@ -23474,7 +23474,7 @@
         <v>45701</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M5" s="5">
         <v>526628</v>
@@ -23513,7 +23513,7 @@
         <v>45709</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M6" s="5">
         <v>1357200</v>
@@ -23552,7 +23552,7 @@
         <v>45717</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M7" s="5">
         <v>148000</v>
@@ -23568,13 +23568,13 @@
         <v>45653</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E8" s="9">
         <v>40000</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G8" s="45">
         <v>45709</v>
@@ -23603,7 +23603,7 @@
         <v>45701</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E9" s="5">
         <v>8000</v>
@@ -23736,11 +23736,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23761,10 +23761,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45653</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23785,10 +23785,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
-        <v>348</v>
-      </c>
-      <c r="I16" s="167"/>
+      <c r="H16" s="153" t="s">
+        <v>346</v>
+      </c>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23806,11 +23806,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24151,19 +24151,19 @@
         <v>88</v>
       </c>
       <c r="H32" s="93" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
-        <v>248</v>
-      </c>
-      <c r="M32" s="144"/>
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
+        <v>246</v>
+      </c>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24182,13 +24182,13 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M33" s="62">
         <v>200000</v>
@@ -24196,7 +24196,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E34" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F34" s="59">
         <f t="shared" ref="F34:F39" si="2">H34*G34</f>
@@ -24211,13 +24211,13 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M34" s="62">
         <v>50000</v>
@@ -24240,13 +24240,13 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M35" s="62">
         <v>200000</v>
@@ -24261,11 +24261,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24282,11 +24282,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24303,11 +24303,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24324,11 +24324,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24346,13 +24346,13 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M40" s="5">
         <f>SUM(M33:M39)</f>
@@ -24361,7 +24361,7 @@
     </row>
     <row r="41" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E41" s="52" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F41" s="109" t="str">
         <f>CONCATENATE(ROUND((F40/F31)*100,2),"%")</f>
@@ -24370,10 +24370,10 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="83" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M41" s="5">
         <f>J40-M40</f>
@@ -24386,11 +24386,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
-        <v>198</v>
-      </c>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="A43" s="147" t="s">
+        <v>196</v>
+      </c>
+      <c r="B43" s="147"/>
+      <c r="C43" s="147"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24417,25 +24417,25 @@
       </c>
       <c r="J44" s="61"/>
       <c r="K44" s="119" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B45"/>
       <c r="F45" s="93" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G45" s="112">
         <v>34</v>
       </c>
       <c r="H45" s="93" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I45" s="112">
         <v>2000</v>
       </c>
       <c r="J45" s="112" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K45" s="124">
         <f>G47/11</f>
@@ -24445,19 +24445,19 @@
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B46"/>
       <c r="F46" s="93" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G46" s="112">
         <v>758</v>
       </c>
       <c r="H46" s="93" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I46" s="61">
         <v>110000</v>
       </c>
       <c r="J46" s="61" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K46" s="119">
         <v>1470</v>
@@ -24465,7 +24465,7 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F47" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G47" s="5">
         <f>(G46*G45*2)+I45</f>
@@ -24478,7 +24478,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F48" s="15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G48" s="111">
         <f>K45*8</f>
@@ -24495,7 +24495,7 @@
     </row>
     <row r="49" spans="3:11" x14ac:dyDescent="0.3">
       <c r="F49" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G49" s="111">
         <f>K45*3</f>
@@ -24515,7 +24515,7 @@
     </row>
     <row r="51" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C51" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52" spans="3:11" x14ac:dyDescent="0.3">
@@ -24538,23 +24538,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24563,6 +24546,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="29" priority="2" operator="greaterThan">
@@ -24614,35 +24614,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
-        <v>274</v>
-      </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="B1" s="161" t="s">
+        <v>272</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45714</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24654,10 +24654,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
-        <v>349</v>
-      </c>
-      <c r="I2" s="156"/>
+      <c r="H2" s="153" t="s">
+        <v>347</v>
+      </c>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24670,25 +24670,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -24741,13 +24741,13 @@
         <v>45714</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E5" s="9">
         <v>257500</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G5" s="45">
         <v>45765</v>
@@ -24766,7 +24766,7 @@
         <v>45775</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M5" s="5">
         <v>368280</v>
@@ -24782,13 +24782,13 @@
         <v>45743</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E6" s="9">
         <v>35000</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G6" s="45">
         <v>45775</v>
@@ -24807,7 +24807,7 @@
         <v>45787</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M6" s="5">
         <v>571064</v>
@@ -24823,7 +24823,7 @@
         <v>45792</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E7" s="9">
         <v>984721</v>
@@ -24846,7 +24846,7 @@
         <v>45791</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="M7" s="5">
         <v>679140</v>
@@ -24862,7 +24862,7 @@
         <v>45792</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E8" s="9">
         <v>108973</v>
@@ -24885,7 +24885,7 @@
         <v>45791</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M8" s="5">
         <v>173206</v>
@@ -25030,11 +25030,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25057,10 +25057,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45743</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25083,10 +25083,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
-        <v>350</v>
-      </c>
-      <c r="I16" s="167"/>
+      <c r="H16" s="153" t="s">
+        <v>348</v>
+      </c>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25106,11 +25106,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25445,19 +25445,19 @@
         <v>88</v>
       </c>
       <c r="H32" s="93" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
-        <v>248</v>
-      </c>
-      <c r="M32" s="144"/>
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
+        <v>246</v>
+      </c>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25476,13 +25476,13 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="M33" s="62">
         <v>400000</v>
@@ -25505,13 +25505,13 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="M34" s="62">
         <v>200000</v>
@@ -25520,7 +25520,7 @@
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C35" s="126"/>
       <c r="E35" s="15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F35" s="59">
         <f t="shared" si="2"/>
@@ -25535,13 +25535,13 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M35" s="62">
         <v>250000</v>
@@ -25564,13 +25564,13 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M36" s="62">
         <v>985721</v>
@@ -25584,11 +25584,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25601,11 +25601,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25618,11 +25618,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25640,13 +25640,13 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M40" s="5">
         <f>SUM(M33:M39)</f>
@@ -25655,7 +25655,7 @@
     </row>
     <row r="41" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E41" s="52" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F41" s="109" t="str">
         <f>CONCATENATE(ROUND((F40/F31)*100,2),"%")</f>
@@ -25664,10 +25664,10 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="83" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M41" s="105">
         <f>J40-M40</f>
@@ -25680,11 +25680,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
-        <v>198</v>
-      </c>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="A43" s="147" t="s">
+        <v>196</v>
+      </c>
+      <c r="B43" s="147"/>
+      <c r="C43" s="147"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25716,6 +25716,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25724,23 +25741,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
@@ -25790,34 +25790,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
-        <v>275</v>
-      </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="A1" s="161" t="s">
+        <v>273</v>
+      </c>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>45840</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -25829,10 +25829,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
-        <v>351</v>
-      </c>
-      <c r="H2" s="156"/>
+      <c r="G2" s="153" t="s">
+        <v>349</v>
+      </c>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25845,25 +25845,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -25914,13 +25914,13 @@
         <v>45840</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D5" s="9">
         <v>300000</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F5" s="45">
         <v>45884</v>
@@ -25939,7 +25939,7 @@
         <v>45893</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L5" s="5">
         <v>521040</v>
@@ -25952,7 +25952,7 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D6" s="5">
         <v>160000</v>
@@ -25975,7 +25975,7 @@
         <v>45900</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L6" s="5">
         <v>756496</v>
@@ -25988,7 +25988,7 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D7" s="5">
         <v>920000</v>
@@ -26011,13 +26011,13 @@
         <v>45901</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="L7" s="5">
         <v>940405.5</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -26026,7 +26026,7 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D8" s="5">
         <v>30000</v>
@@ -26049,7 +26049,7 @@
         <v>45912</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L8" s="5">
         <v>317988</v>
@@ -26181,11 +26181,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26205,10 +26205,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>45840</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26228,10 +26228,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
-        <v>293</v>
-      </c>
-      <c r="H16" s="167"/>
+      <c r="G16" s="153" t="s">
+        <v>291</v>
+      </c>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26248,11 +26248,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26577,13 +26577,13 @@
         <v>1050000</v>
       </c>
       <c r="F31" s="93" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G31" s="130">
         <v>900000</v>
       </c>
       <c r="H31" s="61" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I31" s="175">
         <v>150000</v>
@@ -26603,23 +26603,23 @@
         <v>88</v>
       </c>
       <c r="G32" s="93" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
-        <v>248</v>
-      </c>
-      <c r="L32" s="144"/>
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
+        <v>246</v>
+      </c>
+      <c r="L32" s="159"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E33" s="59">
         <f>G33*F33</f>
@@ -26634,13 +26634,13 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L33" s="62">
         <v>100000</v>
@@ -26648,7 +26648,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D34" s="15" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E34" s="59">
         <f t="shared" ref="E34:E39" si="2">G34*F34</f>
@@ -26663,13 +26663,13 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="L34" s="62">
         <v>600000</v>
@@ -26678,7 +26678,7 @@
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B35" s="126"/>
       <c r="D35" s="15" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E35" s="59">
         <f t="shared" si="2"/>
@@ -26693,13 +26693,13 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L35" s="62">
         <v>700000</v>
@@ -26707,7 +26707,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D36" s="15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E36" s="59">
         <f t="shared" si="2"/>
@@ -26722,11 +26722,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26736,7 +26736,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D37" s="15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E37" s="59">
         <f t="shared" si="2"/>
@@ -26751,13 +26751,13 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L37" s="62">
         <v>16000</v>
@@ -26765,7 +26765,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D38" s="15" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E38" s="59">
         <f t="shared" si="2"/>
@@ -26780,13 +26780,13 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L38" s="62">
         <v>200000</v>
@@ -26801,11 +26801,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26823,13 +26823,13 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L40" s="5">
         <f>SUM(L33:L39)</f>
@@ -26838,7 +26838,7 @@
     </row>
     <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D41" s="52" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E41" s="109" t="str">
         <f>CONCATENATE(ROUND((E40/E31)*100,2),"%")</f>
@@ -26847,10 +26847,10 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L41" s="5">
         <f>I40-L40</f>
@@ -26863,10 +26863,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
-        <v>290</v>
-      </c>
-      <c r="B43" s="172"/>
+      <c r="A43" s="147" t="s">
+        <v>288</v>
+      </c>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -26901,11 +26901,28 @@
     </row>
     <row r="56" spans="5:9" x14ac:dyDescent="0.3">
       <c r="I56" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -26914,23 +26931,6 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5226141-15A9-492F-9C24-8451B05E4E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993AE84D-172A-41A2-9302-3A614262CF97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Term-1" sheetId="4" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="356">
   <si>
     <t>#</t>
   </si>
@@ -1126,6 +1126,9 @@
   </si>
   <si>
     <t>37 days</t>
+  </si>
+  <si>
+    <t>3 tons so far</t>
   </si>
 </sst>
 </file>
@@ -2187,19 +2190,35 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2215,41 +2234,19 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2281,31 +2278,45 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2313,7 +2324,15 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2325,29 +2344,13 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3166,7 +3169,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-343485</c:v>
+                  <c:v>-649485</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3698,7 +3701,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>3247732</c:v>
+                  <c:v>2941732</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4113,7 +4116,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-813207.5</c:v>
+                  <c:v>-1119207.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7972,10 +7975,10 @@
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="168">
         <v>45076</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="169"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
@@ -8005,10 +8008,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="170" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="171"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8021,25 +8024,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8061,10 +8064,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="173" t="s">
+      <c r="H4" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="174"/>
+      <c r="I4" s="153"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -8332,11 +8335,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="154" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="155"/>
+      <c r="I12" s="156"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8397,10 +8400,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="170" t="s">
         <v>328</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="171"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8426,11 +8429,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="173"/>
+      <c r="I15" s="173"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -8457,10 +8460,10 @@
       <c r="G16" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="173" t="s">
+      <c r="H16" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="174"/>
+      <c r="I16" s="153"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -10769,10 +10772,10 @@
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="168">
         <v>45918</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="169"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
@@ -10798,10 +10801,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="170" t="s">
         <v>347</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="171"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10814,25 +10817,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11195,11 +11198,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="154" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="155"/>
+      <c r="H14" s="156"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11219,10 +11222,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="168">
         <v>45918</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="169"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11242,10 +11245,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="170" t="s">
         <v>347</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="185"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11262,11 +11265,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="173"/>
+      <c r="H17" s="176"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11606,14 +11609,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="174" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="174"/>
+      <c r="K32" s="180" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="186"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11633,11 +11636,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="175">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="175"/>
       <c r="K33" s="85" t="s">
         <v>320</v>
       </c>
@@ -11663,11 +11666,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="175">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="175"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11694,11 +11697,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="175">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="175"/>
       <c r="K35" s="85" t="s">
         <v>330</v>
       </c>
@@ -11726,11 +11729,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="175">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="175"/>
       <c r="K36" s="85" t="s">
         <v>331</v>
       </c>
@@ -11756,11 +11759,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="175">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="175"/>
       <c r="K37" s="85" t="s">
         <v>333</v>
       </c>
@@ -11786,11 +11789,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="175">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="175"/>
       <c r="K38" s="85" t="s">
         <v>320</v>
       </c>
@@ -11808,11 +11811,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="175"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11835,11 +11838,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="177">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="177"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -11860,8 +11863,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="178"/>
+      <c r="J41" s="178"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -11877,10 +11880,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="182" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="182"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11900,10 +11903,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="182" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="182"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -12025,10 +12028,10 @@
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="168">
         <v>46016</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="169"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
@@ -12054,10 +12057,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="170" t="s">
         <v>350</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="171"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12070,25 +12073,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12382,11 +12385,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="154" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="155"/>
+      <c r="H14" s="156"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12406,10 +12409,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="168">
         <v>46016</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="169"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12429,10 +12432,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="170" t="s">
         <v>351</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="185"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12449,11 +12452,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="173"/>
+      <c r="H17" s="176"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12775,14 +12778,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="174" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="174"/>
+      <c r="K32" s="180" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="186"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12802,11 +12805,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="175">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="175"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12824,11 +12827,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="144">
+      <c r="I34" s="175">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="175"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12843,11 +12846,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="144">
+      <c r="I35" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="175"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -12863,11 +12866,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="144">
+      <c r="I36" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="175"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12881,11 +12884,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="144">
+      <c r="I37" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="175"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12899,11 +12902,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="175"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12917,11 +12920,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="175"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12940,11 +12943,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="177">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="177"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -12965,8 +12968,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="178"/>
+      <c r="J41" s="178"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -12982,10 +12985,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="182" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="182"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13005,10 +13008,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="182" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="182"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13130,16 +13133,16 @@
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="168">
         <v>46068</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="169"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
       <c r="J1" s="164">
         <f>L2-D2</f>
-        <v>-343485</v>
+        <v>-649485</v>
       </c>
       <c r="K1" s="165"/>
       <c r="L1" s="18"/>
@@ -13153,17 +13156,17 @@
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>343485</v>
+        <v>649485</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="str">
+      <c r="G2" s="170" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>35 days</v>
-      </c>
-      <c r="H2" s="168"/>
+        <v>42 days</v>
+      </c>
+      <c r="H2" s="171"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13176,25 +13179,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13353,9 +13356,15 @@
       <c r="A9" s="41">
         <v>5</v>
       </c>
-      <c r="B9" s="132"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
+      <c r="B9" s="132">
+        <v>46107</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" s="9">
+        <v>6000</v>
+      </c>
       <c r="E9" s="22"/>
       <c r="F9" s="48"/>
       <c r="G9" s="46"/>
@@ -13375,10 +13384,16 @@
       <c r="A10" s="41">
         <v>6</v>
       </c>
-      <c r="B10" s="132"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="22"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" s="9">
+        <v>300000</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>355</v>
+      </c>
       <c r="F10" s="48"/>
       <c r="G10" s="46"/>
       <c r="H10" s="49" t="str">
@@ -13397,8 +13412,9 @@
       <c r="A11" s="41">
         <v>7</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="22"/>
       <c r="F11" s="48"/>
       <c r="G11" s="46"/>
@@ -13462,15 +13478,15 @@
       <c r="A14" s="41">
         <v>10</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="132"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="9"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="154" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="155"/>
+      <c r="H14" s="156"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13490,10 +13506,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="168">
         <v>46068</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="169"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13513,11 +13529,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="str">
+      <c r="G16" s="170" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>35 days</v>
-      </c>
-      <c r="H16" s="154"/>
+        <v>42 days</v>
+      </c>
+      <c r="H16" s="185"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13534,11 +13550,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="173"/>
+      <c r="H17" s="176"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13861,14 +13877,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="174" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="174"/>
+      <c r="K32" s="180" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="186"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -13880,11 +13896,11 @@
       <c r="F33" s="59"/>
       <c r="G33" s="67"/>
       <c r="H33" s="62"/>
-      <c r="I33" s="144">
+      <c r="I33" s="175">
         <f>G33*H33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="175"/>
       <c r="K33" s="85"/>
       <c r="L33" s="136"/>
       <c r="M33" s="15"/>
@@ -13898,11 +13914,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="144">
+      <c r="I34" s="175">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="175"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -13917,11 +13933,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="144">
+      <c r="I35" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="175"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -13937,11 +13953,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="144">
+      <c r="I36" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="175"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -13955,11 +13971,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="144">
+      <c r="I37" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="175"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -13973,11 +13989,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="175"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -13991,11 +14007,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="175"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14014,11 +14030,11 @@
         <v>0</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="177">
         <f>SUM(I33:I39)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="177"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -14039,8 +14055,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="178"/>
+      <c r="J41" s="178"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -14056,20 +14072,26 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="182" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="59"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="131" t="e">
+      <c r="B43" s="182"/>
+      <c r="C43" s="59">
+        <v>800000</v>
+      </c>
+      <c r="D43" s="15">
+        <v>200</v>
+      </c>
+      <c r="E43" s="131">
         <f>C43/D43</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F43" s="62"/>
-      <c r="G43" s="101" t="e">
+        <v>4000</v>
+      </c>
+      <c r="F43" s="62">
+        <v>150</v>
+      </c>
+      <c r="G43" s="101">
         <f>E43*F43</f>
-        <v>#DIV/0!</v>
+        <v>600000</v>
       </c>
       <c r="H43" s="15"/>
       <c r="I43" s="15"/>
@@ -14079,10 +14101,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="182" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="182"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -14215,21 +14237,21 @@
       <c r="H1" s="142" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="185" t="s">
+      <c r="I1" s="150" t="s">
         <v>206</v>
       </c>
-      <c r="J1" s="185"/>
-      <c r="K1" s="185"/>
-      <c r="L1" s="185"/>
-      <c r="M1" s="186"/>
-      <c r="N1" s="182" t="str">
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="147" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>2 year, 11 months, 20 days</v>
-      </c>
-      <c r="O1" s="183"/>
-      <c r="P1" s="183"/>
-      <c r="Q1" s="183"/>
-      <c r="R1" s="184"/>
+        <v>2 year, 11 months, 27 days</v>
+      </c>
+      <c r="O1" s="148"/>
+      <c r="P1" s="148"/>
+      <c r="Q1" s="148"/>
+      <c r="R1" s="149"/>
       <c r="S1" s="8" t="s">
         <v>205</v>
       </c>
@@ -14637,7 +14659,7 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>-343485</v>
+        <v>-649485</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
@@ -14645,7 +14667,7 @@
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
-        <v>343485</v>
+        <v>649485</v>
       </c>
       <c r="G13" s="143">
         <f>MIN('Term-12'!G6:G14)</f>
@@ -14792,14 +14814,14 @@
       <c r="H24" s="141"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="179" t="s">
+      <c r="A25" s="144" t="s">
         <v>189</v>
       </c>
-      <c r="B25" s="180"/>
-      <c r="C25" s="181"/>
+      <c r="B25" s="145"/>
+      <c r="C25" s="146"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>3247732</v>
+        <v>2941732</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
@@ -14807,7 +14829,7 @@
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
-        <v>14173062</v>
+        <v>14479062</v>
       </c>
       <c r="G25" s="143"/>
       <c r="H25" s="89"/>
@@ -14892,7 +14914,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>-813207.5</v>
+        <v>-1119207.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -14923,7 +14945,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>3247732</v>
+        <v>2941732</v>
       </c>
     </row>
   </sheetData>
@@ -15182,10 +15204,10 @@
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="168">
         <v>45163</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="169"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
@@ -15215,10 +15237,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="170" t="s">
         <v>353</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="171"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15231,25 +15253,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -15271,10 +15293,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="173" t="s">
+      <c r="H4" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="174"/>
+      <c r="I4" s="153"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -15496,11 +15518,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="154" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="155"/>
+      <c r="I12" s="156"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15521,10 +15543,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="168">
         <v>45163</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="169"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15545,10 +15567,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="170" t="s">
         <v>353</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="171"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15566,11 +15588,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="173"/>
+      <c r="I15" s="173"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -15591,10 +15613,10 @@
       <c r="G16" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="173" t="s">
+      <c r="H16" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="174"/>
+      <c r="I16" s="153"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -17414,10 +17436,10 @@
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="168">
         <v>45163</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="169"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
@@ -17447,10 +17469,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="170" t="s">
         <v>354</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="171"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17463,25 +17485,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17503,10 +17525,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="173" t="s">
+      <c r="H4" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="174"/>
+      <c r="I4" s="153"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -17724,11 +17746,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="154" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="155"/>
+      <c r="I12" s="156"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17749,10 +17771,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="168">
         <v>45163</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="169"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17773,10 +17795,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="170" t="s">
         <v>354</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="171"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17794,11 +17816,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="173"/>
+      <c r="I15" s="173"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17819,10 +17841,10 @@
       <c r="G16" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="173" t="s">
+      <c r="H16" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="174"/>
+      <c r="I16" s="153"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -19642,10 +19664,10 @@
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="168">
         <v>45345</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="169"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
@@ -19675,10 +19697,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="170" t="s">
         <v>342</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="171"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19691,25 +19713,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -19731,10 +19753,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="173" t="s">
+      <c r="H4" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="174"/>
+      <c r="I4" s="153"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -20051,11 +20073,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="154" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="155"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20076,10 +20098,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="168">
         <v>45345</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="169"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20121,11 +20143,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="173"/>
+      <c r="I17" s="176"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20343,8 +20365,8 @@
       <c r="G27" s="61"/>
       <c r="H27" s="61"/>
       <c r="I27" s="61"/>
-      <c r="J27" s="175"/>
-      <c r="K27" s="175"/>
+      <c r="J27" s="179"/>
+      <c r="K27" s="179"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E28" s="61" t="s">
@@ -20362,10 +20384,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="158" t="s">
+      <c r="J28" s="174" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="158"/>
+      <c r="K28" s="174"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20384,11 +20406,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="144">
+      <c r="J29" s="175">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="144"/>
+      <c r="K29" s="175"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20413,11 +20435,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="144">
+      <c r="J30" s="175">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="144"/>
+      <c r="K30" s="175"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20442,11 +20464,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="144">
+      <c r="J31" s="175">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="144"/>
+      <c r="K31" s="175"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20471,11 +20493,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="144">
+      <c r="J32" s="175">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="144"/>
+      <c r="K32" s="175"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20500,11 +20522,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="175">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="175"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20528,11 +20550,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="175">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="175"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20556,11 +20578,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="175">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="175"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20582,11 +20604,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="145">
+      <c r="J36" s="177">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="145"/>
+      <c r="K36" s="177"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20605,8 +20627,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="146"/>
-      <c r="K37" s="146"/>
+      <c r="J37" s="178"/>
+      <c r="K37" s="178"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20735,10 +20757,10 @@
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="168">
         <v>45477</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="169"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
@@ -20765,10 +20787,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="170" t="s">
         <v>343</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="171"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20781,25 +20803,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -20821,10 +20843,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="173" t="s">
+      <c r="H4" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="174"/>
+      <c r="I4" s="153"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -21133,11 +21155,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="154" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="155"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21160,10 +21182,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="168">
         <v>45477</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="169"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21209,11 +21231,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="173"/>
+      <c r="I17" s="176"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21554,8 +21576,8 @@
       <c r="G31" s="61"/>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="175"/>
+      <c r="J31" s="179"/>
+      <c r="K31" s="179"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C32" s="6" t="s">
@@ -21579,14 +21601,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="174" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="174"/>
+      <c r="L32" s="180" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="180"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -21611,11 +21633,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="175">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="175"/>
       <c r="L33" s="85" t="s">
         <v>172</v>
       </c>
@@ -21643,11 +21665,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="175">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="175"/>
       <c r="L34" s="85" t="s">
         <v>173</v>
       </c>
@@ -21679,11 +21701,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="175">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="175"/>
       <c r="L35" s="85" t="s">
         <v>173</v>
       </c>
@@ -21704,11 +21726,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="145">
+      <c r="J36" s="177">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="145"/>
+      <c r="K36" s="177"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21725,11 +21747,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="175"/>
       <c r="L37" s="85" t="s">
         <v>179</v>
       </c>
@@ -21746,11 +21768,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="175"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21767,11 +21789,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="175"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21789,11 +21811,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="177">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="177"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -21808,8 +21830,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="178"/>
+      <c r="K41" s="178"/>
       <c r="L41" s="52" t="s">
         <v>174</v>
       </c>
@@ -21839,16 +21861,16 @@
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="176" t="s">
+      <c r="A43" s="181" t="s">
         <v>163</v>
       </c>
-      <c r="B43" s="176"/>
-      <c r="C43" s="176"/>
-      <c r="F43" s="176" t="s">
+      <c r="B43" s="181"/>
+      <c r="C43" s="181"/>
+      <c r="F43" s="181" t="s">
         <v>164</v>
       </c>
-      <c r="G43" s="176"/>
-      <c r="H43" s="176"/>
+      <c r="G43" s="181"/>
+      <c r="H43" s="181"/>
       <c r="K43" s="14"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
@@ -21964,10 +21986,10 @@
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="168">
         <v>45548</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="169"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
@@ -21994,10 +22016,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="170" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="171"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22010,25 +22032,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22402,11 +22424,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="154" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="155"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22433,10 +22455,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="168">
         <v>45561</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="169"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22463,10 +22485,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="170" t="s">
         <v>291</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="185"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22490,11 +22512,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="173"/>
+      <c r="I17" s="176"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22838,8 +22860,8 @@
       <c r="G31" s="61"/>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="175"/>
+      <c r="J31" s="179"/>
+      <c r="K31" s="179"/>
       <c r="L31" s="100"/>
       <c r="M31" s="100"/>
     </row>
@@ -22859,14 +22881,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="174" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="174"/>
+      <c r="L32" s="180" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="180"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -22885,11 +22907,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="175">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="175"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -22914,11 +22936,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="175">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="175"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -22943,11 +22965,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="175">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="175"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -22964,11 +22986,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="144">
+      <c r="J36" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="175"/>
       <c r="L36" s="85" t="s">
         <v>172</v>
       </c>
@@ -22985,11 +23007,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="175"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23006,11 +23028,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="175"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23030,11 +23052,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="175"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23048,8 +23070,8 @@
       <c r="G40" s="59"/>
       <c r="H40" s="67"/>
       <c r="I40" s="62"/>
-      <c r="J40" s="177"/>
-      <c r="K40" s="178"/>
+      <c r="J40" s="183"/>
+      <c r="K40" s="184"/>
       <c r="L40" s="85" t="s">
         <v>155</v>
       </c>
@@ -23063,8 +23085,8 @@
       <c r="G41" s="59"/>
       <c r="H41" s="67"/>
       <c r="I41" s="62"/>
-      <c r="J41" s="177"/>
-      <c r="K41" s="178"/>
+      <c r="J41" s="183"/>
+      <c r="K41" s="184"/>
       <c r="L41" s="85" t="s">
         <v>155</v>
       </c>
@@ -23086,11 +23108,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="145">
+      <c r="J42" s="177">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="145"/>
+      <c r="K42" s="177"/>
       <c r="L42" s="52" t="s">
         <v>174</v>
       </c>
@@ -23110,8 +23132,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="146"/>
-      <c r="K43" s="146"/>
+      <c r="J43" s="178"/>
+      <c r="K43" s="178"/>
       <c r="L43" s="83" t="s">
         <v>175</v>
       </c>
@@ -23126,11 +23148,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="147" t="s">
+      <c r="A45" s="182" t="s">
         <v>196</v>
       </c>
-      <c r="B45" s="147"/>
-      <c r="C45" s="147"/>
+      <c r="B45" s="182"/>
+      <c r="C45" s="182"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23332,10 +23354,10 @@
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="168">
         <v>45631</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="169"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
@@ -23362,10 +23384,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="170" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="171"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23378,25 +23400,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23736,11 +23758,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="154" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="155"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23761,10 +23783,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="168">
         <v>45653</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="169"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23785,10 +23807,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="170" t="s">
         <v>346</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="185"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23806,11 +23828,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="173"/>
+      <c r="I17" s="176"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24135,8 +24157,8 @@
       <c r="G31" s="61"/>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="175"/>
+      <c r="J31" s="179"/>
+      <c r="K31" s="179"/>
       <c r="L31" s="100"/>
       <c r="M31" s="100"/>
     </row>
@@ -24156,14 +24178,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="174" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="174"/>
+      <c r="L32" s="180" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="180"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24182,11 +24204,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="175">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="175"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -24211,11 +24233,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="175">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="175"/>
       <c r="L34" s="85" t="s">
         <v>215</v>
       </c>
@@ -24240,11 +24262,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="175">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="175"/>
       <c r="L35" s="85" t="s">
         <v>215</v>
       </c>
@@ -24261,11 +24283,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="144">
+      <c r="J36" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="175"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24282,11 +24304,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="175"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24303,11 +24325,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="175"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24324,11 +24346,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="175"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24346,11 +24368,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="177">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="177"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -24370,8 +24392,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="178"/>
+      <c r="K41" s="178"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -24386,11 +24408,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="182" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="147"/>
+      <c r="B43" s="182"/>
+      <c r="C43" s="182"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24624,10 +24646,10 @@
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="168">
         <v>45714</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="169"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
@@ -24654,10 +24676,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="170" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="171"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24670,25 +24692,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -25030,11 +25052,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="154" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="155"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25057,10 +25079,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="168">
         <v>45743</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="169"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25083,10 +25105,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="170" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="185"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25106,11 +25128,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="173"/>
+      <c r="I17" s="176"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25429,8 +25451,8 @@
       <c r="G31" s="61"/>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="175"/>
+      <c r="J31" s="179"/>
+      <c r="K31" s="179"/>
       <c r="L31" s="100"/>
       <c r="M31" s="100"/>
     </row>
@@ -25450,14 +25472,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="174" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="174"/>
+      <c r="L32" s="180" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="180"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25476,11 +25498,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="175">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="175"/>
       <c r="L33" s="85" t="s">
         <v>257</v>
       </c>
@@ -25505,11 +25527,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="175">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="175"/>
       <c r="L34" s="85" t="s">
         <v>262</v>
       </c>
@@ -25535,11 +25557,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="175">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="175"/>
       <c r="L35" s="85" t="s">
         <v>263</v>
       </c>
@@ -25564,11 +25586,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="144">
+      <c r="J36" s="175">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="175"/>
       <c r="L36" s="85" t="s">
         <v>264</v>
       </c>
@@ -25584,11 +25606,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="175"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25601,11 +25623,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="175"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25618,11 +25640,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="175"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25640,11 +25662,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="177">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="177"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -25664,8 +25686,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="178"/>
+      <c r="K41" s="178"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -25680,11 +25702,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="182" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="147"/>
+      <c r="B43" s="182"/>
+      <c r="C43" s="182"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25800,10 +25822,10 @@
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="168">
         <v>45840</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="169"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
@@ -25829,10 +25851,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="170" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="171"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25845,25 +25867,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -26181,11 +26203,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="154" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="155"/>
+      <c r="H14" s="156"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26205,10 +26227,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="168">
         <v>45840</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="169"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26228,10 +26250,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="170" t="s">
         <v>291</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="185"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26248,11 +26270,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="173"/>
+      <c r="H17" s="176"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26585,10 +26607,10 @@
       <c r="H31" s="61" t="s">
         <v>275</v>
       </c>
-      <c r="I31" s="175">
+      <c r="I31" s="179">
         <v>150000</v>
       </c>
-      <c r="J31" s="175"/>
+      <c r="J31" s="179"/>
       <c r="K31" s="100"/>
       <c r="L31" s="100"/>
     </row>
@@ -26608,14 +26630,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="174" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="174"/>
+      <c r="K32" s="180" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="159"/>
+      <c r="L32" s="180"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -26634,11 +26656,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="175">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="175"/>
       <c r="K33" s="85" t="s">
         <v>287</v>
       </c>
@@ -26663,11 +26685,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="175">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="175"/>
       <c r="K34" s="85" t="s">
         <v>290</v>
       </c>
@@ -26693,11 +26715,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="175">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="175"/>
       <c r="K35" s="85" t="s">
         <v>294</v>
       </c>
@@ -26722,11 +26744,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="175">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="175"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26751,11 +26773,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="175">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="175"/>
       <c r="K37" s="85" t="s">
         <v>295</v>
       </c>
@@ -26780,11 +26802,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="175">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="175"/>
       <c r="K38" s="85" t="s">
         <v>297</v>
       </c>
@@ -26801,11 +26823,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="175">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="175"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26823,11 +26845,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="177">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="177"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -26847,8 +26869,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="178"/>
+      <c r="J41" s="178"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -26863,10 +26885,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="182" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="182"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993AE84D-172A-41A2-9302-3A614262CF97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E8C968-8CE7-4332-BCAC-82D80401E873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1128,7 +1128,7 @@
     <t>37 days</t>
   </si>
   <si>
-    <t>3 tons so far</t>
+    <t>4.5 tons so far</t>
   </si>
 </sst>
 </file>
@@ -2190,6 +2190,144 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2213,144 +2351,6 @@
     </xf>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3169,7 +3169,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-649485</c:v>
+                  <c:v>-799485</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3701,7 +3701,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2941732</c:v>
+                  <c:v>2791732</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4116,7 +4116,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1119207.5</c:v>
+                  <c:v>-1269207.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7965,28 +7965,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="168">
+      <c r="H1" s="149">
         <v>45076</v>
       </c>
-      <c r="I1" s="169"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -7995,8 +7995,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8008,10 +8008,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="170" t="s">
+      <c r="H2" s="155" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="171"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8031,11 +8031,11 @@
       <c r="D3" s="159"/>
       <c r="E3" s="159"/>
       <c r="F3" s="160"/>
-      <c r="G3" s="172" t="s">
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
       <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
@@ -8064,10 +8064,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="152" t="s">
+      <c r="H4" s="173" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="153"/>
+      <c r="I4" s="174"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -8335,11 +8335,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="154" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="155"/>
-      <c r="I12" s="156"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8400,10 +8400,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="170" t="s">
+      <c r="H14" s="155" t="s">
         <v>328</v>
       </c>
-      <c r="I14" s="171"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8429,11 +8429,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="172" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="173"/>
-      <c r="I15" s="173"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -8460,10 +8460,10 @@
       <c r="G16" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="152" t="s">
+      <c r="H16" s="173" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="153"/>
+      <c r="I16" s="174"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -10762,34 +10762,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="168">
+      <c r="G1" s="149">
         <v>45918</v>
       </c>
-      <c r="H1" s="169"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10801,10 +10801,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="170" t="s">
+      <c r="G2" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="H2" s="171"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10824,11 +10824,11 @@
       <c r="C3" s="159"/>
       <c r="D3" s="159"/>
       <c r="E3" s="160"/>
-      <c r="F3" s="172" t="s">
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
       <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
@@ -11198,11 +11198,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="154" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="155"/>
-      <c r="H14" s="156"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11222,10 +11222,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="168">
+      <c r="G15" s="149">
         <v>45918</v>
       </c>
-      <c r="H15" s="169"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11245,10 +11245,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="170" t="s">
+      <c r="G16" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="H16" s="185"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11265,11 +11265,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="172" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="173"/>
-      <c r="H17" s="176"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11609,14 +11609,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="174" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="174"/>
-      <c r="K32" s="180" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="186"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11636,11 +11636,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="175">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="175"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>320</v>
       </c>
@@ -11666,11 +11666,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="175">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="175"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11697,11 +11697,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="175">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="175"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85" t="s">
         <v>330</v>
       </c>
@@ -11729,11 +11729,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="175">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="175"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="85" t="s">
         <v>331</v>
       </c>
@@ -11759,11 +11759,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="175">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="175"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85" t="s">
         <v>333</v>
       </c>
@@ -11789,11 +11789,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="175">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="175"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85" t="s">
         <v>320</v>
       </c>
@@ -11811,11 +11811,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="175">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="175"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11838,11 +11838,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="177">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="177"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -11863,8 +11863,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="178"/>
-      <c r="J41" s="178"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -11880,10 +11880,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="182" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="182"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11903,10 +11903,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="182" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="182"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -11944,15 +11944,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -11969,6 +11960,15 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
@@ -12018,34 +12018,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="168">
+      <c r="G1" s="149">
         <v>46016</v>
       </c>
-      <c r="H1" s="169"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12057,10 +12057,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="170" t="s">
+      <c r="G2" s="155" t="s">
         <v>350</v>
       </c>
-      <c r="H2" s="171"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12080,11 +12080,11 @@
       <c r="C3" s="159"/>
       <c r="D3" s="159"/>
       <c r="E3" s="160"/>
-      <c r="F3" s="172" t="s">
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
       <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
@@ -12385,11 +12385,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="154" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="155"/>
-      <c r="H14" s="156"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12409,10 +12409,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="168">
+      <c r="G15" s="149">
         <v>46016</v>
       </c>
-      <c r="H15" s="169"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12432,10 +12432,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="170" t="s">
+      <c r="G16" s="155" t="s">
         <v>351</v>
       </c>
-      <c r="H16" s="185"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12452,11 +12452,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="172" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="173"/>
-      <c r="H17" s="176"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12778,14 +12778,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="174" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="174"/>
-      <c r="K32" s="180" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="186"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12805,11 +12805,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="175">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="175"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12827,11 +12827,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="175">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="175"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12846,11 +12846,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="175">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="175"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -12866,11 +12866,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="175">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="175"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12884,11 +12884,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="175">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="175"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12902,11 +12902,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="175">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="175"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12920,11 +12920,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="175">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="175"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12943,11 +12943,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="177">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="177"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -12968,8 +12968,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="178"/>
-      <c r="J41" s="178"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -12985,10 +12985,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="182" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="182"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13008,10 +13008,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="182" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="182"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13049,15 +13049,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13069,11 +13065,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
@@ -13123,50 +13123,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="168">
+      <c r="G1" s="149">
         <v>46068</v>
       </c>
-      <c r="H1" s="169"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
-        <v>-649485</v>
-      </c>
-      <c r="K1" s="165"/>
+        <v>-799485</v>
+      </c>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>649485</v>
+        <v>799485</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="170" t="str">
+      <c r="G2" s="155" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>42 days</v>
-      </c>
-      <c r="H2" s="171"/>
+        <v>44 days</v>
+      </c>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13186,11 +13186,11 @@
       <c r="C3" s="159"/>
       <c r="D3" s="159"/>
       <c r="E3" s="160"/>
-      <c r="F3" s="172" t="s">
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
       <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
@@ -13384,12 +13384,14 @@
       <c r="A10" s="41">
         <v>6</v>
       </c>
-      <c r="B10" s="7"/>
+      <c r="B10" s="7">
+        <v>46111</v>
+      </c>
       <c r="C10" s="26" t="s">
         <v>143</v>
       </c>
       <c r="D10" s="9">
-        <v>300000</v>
+        <v>450000</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>355</v>
@@ -13482,11 +13484,11 @@
       <c r="C14" s="26"/>
       <c r="D14" s="9"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="154" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="155"/>
-      <c r="H14" s="156"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13506,10 +13508,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="168">
+      <c r="G15" s="149">
         <v>46068</v>
       </c>
-      <c r="H15" s="169"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13529,11 +13531,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="170" t="str">
+      <c r="G16" s="155" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>42 days</v>
-      </c>
-      <c r="H16" s="185"/>
+        <v>44 days</v>
+      </c>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13550,11 +13552,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="172" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="173"/>
-      <c r="H17" s="176"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13877,14 +13879,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="174" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="174"/>
-      <c r="K32" s="180" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="186"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -13896,11 +13898,11 @@
       <c r="F33" s="59"/>
       <c r="G33" s="67"/>
       <c r="H33" s="62"/>
-      <c r="I33" s="175">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="175"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85"/>
       <c r="L33" s="136"/>
       <c r="M33" s="15"/>
@@ -13914,11 +13916,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="175">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="175"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -13933,11 +13935,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="175">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="175"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -13953,11 +13955,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="175">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="175"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -13971,11 +13973,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="175">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="175"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -13989,11 +13991,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="175">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="175"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -14007,11 +14009,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="175">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="175"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14030,11 +14032,11 @@
         <v>0</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="177">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="177"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -14055,8 +14057,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="178"/>
-      <c r="J41" s="178"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -14072,10 +14074,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="182" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="182"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59">
         <v>800000</v>
       </c>
@@ -14101,10 +14103,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="182" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="182"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -14139,15 +14141,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14159,11 +14157,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
@@ -14237,21 +14239,21 @@
       <c r="H1" s="142" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="185" t="s">
         <v>206</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="147" t="str">
+      <c r="J1" s="185"/>
+      <c r="K1" s="185"/>
+      <c r="L1" s="185"/>
+      <c r="M1" s="186"/>
+      <c r="N1" s="182" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>2 year, 11 months, 27 days</v>
-      </c>
-      <c r="O1" s="148"/>
-      <c r="P1" s="148"/>
-      <c r="Q1" s="148"/>
-      <c r="R1" s="149"/>
+        <v>2 year, 11 months, 29 days</v>
+      </c>
+      <c r="O1" s="183"/>
+      <c r="P1" s="183"/>
+      <c r="Q1" s="183"/>
+      <c r="R1" s="184"/>
       <c r="S1" s="8" t="s">
         <v>205</v>
       </c>
@@ -14659,7 +14661,7 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>-649485</v>
+        <v>-799485</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
@@ -14667,7 +14669,7 @@
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
-        <v>649485</v>
+        <v>799485</v>
       </c>
       <c r="G13" s="143">
         <f>MIN('Term-12'!G6:G14)</f>
@@ -14814,14 +14816,14 @@
       <c r="H24" s="141"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="144" t="s">
+      <c r="A25" s="179" t="s">
         <v>189</v>
       </c>
-      <c r="B25" s="145"/>
-      <c r="C25" s="146"/>
+      <c r="B25" s="180"/>
+      <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>2941732</v>
+        <v>2791732</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
@@ -14829,7 +14831,7 @@
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
-        <v>14479062</v>
+        <v>14629062</v>
       </c>
       <c r="G25" s="143"/>
       <c r="H25" s="89"/>
@@ -14914,7 +14916,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>-1119207.5</v>
+        <v>-1269207.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -14945,7 +14947,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>2941732</v>
+        <v>2791732</v>
       </c>
     </row>
   </sheetData>
@@ -15194,28 +15196,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="168">
+      <c r="H1" s="149">
         <v>45163</v>
       </c>
-      <c r="I1" s="169"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -15224,8 +15226,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -15237,10 +15239,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="170" t="s">
+      <c r="H2" s="155" t="s">
         <v>353</v>
       </c>
-      <c r="I2" s="171"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15260,11 +15262,11 @@
       <c r="D3" s="159"/>
       <c r="E3" s="159"/>
       <c r="F3" s="160"/>
-      <c r="G3" s="172" t="s">
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
       <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
@@ -15293,10 +15295,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="152" t="s">
+      <c r="H4" s="173" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="153"/>
+      <c r="I4" s="174"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -15518,11 +15520,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="154" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="155"/>
-      <c r="I12" s="156"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15543,10 +15545,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="168">
+      <c r="H13" s="149">
         <v>45163</v>
       </c>
-      <c r="I13" s="169"/>
+      <c r="I13" s="150"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15567,10 +15569,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="170" t="s">
+      <c r="H14" s="155" t="s">
         <v>353</v>
       </c>
-      <c r="I14" s="171"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15588,11 +15590,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="172" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="173"/>
-      <c r="I15" s="173"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -15613,10 +15615,10 @@
       <c r="G16" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="152" t="s">
+      <c r="H16" s="173" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="153"/>
+      <c r="I16" s="174"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -17356,12 +17358,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17370,6 +17366,12 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
     <cfRule type="duplicateValues" dxfId="55" priority="6"/>
@@ -17426,28 +17428,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="168">
+      <c r="H1" s="149">
         <v>45163</v>
       </c>
-      <c r="I1" s="169"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17456,8 +17458,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17469,10 +17471,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="170" t="s">
+      <c r="H2" s="155" t="s">
         <v>354</v>
       </c>
-      <c r="I2" s="171"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17492,11 +17494,11 @@
       <c r="D3" s="159"/>
       <c r="E3" s="159"/>
       <c r="F3" s="160"/>
-      <c r="G3" s="172" t="s">
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
       <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
@@ -17525,10 +17527,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="152" t="s">
+      <c r="H4" s="173" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="153"/>
+      <c r="I4" s="174"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -17746,11 +17748,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="154" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="155"/>
-      <c r="I12" s="156"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17771,10 +17773,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="168">
+      <c r="H13" s="149">
         <v>45163</v>
       </c>
-      <c r="I13" s="169"/>
+      <c r="I13" s="150"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17795,10 +17797,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="170" t="s">
+      <c r="H14" s="155" t="s">
         <v>354</v>
       </c>
-      <c r="I14" s="171"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17816,11 +17818,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="172" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="173"/>
-      <c r="I15" s="173"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17841,10 +17843,10 @@
       <c r="G16" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="152" t="s">
+      <c r="H16" s="173" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="153"/>
+      <c r="I16" s="174"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -19654,28 +19656,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="168">
+      <c r="H1" s="149">
         <v>45345</v>
       </c>
-      <c r="I1" s="169"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -19684,8 +19686,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19697,10 +19699,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="170" t="s">
+      <c r="H2" s="155" t="s">
         <v>342</v>
       </c>
-      <c r="I2" s="171"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19720,11 +19722,11 @@
       <c r="D3" s="159"/>
       <c r="E3" s="159"/>
       <c r="F3" s="160"/>
-      <c r="G3" s="172" t="s">
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
       <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
@@ -19753,10 +19755,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="152" t="s">
+      <c r="H4" s="173" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="153"/>
+      <c r="I4" s="174"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -20073,11 +20075,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="154" t="s">
+      <c r="G14" s="164" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="155"/>
-      <c r="I14" s="156"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20098,10 +20100,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="168">
+      <c r="H15" s="149">
         <v>45345</v>
       </c>
-      <c r="I15" s="169"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20143,11 +20145,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="172" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="173"/>
-      <c r="I17" s="176"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20365,8 +20367,8 @@
       <c r="G27" s="61"/>
       <c r="H27" s="61"/>
       <c r="I27" s="61"/>
-      <c r="J27" s="179"/>
-      <c r="K27" s="179"/>
+      <c r="J27" s="175"/>
+      <c r="K27" s="175"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E28" s="61" t="s">
@@ -20384,10 +20386,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="174" t="s">
+      <c r="J28" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="174"/>
+      <c r="K28" s="169"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20406,11 +20408,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="175">
+      <c r="J29" s="163">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="175"/>
+      <c r="K29" s="163"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20435,11 +20437,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="175">
+      <c r="J30" s="163">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="175"/>
+      <c r="K30" s="163"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20464,11 +20466,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="175">
+      <c r="J31" s="163">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="175"/>
+      <c r="K31" s="163"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20493,11 +20495,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="175">
+      <c r="J32" s="163">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="175"/>
+      <c r="K32" s="163"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20522,11 +20524,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="175">
+      <c r="J33" s="163">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="175"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20550,11 +20552,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="175">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="175"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20578,11 +20580,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="175">
+      <c r="J35" s="163">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="175"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20604,11 +20606,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="177">
+      <c r="J36" s="170">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="177"/>
+      <c r="K36" s="170"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20627,8 +20629,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="178"/>
-      <c r="K37" s="178"/>
+      <c r="J37" s="171"/>
+      <c r="K37" s="171"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20677,6 +20679,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J27:K27"/>
@@ -20686,20 +20702,6 @@
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="J35:K35"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="41" priority="4" operator="greaterThan">
@@ -20747,35 +20749,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="168">
+      <c r="H1" s="149">
         <v>45477</v>
       </c>
-      <c r="I1" s="169"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20787,10 +20789,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="170" t="s">
+      <c r="H2" s="155" t="s">
         <v>343</v>
       </c>
-      <c r="I2" s="171"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20810,11 +20812,11 @@
       <c r="D3" s="159"/>
       <c r="E3" s="159"/>
       <c r="F3" s="160"/>
-      <c r="G3" s="172" t="s">
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
       <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
@@ -20843,10 +20845,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="152" t="s">
+      <c r="H4" s="173" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="153"/>
+      <c r="I4" s="174"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -21155,11 +21157,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="154" t="s">
+      <c r="G14" s="164" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="155"/>
-      <c r="I14" s="156"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21182,10 +21184,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="168">
+      <c r="H15" s="149">
         <v>45477</v>
       </c>
-      <c r="I15" s="169"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21231,11 +21233,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="172" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="173"/>
-      <c r="I17" s="176"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21576,8 +21578,8 @@
       <c r="G31" s="61"/>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
-      <c r="J31" s="179"/>
-      <c r="K31" s="179"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="175"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C32" s="6" t="s">
@@ -21601,14 +21603,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="174" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="174"/>
-      <c r="L32" s="180" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="180"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -21633,11 +21635,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="175">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="175"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>172</v>
       </c>
@@ -21665,11 +21667,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="175">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="175"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>173</v>
       </c>
@@ -21701,11 +21703,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="175">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="175"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>173</v>
       </c>
@@ -21726,11 +21728,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="177">
+      <c r="J36" s="170">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="177"/>
+      <c r="K36" s="170"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21747,11 +21749,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="175">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="175"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>179</v>
       </c>
@@ -21768,11 +21770,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="175">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="175"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21789,11 +21791,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="175">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="175"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21811,11 +21813,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="177">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="177"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -21830,8 +21832,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="178"/>
-      <c r="K41" s="178"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="52" t="s">
         <v>174</v>
       </c>
@@ -21861,16 +21863,16 @@
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="181" t="s">
+      <c r="A43" s="176" t="s">
         <v>163</v>
       </c>
-      <c r="B43" s="181"/>
-      <c r="C43" s="181"/>
-      <c r="F43" s="181" t="s">
+      <c r="B43" s="176"/>
+      <c r="C43" s="176"/>
+      <c r="F43" s="176" t="s">
         <v>164</v>
       </c>
-      <c r="G43" s="181"/>
-      <c r="H43" s="181"/>
+      <c r="G43" s="176"/>
+      <c r="H43" s="176"/>
       <c r="K43" s="14"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
@@ -21902,16 +21904,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -21928,6 +21920,16 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
@@ -21976,35 +21978,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="168">
+      <c r="H1" s="149">
         <v>45548</v>
       </c>
-      <c r="I1" s="169"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -22016,10 +22018,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="170" t="s">
+      <c r="H2" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="171"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22039,11 +22041,11 @@
       <c r="D3" s="159"/>
       <c r="E3" s="159"/>
       <c r="F3" s="160"/>
-      <c r="G3" s="172" t="s">
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
       <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
@@ -22424,11 +22426,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="154" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="155"/>
-      <c r="I14" s="156"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22455,10 +22457,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="168">
+      <c r="H15" s="149">
         <v>45561</v>
       </c>
-      <c r="I15" s="169"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22485,10 +22487,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="170" t="s">
+      <c r="H16" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="I16" s="185"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22512,11 +22514,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="172" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="173"/>
-      <c r="I17" s="176"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22860,8 +22862,8 @@
       <c r="G31" s="61"/>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
-      <c r="J31" s="179"/>
-      <c r="K31" s="179"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="175"/>
       <c r="L31" s="100"/>
       <c r="M31" s="100"/>
     </row>
@@ -22881,14 +22883,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="174" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="174"/>
-      <c r="L32" s="180" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="180"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -22907,11 +22909,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="175">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="175"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -22936,11 +22938,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="175">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="175"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -22965,11 +22967,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="175">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="175"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -22986,11 +22988,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="175">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="175"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>172</v>
       </c>
@@ -23007,11 +23009,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="175">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="175"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23028,11 +23030,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="175">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="175"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23052,11 +23054,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="175">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="175"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23070,8 +23072,8 @@
       <c r="G40" s="59"/>
       <c r="H40" s="67"/>
       <c r="I40" s="62"/>
-      <c r="J40" s="183"/>
-      <c r="K40" s="184"/>
+      <c r="J40" s="177"/>
+      <c r="K40" s="178"/>
       <c r="L40" s="85" t="s">
         <v>155</v>
       </c>
@@ -23085,8 +23087,8 @@
       <c r="G41" s="59"/>
       <c r="H41" s="67"/>
       <c r="I41" s="62"/>
-      <c r="J41" s="183"/>
-      <c r="K41" s="184"/>
+      <c r="J41" s="177"/>
+      <c r="K41" s="178"/>
       <c r="L41" s="85" t="s">
         <v>155</v>
       </c>
@@ -23108,11 +23110,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="177">
+      <c r="J42" s="170">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="177"/>
+      <c r="K42" s="170"/>
       <c r="L42" s="52" t="s">
         <v>174</v>
       </c>
@@ -23132,8 +23134,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="178"/>
-      <c r="K43" s="178"/>
+      <c r="J43" s="171"/>
+      <c r="K43" s="171"/>
       <c r="L43" s="83" t="s">
         <v>175</v>
       </c>
@@ -23148,11 +23150,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="182" t="s">
+      <c r="A45" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B45" s="182"/>
-      <c r="C45" s="182"/>
+      <c r="B45" s="172"/>
+      <c r="C45" s="172"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23269,19 +23271,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -23296,6 +23285,19 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="33" priority="1" operator="greaterThan">
@@ -23344,35 +23346,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="168">
+      <c r="H1" s="149">
         <v>45631</v>
       </c>
-      <c r="I1" s="169"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23384,10 +23386,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="170" t="s">
+      <c r="H2" s="155" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="171"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23407,11 +23409,11 @@
       <c r="D3" s="159"/>
       <c r="E3" s="159"/>
       <c r="F3" s="160"/>
-      <c r="G3" s="172" t="s">
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
       <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
@@ -23758,11 +23760,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="154" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="155"/>
-      <c r="I14" s="156"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23783,10 +23785,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="168">
+      <c r="H15" s="149">
         <v>45653</v>
       </c>
-      <c r="I15" s="169"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23807,10 +23809,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="170" t="s">
+      <c r="H16" s="155" t="s">
         <v>346</v>
       </c>
-      <c r="I16" s="185"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23828,11 +23830,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="172" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="173"/>
-      <c r="I17" s="176"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24157,8 +24159,8 @@
       <c r="G31" s="61"/>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
-      <c r="J31" s="179"/>
-      <c r="K31" s="179"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="175"/>
       <c r="L31" s="100"/>
       <c r="M31" s="100"/>
     </row>
@@ -24178,14 +24180,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="174" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="174"/>
-      <c r="L32" s="180" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="180"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24204,11 +24206,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="175">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="175"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -24233,11 +24235,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="175">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="175"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>215</v>
       </c>
@@ -24262,11 +24264,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="175">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="175"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>215</v>
       </c>
@@ -24283,11 +24285,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="175">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="175"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24304,11 +24306,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="175">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="175"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24325,11 +24327,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="175">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="175"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24346,11 +24348,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="175">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="175"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24368,11 +24370,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="177">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="177"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -24392,8 +24394,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="178"/>
-      <c r="K41" s="178"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -24408,11 +24410,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="182" t="s">
+      <c r="A43" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="182"/>
-      <c r="C43" s="182"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24560,6 +24562,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24568,23 +24587,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="29" priority="2" operator="greaterThan">
@@ -24636,35 +24638,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="168">
+      <c r="H1" s="149">
         <v>45714</v>
       </c>
-      <c r="I1" s="169"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24676,10 +24678,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="170" t="s">
+      <c r="H2" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="171"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24699,11 +24701,11 @@
       <c r="D3" s="159"/>
       <c r="E3" s="159"/>
       <c r="F3" s="160"/>
-      <c r="G3" s="172" t="s">
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
       <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
@@ -25052,11 +25054,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="154" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="155"/>
-      <c r="I14" s="156"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25079,10 +25081,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="168">
+      <c r="H15" s="149">
         <v>45743</v>
       </c>
-      <c r="I15" s="169"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25105,10 +25107,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="170" t="s">
+      <c r="H16" s="155" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="185"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25128,11 +25130,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="172" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="173"/>
-      <c r="I17" s="176"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25451,8 +25453,8 @@
       <c r="G31" s="61"/>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
-      <c r="J31" s="179"/>
-      <c r="K31" s="179"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="175"/>
       <c r="L31" s="100"/>
       <c r="M31" s="100"/>
     </row>
@@ -25472,14 +25474,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="174" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="174"/>
-      <c r="L32" s="180" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="180"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25498,11 +25500,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="175">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="175"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>257</v>
       </c>
@@ -25527,11 +25529,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="175">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="175"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>262</v>
       </c>
@@ -25557,11 +25559,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="175">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="175"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>263</v>
       </c>
@@ -25586,11 +25588,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="175">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="175"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>264</v>
       </c>
@@ -25606,11 +25608,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="175">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="175"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25623,11 +25625,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="175">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="175"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25640,11 +25642,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="175">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="175"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25662,11 +25664,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="177">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="177"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -25686,8 +25688,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="178"/>
-      <c r="K41" s="178"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -25702,11 +25704,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="182" t="s">
+      <c r="A43" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="182"/>
-      <c r="C43" s="182"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25738,23 +25740,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25763,6 +25748,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
@@ -25812,34 +25814,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="168">
+      <c r="G1" s="149">
         <v>45840</v>
       </c>
-      <c r="H1" s="169"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -25851,10 +25853,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="170" t="s">
+      <c r="G2" s="155" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="171"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25874,11 +25876,11 @@
       <c r="C3" s="159"/>
       <c r="D3" s="159"/>
       <c r="E3" s="160"/>
-      <c r="F3" s="172" t="s">
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
       <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
@@ -26203,11 +26205,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="154" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="155"/>
-      <c r="H14" s="156"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26227,10 +26229,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="168">
+      <c r="G15" s="149">
         <v>45840</v>
       </c>
-      <c r="H15" s="169"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26250,10 +26252,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="170" t="s">
+      <c r="G16" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="H16" s="185"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26270,11 +26272,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="172" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="173"/>
-      <c r="H17" s="176"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26607,10 +26609,10 @@
       <c r="H31" s="61" t="s">
         <v>275</v>
       </c>
-      <c r="I31" s="179">
+      <c r="I31" s="175">
         <v>150000</v>
       </c>
-      <c r="J31" s="179"/>
+      <c r="J31" s="175"/>
       <c r="K31" s="100"/>
       <c r="L31" s="100"/>
     </row>
@@ -26630,14 +26632,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="174" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="174"/>
-      <c r="K32" s="180" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="180"/>
+      <c r="L32" s="144"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -26656,11 +26658,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="175">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="175"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>287</v>
       </c>
@@ -26685,11 +26687,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="175">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="175"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>290</v>
       </c>
@@ -26715,11 +26717,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="175">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="175"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85" t="s">
         <v>294</v>
       </c>
@@ -26744,11 +26746,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="175">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="175"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26773,11 +26775,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="175">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="175"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85" t="s">
         <v>295</v>
       </c>
@@ -26802,11 +26804,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="175">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="175"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85" t="s">
         <v>297</v>
       </c>
@@ -26823,11 +26825,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="175">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="175"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26845,11 +26847,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="177">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="177"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -26869,8 +26871,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="178"/>
-      <c r="J41" s="178"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -26885,10 +26887,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="182" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="182"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -26928,23 +26930,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -26953,6 +26938,23 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E8C968-8CE7-4332-BCAC-82D80401E873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA6FA27-E0AB-444C-8947-7021CBDCC009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1128,7 +1128,7 @@
     <t>37 days</t>
   </si>
   <si>
-    <t>4.5 tons so far</t>
+    <t>5 tons so far</t>
   </si>
 </sst>
 </file>
@@ -2190,6 +2190,64 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2210,12 +2268,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -2229,10 +2281,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2253,54 +2301,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -3169,7 +3169,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-799485</c:v>
+                  <c:v>-849485</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3701,7 +3701,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2791732</c:v>
+                  <c:v>2741732</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4116,7 +4116,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1269207.5</c:v>
+                  <c:v>-1319207.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7965,28 +7965,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45076</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -7995,8 +7995,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8008,10 +8008,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8024,25 +8024,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8335,11 +8335,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8400,10 +8400,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>328</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8429,11 +8429,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -10762,34 +10762,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>45918</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10801,10 +10801,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10817,25 +10817,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11198,11 +11198,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11222,10 +11222,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>45918</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11245,10 +11245,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11265,11 +11265,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11609,14 +11609,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11636,11 +11636,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>320</v>
       </c>
@@ -11666,11 +11666,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11697,11 +11697,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
         <v>330</v>
       </c>
@@ -11729,11 +11729,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="85" t="s">
         <v>331</v>
       </c>
@@ -11759,11 +11759,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85" t="s">
         <v>333</v>
       </c>
@@ -11789,11 +11789,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85" t="s">
         <v>320</v>
       </c>
@@ -11811,11 +11811,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11838,11 +11838,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -11863,8 +11863,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -11880,10 +11880,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11903,10 +11903,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -11944,6 +11944,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -11960,15 +11969,6 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
@@ -12018,34 +12018,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>46016</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12057,10 +12057,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>350</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12073,25 +12073,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12385,11 +12385,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12409,10 +12409,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>46016</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12432,10 +12432,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>351</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12452,11 +12452,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12778,14 +12778,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12805,11 +12805,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12827,11 +12827,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12846,11 +12846,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -12866,11 +12866,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12884,11 +12884,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12902,11 +12902,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12920,11 +12920,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12943,11 +12943,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -12968,8 +12968,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -12985,10 +12985,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13008,10 +13008,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13049,11 +13049,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13065,15 +13069,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
@@ -13123,50 +13123,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>46068</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
-        <v>-799485</v>
-      </c>
-      <c r="K1" s="152"/>
+        <v>-849485</v>
+      </c>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>799485</v>
+        <v>849485</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="str">
+      <c r="G2" s="153" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>44 days</v>
-      </c>
-      <c r="H2" s="156"/>
+        <v>50 days</v>
+      </c>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13179,25 +13179,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13391,7 +13391,7 @@
         <v>143</v>
       </c>
       <c r="D10" s="9">
-        <v>450000</v>
+        <v>500000</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>355</v>
@@ -13484,11 +13484,11 @@
       <c r="C14" s="26"/>
       <c r="D14" s="9"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13508,10 +13508,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>46068</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13531,11 +13531,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="str">
+      <c r="G16" s="153" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>44 days</v>
-      </c>
-      <c r="H16" s="167"/>
+        <v>50 days</v>
+      </c>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13552,11 +13552,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13879,14 +13879,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -13898,11 +13898,11 @@
       <c r="F33" s="59"/>
       <c r="G33" s="67"/>
       <c r="H33" s="62"/>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85"/>
       <c r="L33" s="136"/>
       <c r="M33" s="15"/>
@@ -13916,11 +13916,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -13935,11 +13935,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -13955,11 +13955,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -13973,11 +13973,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -13991,11 +13991,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -14009,11 +14009,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14032,11 +14032,11 @@
         <v>0</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -14057,8 +14057,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -14074,26 +14074,26 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59">
-        <v>800000</v>
+        <v>700000</v>
       </c>
       <c r="D43" s="15">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E43" s="131">
         <f>C43/D43</f>
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="F43" s="62">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G43" s="101">
         <f>E43*F43</f>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="H43" s="15"/>
       <c r="I43" s="15"/>
@@ -14103,20 +14103,26 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
-      <c r="C44" s="59"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="131" t="e">
+      <c r="B44" s="147"/>
+      <c r="C44" s="59">
+        <v>100000</v>
+      </c>
+      <c r="D44" s="15">
+        <v>150</v>
+      </c>
+      <c r="E44" s="131">
         <f>C44/D44</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F44" s="62"/>
-      <c r="G44" s="101" t="e">
+        <v>666.66666666666663</v>
+      </c>
+      <c r="F44" s="62">
+        <v>0</v>
+      </c>
+      <c r="G44" s="101">
         <f>E44*F44</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="H44" s="15"/>
       <c r="I44" s="15"/>
@@ -14126,9 +14132,9 @@
       <c r="M44" s="15"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="G45" s="111" t="e">
+      <c r="G45" s="111">
         <f>G43+G44</f>
-        <v>#DIV/0!</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="54" spans="5:9" x14ac:dyDescent="0.3">
@@ -14141,11 +14147,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14157,15 +14167,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
@@ -14248,7 +14254,7 @@
       <c r="M1" s="186"/>
       <c r="N1" s="182" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>2 year, 11 months, 29 days</v>
+        <v>2 year, 11 months, 4 days</v>
       </c>
       <c r="O1" s="183"/>
       <c r="P1" s="183"/>
@@ -14661,7 +14667,7 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>-799485</v>
+        <v>-849485</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
@@ -14669,7 +14675,7 @@
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
-        <v>799485</v>
+        <v>849485</v>
       </c>
       <c r="G13" s="143">
         <f>MIN('Term-12'!G6:G14)</f>
@@ -14823,7 +14829,7 @@
       <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>2791732</v>
+        <v>2741732</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
@@ -14831,7 +14837,7 @@
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
-        <v>14629062</v>
+        <v>14679062</v>
       </c>
       <c r="G25" s="143"/>
       <c r="H25" s="89"/>
@@ -14916,7 +14922,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>-1269207.5</v>
+        <v>-1319207.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -14947,7 +14953,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>2791732</v>
+        <v>2741732</v>
       </c>
     </row>
   </sheetData>
@@ -15196,28 +15202,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45163</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -15226,8 +15232,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -15239,10 +15245,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>353</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15255,25 +15261,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -15520,11 +15526,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15545,10 +15551,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="149">
+      <c r="H13" s="151">
         <v>45163</v>
       </c>
-      <c r="I13" s="150"/>
+      <c r="I13" s="152"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15569,10 +15575,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>353</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15590,11 +15596,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17358,6 +17364,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17366,12 +17378,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
     <cfRule type="duplicateValues" dxfId="55" priority="6"/>
@@ -17428,28 +17434,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45163</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17458,8 +17464,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17471,10 +17477,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>354</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17487,25 +17493,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17748,11 +17754,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17773,10 +17779,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="149">
+      <c r="H13" s="151">
         <v>45163</v>
       </c>
-      <c r="I13" s="150"/>
+      <c r="I13" s="152"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17797,10 +17803,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>354</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17818,11 +17824,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -19656,28 +19662,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45345</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -19686,8 +19692,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19699,10 +19705,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>342</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19715,25 +19721,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -20075,11 +20081,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20100,10 +20106,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45345</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20145,11 +20151,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20386,10 +20392,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="169" t="s">
+      <c r="J28" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="169"/>
+      <c r="K28" s="158"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20408,11 +20414,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="163">
+      <c r="J29" s="144">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="163"/>
+      <c r="K29" s="144"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20437,11 +20443,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="163">
+      <c r="J30" s="144">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="163"/>
+      <c r="K30" s="144"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20466,11 +20472,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="163">
+      <c r="J31" s="144">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="163"/>
+      <c r="K31" s="144"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20495,11 +20501,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="163">
+      <c r="J32" s="144">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="163"/>
+      <c r="K32" s="144"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20524,11 +20530,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20552,11 +20558,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20580,11 +20586,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20606,11 +20612,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="170">
+      <c r="J36" s="145">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="170"/>
+      <c r="K36" s="145"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20629,8 +20635,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="171"/>
-      <c r="K37" s="171"/>
+      <c r="J37" s="146"/>
+      <c r="K37" s="146"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20679,6 +20685,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="J29:K29"/>
@@ -20688,20 +20708,6 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="G17:I17"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="41" priority="4" operator="greaterThan">
@@ -20749,35 +20755,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45477</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20789,10 +20795,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>343</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20805,25 +20811,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -21157,11 +21163,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21184,10 +21190,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45477</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21233,11 +21239,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21603,14 +21609,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -21635,11 +21641,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>172</v>
       </c>
@@ -21667,11 +21673,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>173</v>
       </c>
@@ -21703,11 +21709,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>173</v>
       </c>
@@ -21728,11 +21734,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="170">
+      <c r="J36" s="145">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="170"/>
+      <c r="K36" s="145"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21749,11 +21755,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>179</v>
       </c>
@@ -21770,11 +21776,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21791,11 +21797,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21813,11 +21819,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -21832,8 +21838,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="52" t="s">
         <v>174</v>
       </c>
@@ -21904,6 +21910,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -21920,16 +21936,6 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
@@ -21978,35 +21984,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45548</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -22018,10 +22024,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22034,25 +22040,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22426,11 +22432,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22457,10 +22463,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45561</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22487,10 +22493,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22514,11 +22520,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22883,14 +22889,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -22909,11 +22915,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -22938,11 +22944,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -22967,11 +22973,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -22988,11 +22994,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>172</v>
       </c>
@@ -23009,11 +23015,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23030,11 +23036,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23054,11 +23060,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23110,11 +23116,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="170">
+      <c r="J42" s="145">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="170"/>
+      <c r="K42" s="145"/>
       <c r="L42" s="52" t="s">
         <v>174</v>
       </c>
@@ -23134,8 +23140,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="171"/>
-      <c r="K43" s="171"/>
+      <c r="J43" s="146"/>
+      <c r="K43" s="146"/>
       <c r="L43" s="83" t="s">
         <v>175</v>
       </c>
@@ -23150,11 +23156,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="172" t="s">
+      <c r="A45" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B45" s="172"/>
-      <c r="C45" s="172"/>
+      <c r="B45" s="147"/>
+      <c r="C45" s="147"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23271,6 +23277,19 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -23285,19 +23304,6 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="33" priority="1" operator="greaterThan">
@@ -23346,35 +23352,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45631</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23386,10 +23392,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23402,25 +23408,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23760,11 +23766,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23785,10 +23791,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45653</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23809,10 +23815,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>346</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23830,11 +23836,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24180,14 +24186,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24206,11 +24212,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -24235,11 +24241,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>215</v>
       </c>
@@ -24264,11 +24270,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>215</v>
       </c>
@@ -24285,11 +24291,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24306,11 +24312,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24327,11 +24333,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24348,11 +24354,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24370,11 +24376,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -24394,8 +24400,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -24410,11 +24416,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="147"/>
+      <c r="C43" s="147"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24562,23 +24568,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24587,6 +24576,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="29" priority="2" operator="greaterThan">
@@ -24638,35 +24644,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45714</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24678,10 +24684,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24694,25 +24700,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -25054,11 +25060,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25081,10 +25087,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45743</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25107,10 +25113,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25130,11 +25136,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25474,14 +25480,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25500,11 +25506,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>257</v>
       </c>
@@ -25529,11 +25535,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>262</v>
       </c>
@@ -25559,11 +25565,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>263</v>
       </c>
@@ -25588,11 +25594,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>264</v>
       </c>
@@ -25608,11 +25614,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25625,11 +25631,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25642,11 +25648,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25664,11 +25670,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -25688,8 +25694,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -25704,11 +25710,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="147"/>
+      <c r="C43" s="147"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25740,6 +25746,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25748,23 +25771,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
@@ -25814,34 +25820,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>45840</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -25853,10 +25859,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25869,25 +25875,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -26205,11 +26211,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26229,10 +26235,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>45840</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26252,10 +26258,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26272,11 +26278,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26632,14 +26638,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="144"/>
+      <c r="L32" s="159"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -26658,11 +26664,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>287</v>
       </c>
@@ -26687,11 +26693,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>290</v>
       </c>
@@ -26717,11 +26723,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
         <v>294</v>
       </c>
@@ -26746,11 +26752,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26775,11 +26781,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85" t="s">
         <v>295</v>
       </c>
@@ -26804,11 +26810,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85" t="s">
         <v>297</v>
       </c>
@@ -26825,11 +26831,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26847,11 +26853,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -26871,8 +26877,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -26887,10 +26893,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -26930,6 +26936,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -26938,23 +26961,6 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA6FA27-E0AB-444C-8947-7021CBDCC009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0058005-5278-48DC-861E-C9B9E446EF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="356">
   <si>
     <t>#</t>
   </si>
@@ -2190,64 +2190,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2268,6 +2210,12 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -2281,6 +2229,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2301,6 +2253,54 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -3169,7 +3169,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-849485</c:v>
+                  <c:v>-879045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3701,7 +3701,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2741732</c:v>
+                  <c:v>2712172</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4116,7 +4116,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1319207.5</c:v>
+                  <c:v>-1348767.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7965,28 +7965,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45076</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -7995,8 +7995,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8008,10 +8008,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8024,25 +8024,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8335,11 +8335,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8400,10 +8400,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>328</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8429,11 +8429,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -10762,34 +10762,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>45918</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10801,10 +10801,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10817,25 +10817,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11198,11 +11198,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11222,10 +11222,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>45918</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11245,10 +11245,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11265,11 +11265,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11609,14 +11609,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11636,11 +11636,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>320</v>
       </c>
@@ -11666,11 +11666,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11697,11 +11697,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85" t="s">
         <v>330</v>
       </c>
@@ -11729,11 +11729,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="85" t="s">
         <v>331</v>
       </c>
@@ -11759,11 +11759,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85" t="s">
         <v>333</v>
       </c>
@@ -11789,11 +11789,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85" t="s">
         <v>320</v>
       </c>
@@ -11811,11 +11811,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11838,11 +11838,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -11863,8 +11863,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -11880,10 +11880,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11903,10 +11903,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -11944,15 +11944,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -11969,6 +11960,15 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
@@ -12018,34 +12018,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>46016</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12057,10 +12057,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>350</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12073,25 +12073,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12385,11 +12385,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12409,10 +12409,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>46016</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12432,10 +12432,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>351</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12452,11 +12452,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12778,14 +12778,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12805,11 +12805,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12827,11 +12827,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12846,11 +12846,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -12866,11 +12866,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12884,11 +12884,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12902,11 +12902,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12920,11 +12920,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12943,11 +12943,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -12968,8 +12968,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -12985,10 +12985,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13008,10 +13008,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13049,15 +13049,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13069,11 +13065,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
@@ -13123,50 +13123,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>46068</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
-        <v>-849485</v>
-      </c>
-      <c r="K1" s="165"/>
+        <v>-879045</v>
+      </c>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>849485</v>
+        <v>879045</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="str">
+      <c r="G2" s="155" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>50 days</v>
-      </c>
-      <c r="H2" s="168"/>
+        <v>55 days</v>
+      </c>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13179,25 +13179,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13414,9 +13414,15 @@
       <c r="A11" s="41">
         <v>7</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="5"/>
+      <c r="B11" s="7">
+        <v>46127</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="5">
+        <v>29560</v>
+      </c>
       <c r="E11" s="22"/>
       <c r="F11" s="48"/>
       <c r="G11" s="46"/>
@@ -13484,11 +13490,11 @@
       <c r="C14" s="26"/>
       <c r="D14" s="9"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13508,10 +13514,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>46068</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13531,11 +13537,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="str">
+      <c r="G16" s="155" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>50 days</v>
-      </c>
-      <c r="H16" s="154"/>
+        <v>55 days</v>
+      </c>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13552,11 +13558,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13879,14 +13885,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -13898,11 +13904,11 @@
       <c r="F33" s="59"/>
       <c r="G33" s="67"/>
       <c r="H33" s="62"/>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85"/>
       <c r="L33" s="136"/>
       <c r="M33" s="15"/>
@@ -13916,11 +13922,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -13935,11 +13941,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -13955,11 +13961,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -13973,11 +13979,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -13991,11 +13997,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -14009,11 +14015,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14032,11 +14038,11 @@
         <v>0</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -14057,8 +14063,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -14074,10 +14080,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59">
         <v>700000</v>
       </c>
@@ -14089,11 +14095,11 @@
         <v>5000</v>
       </c>
       <c r="F43" s="62">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="G43" s="101">
         <f>E43*F43</f>
-        <v>800000</v>
+        <v>1000000</v>
       </c>
       <c r="H43" s="15"/>
       <c r="I43" s="15"/>
@@ -14103,19 +14109,19 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59">
         <v>100000</v>
       </c>
       <c r="D44" s="15">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E44" s="131">
         <f>C44/D44</f>
-        <v>666.66666666666663</v>
+        <v>714.28571428571433</v>
       </c>
       <c r="F44" s="62">
         <v>0</v>
@@ -14134,7 +14140,7 @@
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="G45" s="111">
         <f>G43+G44</f>
-        <v>800000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="54" spans="5:9" x14ac:dyDescent="0.3">
@@ -14147,15 +14153,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14167,11 +14169,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
@@ -14254,7 +14260,7 @@
       <c r="M1" s="186"/>
       <c r="N1" s="182" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>2 year, 11 months, 4 days</v>
+        <v>3 year, 0 months, 9 days</v>
       </c>
       <c r="O1" s="183"/>
       <c r="P1" s="183"/>
@@ -14667,7 +14673,7 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>-849485</v>
+        <v>-879045</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
@@ -14675,7 +14681,7 @@
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
-        <v>849485</v>
+        <v>879045</v>
       </c>
       <c r="G13" s="143">
         <f>MIN('Term-12'!G6:G14)</f>
@@ -14829,7 +14835,7 @@
       <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>2741732</v>
+        <v>2712172</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
@@ -14837,7 +14843,7 @@
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
-        <v>14679062</v>
+        <v>14708622</v>
       </c>
       <c r="G25" s="143"/>
       <c r="H25" s="89"/>
@@ -14922,7 +14928,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>-1319207.5</v>
+        <v>-1348767.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -14953,7 +14959,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>2741732</v>
+        <v>2712172</v>
       </c>
     </row>
   </sheetData>
@@ -15202,28 +15208,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45163</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -15232,8 +15238,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -15245,10 +15251,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>353</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15261,25 +15267,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -15526,11 +15532,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15551,10 +15557,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="149">
         <v>45163</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="150"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15575,10 +15581,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>353</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15596,11 +15602,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17364,12 +17370,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17378,6 +17378,12 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
     <cfRule type="duplicateValues" dxfId="55" priority="6"/>
@@ -17434,28 +17440,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45163</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17464,8 +17470,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17477,10 +17483,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>354</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17493,25 +17499,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17754,11 +17760,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17779,10 +17785,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="149">
         <v>45163</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="150"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17803,10 +17809,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>354</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17824,11 +17830,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -19662,28 +19668,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45345</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -19692,8 +19698,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19705,10 +19711,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>342</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19721,25 +19727,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -20081,11 +20087,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20106,10 +20112,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45345</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20151,11 +20157,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20392,10 +20398,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="158" t="s">
+      <c r="J28" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="158"/>
+      <c r="K28" s="169"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20414,11 +20420,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="144">
+      <c r="J29" s="163">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="144"/>
+      <c r="K29" s="163"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20443,11 +20449,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="144">
+      <c r="J30" s="163">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="144"/>
+      <c r="K30" s="163"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20472,11 +20478,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="144">
+      <c r="J31" s="163">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="144"/>
+      <c r="K31" s="163"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20501,11 +20507,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="144">
+      <c r="J32" s="163">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="144"/>
+      <c r="K32" s="163"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20530,11 +20536,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20558,11 +20564,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20586,11 +20592,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20612,11 +20618,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="145">
+      <c r="J36" s="170">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="145"/>
+      <c r="K36" s="170"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20635,8 +20641,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="146"/>
-      <c r="K37" s="146"/>
+      <c r="J37" s="171"/>
+      <c r="K37" s="171"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20685,6 +20691,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J27:K27"/>
@@ -20694,20 +20714,6 @@
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="J35:K35"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="41" priority="4" operator="greaterThan">
@@ -20755,35 +20761,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45477</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20795,10 +20801,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>343</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20811,25 +20817,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -21163,11 +21169,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21190,10 +21196,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45477</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21239,11 +21245,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21609,14 +21615,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -21641,11 +21647,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>172</v>
       </c>
@@ -21673,11 +21679,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>173</v>
       </c>
@@ -21709,11 +21715,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>173</v>
       </c>
@@ -21734,11 +21740,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="145">
+      <c r="J36" s="170">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="145"/>
+      <c r="K36" s="170"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21755,11 +21761,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>179</v>
       </c>
@@ -21776,11 +21782,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21797,11 +21803,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21819,11 +21825,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -21838,8 +21844,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="52" t="s">
         <v>174</v>
       </c>
@@ -21910,16 +21916,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -21936,6 +21932,16 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
@@ -21984,35 +21990,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45548</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -22024,10 +22030,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22040,25 +22046,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22432,11 +22438,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22463,10 +22469,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45561</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22493,10 +22499,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22520,11 +22526,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22889,14 +22895,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -22915,11 +22921,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -22944,11 +22950,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -22973,11 +22979,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -22994,11 +23000,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>172</v>
       </c>
@@ -23015,11 +23021,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23036,11 +23042,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23060,11 +23066,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23116,11 +23122,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="145">
+      <c r="J42" s="170">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="145"/>
+      <c r="K42" s="170"/>
       <c r="L42" s="52" t="s">
         <v>174</v>
       </c>
@@ -23140,8 +23146,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="146"/>
-      <c r="K43" s="146"/>
+      <c r="J43" s="171"/>
+      <c r="K43" s="171"/>
       <c r="L43" s="83" t="s">
         <v>175</v>
       </c>
@@ -23156,11 +23162,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="147" t="s">
+      <c r="A45" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B45" s="147"/>
-      <c r="C45" s="147"/>
+      <c r="B45" s="172"/>
+      <c r="C45" s="172"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23277,19 +23283,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -23304,6 +23297,19 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="33" priority="1" operator="greaterThan">
@@ -23352,35 +23358,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45631</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23392,10 +23398,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23408,25 +23414,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23766,11 +23772,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23791,10 +23797,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45653</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23815,10 +23821,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>346</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23836,11 +23842,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24186,14 +24192,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24212,11 +24218,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -24241,11 +24247,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>215</v>
       </c>
@@ -24270,11 +24276,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>215</v>
       </c>
@@ -24291,11 +24297,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24312,11 +24318,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24333,11 +24339,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24354,11 +24360,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24376,11 +24382,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -24400,8 +24406,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -24416,11 +24422,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="147"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24568,6 +24574,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24576,23 +24599,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="29" priority="2" operator="greaterThan">
@@ -24644,35 +24650,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45714</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24684,10 +24690,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24700,25 +24706,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -25060,11 +25066,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25087,10 +25093,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45743</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25113,10 +25119,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25136,11 +25142,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25480,14 +25486,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25506,11 +25512,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>257</v>
       </c>
@@ -25535,11 +25541,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>262</v>
       </c>
@@ -25565,11 +25571,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>263</v>
       </c>
@@ -25594,11 +25600,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>264</v>
       </c>
@@ -25614,11 +25620,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25631,11 +25637,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25648,11 +25654,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25670,11 +25676,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -25694,8 +25700,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -25710,11 +25716,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="147"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25746,23 +25752,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25771,6 +25760,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
@@ -25820,34 +25826,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>45840</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -25859,10 +25865,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25875,25 +25881,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -26211,11 +26217,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26235,10 +26241,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>45840</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26258,10 +26264,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26278,11 +26284,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26638,14 +26644,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="159"/>
+      <c r="L32" s="144"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -26664,11 +26670,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>287</v>
       </c>
@@ -26693,11 +26699,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>290</v>
       </c>
@@ -26723,11 +26729,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85" t="s">
         <v>294</v>
       </c>
@@ -26752,11 +26758,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26781,11 +26787,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85" t="s">
         <v>295</v>
       </c>
@@ -26810,11 +26816,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85" t="s">
         <v>297</v>
       </c>
@@ -26831,11 +26837,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26853,11 +26859,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -26877,8 +26883,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -26893,10 +26899,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -26936,23 +26942,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -26961,6 +26950,23 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0058005-5278-48DC-861E-C9B9E446EF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5734D9C-73E7-4C36-BE99-453A467D41B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1128,7 +1128,7 @@
     <t>37 days</t>
   </si>
   <si>
-    <t>5 tons so far</t>
+    <t>8.5 tons so far</t>
   </si>
 </sst>
 </file>
@@ -2190,6 +2190,64 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2210,12 +2268,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -2229,10 +2281,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2253,54 +2301,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -3169,7 +3169,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-879045</c:v>
+                  <c:v>-1179045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3701,7 +3701,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2712172</c:v>
+                  <c:v>2412172</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4116,7 +4116,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1348767.5</c:v>
+                  <c:v>-1648767.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7965,28 +7965,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45076</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -7995,8 +7995,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8008,10 +8008,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8024,25 +8024,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8335,11 +8335,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8400,10 +8400,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>328</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8429,11 +8429,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -10762,34 +10762,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>45918</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10801,10 +10801,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10817,25 +10817,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11198,11 +11198,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11222,10 +11222,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>45918</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11245,10 +11245,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11265,11 +11265,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11609,14 +11609,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11636,11 +11636,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>320</v>
       </c>
@@ -11666,11 +11666,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11697,11 +11697,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
         <v>330</v>
       </c>
@@ -11729,11 +11729,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="85" t="s">
         <v>331</v>
       </c>
@@ -11759,11 +11759,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85" t="s">
         <v>333</v>
       </c>
@@ -11789,11 +11789,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85" t="s">
         <v>320</v>
       </c>
@@ -11811,11 +11811,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11838,11 +11838,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -11863,8 +11863,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -11880,10 +11880,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11903,10 +11903,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -11944,6 +11944,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -11960,15 +11969,6 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
@@ -12018,34 +12018,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>46016</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12057,10 +12057,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>350</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12073,25 +12073,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12385,11 +12385,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12409,10 +12409,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>46016</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12432,10 +12432,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>351</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12452,11 +12452,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12778,14 +12778,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12805,11 +12805,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12827,11 +12827,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12846,11 +12846,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -12866,11 +12866,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12884,11 +12884,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12902,11 +12902,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12920,11 +12920,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12943,11 +12943,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -12968,8 +12968,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -12985,10 +12985,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13008,10 +13008,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13049,11 +13049,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13065,15 +13069,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
@@ -13123,50 +13123,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>46068</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
-        <v>-879045</v>
-      </c>
-      <c r="K1" s="152"/>
+        <v>-1179045</v>
+      </c>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>879045</v>
+        <v>1179045</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="str">
+      <c r="G2" s="153" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>55 days</v>
-      </c>
-      <c r="H2" s="156"/>
+        <v>58 days</v>
+      </c>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13179,25 +13179,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13254,11 +13254,15 @@
         <v>256000</v>
       </c>
       <c r="E5" s="23"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="46"/>
+      <c r="F5" s="45">
+        <v>46124</v>
+      </c>
+      <c r="G5" s="46">
+        <v>160</v>
+      </c>
       <c r="H5" s="49" t="str">
         <f>IF(ISBLANK(F5),"",CONCATENATE(F5-$G$1+1," days"))</f>
-        <v/>
+        <v>57 days</v>
       </c>
       <c r="I5" s="21">
         <v>1</v>
@@ -13391,7 +13395,7 @@
         <v>143</v>
       </c>
       <c r="D10" s="9">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>355</v>
@@ -13490,11 +13494,11 @@
       <c r="C14" s="26"/>
       <c r="D14" s="9"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13514,10 +13518,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>46068</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13537,11 +13541,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="str">
+      <c r="G16" s="153" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>55 days</v>
-      </c>
-      <c r="H16" s="167"/>
+        <v>58 days</v>
+      </c>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13558,11 +13562,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13604,11 +13608,15 @@
       <c r="C19" s="3"/>
       <c r="D19" s="5"/>
       <c r="E19" s="22"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="46"/>
+      <c r="F19" s="45">
+        <v>46124</v>
+      </c>
+      <c r="G19" s="46">
+        <v>130</v>
+      </c>
       <c r="H19" s="49" t="str">
         <f>IF(ISBLANK(F19),"",CONCATENATE(F19-$G$15+1," days"))</f>
-        <v/>
+        <v>57 days</v>
       </c>
       <c r="I19" s="21">
         <v>15</v>
@@ -13885,14 +13893,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -13904,11 +13912,11 @@
       <c r="F33" s="59"/>
       <c r="G33" s="67"/>
       <c r="H33" s="62"/>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85"/>
       <c r="L33" s="136"/>
       <c r="M33" s="15"/>
@@ -13922,11 +13930,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -13941,11 +13949,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -13961,11 +13969,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -13979,11 +13987,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -13997,11 +14005,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -14015,11 +14023,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14038,11 +14046,11 @@
         <v>0</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -14063,8 +14071,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -14080,26 +14088,26 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59">
         <v>700000</v>
       </c>
       <c r="D43" s="15">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E43" s="131">
         <f>C43/D43</f>
-        <v>5000</v>
+        <v>4375</v>
       </c>
       <c r="F43" s="62">
         <v>200</v>
       </c>
       <c r="G43" s="101">
         <f>E43*F43</f>
-        <v>1000000</v>
+        <v>875000</v>
       </c>
       <c r="H43" s="15"/>
       <c r="I43" s="15"/>
@@ -14109,26 +14117,26 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59">
         <v>100000</v>
       </c>
       <c r="D44" s="15">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E44" s="131">
         <f>C44/D44</f>
-        <v>714.28571428571433</v>
+        <v>769.23076923076928</v>
       </c>
       <c r="F44" s="62">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G44" s="101">
         <f>E44*F44</f>
-        <v>0</v>
+        <v>153846.15384615384</v>
       </c>
       <c r="H44" s="15"/>
       <c r="I44" s="15"/>
@@ -14140,7 +14148,7 @@
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="G45" s="111">
         <f>G43+G44</f>
-        <v>1000000</v>
+        <v>1028846.1538461539</v>
       </c>
     </row>
     <row r="54" spans="5:9" x14ac:dyDescent="0.3">
@@ -14153,11 +14161,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14169,15 +14181,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
@@ -14260,7 +14268,7 @@
       <c r="M1" s="186"/>
       <c r="N1" s="182" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>3 year, 0 months, 9 days</v>
+        <v>3 year, 0 months, 12 days</v>
       </c>
       <c r="O1" s="183"/>
       <c r="P1" s="183"/>
@@ -14673,7 +14681,7 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>-879045</v>
+        <v>-1179045</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
@@ -14681,7 +14689,7 @@
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
-        <v>879045</v>
+        <v>1179045</v>
       </c>
       <c r="G13" s="143">
         <f>MIN('Term-12'!G6:G14)</f>
@@ -14835,7 +14843,7 @@
       <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>2712172</v>
+        <v>2412172</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
@@ -14843,7 +14851,7 @@
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
-        <v>14708622</v>
+        <v>15008622</v>
       </c>
       <c r="G25" s="143"/>
       <c r="H25" s="89"/>
@@ -14928,7 +14936,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>-1348767.5</v>
+        <v>-1648767.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -14959,7 +14967,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>2712172</v>
+        <v>2412172</v>
       </c>
     </row>
   </sheetData>
@@ -15208,28 +15216,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45163</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -15238,8 +15246,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -15251,10 +15259,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>353</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15267,25 +15275,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -15532,11 +15540,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15557,10 +15565,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="149">
+      <c r="H13" s="151">
         <v>45163</v>
       </c>
-      <c r="I13" s="150"/>
+      <c r="I13" s="152"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15581,10 +15589,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>353</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15602,11 +15610,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17370,6 +17378,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17378,12 +17392,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
     <cfRule type="duplicateValues" dxfId="55" priority="6"/>
@@ -17440,28 +17448,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45163</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17470,8 +17478,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17483,10 +17491,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>354</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17499,25 +17507,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17760,11 +17768,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17785,10 +17793,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="149">
+      <c r="H13" s="151">
         <v>45163</v>
       </c>
-      <c r="I13" s="150"/>
+      <c r="I13" s="152"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17809,10 +17817,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>354</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17830,11 +17838,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -19668,28 +19676,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45345</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -19698,8 +19706,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19711,10 +19719,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>342</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19727,25 +19735,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -20087,11 +20095,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20112,10 +20120,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45345</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20157,11 +20165,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20398,10 +20406,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="169" t="s">
+      <c r="J28" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="169"/>
+      <c r="K28" s="158"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20420,11 +20428,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="163">
+      <c r="J29" s="144">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="163"/>
+      <c r="K29" s="144"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20449,11 +20457,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="163">
+      <c r="J30" s="144">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="163"/>
+      <c r="K30" s="144"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20478,11 +20486,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="163">
+      <c r="J31" s="144">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="163"/>
+      <c r="K31" s="144"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20507,11 +20515,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="163">
+      <c r="J32" s="144">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="163"/>
+      <c r="K32" s="144"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20536,11 +20544,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20564,11 +20572,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20592,11 +20600,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20618,11 +20626,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="170">
+      <c r="J36" s="145">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="170"/>
+      <c r="K36" s="145"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20641,8 +20649,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="171"/>
-      <c r="K37" s="171"/>
+      <c r="J37" s="146"/>
+      <c r="K37" s="146"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20691,6 +20699,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="J29:K29"/>
@@ -20700,20 +20722,6 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="G17:I17"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="41" priority="4" operator="greaterThan">
@@ -20761,35 +20769,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45477</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20801,10 +20809,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>343</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20817,25 +20825,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -21169,11 +21177,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21196,10 +21204,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45477</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21245,11 +21253,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21615,14 +21623,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -21647,11 +21655,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>172</v>
       </c>
@@ -21679,11 +21687,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>173</v>
       </c>
@@ -21715,11 +21723,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>173</v>
       </c>
@@ -21740,11 +21748,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="170">
+      <c r="J36" s="145">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="170"/>
+      <c r="K36" s="145"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21761,11 +21769,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>179</v>
       </c>
@@ -21782,11 +21790,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21803,11 +21811,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21825,11 +21833,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -21844,8 +21852,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="52" t="s">
         <v>174</v>
       </c>
@@ -21916,6 +21924,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -21932,16 +21950,6 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
@@ -21990,35 +21998,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45548</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -22030,10 +22038,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22046,25 +22054,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22438,11 +22446,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22469,10 +22477,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45561</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22499,10 +22507,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22526,11 +22534,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22895,14 +22903,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -22921,11 +22929,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -22950,11 +22958,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -22979,11 +22987,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -23000,11 +23008,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>172</v>
       </c>
@@ -23021,11 +23029,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23042,11 +23050,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23066,11 +23074,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23122,11 +23130,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="170">
+      <c r="J42" s="145">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="170"/>
+      <c r="K42" s="145"/>
       <c r="L42" s="52" t="s">
         <v>174</v>
       </c>
@@ -23146,8 +23154,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="171"/>
-      <c r="K43" s="171"/>
+      <c r="J43" s="146"/>
+      <c r="K43" s="146"/>
       <c r="L43" s="83" t="s">
         <v>175</v>
       </c>
@@ -23162,11 +23170,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="172" t="s">
+      <c r="A45" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B45" s="172"/>
-      <c r="C45" s="172"/>
+      <c r="B45" s="147"/>
+      <c r="C45" s="147"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23283,6 +23291,19 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -23297,19 +23318,6 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="33" priority="1" operator="greaterThan">
@@ -23358,35 +23366,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45631</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23398,10 +23406,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23414,25 +23422,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23772,11 +23780,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23797,10 +23805,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45653</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23821,10 +23829,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>346</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23842,11 +23850,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24192,14 +24200,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24218,11 +24226,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -24247,11 +24255,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>215</v>
       </c>
@@ -24276,11 +24284,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>215</v>
       </c>
@@ -24297,11 +24305,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24318,11 +24326,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24339,11 +24347,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24360,11 +24368,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24382,11 +24390,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -24406,8 +24414,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -24422,11 +24430,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="147"/>
+      <c r="C43" s="147"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24574,23 +24582,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24599,6 +24590,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="29" priority="2" operator="greaterThan">
@@ -24650,35 +24658,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45714</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24690,10 +24698,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24706,25 +24714,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -25066,11 +25074,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25093,10 +25101,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45743</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25119,10 +25127,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25142,11 +25150,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25486,14 +25494,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25512,11 +25520,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>257</v>
       </c>
@@ -25541,11 +25549,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>262</v>
       </c>
@@ -25571,11 +25579,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>263</v>
       </c>
@@ -25600,11 +25608,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>264</v>
       </c>
@@ -25620,11 +25628,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25637,11 +25645,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25654,11 +25662,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25676,11 +25684,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -25700,8 +25708,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -25716,11 +25724,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="147"/>
+      <c r="C43" s="147"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25752,6 +25760,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25760,23 +25785,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
@@ -25826,34 +25834,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>45840</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -25865,10 +25873,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25881,25 +25889,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -26217,11 +26225,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26241,10 +26249,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>45840</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26264,10 +26272,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26284,11 +26292,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26644,14 +26652,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="144"/>
+      <c r="L32" s="159"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -26670,11 +26678,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>287</v>
       </c>
@@ -26699,11 +26707,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>290</v>
       </c>
@@ -26729,11 +26737,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
         <v>294</v>
       </c>
@@ -26758,11 +26766,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26787,11 +26795,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85" t="s">
         <v>295</v>
       </c>
@@ -26816,11 +26824,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85" t="s">
         <v>297</v>
       </c>
@@ -26837,11 +26845,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26859,11 +26867,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -26883,8 +26891,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -26899,10 +26907,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -26942,6 +26950,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -26950,23 +26975,6 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5734D9C-73E7-4C36-BE99-453A467D41B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23594A22-61C1-4EF8-BB3E-FAB7DF2B3D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2190,64 +2190,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2268,6 +2210,12 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -2281,6 +2229,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2301,6 +2253,54 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -7965,28 +7965,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45076</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -7995,8 +7995,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8008,10 +8008,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8024,25 +8024,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8335,11 +8335,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8400,10 +8400,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>328</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8429,11 +8429,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -10762,34 +10762,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>45918</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10801,10 +10801,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10817,25 +10817,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11198,11 +11198,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11222,10 +11222,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>45918</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11245,10 +11245,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11265,11 +11265,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11609,14 +11609,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11636,11 +11636,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>320</v>
       </c>
@@ -11666,11 +11666,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11697,11 +11697,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85" t="s">
         <v>330</v>
       </c>
@@ -11729,11 +11729,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="85" t="s">
         <v>331</v>
       </c>
@@ -11759,11 +11759,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85" t="s">
         <v>333</v>
       </c>
@@ -11789,11 +11789,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85" t="s">
         <v>320</v>
       </c>
@@ -11811,11 +11811,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11838,11 +11838,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -11863,8 +11863,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -11880,10 +11880,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11903,10 +11903,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -11944,15 +11944,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -11969,6 +11960,15 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
@@ -12018,34 +12018,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>46016</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12057,10 +12057,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>350</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12073,25 +12073,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12385,11 +12385,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12409,10 +12409,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>46016</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12432,10 +12432,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>351</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12452,11 +12452,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12778,14 +12778,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12805,11 +12805,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12827,11 +12827,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12846,11 +12846,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -12866,11 +12866,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12884,11 +12884,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12902,11 +12902,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12920,11 +12920,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12943,11 +12943,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -12968,8 +12968,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -12985,10 +12985,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13008,10 +13008,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13049,15 +13049,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13069,11 +13065,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
@@ -13123,34 +13123,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>46068</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>-1179045</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -13162,11 +13162,11 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="str">
+      <c r="G2" s="155" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
         <v>58 days</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13179,25 +13179,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13258,7 +13258,7 @@
         <v>46124</v>
       </c>
       <c r="G5" s="46">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="H5" s="49" t="str">
         <f>IF(ISBLANK(F5),"",CONCATENATE(F5-$G$1+1," days"))</f>
@@ -13491,14 +13491,14 @@
         <v>10</v>
       </c>
       <c r="B14" s="132"/>
-      <c r="C14" s="26"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="9"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13518,10 +13518,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>46068</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13541,11 +13541,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="str">
+      <c r="G16" s="155" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
         <v>58 days</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13562,11 +13562,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13612,7 +13612,7 @@
         <v>46124</v>
       </c>
       <c r="G19" s="46">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H19" s="49" t="str">
         <f>IF(ISBLANK(F19),"",CONCATENATE(F19-$G$15+1," days"))</f>
@@ -13893,14 +13893,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -13912,11 +13912,11 @@
       <c r="F33" s="59"/>
       <c r="G33" s="67"/>
       <c r="H33" s="62"/>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85"/>
       <c r="L33" s="136"/>
       <c r="M33" s="15"/>
@@ -13930,11 +13930,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -13949,11 +13949,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -13969,11 +13969,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -13987,11 +13987,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -14005,11 +14005,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -14023,11 +14023,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14046,11 +14046,11 @@
         <v>0</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -14071,8 +14071,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -14088,10 +14088,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59">
         <v>700000</v>
       </c>
@@ -14117,10 +14117,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59">
         <v>100000</v>
       </c>
@@ -14161,15 +14161,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14181,11 +14177,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
@@ -15216,28 +15216,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45163</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -15246,8 +15246,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -15259,10 +15259,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>353</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15275,25 +15275,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -15540,11 +15540,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15565,10 +15565,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="149">
         <v>45163</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="150"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15589,10 +15589,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>353</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15610,11 +15610,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17378,12 +17378,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17392,6 +17386,12 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
     <cfRule type="duplicateValues" dxfId="55" priority="6"/>
@@ -17448,28 +17448,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45163</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17478,8 +17478,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17491,10 +17491,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>354</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17507,25 +17507,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17768,11 +17768,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17793,10 +17793,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="149">
         <v>45163</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="150"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17817,10 +17817,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>354</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17838,11 +17838,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -19676,28 +19676,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45345</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -19706,8 +19706,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19719,10 +19719,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>342</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19735,25 +19735,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -20095,11 +20095,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20120,10 +20120,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45345</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20165,11 +20165,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20406,10 +20406,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="158" t="s">
+      <c r="J28" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="158"/>
+      <c r="K28" s="169"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20428,11 +20428,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="144">
+      <c r="J29" s="163">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="144"/>
+      <c r="K29" s="163"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20457,11 +20457,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="144">
+      <c r="J30" s="163">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="144"/>
+      <c r="K30" s="163"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20486,11 +20486,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="144">
+      <c r="J31" s="163">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="144"/>
+      <c r="K31" s="163"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20515,11 +20515,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="144">
+      <c r="J32" s="163">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="144"/>
+      <c r="K32" s="163"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20544,11 +20544,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20572,11 +20572,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20600,11 +20600,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20626,11 +20626,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="145">
+      <c r="J36" s="170">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="145"/>
+      <c r="K36" s="170"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20649,8 +20649,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="146"/>
-      <c r="K37" s="146"/>
+      <c r="J37" s="171"/>
+      <c r="K37" s="171"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20699,6 +20699,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J27:K27"/>
@@ -20708,20 +20722,6 @@
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="J35:K35"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="41" priority="4" operator="greaterThan">
@@ -20769,35 +20769,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45477</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20809,10 +20809,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>343</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20825,25 +20825,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -21177,11 +21177,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21204,10 +21204,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45477</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21253,11 +21253,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21623,14 +21623,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -21655,11 +21655,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>172</v>
       </c>
@@ -21687,11 +21687,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>173</v>
       </c>
@@ -21723,11 +21723,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>173</v>
       </c>
@@ -21748,11 +21748,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="145">
+      <c r="J36" s="170">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="145"/>
+      <c r="K36" s="170"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21769,11 +21769,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>179</v>
       </c>
@@ -21790,11 +21790,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21811,11 +21811,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21833,11 +21833,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -21852,8 +21852,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="52" t="s">
         <v>174</v>
       </c>
@@ -21924,16 +21924,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -21950,6 +21940,16 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
@@ -21998,35 +21998,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45548</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -22038,10 +22038,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22054,25 +22054,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22446,11 +22446,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22477,10 +22477,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45561</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22507,10 +22507,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22534,11 +22534,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22903,14 +22903,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -22929,11 +22929,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -22958,11 +22958,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -22987,11 +22987,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -23008,11 +23008,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>172</v>
       </c>
@@ -23029,11 +23029,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23050,11 +23050,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23074,11 +23074,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23130,11 +23130,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="145">
+      <c r="J42" s="170">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="145"/>
+      <c r="K42" s="170"/>
       <c r="L42" s="52" t="s">
         <v>174</v>
       </c>
@@ -23154,8 +23154,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="146"/>
-      <c r="K43" s="146"/>
+      <c r="J43" s="171"/>
+      <c r="K43" s="171"/>
       <c r="L43" s="83" t="s">
         <v>175</v>
       </c>
@@ -23170,11 +23170,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="147" t="s">
+      <c r="A45" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B45" s="147"/>
-      <c r="C45" s="147"/>
+      <c r="B45" s="172"/>
+      <c r="C45" s="172"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23291,19 +23291,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -23318,6 +23305,19 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="33" priority="1" operator="greaterThan">
@@ -23366,35 +23366,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45631</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23406,10 +23406,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23422,25 +23422,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23780,11 +23780,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23805,10 +23805,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45653</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23829,10 +23829,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>346</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23850,11 +23850,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24200,14 +24200,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24226,11 +24226,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -24255,11 +24255,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>215</v>
       </c>
@@ -24284,11 +24284,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>215</v>
       </c>
@@ -24305,11 +24305,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24326,11 +24326,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24347,11 +24347,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24368,11 +24368,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24390,11 +24390,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -24414,8 +24414,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -24430,11 +24430,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="147"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24582,6 +24582,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24590,23 +24607,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="29" priority="2" operator="greaterThan">
@@ -24658,35 +24658,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45714</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24698,10 +24698,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24714,25 +24714,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -25074,11 +25074,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25101,10 +25101,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45743</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25127,10 +25127,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25150,11 +25150,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25494,14 +25494,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25520,11 +25520,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>257</v>
       </c>
@@ -25549,11 +25549,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>262</v>
       </c>
@@ -25579,11 +25579,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>263</v>
       </c>
@@ -25608,11 +25608,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>264</v>
       </c>
@@ -25628,11 +25628,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25645,11 +25645,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25662,11 +25662,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25684,11 +25684,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -25708,8 +25708,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -25724,11 +25724,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="147"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25760,23 +25760,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25785,6 +25768,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
@@ -25834,34 +25834,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>45840</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -25873,10 +25873,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25889,25 +25889,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -26225,11 +26225,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26249,10 +26249,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>45840</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26272,10 +26272,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26292,11 +26292,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26652,14 +26652,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="159"/>
+      <c r="L32" s="144"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -26678,11 +26678,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>287</v>
       </c>
@@ -26707,11 +26707,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>290</v>
       </c>
@@ -26737,11 +26737,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85" t="s">
         <v>294</v>
       </c>
@@ -26766,11 +26766,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26795,11 +26795,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85" t="s">
         <v>295</v>
       </c>
@@ -26824,11 +26824,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85" t="s">
         <v>297</v>
       </c>
@@ -26845,11 +26845,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26867,11 +26867,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -26891,8 +26891,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -26907,10 +26907,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -26950,23 +26950,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -26975,6 +26958,23 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23594A22-61C1-4EF8-BB3E-FAB7DF2B3D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645414BF-25AB-41BB-AB06-7B0EDC77F96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1128,7 +1128,7 @@
     <t>37 days</t>
   </si>
   <si>
-    <t>8.5 tons so far</t>
+    <t>9.5 tons so far</t>
   </si>
 </sst>
 </file>
@@ -2190,6 +2190,64 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2210,12 +2268,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -2229,10 +2281,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2253,54 +2301,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -3169,7 +3169,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1179045</c:v>
+                  <c:v>-1279045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3701,7 +3701,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2412172</c:v>
+                  <c:v>2312172</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4116,7 +4116,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1648767.5</c:v>
+                  <c:v>-1748767.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7965,28 +7965,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45076</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -7995,8 +7995,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8008,10 +8008,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8024,25 +8024,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8335,11 +8335,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8400,10 +8400,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>328</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8429,11 +8429,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -10762,34 +10762,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>45918</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10801,10 +10801,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10817,25 +10817,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11198,11 +11198,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11222,10 +11222,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>45918</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11245,10 +11245,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11265,11 +11265,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11609,14 +11609,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11636,11 +11636,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>320</v>
       </c>
@@ -11666,11 +11666,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11697,11 +11697,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
         <v>330</v>
       </c>
@@ -11729,11 +11729,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="85" t="s">
         <v>331</v>
       </c>
@@ -11759,11 +11759,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85" t="s">
         <v>333</v>
       </c>
@@ -11789,11 +11789,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85" t="s">
         <v>320</v>
       </c>
@@ -11811,11 +11811,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11838,11 +11838,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -11863,8 +11863,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -11880,10 +11880,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11903,10 +11903,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -11944,6 +11944,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -11960,15 +11969,6 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
@@ -12018,34 +12018,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>46016</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12057,10 +12057,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>350</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12073,25 +12073,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12385,11 +12385,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12409,10 +12409,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>46016</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12432,10 +12432,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>351</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12452,11 +12452,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12778,14 +12778,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12805,11 +12805,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12827,11 +12827,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12846,11 +12846,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -12866,11 +12866,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12884,11 +12884,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12902,11 +12902,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12920,11 +12920,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12943,11 +12943,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -12968,8 +12968,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -12985,10 +12985,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13008,10 +13008,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13049,11 +13049,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13065,15 +13069,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
@@ -13123,50 +13123,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>46068</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
-        <v>-1179045</v>
-      </c>
-      <c r="K1" s="152"/>
+        <v>-1279045</v>
+      </c>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>1179045</v>
+        <v>1279045</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="str">
+      <c r="G2" s="153" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>58 days</v>
-      </c>
-      <c r="H2" s="156"/>
+        <v>62 days</v>
+      </c>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13179,25 +13179,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13286,11 +13286,15 @@
         <v>33000</v>
       </c>
       <c r="E6" s="23"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="46"/>
+      <c r="F6" s="45">
+        <v>46127</v>
+      </c>
+      <c r="G6" s="46">
+        <v>150</v>
+      </c>
       <c r="H6" s="49" t="str">
         <f t="shared" ref="H6:H13" si="0">IF(ISBLANK(F6),"",CONCATENATE(F6-$G$1+1," days"))</f>
-        <v/>
+        <v>60 days</v>
       </c>
       <c r="I6" s="21">
         <v>2</v>
@@ -13395,7 +13399,7 @@
         <v>143</v>
       </c>
       <c r="D10" s="9">
-        <v>800000</v>
+        <v>900000</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>355</v>
@@ -13494,11 +13498,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="9"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13518,10 +13522,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>46068</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13541,11 +13545,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="str">
+      <c r="G16" s="153" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>58 days</v>
-      </c>
-      <c r="H16" s="167"/>
+        <v>62 days</v>
+      </c>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13562,11 +13566,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13893,14 +13897,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -13912,11 +13916,11 @@
       <c r="F33" s="59"/>
       <c r="G33" s="67"/>
       <c r="H33" s="62"/>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85"/>
       <c r="L33" s="136"/>
       <c r="M33" s="15"/>
@@ -13930,11 +13934,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -13949,11 +13953,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -13969,11 +13973,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -13987,11 +13991,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -14005,11 +14009,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -14023,11 +14027,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14046,11 +14050,11 @@
         <v>0</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -14071,8 +14075,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -14088,10 +14092,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59">
         <v>700000</v>
       </c>
@@ -14117,10 +14121,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59">
         <v>100000</v>
       </c>
@@ -14161,11 +14165,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14177,15 +14185,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
@@ -14268,7 +14272,7 @@
       <c r="M1" s="186"/>
       <c r="N1" s="182" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>3 year, 0 months, 12 days</v>
+        <v>3 year, 0 months, 16 days</v>
       </c>
       <c r="O1" s="183"/>
       <c r="P1" s="183"/>
@@ -14681,7 +14685,7 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>-1179045</v>
+        <v>-1279045</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
@@ -14689,11 +14693,11 @@
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
-        <v>1179045</v>
+        <v>1279045</v>
       </c>
       <c r="G13" s="143">
         <f>MIN('Term-12'!G6:G14)</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H13" s="141" cm="1">
         <f t="array" ref="H13:I13">'Term-12'!G3:H3</f>
@@ -14843,7 +14847,7 @@
       <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>2412172</v>
+        <v>2312172</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
@@ -14851,7 +14855,7 @@
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
-        <v>15008622</v>
+        <v>15108622</v>
       </c>
       <c r="G25" s="143"/>
       <c r="H25" s="89"/>
@@ -14936,7 +14940,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>-1648767.5</v>
+        <v>-1748767.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -14967,7 +14971,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>2412172</v>
+        <v>2312172</v>
       </c>
     </row>
   </sheetData>
@@ -15216,28 +15220,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45163</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -15246,8 +15250,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -15259,10 +15263,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>353</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15275,25 +15279,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -15540,11 +15544,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15565,10 +15569,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="149">
+      <c r="H13" s="151">
         <v>45163</v>
       </c>
-      <c r="I13" s="150"/>
+      <c r="I13" s="152"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15589,10 +15593,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>353</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15610,11 +15614,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17378,6 +17382,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17386,12 +17396,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
     <cfRule type="duplicateValues" dxfId="55" priority="6"/>
@@ -17448,28 +17452,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45163</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17478,8 +17482,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17491,10 +17495,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>354</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17507,25 +17511,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17768,11 +17772,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17793,10 +17797,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="149">
+      <c r="H13" s="151">
         <v>45163</v>
       </c>
-      <c r="I13" s="150"/>
+      <c r="I13" s="152"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17817,10 +17821,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>354</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17838,11 +17842,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -19676,28 +19680,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45345</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -19706,8 +19710,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19719,10 +19723,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>342</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19735,25 +19739,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -20095,11 +20099,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20120,10 +20124,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45345</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20165,11 +20169,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20406,10 +20410,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="169" t="s">
+      <c r="J28" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="169"/>
+      <c r="K28" s="158"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20428,11 +20432,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="163">
+      <c r="J29" s="144">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="163"/>
+      <c r="K29" s="144"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20457,11 +20461,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="163">
+      <c r="J30" s="144">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="163"/>
+      <c r="K30" s="144"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20486,11 +20490,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="163">
+      <c r="J31" s="144">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="163"/>
+      <c r="K31" s="144"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20515,11 +20519,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="163">
+      <c r="J32" s="144">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="163"/>
+      <c r="K32" s="144"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20544,11 +20548,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20572,11 +20576,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20600,11 +20604,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20626,11 +20630,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="170">
+      <c r="J36" s="145">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="170"/>
+      <c r="K36" s="145"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20649,8 +20653,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="171"/>
-      <c r="K37" s="171"/>
+      <c r="J37" s="146"/>
+      <c r="K37" s="146"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20699,6 +20703,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="J29:K29"/>
@@ -20708,20 +20726,6 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="G17:I17"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="41" priority="4" operator="greaterThan">
@@ -20769,35 +20773,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45477</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20809,10 +20813,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>343</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20825,25 +20829,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -21177,11 +21181,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21204,10 +21208,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45477</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21253,11 +21257,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21623,14 +21627,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -21655,11 +21659,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>172</v>
       </c>
@@ -21687,11 +21691,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>173</v>
       </c>
@@ -21723,11 +21727,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>173</v>
       </c>
@@ -21748,11 +21752,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="170">
+      <c r="J36" s="145">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="170"/>
+      <c r="K36" s="145"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21769,11 +21773,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>179</v>
       </c>
@@ -21790,11 +21794,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21811,11 +21815,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21833,11 +21837,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -21852,8 +21856,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="52" t="s">
         <v>174</v>
       </c>
@@ -21924,6 +21928,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -21940,16 +21954,6 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
@@ -21998,35 +22002,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45548</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -22038,10 +22042,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22054,25 +22058,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22446,11 +22450,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22477,10 +22481,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45561</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22507,10 +22511,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22534,11 +22538,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22903,14 +22907,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -22929,11 +22933,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -22958,11 +22962,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -22987,11 +22991,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -23008,11 +23012,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>172</v>
       </c>
@@ -23029,11 +23033,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23050,11 +23054,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23074,11 +23078,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23130,11 +23134,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="170">
+      <c r="J42" s="145">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="170"/>
+      <c r="K42" s="145"/>
       <c r="L42" s="52" t="s">
         <v>174</v>
       </c>
@@ -23154,8 +23158,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="171"/>
-      <c r="K43" s="171"/>
+      <c r="J43" s="146"/>
+      <c r="K43" s="146"/>
       <c r="L43" s="83" t="s">
         <v>175</v>
       </c>
@@ -23170,11 +23174,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="172" t="s">
+      <c r="A45" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B45" s="172"/>
-      <c r="C45" s="172"/>
+      <c r="B45" s="147"/>
+      <c r="C45" s="147"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23291,6 +23295,19 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -23305,19 +23322,6 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="33" priority="1" operator="greaterThan">
@@ -23366,35 +23370,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45631</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23406,10 +23410,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23422,25 +23426,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23780,11 +23784,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23805,10 +23809,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45653</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23829,10 +23833,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>346</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23850,11 +23854,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24200,14 +24204,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24226,11 +24230,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -24255,11 +24259,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>215</v>
       </c>
@@ -24284,11 +24288,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>215</v>
       </c>
@@ -24305,11 +24309,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24326,11 +24330,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24347,11 +24351,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24368,11 +24372,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24390,11 +24394,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -24414,8 +24418,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -24430,11 +24434,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="147"/>
+      <c r="C43" s="147"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24582,23 +24586,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24607,6 +24594,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="29" priority="2" operator="greaterThan">
@@ -24658,35 +24662,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45714</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24698,10 +24702,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24714,25 +24718,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -25074,11 +25078,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25101,10 +25105,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45743</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25127,10 +25131,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25150,11 +25154,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25494,14 +25498,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25520,11 +25524,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>257</v>
       </c>
@@ -25549,11 +25553,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>262</v>
       </c>
@@ -25579,11 +25583,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>263</v>
       </c>
@@ -25608,11 +25612,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>264</v>
       </c>
@@ -25628,11 +25632,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25645,11 +25649,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25662,11 +25666,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25684,11 +25688,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -25708,8 +25712,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -25724,11 +25728,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="147"/>
+      <c r="C43" s="147"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25760,6 +25764,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25768,23 +25789,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
@@ -25834,34 +25838,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>45840</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -25873,10 +25877,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25889,25 +25893,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -26225,11 +26229,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26249,10 +26253,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>45840</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26272,10 +26276,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26292,11 +26296,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26652,14 +26656,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="144"/>
+      <c r="L32" s="159"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -26678,11 +26682,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>287</v>
       </c>
@@ -26707,11 +26711,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>290</v>
       </c>
@@ -26737,11 +26741,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
         <v>294</v>
       </c>
@@ -26766,11 +26770,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26795,11 +26799,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85" t="s">
         <v>295</v>
       </c>
@@ -26824,11 +26828,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85" t="s">
         <v>297</v>
       </c>
@@ -26845,11 +26849,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26867,11 +26871,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -26891,8 +26895,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -26907,10 +26911,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -26950,6 +26954,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -26958,23 +26979,6 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645414BF-25AB-41BB-AB06-7B0EDC77F96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147DCF66-7B88-430A-85BB-7D44F632D22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1128,7 +1128,7 @@
     <t>37 days</t>
   </si>
   <si>
-    <t>9.5 tons so far</t>
+    <t>105 tons so far</t>
   </si>
 </sst>
 </file>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="G2" s="153" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>62 days</v>
+        <v>64 days</v>
       </c>
       <c r="H2" s="168"/>
       <c r="I2" s="38"/>
@@ -13318,11 +13318,15 @@
         <v>38672</v>
       </c>
       <c r="E7" s="23"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="46"/>
+      <c r="F7" s="45">
+        <v>46131</v>
+      </c>
+      <c r="G7" s="46">
+        <v>134</v>
+      </c>
       <c r="H7" s="49" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>64 days</v>
       </c>
       <c r="I7" s="21">
         <v>3</v>
@@ -13547,7 +13551,7 @@
       </c>
       <c r="G16" s="153" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>62 days</v>
+        <v>64 days</v>
       </c>
       <c r="H16" s="154"/>
       <c r="I16" s="21">
@@ -13638,11 +13642,15 @@
       <c r="C20" s="3"/>
       <c r="D20" s="5"/>
       <c r="E20" s="22"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46"/>
+      <c r="F20" s="45">
+        <v>46131</v>
+      </c>
+      <c r="G20" s="46">
+        <v>97</v>
+      </c>
       <c r="H20" s="49" t="str">
         <f t="shared" ref="H20:H25" si="1">IF(ISBLANK(F20),"",CONCATENATE(F20-$G$15+1," days"))</f>
-        <v/>
+        <v>64 days</v>
       </c>
       <c r="I20" s="21">
         <v>16</v>
@@ -14100,18 +14108,18 @@
         <v>700000</v>
       </c>
       <c r="D43" s="15">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E43" s="131">
         <f>C43/D43</f>
-        <v>4375</v>
+        <v>4666.666666666667</v>
       </c>
       <c r="F43" s="62">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="G43" s="101">
         <f>E43*F43</f>
-        <v>875000</v>
+        <v>840000</v>
       </c>
       <c r="H43" s="15"/>
       <c r="I43" s="15"/>
@@ -14152,7 +14160,7 @@
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="G45" s="111">
         <f>G43+G44</f>
-        <v>1028846.1538461539</v>
+        <v>993846.15384615387</v>
       </c>
     </row>
     <row r="54" spans="5:9" x14ac:dyDescent="0.3">
@@ -14272,7 +14280,7 @@
       <c r="M1" s="186"/>
       <c r="N1" s="182" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>3 year, 0 months, 16 days</v>
+        <v>3 year, 0 months, 18 days</v>
       </c>
       <c r="O1" s="183"/>
       <c r="P1" s="183"/>
@@ -14697,7 +14705,7 @@
       </c>
       <c r="G13" s="143">
         <f>MIN('Term-12'!G6:G14)</f>
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="H13" s="141" cm="1">
         <f t="array" ref="H13:I13">'Term-12'!G3:H3</f>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147DCF66-7B88-430A-85BB-7D44F632D22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DA9D46-6639-438B-AE48-75A382CF6F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="359">
   <si>
     <t>#</t>
   </si>
@@ -1128,7 +1128,16 @@
     <t>37 days</t>
   </si>
   <si>
-    <t>105 tons so far</t>
+    <t>Pending from Term-11</t>
+  </si>
+  <si>
+    <t>Land Lease</t>
+  </si>
+  <si>
+    <t>10 tons so far</t>
+  </si>
+  <si>
+    <t>Big Tank-1st Middle - 131C-234R-1950T</t>
   </si>
 </sst>
 </file>
@@ -2190,64 +2199,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2268,6 +2219,12 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -2281,6 +2238,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2301,6 +2262,54 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2356,7 +2365,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="64">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3169,7 +3185,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1279045</c:v>
+                  <c:v>-920795</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3701,7 +3717,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2312172</c:v>
+                  <c:v>2670422</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4116,7 +4132,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1748767.5</c:v>
+                  <c:v>-1390517.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7965,28 +7981,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45076</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -7995,8 +8011,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8008,10 +8024,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8024,25 +8040,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8335,11 +8351,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8400,10 +8416,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>328</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8429,11 +8445,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -10707,27 +10723,27 @@
     <mergeCell ref="H14:I14"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D107">
-    <cfRule type="duplicateValues" dxfId="62" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E107">
-    <cfRule type="duplicateValues" dxfId="61" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="60" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L51">
-    <cfRule type="duplicateValues" dxfId="58" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M51">
-    <cfRule type="duplicateValues" dxfId="57" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S24:S26">
-    <cfRule type="duplicateValues" dxfId="56" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10762,34 +10778,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>45918</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10801,10 +10817,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10817,25 +10833,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11198,11 +11214,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11222,10 +11238,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>45918</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11245,10 +11261,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11265,11 +11281,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11609,14 +11625,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11636,11 +11652,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>320</v>
       </c>
@@ -11666,11 +11682,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11697,11 +11713,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85" t="s">
         <v>330</v>
       </c>
@@ -11729,11 +11745,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="85" t="s">
         <v>331</v>
       </c>
@@ -11759,11 +11775,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85" t="s">
         <v>333</v>
       </c>
@@ -11789,11 +11805,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85" t="s">
         <v>320</v>
       </c>
@@ -11811,11 +11827,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11838,11 +11854,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -11863,8 +11879,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -11880,10 +11896,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11903,10 +11919,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -11944,15 +11960,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -11969,23 +11976,32 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K6">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K22">
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12018,34 +12034,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>46016</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12057,10 +12073,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>350</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12073,25 +12089,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12385,11 +12401,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12409,10 +12425,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>46016</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12432,10 +12448,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>351</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12452,11 +12468,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12778,14 +12794,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12805,11 +12821,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12827,11 +12843,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12846,11 +12862,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -12866,11 +12882,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12884,11 +12900,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12902,11 +12918,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12920,11 +12936,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12943,11 +12959,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -12968,8 +12984,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -12985,10 +13001,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13008,10 +13024,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13049,15 +13065,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13069,28 +13081,32 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K6">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K22">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13123,50 +13139,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>46068</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
-        <v>-1279045</v>
-      </c>
-      <c r="K1" s="165"/>
+        <v>-920795</v>
+      </c>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>1279045</v>
+        <v>1379045</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="str">
+      <c r="G2" s="155" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>64 days</v>
-      </c>
-      <c r="H2" s="168"/>
+        <v>65 days</v>
+      </c>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13174,30 +13190,30 @@
       </c>
       <c r="L2" s="12">
         <f>SUM(L5:L22)</f>
-        <v>0</v>
+        <v>458250</v>
       </c>
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13267,9 +13283,15 @@
       <c r="I5" s="21">
         <v>1</v>
       </c>
-      <c r="J5" s="45"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="5"/>
+      <c r="J5" s="45">
+        <v>46132</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="L5" s="5">
+        <v>458250</v>
+      </c>
       <c r="M5" s="22"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -13322,7 +13344,7 @@
         <v>46131</v>
       </c>
       <c r="G7" s="46">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H7" s="49" t="str">
         <f t="shared" si="0"/>
@@ -13350,11 +13372,15 @@
         <v>15813</v>
       </c>
       <c r="E8" s="22"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="46"/>
+      <c r="F8" s="45">
+        <v>46132</v>
+      </c>
+      <c r="G8" s="46">
+        <v>131</v>
+      </c>
       <c r="H8" s="49" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>65 days</v>
       </c>
       <c r="I8" s="21">
         <v>4</v>
@@ -13371,7 +13397,7 @@
       <c r="B9" s="132">
         <v>46107</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="3" t="s">
         <v>308</v>
       </c>
       <c r="D9" s="9">
@@ -13396,17 +13422,17 @@
       <c r="A10" s="41">
         <v>6</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="132">
         <v>46111</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="3" t="s">
         <v>143</v>
       </c>
       <c r="D10" s="9">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F10" s="48"/>
       <c r="G10" s="46"/>
@@ -13502,11 +13528,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="9"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13526,10 +13552,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>46068</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13549,11 +13575,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="str">
+      <c r="G16" s="155" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>64 days</v>
-      </c>
-      <c r="H16" s="154"/>
+        <v>65 days</v>
+      </c>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13570,11 +13596,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13905,32 +13931,44 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D33" s="15"/>
+      <c r="D33" s="15" t="s">
+        <v>306</v>
+      </c>
       <c r="E33" s="59">
         <f>G33*F33</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="59"/>
-      <c r="G33" s="67"/>
-      <c r="H33" s="62"/>
-      <c r="I33" s="144">
+        <v>255450</v>
+      </c>
+      <c r="F33" s="59">
+        <v>131</v>
+      </c>
+      <c r="G33" s="67">
+        <v>1950</v>
+      </c>
+      <c r="H33" s="62">
+        <v>234</v>
+      </c>
+      <c r="I33" s="163">
         <f>G33*H33</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="144"/>
-      <c r="K33" s="85"/>
-      <c r="L33" s="136"/>
+        <v>456300</v>
+      </c>
+      <c r="J33" s="163"/>
+      <c r="K33" s="85" t="s">
+        <v>355</v>
+      </c>
+      <c r="L33" s="136">
+        <v>134000</v>
+      </c>
       <c r="M33" s="15"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
@@ -13942,13 +13980,17 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="144"/>
-      <c r="K34" s="85"/>
-      <c r="L34" s="136"/>
+      <c r="J34" s="163"/>
+      <c r="K34" s="85" t="s">
+        <v>356</v>
+      </c>
+      <c r="L34" s="136">
+        <v>200000</v>
+      </c>
       <c r="M34" s="15"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
@@ -13961,11 +14003,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -13981,11 +14023,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -13999,11 +14041,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -14017,11 +14059,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -14035,11 +14077,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14050,25 +14092,25 @@
       </c>
       <c r="E40" s="60">
         <f>SUM(E33:E38)</f>
-        <v>0</v>
+        <v>255450</v>
       </c>
       <c r="F40" s="60"/>
       <c r="G40" s="84">
         <f>SUM(G33:G39)</f>
-        <v>0</v>
+        <v>1950</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="145"/>
+        <v>456300</v>
+      </c>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
       <c r="L40" s="137">
         <f>SUM(L33:L39)</f>
-        <v>0</v>
+        <v>334000</v>
       </c>
       <c r="M40" s="15"/>
     </row>
@@ -14078,19 +14120,19 @@
       </c>
       <c r="E41" s="109" t="str">
         <f>CONCATENATE(ROUND((E40/E31)*100,2),"%")</f>
-        <v>0%</v>
+        <v>31.93%</v>
       </c>
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
       <c r="L41" s="105">
         <f>I40-L40</f>
-        <v>0</v>
+        <v>122300</v>
       </c>
       <c r="M41" s="15"/>
     </row>
@@ -14100,26 +14142,26 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59">
-        <v>700000</v>
+        <v>450000</v>
       </c>
       <c r="D43" s="15">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="E43" s="131">
         <f>C43/D43</f>
-        <v>4666.666666666667</v>
+        <v>3435.1145038167938</v>
       </c>
       <c r="F43" s="62">
-        <v>180</v>
+        <v>235</v>
       </c>
       <c r="G43" s="101">
         <f>E43*F43</f>
-        <v>840000</v>
+        <v>807251.9083969465</v>
       </c>
       <c r="H43" s="15"/>
       <c r="I43" s="15"/>
@@ -14129,26 +14171,26 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59">
         <v>100000</v>
       </c>
       <c r="D44" s="15">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="E44" s="131">
         <f>C44/D44</f>
-        <v>769.23076923076928</v>
+        <v>1030.9278350515465</v>
       </c>
       <c r="F44" s="62">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="G44" s="101">
         <f>E44*F44</f>
-        <v>153846.15384615384</v>
+        <v>273195.87628865981</v>
       </c>
       <c r="H44" s="15"/>
       <c r="I44" s="15"/>
@@ -14160,7 +14202,7 @@
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="G45" s="111">
         <f>G43+G44</f>
-        <v>993846.15384615387</v>
+        <v>1080447.7846856064</v>
       </c>
     </row>
     <row r="54" spans="5:9" x14ac:dyDescent="0.3">
@@ -14173,15 +14215,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14193,28 +14231,35 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K6">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  <conditionalFormatting sqref="K6">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K22">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14280,7 +14325,7 @@
       <c r="M1" s="186"/>
       <c r="N1" s="182" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>3 year, 0 months, 18 days</v>
+        <v>3 year, 0 months, 19 days</v>
       </c>
       <c r="O1" s="183"/>
       <c r="P1" s="183"/>
@@ -14693,19 +14738,19 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>-1279045</v>
+        <v>-920795</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
-        <v>0</v>
+        <v>458250</v>
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
-        <v>1279045</v>
+        <v>1379045</v>
       </c>
       <c r="G13" s="143">
         <f>MIN('Term-12'!G6:G14)</f>
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H13" s="141" cm="1">
         <f t="array" ref="H13:I13">'Term-12'!G3:H3</f>
@@ -14855,15 +14900,15 @@
       <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>2312172</v>
+        <v>2670422</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
-        <v>17420794</v>
+        <v>17879044</v>
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
-        <v>15108622</v>
+        <v>15208622</v>
       </c>
       <c r="G25" s="143"/>
       <c r="H25" s="89"/>
@@ -14948,7 +14993,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>-1748767.5</v>
+        <v>-1390517.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -14979,7 +15024,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>2312172</v>
+        <v>2670422</v>
       </c>
     </row>
   </sheetData>
@@ -15228,28 +15273,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45163</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -15258,8 +15303,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -15271,10 +15316,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>353</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15287,25 +15332,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -15552,11 +15597,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15577,10 +15622,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="149">
         <v>45163</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="150"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15601,10 +15646,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>353</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15622,11 +15667,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17390,12 +17435,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17404,29 +17443,35 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
-    <cfRule type="duplicateValues" dxfId="55" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E106">
-    <cfRule type="duplicateValues" dxfId="54" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="53" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L51">
-    <cfRule type="duplicateValues" dxfId="51" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M51">
-    <cfRule type="duplicateValues" dxfId="50" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S24:S26">
-    <cfRule type="duplicateValues" dxfId="49" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -17460,28 +17505,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45163</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17490,8 +17535,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17503,10 +17548,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>354</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17519,25 +17564,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17780,11 +17825,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17805,10 +17850,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="149">
         <v>45163</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="150"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17829,10 +17874,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>354</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17850,11 +17895,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -19634,27 +19679,27 @@
     <mergeCell ref="G15:I15"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
-    <cfRule type="duplicateValues" dxfId="48" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E106">
-    <cfRule type="duplicateValues" dxfId="47" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="46" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L51">
-    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M51">
-    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S24:S26">
-    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -19688,28 +19733,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45345</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -19718,8 +19763,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19731,10 +19776,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>342</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19747,25 +19792,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -20107,11 +20152,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20132,10 +20177,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45345</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20177,11 +20222,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20418,10 +20463,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="158" t="s">
+      <c r="J28" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="158"/>
+      <c r="K28" s="169"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20440,11 +20485,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="144">
+      <c r="J29" s="163">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="144"/>
+      <c r="K29" s="163"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20469,11 +20514,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="144">
+      <c r="J30" s="163">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="144"/>
+      <c r="K30" s="163"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20498,11 +20543,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="144">
+      <c r="J31" s="163">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="144"/>
+      <c r="K31" s="163"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20527,11 +20572,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="144">
+      <c r="J32" s="163">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="144"/>
+      <c r="K32" s="163"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20556,11 +20601,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20584,11 +20629,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20612,11 +20657,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20638,11 +20683,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="145">
+      <c r="J36" s="170">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="145"/>
+      <c r="K36" s="170"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20661,8 +20706,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="146"/>
-      <c r="K37" s="146"/>
+      <c r="J37" s="171"/>
+      <c r="K37" s="171"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20711,6 +20756,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J27:K27"/>
@@ -20720,34 +20779,20 @@
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="J35:K35"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="41" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="39" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="38" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="21"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20781,35 +20826,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45477</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20821,10 +20866,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>343</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20837,25 +20882,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -21189,11 +21234,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21216,10 +21261,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45477</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21265,11 +21310,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21635,14 +21680,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -21667,11 +21712,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>172</v>
       </c>
@@ -21699,11 +21744,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>173</v>
       </c>
@@ -21735,11 +21780,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>173</v>
       </c>
@@ -21760,11 +21805,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="145">
+      <c r="J36" s="170">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="145"/>
+      <c r="K36" s="170"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21781,11 +21826,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>179</v>
       </c>
@@ -21802,11 +21847,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21823,11 +21868,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21845,11 +21890,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -21864,8 +21909,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="52" t="s">
         <v>174</v>
       </c>
@@ -21936,16 +21981,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -21962,20 +21997,30 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="34" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -22010,35 +22055,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45548</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -22050,10 +22095,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22066,25 +22111,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22458,11 +22503,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22489,10 +22534,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45561</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22519,10 +22564,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22546,11 +22591,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22915,14 +22960,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -22941,11 +22986,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -22970,11 +23015,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -22999,11 +23044,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -23020,11 +23065,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>172</v>
       </c>
@@ -23041,11 +23086,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23062,11 +23107,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23086,11 +23131,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23142,11 +23187,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="145">
+      <c r="J42" s="170">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="145"/>
+      <c r="K42" s="170"/>
       <c r="L42" s="52" t="s">
         <v>174</v>
       </c>
@@ -23166,8 +23211,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="146"/>
-      <c r="K43" s="146"/>
+      <c r="J43" s="171"/>
+      <c r="K43" s="171"/>
       <c r="L43" s="83" t="s">
         <v>175</v>
       </c>
@@ -23182,11 +23227,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="147" t="s">
+      <c r="A45" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B45" s="147"/>
-      <c r="C45" s="147"/>
+      <c r="B45" s="172"/>
+      <c r="C45" s="172"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23303,19 +23348,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -23330,20 +23362,33 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="33" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="31" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="30" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -23378,35 +23423,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45631</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23418,10 +23463,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23434,25 +23479,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23792,11 +23837,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23817,10 +23862,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45653</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23841,10 +23886,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>346</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23862,11 +23907,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24212,14 +24257,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24238,11 +24283,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -24267,11 +24312,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>215</v>
       </c>
@@ -24296,11 +24341,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>215</v>
       </c>
@@ -24317,11 +24362,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24338,11 +24383,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24359,11 +24404,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24380,11 +24425,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24402,11 +24447,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -24426,8 +24471,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -24442,11 +24487,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="147"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24594,6 +24639,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24602,40 +24664,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="29" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5">
-    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L22">
-    <cfRule type="duplicateValues" dxfId="26" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="25" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -24670,35 +24715,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45714</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24710,10 +24755,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24726,25 +24771,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -25086,11 +25131,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25113,10 +25158,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45743</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25139,10 +25184,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25162,11 +25207,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25506,14 +25551,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25532,11 +25577,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>257</v>
       </c>
@@ -25561,11 +25606,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>262</v>
       </c>
@@ -25591,11 +25636,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>263</v>
       </c>
@@ -25620,11 +25665,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>264</v>
       </c>
@@ -25640,11 +25685,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25657,11 +25702,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25674,11 +25719,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25696,11 +25741,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -25720,8 +25765,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -25736,11 +25781,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="147"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25772,23 +25817,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25797,23 +25825,40 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5">
-    <cfRule type="duplicateValues" dxfId="22" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L22">
-    <cfRule type="duplicateValues" dxfId="21" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -25846,34 +25891,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>45840</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -25885,10 +25930,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25901,25 +25946,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -26237,11 +26282,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26261,10 +26306,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>45840</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26284,10 +26329,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26304,11 +26349,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26664,14 +26709,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="159"/>
+      <c r="L32" s="144"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -26690,11 +26735,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>287</v>
       </c>
@@ -26719,11 +26764,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>290</v>
       </c>
@@ -26749,11 +26794,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85" t="s">
         <v>294</v>
       </c>
@@ -26778,11 +26823,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26807,11 +26852,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85" t="s">
         <v>295</v>
       </c>
@@ -26836,11 +26881,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85" t="s">
         <v>297</v>
       </c>
@@ -26857,11 +26902,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26879,11 +26924,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -26903,8 +26948,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -26919,10 +26964,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -26962,23 +27007,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -26987,23 +27015,40 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K22">
-    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DA9D46-6639-438B-AE48-75A382CF6F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA952C6-E74B-495B-B9C3-3C78105E10BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3185,7 +3185,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-920795</c:v>
+                  <c:v>-922745</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3717,7 +3717,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2670422</c:v>
+                  <c:v>2668472</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4132,7 +4132,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1390517.5</c:v>
+                  <c:v>-1392467.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13158,7 +13158,7 @@
       </c>
       <c r="J1" s="151">
         <f>L2-D2</f>
-        <v>-920795</v>
+        <v>-922745</v>
       </c>
       <c r="K1" s="152"/>
       <c r="L1" s="18"/>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="L2" s="12">
         <f>SUM(L5:L22)</f>
-        <v>458250</v>
+        <v>456300</v>
       </c>
       <c r="M2" s="20"/>
     </row>
@@ -13290,7 +13290,7 @@
         <v>358</v>
       </c>
       <c r="L5" s="5">
-        <v>458250</v>
+        <v>456300</v>
       </c>
       <c r="M5" s="22"/>
     </row>
@@ -14738,11 +14738,11 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>-920795</v>
+        <v>-922745</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
-        <v>458250</v>
+        <v>456300</v>
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
@@ -14900,11 +14900,11 @@
       <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>2670422</v>
+        <v>2668472</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
-        <v>17879044</v>
+        <v>17877094</v>
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>-1390517.5</v>
+        <v>-1392467.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>2670422</v>
+        <v>2668472</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA952C6-E74B-495B-B9C3-3C78105E10BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6517B5F3-C560-4A0E-8716-4B52898C0506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2199,6 +2199,64 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2219,12 +2277,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -2238,10 +2290,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2262,54 +2310,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -3185,7 +3185,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-922745</c:v>
+                  <c:v>-922277</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3717,7 +3717,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2668472</c:v>
+                  <c:v>2668940</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4132,7 +4132,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1392467.5</c:v>
+                  <c:v>-1391999.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7981,28 +7981,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45076</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -8011,8 +8011,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8024,10 +8024,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8040,25 +8040,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8351,11 +8351,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8416,10 +8416,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>328</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8445,11 +8445,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -10778,34 +10778,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>45918</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10817,10 +10817,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10833,25 +10833,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11214,11 +11214,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11238,10 +11238,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>45918</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11261,10 +11261,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11281,11 +11281,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11625,14 +11625,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11652,11 +11652,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>320</v>
       </c>
@@ -11682,11 +11682,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11713,11 +11713,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
         <v>330</v>
       </c>
@@ -11745,11 +11745,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="85" t="s">
         <v>331</v>
       </c>
@@ -11775,11 +11775,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85" t="s">
         <v>333</v>
       </c>
@@ -11805,11 +11805,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85" t="s">
         <v>320</v>
       </c>
@@ -11827,11 +11827,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11854,11 +11854,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -11879,8 +11879,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -11896,10 +11896,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11919,10 +11919,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -11960,6 +11960,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -11976,15 +11985,6 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
@@ -12034,34 +12034,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>46016</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12073,10 +12073,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>350</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12089,25 +12089,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12401,11 +12401,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12425,10 +12425,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>46016</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12448,10 +12448,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>351</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12468,11 +12468,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12794,14 +12794,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12821,11 +12821,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12843,11 +12843,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12862,11 +12862,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -12882,11 +12882,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12900,11 +12900,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12918,11 +12918,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12936,11 +12936,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12959,11 +12959,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -12984,8 +12984,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -13001,10 +13001,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13024,10 +13024,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13065,11 +13065,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13081,15 +13085,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
@@ -13139,34 +13139,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>46068</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
-        <v>-922745</v>
-      </c>
-      <c r="K1" s="152"/>
+        <v>-922277</v>
+      </c>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -13178,11 +13178,11 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="str">
+      <c r="G2" s="153" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
         <v>65 days</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13190,30 +13190,30 @@
       </c>
       <c r="L2" s="12">
         <f>SUM(L5:L22)</f>
-        <v>456300</v>
+        <v>456768</v>
       </c>
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13290,7 +13290,7 @@
         <v>358</v>
       </c>
       <c r="L5" s="5">
-        <v>456300</v>
+        <v>456768</v>
       </c>
       <c r="M5" s="22"/>
     </row>
@@ -13528,11 +13528,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="9"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13552,10 +13552,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>46068</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13575,11 +13575,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="str">
+      <c r="G16" s="153" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
         <v>65 days</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13596,11 +13596,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13931,14 +13931,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -13947,22 +13947,22 @@
       </c>
       <c r="E33" s="59">
         <f>G33*F33</f>
-        <v>255450</v>
+        <v>255712</v>
       </c>
       <c r="F33" s="59">
         <v>131</v>
       </c>
       <c r="G33" s="67">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="H33" s="62">
         <v>234</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
-        <v>456300</v>
-      </c>
-      <c r="J33" s="163"/>
+        <v>456768</v>
+      </c>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>355</v>
       </c>
@@ -13980,11 +13980,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>356</v>
       </c>
@@ -14003,11 +14003,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -14023,11 +14023,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -14041,11 +14041,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -14059,11 +14059,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -14077,11 +14077,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14092,19 +14092,19 @@
       </c>
       <c r="E40" s="60">
         <f>SUM(E33:E38)</f>
-        <v>255450</v>
+        <v>255712</v>
       </c>
       <c r="F40" s="60"/>
       <c r="G40" s="84">
         <f>SUM(G33:G39)</f>
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
-        <v>456300</v>
-      </c>
-      <c r="J40" s="170"/>
+        <v>456768</v>
+      </c>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -14120,19 +14120,19 @@
       </c>
       <c r="E41" s="109" t="str">
         <f>CONCATENATE(ROUND((E40/E31)*100,2),"%")</f>
-        <v>31.93%</v>
+        <v>31.96%</v>
       </c>
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
       <c r="L41" s="105">
         <f>I40-L40</f>
-        <v>122300</v>
+        <v>122768</v>
       </c>
       <c r="M41" s="15"/>
     </row>
@@ -14142,10 +14142,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59">
         <v>450000</v>
       </c>
@@ -14171,10 +14171,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59">
         <v>100000</v>
       </c>
@@ -14215,11 +14215,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14231,15 +14235,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
@@ -14249,17 +14249,17 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K5">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K6">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K22">
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14738,11 +14738,11 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>-922745</v>
+        <v>-922277</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
-        <v>456300</v>
+        <v>456768</v>
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
@@ -14900,11 +14900,11 @@
       <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>2668472</v>
+        <v>2668940</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
-        <v>17877094</v>
+        <v>17877562</v>
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>-1392467.5</v>
+        <v>-1391999.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>2668472</v>
+        <v>2668940</v>
       </c>
     </row>
   </sheetData>
@@ -15273,28 +15273,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45163</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -15303,8 +15303,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -15316,10 +15316,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>353</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15332,25 +15332,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -15597,11 +15597,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15622,10 +15622,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="149">
+      <c r="H13" s="151">
         <v>45163</v>
       </c>
-      <c r="I13" s="150"/>
+      <c r="I13" s="152"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15646,10 +15646,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>353</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15667,11 +15667,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17435,6 +17435,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17443,12 +17449,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
     <cfRule type="duplicateValues" dxfId="56" priority="6"/>
@@ -17505,28 +17505,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45163</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17535,8 +17535,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17548,10 +17548,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>354</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17564,25 +17564,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17825,11 +17825,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17850,10 +17850,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="149">
+      <c r="H13" s="151">
         <v>45163</v>
       </c>
-      <c r="I13" s="150"/>
+      <c r="I13" s="152"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17874,10 +17874,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>354</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17895,11 +17895,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -19733,28 +19733,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45345</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -19763,8 +19763,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19776,10 +19776,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>342</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19792,25 +19792,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -20152,11 +20152,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20177,10 +20177,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45345</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20222,11 +20222,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20463,10 +20463,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="169" t="s">
+      <c r="J28" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="169"/>
+      <c r="K28" s="158"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20485,11 +20485,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="163">
+      <c r="J29" s="144">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="163"/>
+      <c r="K29" s="144"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20514,11 +20514,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="163">
+      <c r="J30" s="144">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="163"/>
+      <c r="K30" s="144"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20543,11 +20543,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="163">
+      <c r="J31" s="144">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="163"/>
+      <c r="K31" s="144"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20572,11 +20572,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="163">
+      <c r="J32" s="144">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="163"/>
+      <c r="K32" s="144"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20601,11 +20601,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20629,11 +20629,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20657,11 +20657,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20683,11 +20683,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="170">
+      <c r="J36" s="145">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="170"/>
+      <c r="K36" s="145"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20706,8 +20706,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="171"/>
-      <c r="K37" s="171"/>
+      <c r="J37" s="146"/>
+      <c r="K37" s="146"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20756,6 +20756,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="J29:K29"/>
@@ -20765,20 +20779,6 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="G17:I17"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="42" priority="4" operator="greaterThan">
@@ -20826,35 +20826,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45477</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20866,10 +20866,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>343</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20882,25 +20882,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -21234,11 +21234,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21261,10 +21261,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45477</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21310,11 +21310,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21680,14 +21680,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -21712,11 +21712,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>172</v>
       </c>
@@ -21744,11 +21744,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>173</v>
       </c>
@@ -21780,11 +21780,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>173</v>
       </c>
@@ -21805,11 +21805,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="170">
+      <c r="J36" s="145">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="170"/>
+      <c r="K36" s="145"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21826,11 +21826,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>179</v>
       </c>
@@ -21847,11 +21847,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21868,11 +21868,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21890,11 +21890,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -21909,8 +21909,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="52" t="s">
         <v>174</v>
       </c>
@@ -21981,6 +21981,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -21997,16 +22007,6 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="38" priority="1" operator="greaterThan">
@@ -22055,35 +22055,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45548</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -22095,10 +22095,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22111,25 +22111,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22503,11 +22503,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22534,10 +22534,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45561</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22564,10 +22564,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22591,11 +22591,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22960,14 +22960,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -22986,11 +22986,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -23015,11 +23015,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -23044,11 +23044,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -23065,11 +23065,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>172</v>
       </c>
@@ -23086,11 +23086,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23107,11 +23107,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23131,11 +23131,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23187,11 +23187,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="170">
+      <c r="J42" s="145">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="170"/>
+      <c r="K42" s="145"/>
       <c r="L42" s="52" t="s">
         <v>174</v>
       </c>
@@ -23211,8 +23211,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="171"/>
-      <c r="K43" s="171"/>
+      <c r="J43" s="146"/>
+      <c r="K43" s="146"/>
       <c r="L43" s="83" t="s">
         <v>175</v>
       </c>
@@ -23227,11 +23227,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="172" t="s">
+      <c r="A45" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B45" s="172"/>
-      <c r="C45" s="172"/>
+      <c r="B45" s="147"/>
+      <c r="C45" s="147"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23348,6 +23348,19 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -23362,19 +23375,6 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="34" priority="1" operator="greaterThan">
@@ -23423,35 +23423,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45631</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23463,10 +23463,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23479,25 +23479,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23837,11 +23837,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23862,10 +23862,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45653</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23886,10 +23886,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>346</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23907,11 +23907,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24257,14 +24257,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24283,11 +24283,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -24312,11 +24312,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>215</v>
       </c>
@@ -24341,11 +24341,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>215</v>
       </c>
@@ -24362,11 +24362,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24383,11 +24383,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24404,11 +24404,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24425,11 +24425,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24447,11 +24447,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -24471,8 +24471,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -24487,11 +24487,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="147"/>
+      <c r="C43" s="147"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24639,23 +24639,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24664,6 +24647,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="30" priority="2" operator="greaterThan">
@@ -24715,35 +24715,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45714</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24755,10 +24755,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24771,25 +24771,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -25131,11 +25131,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25158,10 +25158,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45743</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25184,10 +25184,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25207,11 +25207,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25551,14 +25551,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25577,11 +25577,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>257</v>
       </c>
@@ -25606,11 +25606,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>262</v>
       </c>
@@ -25636,11 +25636,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>263</v>
       </c>
@@ -25665,11 +25665,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>264</v>
       </c>
@@ -25685,11 +25685,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25702,11 +25702,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25719,11 +25719,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25741,11 +25741,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -25765,8 +25765,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -25781,11 +25781,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="147"/>
+      <c r="C43" s="147"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25817,6 +25817,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25825,23 +25842,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="25" priority="2" operator="greaterThan">
@@ -25891,34 +25891,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>45840</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -25930,10 +25930,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25946,25 +25946,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -26282,11 +26282,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26306,10 +26306,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>45840</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26329,10 +26329,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26349,11 +26349,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26709,14 +26709,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="144"/>
+      <c r="L32" s="159"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -26735,11 +26735,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>287</v>
       </c>
@@ -26764,11 +26764,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>290</v>
       </c>
@@ -26794,11 +26794,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
         <v>294</v>
       </c>
@@ -26823,11 +26823,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26852,11 +26852,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85" t="s">
         <v>295</v>
       </c>
@@ -26881,11 +26881,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85" t="s">
         <v>297</v>
       </c>
@@ -26902,11 +26902,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26924,11 +26924,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -26948,8 +26948,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -26964,10 +26964,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -27007,6 +27007,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -27015,23 +27032,6 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6517B5F3-C560-4A0E-8716-4B52898C0506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCC3ADA-BF71-41D8-84E4-00983D795271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="360">
   <si>
     <t>#</t>
   </si>
@@ -1134,10 +1134,13 @@
     <t>Land Lease</t>
   </si>
   <si>
-    <t>10 tons so far</t>
-  </si>
-  <si>
     <t>Big Tank-1st Middle - 131C-234R-1950T</t>
+  </si>
+  <si>
+    <t>11 tons so far</t>
+  </si>
+  <si>
+    <t>Cash Credits-24-04-2026</t>
   </si>
 </sst>
 </file>
@@ -2199,64 +2202,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2277,6 +2222,12 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -2290,6 +2241,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2310,6 +2265,54 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -3185,7 +3188,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-922277</c:v>
+                  <c:v>-1022277</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3717,7 +3720,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2668940</c:v>
+                  <c:v>2568940</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4132,7 +4135,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1391999.5</c:v>
+                  <c:v>-1491999.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7981,28 +7984,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45076</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -8011,8 +8014,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8024,10 +8027,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8040,25 +8043,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8351,11 +8354,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8416,10 +8419,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>328</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8445,11 +8448,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -10778,34 +10781,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>45918</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10817,10 +10820,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10833,25 +10836,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11214,11 +11217,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11238,10 +11241,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>45918</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11261,10 +11264,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11281,11 +11284,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11625,14 +11628,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11652,11 +11655,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>320</v>
       </c>
@@ -11682,11 +11685,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11713,11 +11716,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85" t="s">
         <v>330</v>
       </c>
@@ -11745,11 +11748,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="85" t="s">
         <v>331</v>
       </c>
@@ -11775,11 +11778,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85" t="s">
         <v>333</v>
       </c>
@@ -11805,11 +11808,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85" t="s">
         <v>320</v>
       </c>
@@ -11827,11 +11830,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11854,11 +11857,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -11879,8 +11882,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -11896,10 +11899,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11919,10 +11922,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -11960,15 +11963,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -11985,6 +11979,15 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
@@ -12034,34 +12037,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>46016</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12073,10 +12076,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>350</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12089,25 +12092,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12401,11 +12404,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12425,10 +12428,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>46016</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12448,10 +12451,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>351</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12468,11 +12471,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12794,14 +12797,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12821,11 +12824,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12843,11 +12846,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12862,11 +12865,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -12882,11 +12885,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12900,11 +12903,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12918,11 +12921,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12936,11 +12939,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12959,11 +12962,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -12984,8 +12987,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -13001,10 +13004,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13024,10 +13027,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13065,15 +13068,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13085,11 +13084,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
@@ -13139,50 +13142,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>46068</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
-        <v>-922277</v>
-      </c>
-      <c r="K1" s="165"/>
+        <v>-1022277</v>
+      </c>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>1379045</v>
+        <v>1479045</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="str">
+      <c r="G2" s="155" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>65 days</v>
-      </c>
-      <c r="H2" s="168"/>
+        <v>70 days</v>
+      </c>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13195,25 +13198,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13287,7 +13290,7 @@
         <v>46132</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L5" s="5">
         <v>456768</v>
@@ -13404,11 +13407,15 @@
         <v>6000</v>
       </c>
       <c r="E9" s="22"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="46"/>
+      <c r="F9" s="48">
+        <v>46136</v>
+      </c>
+      <c r="G9" s="46">
+        <v>126</v>
+      </c>
       <c r="H9" s="49" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>69 days</v>
       </c>
       <c r="I9" s="21">
         <v>5</v>
@@ -13432,13 +13439,17 @@
         <v>1000000</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>357</v>
-      </c>
-      <c r="F10" s="48"/>
-      <c r="G10" s="46"/>
+        <v>358</v>
+      </c>
+      <c r="F10" s="48">
+        <v>46137</v>
+      </c>
+      <c r="G10" s="46">
+        <v>125</v>
+      </c>
       <c r="H10" s="49" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>70 days</v>
       </c>
       <c r="I10" s="21">
         <v>6</v>
@@ -13480,9 +13491,15 @@
       <c r="A12" s="41">
         <v>8</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="5"/>
+      <c r="B12" s="7">
+        <v>46127</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="5">
+        <v>100000</v>
+      </c>
       <c r="E12" s="57"/>
       <c r="F12" s="48"/>
       <c r="G12" s="113"/>
@@ -13528,11 +13545,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="9"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13552,10 +13569,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>46068</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13575,11 +13592,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="str">
+      <c r="G16" s="155" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>65 days</v>
-      </c>
-      <c r="H16" s="154"/>
+        <v>70 days</v>
+      </c>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13596,11 +13613,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13694,11 +13711,15 @@
       <c r="C21" s="3"/>
       <c r="D21" s="5"/>
       <c r="E21" s="22"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="46"/>
+      <c r="F21" s="48">
+        <v>46136</v>
+      </c>
+      <c r="G21" s="46">
+        <v>85</v>
+      </c>
       <c r="H21" s="49" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>69 days</v>
       </c>
       <c r="I21" s="21">
         <v>17</v>
@@ -13716,11 +13737,15 @@
       <c r="C22" s="3"/>
       <c r="D22" s="5"/>
       <c r="E22" s="22"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="46"/>
+      <c r="F22" s="48">
+        <v>46137</v>
+      </c>
+      <c r="G22" s="46">
+        <v>76</v>
+      </c>
       <c r="H22" s="49" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>70 days</v>
       </c>
       <c r="I22" s="21">
         <v>18</v>
@@ -13931,14 +13956,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="145"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -13958,11 +13983,11 @@
       <c r="H33" s="62">
         <v>234</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>456768</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>355</v>
       </c>
@@ -13980,11 +14005,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>356</v>
       </c>
@@ -14003,13 +14028,17 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="144"/>
-      <c r="K35" s="85"/>
-      <c r="L35" s="136"/>
+      <c r="J35" s="163"/>
+      <c r="K35" s="85" t="s">
+        <v>359</v>
+      </c>
+      <c r="L35" s="136">
+        <v>50000</v>
+      </c>
       <c r="M35" s="15" t="s">
         <v>226</v>
       </c>
@@ -14023,11 +14052,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -14041,11 +14070,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -14059,11 +14088,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -14077,11 +14106,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14100,17 +14129,17 @@
         <v>1952</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>456768</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
       <c r="L40" s="137">
         <f>SUM(L33:L39)</f>
-        <v>334000</v>
+        <v>384000</v>
       </c>
       <c r="M40" s="15"/>
     </row>
@@ -14125,14 +14154,14 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
       <c r="L41" s="105">
         <f>I40-L40</f>
-        <v>122768</v>
+        <v>72768</v>
       </c>
       <c r="M41" s="15"/>
     </row>
@@ -14142,26 +14171,26 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59">
         <v>450000</v>
       </c>
       <c r="D43" s="15">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E43" s="131">
         <f>C43/D43</f>
-        <v>3435.1145038167938</v>
+        <v>3571.4285714285716</v>
       </c>
       <c r="F43" s="62">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="G43" s="101">
         <f>E43*F43</f>
-        <v>807251.9083969465</v>
+        <v>892857.14285714284</v>
       </c>
       <c r="H43" s="15"/>
       <c r="I43" s="15"/>
@@ -14171,26 +14200,26 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="172"/>
       <c r="C44" s="59">
         <v>100000</v>
       </c>
       <c r="D44" s="15">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="E44" s="131">
         <f>C44/D44</f>
-        <v>1030.9278350515465</v>
+        <v>1315.7894736842106</v>
       </c>
       <c r="F44" s="62">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="G44" s="101">
         <f>E44*F44</f>
-        <v>273195.87628865981</v>
+        <v>394736.8421052632</v>
       </c>
       <c r="H44" s="15"/>
       <c r="I44" s="15"/>
@@ -14202,7 +14231,7 @@
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="G45" s="111">
         <f>G43+G44</f>
-        <v>1080447.7846856064</v>
+        <v>1287593.9849624061</v>
       </c>
     </row>
     <row r="54" spans="5:9" x14ac:dyDescent="0.3">
@@ -14215,15 +14244,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14235,11 +14260,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
@@ -14325,7 +14354,7 @@
       <c r="M1" s="186"/>
       <c r="N1" s="182" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>3 year, 0 months, 19 days</v>
+        <v>3 year, 0 months, 24 days</v>
       </c>
       <c r="O1" s="183"/>
       <c r="P1" s="183"/>
@@ -14738,7 +14767,7 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>-922277</v>
+        <v>-1022277</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
@@ -14746,11 +14775,11 @@
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
-        <v>1379045</v>
+        <v>1479045</v>
       </c>
       <c r="G13" s="143">
         <f>MIN('Term-12'!G6:G14)</f>
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H13" s="141" cm="1">
         <f t="array" ref="H13:I13">'Term-12'!G3:H3</f>
@@ -14900,7 +14929,7 @@
       <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>2668940</v>
+        <v>2568940</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
@@ -14908,7 +14937,7 @@
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
-        <v>15208622</v>
+        <v>15308622</v>
       </c>
       <c r="G25" s="143"/>
       <c r="H25" s="89"/>
@@ -14993,7 +15022,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>-1391999.5</v>
+        <v>-1491999.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -15024,7 +15053,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>2668940</v>
+        <v>2568940</v>
       </c>
     </row>
   </sheetData>
@@ -15273,28 +15302,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45163</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -15303,8 +15332,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -15316,10 +15345,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>353</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15332,25 +15361,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -15597,11 +15626,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15622,10 +15651,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="149">
         <v>45163</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="150"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15646,10 +15675,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>353</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15667,11 +15696,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17435,12 +17464,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17449,6 +17472,12 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
     <cfRule type="duplicateValues" dxfId="56" priority="6"/>
@@ -17505,28 +17534,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45163</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17535,8 +17564,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17548,10 +17577,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>354</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17564,25 +17593,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17825,11 +17854,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17850,10 +17879,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="149">
         <v>45163</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="150"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17874,10 +17903,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="155" t="s">
         <v>354</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17895,11 +17924,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -19733,28 +19762,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45345</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -19763,8 +19792,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19776,10 +19805,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>342</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19792,25 +19821,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -20152,11 +20181,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20177,10 +20206,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45345</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20222,11 +20251,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20463,10 +20492,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="158" t="s">
+      <c r="J28" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="158"/>
+      <c r="K28" s="169"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20485,11 +20514,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="144">
+      <c r="J29" s="163">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="144"/>
+      <c r="K29" s="163"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20514,11 +20543,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="144">
+      <c r="J30" s="163">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="144"/>
+      <c r="K30" s="163"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20543,11 +20572,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="144">
+      <c r="J31" s="163">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="144"/>
+      <c r="K31" s="163"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20572,11 +20601,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="144">
+      <c r="J32" s="163">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="144"/>
+      <c r="K32" s="163"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20601,11 +20630,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20629,11 +20658,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20657,11 +20686,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20683,11 +20712,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="145">
+      <c r="J36" s="170">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="145"/>
+      <c r="K36" s="170"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20706,8 +20735,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="146"/>
-      <c r="K37" s="146"/>
+      <c r="J37" s="171"/>
+      <c r="K37" s="171"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20756,6 +20785,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J27:K27"/>
@@ -20765,20 +20808,6 @@
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="J35:K35"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="42" priority="4" operator="greaterThan">
@@ -20826,35 +20855,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45477</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20866,10 +20895,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>343</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20882,25 +20911,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -21234,11 +21263,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21261,10 +21290,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45477</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21310,11 +21339,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21680,14 +21709,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -21712,11 +21741,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>172</v>
       </c>
@@ -21744,11 +21773,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>173</v>
       </c>
@@ -21780,11 +21809,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>173</v>
       </c>
@@ -21805,11 +21834,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="145">
+      <c r="J36" s="170">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="145"/>
+      <c r="K36" s="170"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21826,11 +21855,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>179</v>
       </c>
@@ -21847,11 +21876,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21868,11 +21897,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21890,11 +21919,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -21909,8 +21938,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="52" t="s">
         <v>174</v>
       </c>
@@ -21981,16 +22010,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -22007,6 +22026,16 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="38" priority="1" operator="greaterThan">
@@ -22055,35 +22084,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45548</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -22095,10 +22124,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22111,25 +22140,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22503,11 +22532,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22534,10 +22563,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45561</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22564,10 +22593,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22591,11 +22620,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22960,14 +22989,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -22986,11 +23015,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -23015,11 +23044,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -23044,11 +23073,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -23065,11 +23094,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>172</v>
       </c>
@@ -23086,11 +23115,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23107,11 +23136,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23131,11 +23160,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23187,11 +23216,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="145">
+      <c r="J42" s="170">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="145"/>
+      <c r="K42" s="170"/>
       <c r="L42" s="52" t="s">
         <v>174</v>
       </c>
@@ -23211,8 +23240,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="146"/>
-      <c r="K43" s="146"/>
+      <c r="J43" s="171"/>
+      <c r="K43" s="171"/>
       <c r="L43" s="83" t="s">
         <v>175</v>
       </c>
@@ -23227,11 +23256,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="147" t="s">
+      <c r="A45" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B45" s="147"/>
-      <c r="C45" s="147"/>
+      <c r="B45" s="172"/>
+      <c r="C45" s="172"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23348,19 +23377,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -23375,6 +23391,19 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="34" priority="1" operator="greaterThan">
@@ -23423,35 +23452,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45631</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23463,10 +23492,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23479,25 +23508,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23837,11 +23866,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23862,10 +23891,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45653</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23886,10 +23915,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>346</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23907,11 +23936,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24257,14 +24286,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24283,11 +24312,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -24312,11 +24341,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>215</v>
       </c>
@@ -24341,11 +24370,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>215</v>
       </c>
@@ -24362,11 +24391,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24383,11 +24412,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24404,11 +24433,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24425,11 +24454,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24447,11 +24476,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -24471,8 +24500,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -24487,11 +24516,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="147"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24639,6 +24668,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24647,23 +24693,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="30" priority="2" operator="greaterThan">
@@ -24715,35 +24744,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="146" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="149">
         <v>45714</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="150"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="151">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="152"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="154"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24755,10 +24784,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="155" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="156"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24771,25 +24800,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="160"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -25131,11 +25160,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="166"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25158,10 +25187,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="149">
         <v>45743</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="150"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25184,10 +25213,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="155" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25207,11 +25236,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25551,14 +25580,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="169"/>
+      <c r="L32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="144"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25577,11 +25606,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="163">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="163"/>
       <c r="L33" s="85" t="s">
         <v>257</v>
       </c>
@@ -25606,11 +25635,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="163">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="163"/>
       <c r="L34" s="85" t="s">
         <v>262</v>
       </c>
@@ -25636,11 +25665,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="163">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="163"/>
       <c r="L35" s="85" t="s">
         <v>263</v>
       </c>
@@ -25665,11 +25694,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="144">
+      <c r="J36" s="163">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="163"/>
       <c r="L36" s="85" t="s">
         <v>264</v>
       </c>
@@ -25685,11 +25714,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="163"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25702,11 +25731,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="163"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25719,11 +25748,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="163"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25741,11 +25770,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="170">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="170"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -25765,8 +25794,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -25781,11 +25810,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="147"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25817,23 +25846,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25842,6 +25854,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="25" priority="2" operator="greaterThan">
@@ -25891,34 +25920,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="146" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="149">
         <v>45840</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="150"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="151">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -25930,10 +25959,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="155" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25946,25 +25975,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="160"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -26282,11 +26311,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="164" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26306,10 +26335,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="149">
         <v>45840</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="150"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26329,10 +26358,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26349,11 +26378,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26709,14 +26738,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="169"/>
+      <c r="K32" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="159"/>
+      <c r="L32" s="144"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -26735,11 +26764,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="163">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="163"/>
       <c r="K33" s="85" t="s">
         <v>287</v>
       </c>
@@ -26764,11 +26793,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="163">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="163"/>
       <c r="K34" s="85" t="s">
         <v>290</v>
       </c>
@@ -26794,11 +26823,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="163">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="163"/>
       <c r="K35" s="85" t="s">
         <v>294</v>
       </c>
@@ -26823,11 +26852,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="163">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="163"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26852,11 +26881,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="163">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="163"/>
       <c r="K37" s="85" t="s">
         <v>295</v>
       </c>
@@ -26881,11 +26910,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="163">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="163"/>
       <c r="K38" s="85" t="s">
         <v>297</v>
       </c>
@@ -26902,11 +26931,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="163">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="163"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26924,11 +26953,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="170">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="170"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -26948,8 +26977,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -26964,10 +26993,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="172" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="172"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -27007,23 +27036,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -27032,6 +27044,23 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCC3ADA-BF71-41D8-84E4-00983D795271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A92DA6B-C793-4853-A63D-C7D64001D34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,8 +20,9 @@
     <sheet name="Term-10" sheetId="17" r:id="rId10"/>
     <sheet name="Term-11" sheetId="18" r:id="rId11"/>
     <sheet name="Term-12" sheetId="19" r:id="rId12"/>
-    <sheet name="Summary" sheetId="12" r:id="rId13"/>
-    <sheet name="Notes" sheetId="14" r:id="rId14"/>
+    <sheet name="Term-13" sheetId="20" r:id="rId13"/>
+    <sheet name="Summary" sheetId="12" r:id="rId14"/>
+    <sheet name="Notes" sheetId="14" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="367">
   <si>
     <t>#</t>
   </si>
@@ -1141,6 +1142,27 @@
   </si>
   <si>
     <t>Cash Credits-24-04-2026</t>
+  </si>
+  <si>
+    <t>Big Tank-Final-120C-250R-6017T</t>
+  </si>
+  <si>
+    <t>Small Tank-Final-90C-280R-650Q</t>
+  </si>
+  <si>
+    <t>Big Tank Final-Macrosis</t>
+  </si>
+  <si>
+    <t>Small Tank Final-S/L</t>
+  </si>
+  <si>
+    <t>71 days</t>
+  </si>
+  <si>
+    <t>Vala kIray</t>
+  </si>
+  <si>
+    <t>Adjustments</t>
   </si>
 </sst>
 </file>
@@ -1754,7 +1776,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -2202,6 +2224,64 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2222,12 +2302,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -2241,10 +2315,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2265,54 +2335,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2364,11 +2386,57 @@
     <xf numFmtId="168" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="64">
+  <dxfs count="70">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3188,7 +3256,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1022277</c:v>
+                  <c:v>651715</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3720,7 +3788,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2568940</c:v>
+                  <c:v>4242932</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4135,7 +4203,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1491999.5</c:v>
+                  <c:v>181992.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6345,6 +6413,226 @@
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>15241</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>5106</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>285751</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>14796</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5E704EB-24C8-146E-5329-6FDBA423FC20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>287229</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>3144</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>290397</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>3144</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{179E10D5-0BA0-D90F-B9EF-68418316466D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>226736</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>44390</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>299786</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A335A642-4BD7-BA4B-5FF0-1EC7F44A5CA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8206954" y="224499"/>
+          <a:ext cx="682650" cy="411078"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>407633</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>14224</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>298039</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>137633</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63BE548A-480F-BBA8-CAEE-B9B166E61A42}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6081069" y="194333"/>
+          <a:ext cx="500008" cy="483627"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>270510</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>9690</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBD8CD7C-1605-4206-AB52-CB0FB9E0DA59}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -7456,165 +7744,36 @@
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>15241</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>5106</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>285751</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>14796</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>96982</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5E704EB-24C8-146E-5329-6FDBA423FC20}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B384FAD-257C-4639-814A-93EB3E765B18}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>287229</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>3144</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>290397</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>3144</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{179E10D5-0BA0-D90F-B9EF-68418316466D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>226736</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>44390</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>299786</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A335A642-4BD7-BA4B-5FF0-1EC7F44A5CA8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8206954" y="224499"/>
-          <a:ext cx="682650" cy="411078"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>407633</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>14224</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>298039</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>137633</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63BE548A-480F-BBA8-CAEE-B9B166E61A42}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6081069" y="194333"/>
-          <a:ext cx="500008" cy="483627"/>
+          <a:off x="0" y="8115300"/>
+          <a:ext cx="302722" cy="304800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7630,45 +7789,55 @@
           </a:ext>
         </a:extLst>
       </xdr:spPr>
-    </xdr:pic>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>270510</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>9690</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart 7">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBD8CD7C-1605-4206-AB52-CB0FB9E0DA59}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EC59970-DCE6-4024-A7A7-4B0E8616C836}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="205740" y="8115300"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -7984,28 +8153,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45076</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -8014,8 +8183,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8027,10 +8196,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8043,25 +8212,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8354,11 +8523,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8419,10 +8588,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>328</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8448,11 +8617,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -10726,27 +10895,27 @@
     <mergeCell ref="H14:I14"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D107">
-    <cfRule type="duplicateValues" dxfId="63" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E107">
-    <cfRule type="duplicateValues" dxfId="62" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="61" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="66" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L51">
-    <cfRule type="duplicateValues" dxfId="59" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M51">
-    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S24:S26">
-    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10781,34 +10950,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>45918</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10820,10 +10989,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10836,25 +11005,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11217,11 +11386,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11241,10 +11410,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>45918</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11264,10 +11433,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11284,11 +11453,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11628,14 +11797,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11655,11 +11824,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>320</v>
       </c>
@@ -11685,11 +11854,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11716,11 +11885,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
         <v>330</v>
       </c>
@@ -11748,11 +11917,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="85" t="s">
         <v>331</v>
       </c>
@@ -11778,11 +11947,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85" t="s">
         <v>333</v>
       </c>
@@ -11808,11 +11977,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85" t="s">
         <v>320</v>
       </c>
@@ -11830,11 +11999,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -11857,11 +12026,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -11882,8 +12051,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -11899,10 +12068,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -11922,10 +12091,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -11963,6 +12132,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -11979,32 +12157,23 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K6">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K22">
-    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12037,34 +12206,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>46016</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12076,10 +12245,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>350</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12092,25 +12261,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12404,11 +12573,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12428,10 +12597,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>46016</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12451,10 +12620,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>351</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12471,11 +12640,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12797,14 +12966,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12824,11 +12993,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -12846,11 +13015,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -12865,11 +13034,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -12885,11 +13054,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -12903,11 +13072,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -12921,11 +13090,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -12939,11 +13108,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -12962,11 +13131,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -12987,8 +13156,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -13004,10 +13173,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13027,10 +13196,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13068,11 +13237,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13084,32 +13257,28 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K6">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K22">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13128,7 +13297,7 @@
     <col min="1" max="1" width="3" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.88671875" style="6" customWidth="1"/>
     <col min="3" max="3" width="11.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
@@ -13142,50 +13311,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>46068</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
-        <v>-1022277</v>
-      </c>
-      <c r="K1" s="152"/>
+        <v>651715</v>
+      </c>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>1479045</v>
+        <v>1507045</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="str">
-        <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>70 days</v>
-      </c>
-      <c r="H2" s="156"/>
+      <c r="G2" s="153" t="s">
+        <v>364</v>
+      </c>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13193,30 +13361,30 @@
       </c>
       <c r="L2" s="12">
         <f>SUM(L5:L22)</f>
-        <v>456768</v>
+        <v>2158760</v>
       </c>
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13324,9 +13492,15 @@
       <c r="I6" s="21">
         <v>2</v>
       </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="5"/>
+      <c r="J6" s="4">
+        <v>46138</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1494217</v>
+      </c>
       <c r="M6" s="22"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -13356,9 +13530,15 @@
       <c r="I7" s="21">
         <v>3</v>
       </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="5"/>
+      <c r="J7" s="4">
+        <v>46138</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="L7" s="5">
+        <v>207775</v>
+      </c>
       <c r="M7" s="22"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -13473,11 +13653,15 @@
         <v>29560</v>
       </c>
       <c r="E11" s="22"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="46"/>
+      <c r="F11" s="48">
+        <v>46138</v>
+      </c>
+      <c r="G11" s="46">
+        <v>121</v>
+      </c>
       <c r="H11" s="49" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>71 days</v>
       </c>
       <c r="I11" s="21">
         <v>7</v>
@@ -13519,9 +13703,15 @@
       <c r="A13" s="41">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="5"/>
+      <c r="B13" s="7">
+        <v>46138</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D13" s="5">
+        <v>20000</v>
+      </c>
       <c r="E13" s="57"/>
       <c r="F13" s="48"/>
       <c r="G13" s="113"/>
@@ -13541,15 +13731,21 @@
       <c r="A14" s="41">
         <v>10</v>
       </c>
-      <c r="B14" s="132"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="7">
+        <v>46138</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D14" s="9">
+        <v>8000</v>
+      </c>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13569,10 +13765,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>46068</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13592,11 +13788,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="str">
-        <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>70 days</v>
-      </c>
-      <c r="H16" s="167"/>
+      <c r="G16" s="153" t="s">
+        <v>364</v>
+      </c>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13613,11 +13808,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -13763,11 +13958,15 @@
       <c r="C23" s="3"/>
       <c r="D23" s="5"/>
       <c r="E23" s="22"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="46"/>
+      <c r="F23" s="48">
+        <v>46138</v>
+      </c>
+      <c r="G23" s="46">
+        <v>90</v>
+      </c>
       <c r="H23" s="49" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>71 days</v>
       </c>
       <c r="I23" s="21">
         <v>19</v>
@@ -13956,14 +14155,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -13983,11 +14182,11 @@
       <c r="H33" s="62">
         <v>234</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>456768</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>355</v>
       </c>
@@ -13997,19 +14196,27 @@
       <c r="M33" s="15"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D34" s="15"/>
+      <c r="D34" s="15" t="s">
+        <v>201</v>
+      </c>
       <c r="E34" s="59">
         <f t="shared" ref="E34:E39" si="2">G34*F34</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="59"/>
-      <c r="G34" s="67"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="163">
+        <v>723967.2</v>
+      </c>
+      <c r="F34" s="59">
+        <v>121</v>
+      </c>
+      <c r="G34" s="67">
+        <v>5983.2</v>
+      </c>
+      <c r="H34" s="62">
+        <v>249</v>
+      </c>
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="163"/>
+        <v>1489816.8</v>
+      </c>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>356</v>
       </c>
@@ -14020,19 +14227,27 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B35" s="126"/>
-      <c r="D35" s="15"/>
+      <c r="D35" s="15" t="s">
+        <v>362</v>
+      </c>
       <c r="E35" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F35" s="59"/>
-      <c r="G35" s="67"/>
-      <c r="H35" s="62"/>
-      <c r="I35" s="163">
+        <v>4500</v>
+      </c>
+      <c r="F35" s="59">
+        <v>90</v>
+      </c>
+      <c r="G35" s="67">
+        <v>50</v>
+      </c>
+      <c r="H35" s="62">
+        <v>100</v>
+      </c>
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J35" s="163"/>
+        <v>5000</v>
+      </c>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
         <v>359</v>
       </c>
@@ -14044,37 +14259,57 @@
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D36" s="15"/>
+      <c r="D36" s="15" t="s">
+        <v>231</v>
+      </c>
       <c r="E36" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="59"/>
-      <c r="G36" s="67"/>
-      <c r="H36" s="62"/>
-      <c r="I36" s="163">
+        <v>64350</v>
+      </c>
+      <c r="F36" s="59">
+        <v>90</v>
+      </c>
+      <c r="G36" s="67">
+        <v>715</v>
+      </c>
+      <c r="H36" s="62">
+        <v>285</v>
+      </c>
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J36" s="163"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="136"/>
+        <v>203775</v>
+      </c>
+      <c r="J36" s="144"/>
+      <c r="K36" s="187" t="s">
+        <v>143</v>
+      </c>
+      <c r="L36" s="136">
+        <v>1000000</v>
+      </c>
       <c r="M36" s="15"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D37" s="15"/>
+      <c r="D37" s="15" t="s">
+        <v>363</v>
+      </c>
       <c r="E37" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F37" s="59"/>
-      <c r="G37" s="67"/>
-      <c r="H37" s="62"/>
-      <c r="I37" s="163">
+        <v>3600</v>
+      </c>
+      <c r="F37" s="59">
+        <v>90</v>
+      </c>
+      <c r="G37" s="67">
+        <v>40</v>
+      </c>
+      <c r="H37" s="62">
+        <v>100</v>
+      </c>
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J37" s="163"/>
+        <v>4000</v>
+      </c>
+      <c r="J37" s="144"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -14088,11 +14323,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -14106,11 +14341,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14121,25 +14356,25 @@
       </c>
       <c r="E40" s="60">
         <f>SUM(E33:E38)</f>
-        <v>255712</v>
+        <v>1052129.2</v>
       </c>
       <c r="F40" s="60"/>
       <c r="G40" s="84">
         <f>SUM(G33:G39)</f>
-        <v>1952</v>
+        <v>8740.2000000000007</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
-        <v>456768</v>
-      </c>
-      <c r="J40" s="170"/>
+        <v>2159359.7999999998</v>
+      </c>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
       <c r="L40" s="137">
         <f>SUM(L33:L39)</f>
-        <v>384000</v>
+        <v>1384000</v>
       </c>
       <c r="M40" s="15"/>
     </row>
@@ -14149,19 +14384,19 @@
       </c>
       <c r="E41" s="109" t="str">
         <f>CONCATENATE(ROUND((E40/E31)*100,2),"%")</f>
-        <v>31.96%</v>
+        <v>131.52%</v>
       </c>
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
       <c r="L41" s="105">
         <f>I40-L40</f>
-        <v>72768</v>
+        <v>775359.79999999981</v>
       </c>
       <c r="M41" s="15"/>
     </row>
@@ -14171,10 +14406,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59">
         <v>450000</v>
       </c>
@@ -14200,10 +14435,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="172" t="s">
+      <c r="A44" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="172"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="59">
         <v>100000</v>
       </c>
@@ -14244,11 +14479,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14260,6 +14499,1237 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
+  </mergeCells>
+  <conditionalFormatting sqref="J1:K1">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5">
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6">
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7:K22">
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L5:L22">
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;8&amp;K000000 INTERNAL USE</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC6FD52-3033-4087-B599-2D13A03E21B7}">
+  <dimension ref="A1:M56"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5546875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="161" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="151">
+        <v>46068</v>
+      </c>
+      <c r="H1" s="152"/>
+      <c r="I1" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="164">
+        <f>L2-D2</f>
+        <v>679715</v>
+      </c>
+      <c r="K1" s="165"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="19"/>
+    </row>
+    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="12">
+        <f>SUM(D5:D30)</f>
+        <v>1479045</v>
+      </c>
+      <c r="E2" s="20"/>
+      <c r="F2" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" s="153" t="str">
+        <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
+        <v>71 days</v>
+      </c>
+      <c r="H2" s="168"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="12">
+        <f>SUM(L5:L22)</f>
+        <v>2158760</v>
+      </c>
+      <c r="M2" s="20"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="169" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
+        <v>117</v>
+      </c>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="103" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="103" t="s">
+        <v>100</v>
+      </c>
+      <c r="I4" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="41">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7">
+        <v>46068</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="9">
+        <v>256000</v>
+      </c>
+      <c r="E5" s="23"/>
+      <c r="F5" s="45">
+        <v>46124</v>
+      </c>
+      <c r="G5" s="46">
+        <v>166</v>
+      </c>
+      <c r="H5" s="49" t="str">
+        <f>IF(ISBLANK(F5),"",CONCATENATE(F5-$G$1+1," days"))</f>
+        <v>57 days</v>
+      </c>
+      <c r="I5" s="21">
+        <v>1</v>
+      </c>
+      <c r="J5" s="45">
+        <v>46132</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="L5" s="5">
+        <v>456768</v>
+      </c>
+      <c r="M5" s="22"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="41">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7">
+        <v>46068</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D6" s="5">
+        <v>33000</v>
+      </c>
+      <c r="E6" s="23"/>
+      <c r="F6" s="45">
+        <v>46127</v>
+      </c>
+      <c r="G6" s="46">
+        <v>150</v>
+      </c>
+      <c r="H6" s="49" t="str">
+        <f t="shared" ref="H6:H13" si="0">IF(ISBLANK(F6),"",CONCATENATE(F6-$G$1+1," days"))</f>
+        <v>60 days</v>
+      </c>
+      <c r="I6" s="21">
+        <v>2</v>
+      </c>
+      <c r="J6" s="4">
+        <v>46138</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1494217</v>
+      </c>
+      <c r="M6" s="22"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="41">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7">
+        <v>46072</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="5">
+        <v>38672</v>
+      </c>
+      <c r="E7" s="23"/>
+      <c r="F7" s="45">
+        <v>46131</v>
+      </c>
+      <c r="G7" s="46">
+        <v>133</v>
+      </c>
+      <c r="H7" s="49" t="str">
+        <f t="shared" si="0"/>
+        <v>64 days</v>
+      </c>
+      <c r="I7" s="21">
+        <v>3</v>
+      </c>
+      <c r="J7" s="4">
+        <v>46138</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="L7" s="5">
+        <v>207775</v>
+      </c>
+      <c r="M7" s="22"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="41">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7">
+        <v>46067</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="5">
+        <v>15813</v>
+      </c>
+      <c r="E8" s="22"/>
+      <c r="F8" s="45">
+        <v>46132</v>
+      </c>
+      <c r="G8" s="46">
+        <v>131</v>
+      </c>
+      <c r="H8" s="49" t="str">
+        <f t="shared" si="0"/>
+        <v>65 days</v>
+      </c>
+      <c r="I8" s="21">
+        <v>4</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="22"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="41">
+        <v>5</v>
+      </c>
+      <c r="B9" s="132">
+        <v>46107</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" s="9">
+        <v>6000</v>
+      </c>
+      <c r="E9" s="22"/>
+      <c r="F9" s="48">
+        <v>46136</v>
+      </c>
+      <c r="G9" s="46">
+        <v>126</v>
+      </c>
+      <c r="H9" s="49" t="str">
+        <f t="shared" si="0"/>
+        <v>69 days</v>
+      </c>
+      <c r="I9" s="21">
+        <v>5</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="22"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="41">
+        <v>6</v>
+      </c>
+      <c r="B10" s="132">
+        <v>46111</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="F10" s="48">
+        <v>46137</v>
+      </c>
+      <c r="G10" s="46">
+        <v>125</v>
+      </c>
+      <c r="H10" s="49" t="str">
+        <f t="shared" si="0"/>
+        <v>70 days</v>
+      </c>
+      <c r="I10" s="21">
+        <v>6</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="22"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="41">
+        <v>7</v>
+      </c>
+      <c r="B11" s="7">
+        <v>46127</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="5">
+        <v>29560</v>
+      </c>
+      <c r="E11" s="22"/>
+      <c r="F11" s="48">
+        <v>46138</v>
+      </c>
+      <c r="G11" s="46">
+        <v>121</v>
+      </c>
+      <c r="H11" s="49" t="str">
+        <f t="shared" si="0"/>
+        <v>71 days</v>
+      </c>
+      <c r="I11" s="21">
+        <v>7</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="22"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="41">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7">
+        <v>46127</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="5">
+        <v>100000</v>
+      </c>
+      <c r="E12" s="57"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="113"/>
+      <c r="H12" s="125" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I12" s="41">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="22"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="41">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="113"/>
+      <c r="H13" s="125" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I13" s="41">
+        <v>9</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="22"/>
+    </row>
+    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="41">
+        <v>10</v>
+      </c>
+      <c r="B14" s="132"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="148" t="s">
+        <v>140</v>
+      </c>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="21">
+        <v>10</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="22"/>
+    </row>
+    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="41">
+        <v>11</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="151">
+        <v>46068</v>
+      </c>
+      <c r="H15" s="152"/>
+      <c r="I15" s="21">
+        <v>11</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="22"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="41">
+        <v>12</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="153" t="str">
+        <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
+        <v>71 days</v>
+      </c>
+      <c r="H16" s="154"/>
+      <c r="I16" s="21">
+        <v>12</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="22"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="41">
+        <v>13</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="155" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="21">
+        <v>13</v>
+      </c>
+      <c r="J17" s="2"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="22"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="41">
+        <v>14</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I18" s="41">
+        <v>14</v>
+      </c>
+      <c r="J18" s="2"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="22"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="41">
+        <v>15</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="45">
+        <v>46124</v>
+      </c>
+      <c r="G19" s="46">
+        <v>135</v>
+      </c>
+      <c r="H19" s="49" t="str">
+        <f>IF(ISBLANK(F19),"",CONCATENATE(F19-$G$15+1," days"))</f>
+        <v>57 days</v>
+      </c>
+      <c r="I19" s="21">
+        <v>15</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="22"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="41">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="45">
+        <v>46131</v>
+      </c>
+      <c r="G20" s="46">
+        <v>97</v>
+      </c>
+      <c r="H20" s="49" t="str">
+        <f t="shared" ref="H20:H25" si="1">IF(ISBLANK(F20),"",CONCATENATE(F20-$G$15+1," days"))</f>
+        <v>64 days</v>
+      </c>
+      <c r="I20" s="21">
+        <v>16</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="22"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="41">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="48">
+        <v>46136</v>
+      </c>
+      <c r="G21" s="46">
+        <v>85</v>
+      </c>
+      <c r="H21" s="49" t="str">
+        <f t="shared" si="1"/>
+        <v>69 days</v>
+      </c>
+      <c r="I21" s="21">
+        <v>17</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="22"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="41">
+        <v>18</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="48">
+        <v>46137</v>
+      </c>
+      <c r="G22" s="46">
+        <v>76</v>
+      </c>
+      <c r="H22" s="49" t="str">
+        <f t="shared" si="1"/>
+        <v>70 days</v>
+      </c>
+      <c r="I22" s="21">
+        <v>18</v>
+      </c>
+      <c r="J22" s="2"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="22"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="41">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="48">
+        <v>46138</v>
+      </c>
+      <c r="G23" s="46">
+        <v>90</v>
+      </c>
+      <c r="H23" s="49" t="str">
+        <f t="shared" si="1"/>
+        <v>71 days</v>
+      </c>
+      <c r="I23" s="21">
+        <v>19</v>
+      </c>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="34"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="41">
+        <v>20</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="49" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I24" s="21">
+        <v>20</v>
+      </c>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="34"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="41">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="49" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I25" s="21">
+        <v>21</v>
+      </c>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="34"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="41">
+        <v>22</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="21">
+        <v>22</v>
+      </c>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="34"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" s="41">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="21">
+        <v>23</v>
+      </c>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="34"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="41">
+        <v>24</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="21">
+        <v>24</v>
+      </c>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="34"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="41">
+        <v>25</v>
+      </c>
+      <c r="B29" s="71"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="75"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="21">
+        <v>25</v>
+      </c>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="70"/>
+      <c r="M29" s="78"/>
+    </row>
+    <row r="30" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="79"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="70"/>
+      <c r="M30" s="78"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="24"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="66" t="s">
+        <v>149</v>
+      </c>
+      <c r="E31" s="86">
+        <f>G31+I31</f>
+        <v>800000</v>
+      </c>
+      <c r="F31" s="93" t="s">
+        <v>274</v>
+      </c>
+      <c r="G31" s="86">
+        <v>700000</v>
+      </c>
+      <c r="H31" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="I31" s="86">
+        <v>100000</v>
+      </c>
+      <c r="J31" s="86"/>
+      <c r="K31" s="100"/>
+      <c r="L31" s="135"/>
+      <c r="M31" s="15"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D32" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" s="93" t="s">
+        <v>136</v>
+      </c>
+      <c r="F32" s="93" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" s="93" t="s">
+        <v>181</v>
+      </c>
+      <c r="H32" s="93" t="s">
+        <v>147</v>
+      </c>
+      <c r="I32" s="158" t="s">
+        <v>148</v>
+      </c>
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
+        <v>246</v>
+      </c>
+      <c r="L32" s="160"/>
+      <c r="M32" s="15"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D33" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="E33" s="59">
+        <f>G33*F33</f>
+        <v>255712</v>
+      </c>
+      <c r="F33" s="59">
+        <v>131</v>
+      </c>
+      <c r="G33" s="67">
+        <v>1952</v>
+      </c>
+      <c r="H33" s="62">
+        <v>234</v>
+      </c>
+      <c r="I33" s="144">
+        <f>G33*H33</f>
+        <v>456768</v>
+      </c>
+      <c r="J33" s="144"/>
+      <c r="K33" s="85" t="s">
+        <v>355</v>
+      </c>
+      <c r="L33" s="136">
+        <v>134000</v>
+      </c>
+      <c r="M33" s="15"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D34" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="E34" s="59">
+        <f t="shared" ref="E34:E39" si="2">G34*F34</f>
+        <v>723967.2</v>
+      </c>
+      <c r="F34" s="59">
+        <v>121</v>
+      </c>
+      <c r="G34" s="67">
+        <v>5983.2</v>
+      </c>
+      <c r="H34" s="62">
+        <v>249</v>
+      </c>
+      <c r="I34" s="144">
+        <f t="shared" ref="I34:I39" si="3">G34*H34</f>
+        <v>1489816.8</v>
+      </c>
+      <c r="J34" s="144"/>
+      <c r="K34" s="85" t="s">
+        <v>356</v>
+      </c>
+      <c r="L34" s="136">
+        <v>200000</v>
+      </c>
+      <c r="M34" s="15"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B35" s="126"/>
+      <c r="D35" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="E35" s="59">
+        <f t="shared" si="2"/>
+        <v>4500</v>
+      </c>
+      <c r="F35" s="59">
+        <v>90</v>
+      </c>
+      <c r="G35" s="67">
+        <v>50</v>
+      </c>
+      <c r="H35" s="62">
+        <v>100</v>
+      </c>
+      <c r="I35" s="144">
+        <f t="shared" si="3"/>
+        <v>5000</v>
+      </c>
+      <c r="J35" s="144"/>
+      <c r="K35" s="85" t="s">
+        <v>359</v>
+      </c>
+      <c r="L35" s="136">
+        <v>50000</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D36" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="E36" s="59">
+        <f t="shared" si="2"/>
+        <v>64350</v>
+      </c>
+      <c r="F36" s="59">
+        <v>90</v>
+      </c>
+      <c r="G36" s="67">
+        <v>715</v>
+      </c>
+      <c r="H36" s="62">
+        <v>285</v>
+      </c>
+      <c r="I36" s="144">
+        <f t="shared" si="3"/>
+        <v>203775</v>
+      </c>
+      <c r="J36" s="144"/>
+      <c r="K36" s="187" t="s">
+        <v>143</v>
+      </c>
+      <c r="L36" s="136">
+        <v>1000000</v>
+      </c>
+      <c r="M36" s="15"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D37" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="E37" s="59">
+        <f t="shared" si="2"/>
+        <v>3600</v>
+      </c>
+      <c r="F37" s="59">
+        <v>90</v>
+      </c>
+      <c r="G37" s="67">
+        <v>40</v>
+      </c>
+      <c r="H37" s="62">
+        <v>100</v>
+      </c>
+      <c r="I37" s="144">
+        <f t="shared" si="3"/>
+        <v>4000</v>
+      </c>
+      <c r="J37" s="144"/>
+      <c r="K37" s="85"/>
+      <c r="L37" s="136"/>
+      <c r="M37" s="15"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D38" s="15"/>
+      <c r="E38" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="59"/>
+      <c r="G38" s="67"/>
+      <c r="H38" s="62"/>
+      <c r="I38" s="144">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="144"/>
+      <c r="K38" s="85"/>
+      <c r="L38" s="136"/>
+      <c r="M38" s="15"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D39" s="15"/>
+      <c r="E39" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="59"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="62"/>
+      <c r="I39" s="144">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="144"/>
+      <c r="K39" s="85"/>
+      <c r="L39" s="136"/>
+      <c r="M39" s="15"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D40" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="E40" s="60">
+        <f>SUM(E33:E38)</f>
+        <v>1052129.2</v>
+      </c>
+      <c r="F40" s="60"/>
+      <c r="G40" s="84">
+        <f>SUM(G33:G39)</f>
+        <v>8740.2000000000007</v>
+      </c>
+      <c r="H40" s="52"/>
+      <c r="I40" s="145">
+        <f>SUM(I33:I39)</f>
+        <v>2159359.7999999998</v>
+      </c>
+      <c r="J40" s="145"/>
+      <c r="K40" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="L40" s="137">
+        <f>SUM(L33:L39)</f>
+        <v>1384000</v>
+      </c>
+      <c r="M40" s="15"/>
+    </row>
+    <row r="41" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D41" s="52" t="s">
+        <v>214</v>
+      </c>
+      <c r="E41" s="109" t="str">
+        <f>CONCATENATE(ROUND((E40/E31)*100,2),"%")</f>
+        <v>131.52%</v>
+      </c>
+      <c r="F41" s="15"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="83" t="s">
+        <v>175</v>
+      </c>
+      <c r="L41" s="105">
+        <f>I40-L40</f>
+        <v>775359.79999999981</v>
+      </c>
+      <c r="M41" s="15"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C42" s="40"/>
+      <c r="K42" s="68"/>
+      <c r="L42" s="40"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" s="147" t="s">
+        <v>288</v>
+      </c>
+      <c r="B43" s="147"/>
+      <c r="C43" s="59">
+        <v>450000</v>
+      </c>
+      <c r="D43" s="15">
+        <v>126</v>
+      </c>
+      <c r="E43" s="131">
+        <f>C43/D43</f>
+        <v>3571.4285714285716</v>
+      </c>
+      <c r="F43" s="62">
+        <v>250</v>
+      </c>
+      <c r="G43" s="101">
+        <f>E43*F43</f>
+        <v>892857.14285714284</v>
+      </c>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="15"/>
+      <c r="M43" s="15"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" s="147" t="s">
+        <v>288</v>
+      </c>
+      <c r="B44" s="147"/>
+      <c r="C44" s="59">
+        <v>100000</v>
+      </c>
+      <c r="D44" s="15">
+        <v>76</v>
+      </c>
+      <c r="E44" s="131">
+        <f>C44/D44</f>
+        <v>1315.7894736842106</v>
+      </c>
+      <c r="F44" s="62">
+        <v>300</v>
+      </c>
+      <c r="G44" s="101">
+        <f>E44*F44</f>
+        <v>394736.8421052632</v>
+      </c>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="15"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="G45" s="111">
+        <f>G43+G44</f>
+        <v>1287593.9849624061</v>
+      </c>
+    </row>
+    <row r="54" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="E54" s="40"/>
+    </row>
+    <row r="56" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="I56" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:H1"/>
@@ -14299,7 +15769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6D7927-4220-4E4C-ACDC-68E20558EC44}">
   <dimension ref="A1:V35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -14354,7 +15824,7 @@
       <c r="M1" s="186"/>
       <c r="N1" s="182" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>3 year, 0 months, 24 days</v>
+        <v>3 year, 0 months, 25 days</v>
       </c>
       <c r="O1" s="183"/>
       <c r="P1" s="183"/>
@@ -14767,23 +16237,23 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>-1022277</v>
+        <v>651715</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
-        <v>456768</v>
+        <v>2158760</v>
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
-        <v>1479045</v>
+        <v>1507045</v>
       </c>
       <c r="G13" s="143">
         <f>MIN('Term-12'!G6:G14)</f>
-        <v>125</v>
-      </c>
-      <c r="H13" s="141" cm="1">
-        <f t="array" ref="H13:I13">'Term-12'!G3:H3</f>
-        <v>0</v>
+        <v>121</v>
+      </c>
+      <c r="H13" s="141" t="str" cm="1">
+        <f t="array" ref="H13:I13">'Term-12'!G2:H2</f>
+        <v>71 days</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -14929,15 +16399,15 @@
       <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>2568940</v>
+        <v>4242932</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
-        <v>17877562</v>
+        <v>19579554</v>
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
-        <v>15308622</v>
+        <v>15336622</v>
       </c>
       <c r="G25" s="143"/>
       <c r="H25" s="89"/>
@@ -15022,7 +16492,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>-1491999.5</v>
+        <v>181992.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -15053,7 +16523,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>2568940</v>
+        <v>4242932</v>
       </c>
     </row>
   </sheetData>
@@ -15068,7 +16538,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F397FBE2-11C6-4994-AF06-5D9D4133A216}">
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -15302,28 +16772,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45163</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -15332,8 +16802,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -15345,10 +16815,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>353</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -15361,25 +16831,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -15626,11 +17096,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -15651,10 +17121,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="149">
+      <c r="H13" s="151">
         <v>45163</v>
       </c>
-      <c r="I13" s="150"/>
+      <c r="I13" s="152"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -15675,10 +17145,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>353</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -15696,11 +17166,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17464,6 +18934,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17472,35 +18948,29 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
-    <cfRule type="duplicateValues" dxfId="56" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E106">
-    <cfRule type="duplicateValues" dxfId="55" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="54" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L51">
-    <cfRule type="duplicateValues" dxfId="52" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M51">
-    <cfRule type="duplicateValues" dxfId="51" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S24:S26">
-    <cfRule type="duplicateValues" dxfId="50" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -17534,28 +19004,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45163</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17564,8 +19034,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17577,10 +19047,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>354</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17593,25 +19063,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17854,11 +19324,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="165"/>
-      <c r="I12" s="166"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17879,10 +19349,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="149">
+      <c r="H13" s="151">
         <v>45163</v>
       </c>
-      <c r="I13" s="150"/>
+      <c r="I13" s="152"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17903,10 +19373,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="155" t="s">
+      <c r="H14" s="153" t="s">
         <v>354</v>
       </c>
-      <c r="I14" s="156"/>
+      <c r="I14" s="168"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17924,11 +19394,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -19708,27 +21178,27 @@
     <mergeCell ref="G15:I15"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
-    <cfRule type="duplicateValues" dxfId="49" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E106">
-    <cfRule type="duplicateValues" dxfId="48" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="53" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L51">
-    <cfRule type="duplicateValues" dxfId="45" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M51">
-    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S24:S26">
-    <cfRule type="duplicateValues" dxfId="43" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -19762,28 +21232,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45345</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -19792,8 +21262,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19805,10 +21275,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>342</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19821,25 +21291,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -20181,11 +21651,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -20206,10 +21676,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45345</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -20251,11 +21721,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20492,10 +21962,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="169" t="s">
+      <c r="J28" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="169"/>
+      <c r="K28" s="158"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -20514,11 +21984,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="163">
+      <c r="J29" s="144">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="163"/>
+      <c r="K29" s="144"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -20543,11 +22013,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="163">
+      <c r="J30" s="144">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="163"/>
+      <c r="K30" s="144"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -20572,11 +22042,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="163">
+      <c r="J31" s="144">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="163"/>
+      <c r="K31" s="144"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -20601,11 +22071,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="163">
+      <c r="J32" s="144">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="163"/>
+      <c r="K32" s="144"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -20630,11 +22100,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -20658,11 +22128,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -20686,11 +22156,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -20712,11 +22182,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="170">
+      <c r="J36" s="145">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="170"/>
+      <c r="K36" s="145"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -20735,8 +22205,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="171"/>
-      <c r="K37" s="171"/>
+      <c r="J37" s="146"/>
+      <c r="K37" s="146"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -20785,6 +22255,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="J29:K29"/>
@@ -20794,34 +22278,20 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="G17:I17"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="42" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="40" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="39" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="21"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20855,35 +22325,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45477</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20895,10 +22365,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>343</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20911,25 +22381,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -21263,11 +22733,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21290,10 +22760,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45477</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21339,11 +22809,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21709,14 +23179,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -21741,11 +23211,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>172</v>
       </c>
@@ -21773,11 +23243,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>173</v>
       </c>
@@ -21809,11 +23279,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>173</v>
       </c>
@@ -21834,11 +23304,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="170">
+      <c r="J36" s="145">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="170"/>
+      <c r="K36" s="145"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -21855,11 +23325,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>179</v>
       </c>
@@ -21876,11 +23346,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -21897,11 +23367,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -21919,11 +23389,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -21938,8 +23408,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="52" t="s">
         <v>174</v>
       </c>
@@ -22010,6 +23480,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -22026,30 +23506,20 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="38" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="36" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="35" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -22084,35 +23554,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45548</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -22124,10 +23594,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22140,25 +23610,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22532,11 +24002,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22563,10 +24033,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45561</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22593,10 +24063,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22620,11 +24090,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22989,14 +24459,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -23015,11 +24485,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -23044,11 +24514,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -23073,11 +24543,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -23094,11 +24564,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>172</v>
       </c>
@@ -23115,11 +24585,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -23136,11 +24606,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23160,11 +24630,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -23216,11 +24686,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="170">
+      <c r="J42" s="145">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="170"/>
+      <c r="K42" s="145"/>
       <c r="L42" s="52" t="s">
         <v>174</v>
       </c>
@@ -23240,8 +24710,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="171"/>
-      <c r="K43" s="171"/>
+      <c r="J43" s="146"/>
+      <c r="K43" s="146"/>
       <c r="L43" s="83" t="s">
         <v>175</v>
       </c>
@@ -23256,11 +24726,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="172" t="s">
+      <c r="A45" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B45" s="172"/>
-      <c r="C45" s="172"/>
+      <c r="B45" s="147"/>
+      <c r="C45" s="147"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -23377,6 +24847,19 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -23391,33 +24874,20 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="31" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -23452,35 +24922,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45631</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23492,10 +24962,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23508,25 +24978,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23866,11 +25336,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23891,10 +25361,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45653</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23915,10 +25385,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>346</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23936,11 +25406,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24286,14 +25756,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24312,11 +25782,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -24341,11 +25811,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>215</v>
       </c>
@@ -24370,11 +25840,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>215</v>
       </c>
@@ -24391,11 +25861,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -24412,11 +25882,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24433,11 +25903,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24454,11 +25924,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -24476,11 +25946,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -24500,8 +25970,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -24516,11 +25986,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="147"/>
+      <c r="C43" s="147"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -24668,23 +26138,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -24693,23 +26146,40 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="30" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5">
-    <cfRule type="duplicateValues" dxfId="28" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L22">
-    <cfRule type="duplicateValues" dxfId="27" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="26" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -24744,35 +26214,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="161" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="149">
+      <c r="H1" s="151">
         <v>45714</v>
       </c>
-      <c r="I1" s="150"/>
+      <c r="I1" s="152"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="151">
+      <c r="K1" s="164">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="152"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="167"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24784,10 +26254,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="155" t="s">
+      <c r="H2" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="156"/>
+      <c r="I2" s="168"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24800,25 +26270,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="161" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="157" t="s">
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="160"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -25160,11 +26630,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="164" t="s">
+      <c r="G14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="165"/>
-      <c r="I14" s="166"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="150"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25187,10 +26657,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="149">
+      <c r="H15" s="151">
         <v>45743</v>
       </c>
-      <c r="I15" s="150"/>
+      <c r="I15" s="152"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25213,10 +26683,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="153" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="167"/>
+      <c r="I16" s="154"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25236,11 +26706,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="161" t="s">
+      <c r="G17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="162"/>
-      <c r="I17" s="168"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="157"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25580,14 +27050,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="169" t="s">
+      <c r="J32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="144" t="s">
+      <c r="K32" s="158"/>
+      <c r="L32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="144"/>
+      <c r="M32" s="159"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25606,11 +27076,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="163">
+      <c r="J33" s="144">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="163"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="85" t="s">
         <v>257</v>
       </c>
@@ -25635,11 +27105,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="163">
+      <c r="J34" s="144">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="163"/>
+      <c r="K34" s="144"/>
       <c r="L34" s="85" t="s">
         <v>262</v>
       </c>
@@ -25665,11 +27135,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="163">
+      <c r="J35" s="144">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="163"/>
+      <c r="K35" s="144"/>
       <c r="L35" s="85" t="s">
         <v>263</v>
       </c>
@@ -25694,11 +27164,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="163">
+      <c r="J36" s="144">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="163"/>
+      <c r="K36" s="144"/>
       <c r="L36" s="85" t="s">
         <v>264</v>
       </c>
@@ -25714,11 +27184,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="163">
+      <c r="J37" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="163"/>
+      <c r="K37" s="144"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -25731,11 +27201,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="163">
+      <c r="J38" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="163"/>
+      <c r="K38" s="144"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -25748,11 +27218,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="163">
+      <c r="J39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="163"/>
+      <c r="K39" s="144"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25770,11 +27240,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="170">
+      <c r="J40" s="145">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="170"/>
+      <c r="K40" s="145"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -25794,8 +27264,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -25810,11 +27280,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="147"/>
+      <c r="C43" s="147"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -25846,6 +27316,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25854,40 +27341,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5">
-    <cfRule type="duplicateValues" dxfId="23" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L22">
-    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M22">
-    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -25920,34 +27390,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="161" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="148"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="149">
+      <c r="G1" s="151">
         <v>45840</v>
       </c>
-      <c r="H1" s="150"/>
+      <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="151">
+      <c r="J1" s="164">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="152"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="153"/>
-      <c r="B2" s="154"/>
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -25959,10 +27429,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="153" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="156"/>
+      <c r="H2" s="168"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -25975,25 +27445,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161" t="s">
+      <c r="B3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="160"/>
+      <c r="J3" s="170"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="172"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -26311,11 +27781,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="164" t="s">
+      <c r="F14" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="166"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -26335,10 +27805,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="149">
+      <c r="G15" s="151">
         <v>45840</v>
       </c>
-      <c r="H15" s="150"/>
+      <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -26358,10 +27828,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="155" t="s">
+      <c r="G16" s="153" t="s">
         <v>291</v>
       </c>
-      <c r="H16" s="167"/>
+      <c r="H16" s="154"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -26378,11 +27848,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="161" t="s">
+      <c r="F17" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="162"/>
-      <c r="H17" s="168"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="157"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -26738,14 +28208,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="169" t="s">
+      <c r="I32" s="158" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="144" t="s">
+      <c r="J32" s="158"/>
+      <c r="K32" s="159" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="144"/>
+      <c r="L32" s="159"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -26764,11 +28234,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="163">
+      <c r="I33" s="144">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="163"/>
+      <c r="J33" s="144"/>
       <c r="K33" s="85" t="s">
         <v>287</v>
       </c>
@@ -26793,11 +28263,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="163">
+      <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="163"/>
+      <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
         <v>290</v>
       </c>
@@ -26823,11 +28293,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="163">
+      <c r="I35" s="144">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="163"/>
+      <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
         <v>294</v>
       </c>
@@ -26852,11 +28322,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="163">
+      <c r="I36" s="144">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="163"/>
+      <c r="J36" s="144"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -26881,11 +28351,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="163">
+      <c r="I37" s="144">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="163"/>
+      <c r="J37" s="144"/>
       <c r="K37" s="85" t="s">
         <v>295</v>
       </c>
@@ -26910,11 +28380,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="163">
+      <c r="I38" s="144">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="163"/>
+      <c r="J38" s="144"/>
       <c r="K38" s="85" t="s">
         <v>297</v>
       </c>
@@ -26931,11 +28401,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="163">
+      <c r="I39" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="163"/>
+      <c r="J39" s="144"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -26953,11 +28423,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="170">
+      <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="170"/>
+      <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -26977,8 +28447,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -26993,10 +28463,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="172" t="s">
+      <c r="A43" s="147" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="172"/>
+      <c r="B43" s="147"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -27036,6 +28506,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -27044,40 +28531,23 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K22">
-    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
-    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A92DA6B-C793-4853-A63D-C7D64001D34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E97C2C5-022A-4984-9CA6-0CC0F538FF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Term-1" sheetId="4" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="367">
   <si>
     <t>#</t>
   </si>
@@ -14566,16 +14566,14 @@
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
-        <v>46068</v>
-      </c>
+      <c r="G1" s="151"/>
       <c r="H1" s="152"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
       <c r="J1" s="164">
         <f>L2-D2</f>
-        <v>679715</v>
+        <v>0</v>
       </c>
       <c r="K1" s="165"/>
       <c r="L1" s="18"/>
@@ -14589,7 +14587,7 @@
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>1479045</v>
+        <v>0</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
@@ -14597,7 +14595,7 @@
       </c>
       <c r="G2" s="153" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>71 days</v>
+        <v/>
       </c>
       <c r="H2" s="168"/>
       <c r="I2" s="38"/>
@@ -14607,7 +14605,7 @@
       </c>
       <c r="L2" s="12">
         <f>SUM(L5:L22)</f>
-        <v>2158760</v>
+        <v>0</v>
       </c>
       <c r="M2" s="20"/>
     </row>
@@ -14677,139 +14675,81 @@
       <c r="A5" s="41">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
-        <v>46068</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="9">
-        <v>256000</v>
-      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="23"/>
-      <c r="F5" s="45">
-        <v>46124</v>
-      </c>
-      <c r="G5" s="46">
-        <v>166</v>
-      </c>
+      <c r="F5" s="45"/>
+      <c r="G5" s="46"/>
       <c r="H5" s="49" t="str">
         <f>IF(ISBLANK(F5),"",CONCATENATE(F5-$G$1+1," days"))</f>
-        <v>57 days</v>
+        <v/>
       </c>
       <c r="I5" s="21">
         <v>1</v>
       </c>
-      <c r="J5" s="45">
-        <v>46132</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="L5" s="5">
-        <v>456768</v>
-      </c>
+      <c r="J5" s="45"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="5"/>
       <c r="M5" s="22"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="41">
         <v>2</v>
       </c>
-      <c r="B6" s="7">
-        <v>46068</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D6" s="5">
-        <v>33000</v>
-      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="23"/>
-      <c r="F6" s="45">
-        <v>46127</v>
-      </c>
-      <c r="G6" s="46">
-        <v>150</v>
-      </c>
+      <c r="F6" s="45"/>
+      <c r="G6" s="46"/>
       <c r="H6" s="49" t="str">
         <f t="shared" ref="H6:H13" si="0">IF(ISBLANK(F6),"",CONCATENATE(F6-$G$1+1," days"))</f>
-        <v>60 days</v>
+        <v/>
       </c>
       <c r="I6" s="21">
         <v>2</v>
       </c>
-      <c r="J6" s="4">
-        <v>46138</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1494217</v>
-      </c>
+      <c r="J6" s="4"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="5"/>
       <c r="M6" s="22"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="41">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
-        <v>46072</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" s="5">
-        <v>38672</v>
-      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="23"/>
-      <c r="F7" s="45">
-        <v>46131</v>
-      </c>
-      <c r="G7" s="46">
-        <v>133</v>
-      </c>
+      <c r="F7" s="45"/>
+      <c r="G7" s="46"/>
       <c r="H7" s="49" t="str">
         <f t="shared" si="0"/>
-        <v>64 days</v>
+        <v/>
       </c>
       <c r="I7" s="21">
         <v>3</v>
       </c>
-      <c r="J7" s="4">
-        <v>46138</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="L7" s="5">
-        <v>207775</v>
-      </c>
+      <c r="J7" s="4"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="5"/>
       <c r="M7" s="22"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <v>4</v>
       </c>
-      <c r="B8" s="7">
-        <v>46067</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" s="5">
-        <v>15813</v>
-      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="22"/>
-      <c r="F8" s="45">
-        <v>46132</v>
-      </c>
-      <c r="G8" s="46">
-        <v>131</v>
-      </c>
+      <c r="F8" s="45"/>
+      <c r="G8" s="46"/>
       <c r="H8" s="49" t="str">
         <f t="shared" si="0"/>
-        <v>65 days</v>
+        <v/>
       </c>
       <c r="I8" s="21">
         <v>4</v>
@@ -14823,25 +14763,15 @@
       <c r="A9" s="41">
         <v>5</v>
       </c>
-      <c r="B9" s="132">
-        <v>46107</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="D9" s="9">
-        <v>6000</v>
-      </c>
+      <c r="B9" s="132"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="9"/>
       <c r="E9" s="22"/>
-      <c r="F9" s="48">
-        <v>46136</v>
-      </c>
-      <c r="G9" s="46">
-        <v>126</v>
-      </c>
+      <c r="F9" s="48"/>
+      <c r="G9" s="46"/>
       <c r="H9" s="49" t="str">
         <f t="shared" si="0"/>
-        <v>69 days</v>
+        <v/>
       </c>
       <c r="I9" s="21">
         <v>5</v>
@@ -14855,27 +14785,15 @@
       <c r="A10" s="41">
         <v>6</v>
       </c>
-      <c r="B10" s="132">
-        <v>46111</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="9">
-        <v>1000000</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>358</v>
-      </c>
-      <c r="F10" s="48">
-        <v>46137</v>
-      </c>
-      <c r="G10" s="46">
-        <v>125</v>
-      </c>
+      <c r="B10" s="132"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="46"/>
       <c r="H10" s="49" t="str">
         <f t="shared" si="0"/>
-        <v>70 days</v>
+        <v/>
       </c>
       <c r="I10" s="21">
         <v>6</v>
@@ -14889,25 +14807,15 @@
       <c r="A11" s="41">
         <v>7</v>
       </c>
-      <c r="B11" s="7">
-        <v>46127</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" s="5">
-        <v>29560</v>
-      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="22"/>
-      <c r="F11" s="48">
-        <v>46138</v>
-      </c>
-      <c r="G11" s="46">
-        <v>121</v>
-      </c>
+      <c r="F11" s="48"/>
+      <c r="G11" s="46"/>
       <c r="H11" s="49" t="str">
         <f t="shared" si="0"/>
-        <v>71 days</v>
+        <v/>
       </c>
       <c r="I11" s="21">
         <v>7</v>
@@ -14921,15 +14829,9 @@
       <c r="A12" s="41">
         <v>8</v>
       </c>
-      <c r="B12" s="7">
-        <v>46127</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D12" s="5">
-        <v>100000</v>
-      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="5"/>
       <c r="E12" s="57"/>
       <c r="F12" s="48"/>
       <c r="G12" s="113"/>
@@ -14999,9 +14901,7 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
-        <v>46068</v>
-      </c>
+      <c r="G15" s="151"/>
       <c r="H15" s="152"/>
       <c r="I15" s="21">
         <v>11</v>
@@ -15024,7 +14924,7 @@
       </c>
       <c r="G16" s="153" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>71 days</v>
+        <v/>
       </c>
       <c r="H16" s="154"/>
       <c r="I16" s="21">
@@ -15089,15 +14989,11 @@
       <c r="C19" s="3"/>
       <c r="D19" s="5"/>
       <c r="E19" s="22"/>
-      <c r="F19" s="45">
-        <v>46124</v>
-      </c>
-      <c r="G19" s="46">
-        <v>135</v>
-      </c>
+      <c r="F19" s="45"/>
+      <c r="G19" s="46"/>
       <c r="H19" s="49" t="str">
         <f>IF(ISBLANK(F19),"",CONCATENATE(F19-$G$15+1," days"))</f>
-        <v>57 days</v>
+        <v/>
       </c>
       <c r="I19" s="21">
         <v>15</v>
@@ -15115,15 +15011,11 @@
       <c r="C20" s="3"/>
       <c r="D20" s="5"/>
       <c r="E20" s="22"/>
-      <c r="F20" s="45">
-        <v>46131</v>
-      </c>
-      <c r="G20" s="46">
-        <v>97</v>
-      </c>
+      <c r="F20" s="45"/>
+      <c r="G20" s="46"/>
       <c r="H20" s="49" t="str">
         <f t="shared" ref="H20:H25" si="1">IF(ISBLANK(F20),"",CONCATENATE(F20-$G$15+1," days"))</f>
-        <v>64 days</v>
+        <v/>
       </c>
       <c r="I20" s="21">
         <v>16</v>
@@ -15141,15 +15033,11 @@
       <c r="C21" s="3"/>
       <c r="D21" s="5"/>
       <c r="E21" s="22"/>
-      <c r="F21" s="48">
-        <v>46136</v>
-      </c>
-      <c r="G21" s="46">
-        <v>85</v>
-      </c>
+      <c r="F21" s="48"/>
+      <c r="G21" s="46"/>
       <c r="H21" s="49" t="str">
         <f t="shared" si="1"/>
-        <v>69 days</v>
+        <v/>
       </c>
       <c r="I21" s="21">
         <v>17</v>
@@ -15167,15 +15055,11 @@
       <c r="C22" s="3"/>
       <c r="D22" s="5"/>
       <c r="E22" s="22"/>
-      <c r="F22" s="48">
-        <v>46137</v>
-      </c>
-      <c r="G22" s="46">
-        <v>76</v>
-      </c>
+      <c r="F22" s="48"/>
+      <c r="G22" s="46"/>
       <c r="H22" s="49" t="str">
         <f t="shared" si="1"/>
-        <v>70 days</v>
+        <v/>
       </c>
       <c r="I22" s="21">
         <v>18</v>
@@ -15193,15 +15077,11 @@
       <c r="C23" s="3"/>
       <c r="D23" s="5"/>
       <c r="E23" s="22"/>
-      <c r="F23" s="48">
-        <v>46138</v>
-      </c>
-      <c r="G23" s="46">
-        <v>90</v>
-      </c>
+      <c r="F23" s="48"/>
+      <c r="G23" s="46"/>
       <c r="H23" s="49" t="str">
         <f t="shared" si="1"/>
-        <v>71 days</v>
+        <v/>
       </c>
       <c r="I23" s="21">
         <v>19</v>
@@ -15401,148 +15281,92 @@
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D33" s="15" t="s">
-        <v>306</v>
-      </c>
+      <c r="D33" s="15"/>
       <c r="E33" s="59">
         <f>G33*F33</f>
-        <v>255712</v>
-      </c>
-      <c r="F33" s="59">
-        <v>131</v>
-      </c>
-      <c r="G33" s="67">
-        <v>1952</v>
-      </c>
-      <c r="H33" s="62">
-        <v>234</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F33" s="59"/>
+      <c r="G33" s="67"/>
+      <c r="H33" s="62"/>
       <c r="I33" s="144">
         <f>G33*H33</f>
-        <v>456768</v>
+        <v>0</v>
       </c>
       <c r="J33" s="144"/>
-      <c r="K33" s="85" t="s">
-        <v>355</v>
-      </c>
-      <c r="L33" s="136">
-        <v>134000</v>
-      </c>
+      <c r="K33" s="85"/>
+      <c r="L33" s="136"/>
       <c r="M33" s="15"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D34" s="15" t="s">
-        <v>201</v>
-      </c>
+      <c r="D34" s="15"/>
       <c r="E34" s="59">
         <f t="shared" ref="E34:E39" si="2">G34*F34</f>
-        <v>723967.2</v>
-      </c>
-      <c r="F34" s="59">
-        <v>121</v>
-      </c>
-      <c r="G34" s="67">
-        <v>5983.2</v>
-      </c>
-      <c r="H34" s="62">
-        <v>249</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F34" s="59"/>
+      <c r="G34" s="67"/>
+      <c r="H34" s="62"/>
       <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
-        <v>1489816.8</v>
+        <v>0</v>
       </c>
       <c r="J34" s="144"/>
-      <c r="K34" s="85" t="s">
-        <v>356</v>
-      </c>
-      <c r="L34" s="136">
-        <v>200000</v>
-      </c>
+      <c r="K34" s="85"/>
+      <c r="L34" s="136"/>
       <c r="M34" s="15"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B35" s="126"/>
-      <c r="D35" s="15" t="s">
-        <v>362</v>
-      </c>
+      <c r="D35" s="15"/>
       <c r="E35" s="59">
         <f t="shared" si="2"/>
-        <v>4500</v>
-      </c>
-      <c r="F35" s="59">
-        <v>90</v>
-      </c>
-      <c r="G35" s="67">
-        <v>50</v>
-      </c>
-      <c r="H35" s="62">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F35" s="59"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="62"/>
       <c r="I35" s="144">
         <f t="shared" si="3"/>
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J35" s="144"/>
-      <c r="K35" s="85" t="s">
-        <v>359</v>
-      </c>
-      <c r="L35" s="136">
-        <v>50000</v>
-      </c>
+      <c r="K35" s="85"/>
+      <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D36" s="15" t="s">
-        <v>231</v>
-      </c>
+      <c r="D36" s="15"/>
       <c r="E36" s="59">
         <f t="shared" si="2"/>
-        <v>64350</v>
-      </c>
-      <c r="F36" s="59">
-        <v>90</v>
-      </c>
-      <c r="G36" s="67">
-        <v>715</v>
-      </c>
-      <c r="H36" s="62">
-        <v>285</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F36" s="59"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="62"/>
       <c r="I36" s="144">
         <f t="shared" si="3"/>
-        <v>203775</v>
+        <v>0</v>
       </c>
       <c r="J36" s="144"/>
-      <c r="K36" s="187" t="s">
-        <v>143</v>
-      </c>
-      <c r="L36" s="136">
-        <v>1000000</v>
-      </c>
+      <c r="K36" s="187"/>
+      <c r="L36" s="136"/>
       <c r="M36" s="15"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D37" s="15" t="s">
-        <v>363</v>
-      </c>
+      <c r="D37" s="15"/>
       <c r="E37" s="59">
         <f t="shared" si="2"/>
-        <v>3600</v>
-      </c>
-      <c r="F37" s="59">
-        <v>90</v>
-      </c>
-      <c r="G37" s="67">
-        <v>40</v>
-      </c>
-      <c r="H37" s="62">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F37" s="59"/>
+      <c r="G37" s="67"/>
+      <c r="H37" s="62"/>
       <c r="I37" s="144">
         <f t="shared" si="3"/>
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="J37" s="144"/>
       <c r="K37" s="85"/>
@@ -15591,17 +15415,17 @@
       </c>
       <c r="E40" s="60">
         <f>SUM(E33:E38)</f>
-        <v>1052129.2</v>
+        <v>0</v>
       </c>
       <c r="F40" s="60"/>
       <c r="G40" s="84">
         <f>SUM(G33:G39)</f>
-        <v>8740.2000000000007</v>
+        <v>0</v>
       </c>
       <c r="H40" s="52"/>
       <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
-        <v>2159359.7999999998</v>
+        <v>0</v>
       </c>
       <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
@@ -15609,7 +15433,7 @@
       </c>
       <c r="L40" s="137">
         <f>SUM(L33:L39)</f>
-        <v>1384000</v>
+        <v>0</v>
       </c>
       <c r="M40" s="15"/>
     </row>
@@ -15619,7 +15443,7 @@
       </c>
       <c r="E41" s="109" t="str">
         <f>CONCATENATE(ROUND((E40/E31)*100,2),"%")</f>
-        <v>131.52%</v>
+        <v>0%</v>
       </c>
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
@@ -15631,7 +15455,7 @@
       </c>
       <c r="L41" s="105">
         <f>I40-L40</f>
-        <v>775359.79999999981</v>
+        <v>0</v>
       </c>
       <c r="M41" s="15"/>
     </row>
@@ -15645,22 +15469,16 @@
         <v>288</v>
       </c>
       <c r="B43" s="147"/>
-      <c r="C43" s="59">
-        <v>450000</v>
-      </c>
-      <c r="D43" s="15">
-        <v>126</v>
-      </c>
-      <c r="E43" s="131">
+      <c r="C43" s="59"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="131" t="e">
         <f>C43/D43</f>
-        <v>3571.4285714285716</v>
-      </c>
-      <c r="F43" s="62">
-        <v>250</v>
-      </c>
-      <c r="G43" s="101">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F43" s="62"/>
+      <c r="G43" s="101" t="e">
         <f>E43*F43</f>
-        <v>892857.14285714284</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H43" s="15"/>
       <c r="I43" s="15"/>
@@ -15674,22 +15492,16 @@
         <v>288</v>
       </c>
       <c r="B44" s="147"/>
-      <c r="C44" s="59">
-        <v>100000</v>
-      </c>
-      <c r="D44" s="15">
-        <v>76</v>
-      </c>
-      <c r="E44" s="131">
+      <c r="C44" s="59"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="131" t="e">
         <f>C44/D44</f>
-        <v>1315.7894736842106</v>
-      </c>
-      <c r="F44" s="62">
-        <v>300</v>
-      </c>
-      <c r="G44" s="101">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F44" s="62"/>
+      <c r="G44" s="101" t="e">
         <f>E44*F44</f>
-        <v>394736.8421052632</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H44" s="15"/>
       <c r="I44" s="15"/>
@@ -15699,9 +15511,9 @@
       <c r="M44" s="15"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="G45" s="111">
+      <c r="G45" s="111" t="e">
         <f>G43+G44</f>
-        <v>1287593.9849624061</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="54" spans="5:9" x14ac:dyDescent="0.3">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E97C2C5-022A-4984-9CA6-0CC0F538FF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7A4357-85B7-4F15-B5E7-3A6FB11AAE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Term-1" sheetId="4" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="367">
   <si>
     <t>#</t>
   </si>
@@ -3256,7 +3256,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>651715</c:v>
+                  <c:v>609915</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3788,7 +3788,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4242932</c:v>
+                  <c:v>4201132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4203,7 +4203,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>181992.5</c:v>
+                  <c:v>140192.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="J1" s="164">
         <f>L2-D2</f>
-        <v>651715</v>
+        <v>609915</v>
       </c>
       <c r="K1" s="165"/>
       <c r="L1" s="18"/>
@@ -13344,7 +13344,7 @@
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>1507045</v>
+        <v>1548845</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
@@ -13710,7 +13710,7 @@
         <v>365</v>
       </c>
       <c r="D13" s="5">
-        <v>20000</v>
+        <v>20800</v>
       </c>
       <c r="E13" s="57"/>
       <c r="F13" s="48"/>
@@ -13738,7 +13738,7 @@
         <v>366</v>
       </c>
       <c r="D14" s="9">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="E14" s="69"/>
       <c r="F14" s="148" t="s">
@@ -13758,9 +13758,15 @@
       <c r="A15" s="41">
         <v>11</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="5"/>
+      <c r="B15" s="7">
+        <v>46138</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D15" s="5">
+        <v>45000</v>
+      </c>
       <c r="E15" s="22"/>
       <c r="F15" s="16" t="s">
         <v>87</v>
@@ -14210,11 +14216,11 @@
         <v>5983.2</v>
       </c>
       <c r="H34" s="62">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I34" s="144">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
-        <v>1489816.8</v>
+        <v>1519732.8</v>
       </c>
       <c r="J34" s="144"/>
       <c r="K34" s="85" t="s">
@@ -14366,7 +14372,7 @@
       <c r="H40" s="52"/>
       <c r="I40" s="145">
         <f>SUM(I33:I39)</f>
-        <v>2159359.7999999998</v>
+        <v>2189275.7999999998</v>
       </c>
       <c r="J40" s="145"/>
       <c r="K40" s="52" t="s">
@@ -14396,7 +14402,7 @@
       </c>
       <c r="L41" s="105">
         <f>I40-L40</f>
-        <v>775359.79999999981</v>
+        <v>805275.79999999981</v>
       </c>
       <c r="M41" s="15"/>
     </row>
@@ -16049,7 +16055,7 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>651715</v>
+        <v>609915</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
@@ -16057,7 +16063,7 @@
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
-        <v>1507045</v>
+        <v>1548845</v>
       </c>
       <c r="G13" s="143">
         <f>MIN('Term-12'!G6:G14)</f>
@@ -16211,7 +16217,7 @@
       <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>4242932</v>
+        <v>4201132</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
@@ -16219,7 +16225,7 @@
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
-        <v>15336622</v>
+        <v>15378422</v>
       </c>
       <c r="G25" s="143"/>
       <c r="H25" s="89"/>
@@ -16304,7 +16310,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>181992.5</v>
+        <v>140192.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -16335,7 +16341,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>4242932</v>
+        <v>4201132</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7A4357-85B7-4F15-B5E7-3A6FB11AAE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2EEAC7-7249-419A-A75D-206ECA555E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3256,7 +3256,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>609915</c:v>
+                  <c:v>640431</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3788,7 +3788,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4201132</c:v>
+                  <c:v>4231648</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4203,7 +4203,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>140192.5</c:v>
+                  <c:v>170708.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="J1" s="164">
         <f>L2-D2</f>
-        <v>609915</v>
+        <v>640431</v>
       </c>
       <c r="K1" s="165"/>
       <c r="L1" s="18"/>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="L2" s="12">
         <f>SUM(L5:L22)</f>
-        <v>2158760</v>
+        <v>2189276</v>
       </c>
       <c r="M2" s="20"/>
     </row>
@@ -13499,7 +13499,7 @@
         <v>360</v>
       </c>
       <c r="L6" s="5">
-        <v>1494217</v>
+        <v>1524733</v>
       </c>
       <c r="M6" s="22"/>
     </row>
@@ -16055,11 +16055,11 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>609915</v>
+        <v>640431</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
-        <v>2158760</v>
+        <v>2189276</v>
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
@@ -16217,11 +16217,11 @@
       <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>4201132</v>
+        <v>4231648</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
-        <v>19579554</v>
+        <v>19610070</v>
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>140192.5</v>
+        <v>170708.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -16341,7 +16341,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>4201132</v>
+        <v>4231648</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2EEAC7-7249-419A-A75D-206ECA555E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F207E58-29D4-49DA-88C6-005388BF7F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="367">
   <si>
     <t>#</t>
   </si>
@@ -1141,9 +1141,6 @@
     <t>11 tons so far</t>
   </si>
   <si>
-    <t>Cash Credits-24-04-2026</t>
-  </si>
-  <si>
     <t>Big Tank-Final-120C-250R-6017T</t>
   </si>
   <si>
@@ -1163,6 +1160,9 @@
   </si>
   <si>
     <t>Adjustments</t>
+  </si>
+  <si>
+    <t>Cash-24-04-2026</t>
   </si>
 </sst>
 </file>
@@ -1776,7 +1776,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -2385,10 +2385,6 @@
     </xf>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3256,7 +3252,7 @@
                   <c:v>-469722.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>640431</c:v>
+                  <c:v>610376</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3788,7 +3784,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4231648</c:v>
+                  <c:v>4201593</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4203,7 +4199,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>170708.5</c:v>
+                  <c:v>140653.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13303,7 +13299,7 @@
     <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.77734375" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="40" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.88671875" style="1" customWidth="1"/>
     <col min="13" max="13" width="22.5546875" style="1" customWidth="1"/>
@@ -13330,7 +13326,7 @@
       </c>
       <c r="J1" s="164">
         <f>L2-D2</f>
-        <v>640431</v>
+        <v>610376</v>
       </c>
       <c r="K1" s="165"/>
       <c r="L1" s="18"/>
@@ -13344,14 +13340,14 @@
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>1548845</v>
+        <v>1578900</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
       <c r="G2" s="153" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H2" s="168"/>
       <c r="I2" s="38"/>
@@ -13496,7 +13492,7 @@
         <v>46138</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L6" s="5">
         <v>1524733</v>
@@ -13534,7 +13530,7 @@
         <v>46138</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L7" s="5">
         <v>207775</v>
@@ -13616,7 +13612,7 @@
         <v>143</v>
       </c>
       <c r="D10" s="9">
-        <v>1000000</v>
+        <v>1030055</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>358</v>
@@ -13707,7 +13703,7 @@
         <v>46138</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D13" s="5">
         <v>20800</v>
@@ -13735,7 +13731,7 @@
         <v>46138</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D14" s="9">
         <v>4000</v>
@@ -13795,7 +13791,7 @@
         <v>100</v>
       </c>
       <c r="G16" s="153" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H16" s="154"/>
       <c r="I16" s="21">
@@ -14197,7 +14193,7 @@
         <v>355</v>
       </c>
       <c r="L33" s="136">
-        <v>134000</v>
+        <v>134360</v>
       </c>
       <c r="M33" s="15"/>
     </row>
@@ -14234,7 +14230,7 @@
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B35" s="126"/>
       <c r="D35" s="15" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E35" s="59">
         <f t="shared" si="2"/>
@@ -14255,7 +14251,7 @@
       </c>
       <c r="J35" s="144"/>
       <c r="K35" s="85" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="L35" s="136">
         <v>50000</v>
@@ -14286,17 +14282,17 @@
         <v>203775</v>
       </c>
       <c r="J36" s="144"/>
-      <c r="K36" s="187" t="s">
+      <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
       <c r="L36" s="136">
-        <v>1000000</v>
+        <v>1030055</v>
       </c>
       <c r="M36" s="15"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D37" s="15" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E37" s="59">
         <f t="shared" si="2"/>
@@ -14316,8 +14312,12 @@
         <v>4000</v>
       </c>
       <c r="J37" s="144"/>
-      <c r="K37" s="85"/>
-      <c r="L37" s="136"/>
+      <c r="K37" s="85" t="s">
+        <v>215</v>
+      </c>
+      <c r="L37" s="136">
+        <v>200000</v>
+      </c>
       <c r="M37" s="15"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="L40" s="137">
         <f>SUM(L33:L39)</f>
-        <v>1384000</v>
+        <v>1614415</v>
       </c>
       <c r="M40" s="15"/>
     </row>
@@ -14402,7 +14402,7 @@
       </c>
       <c r="L41" s="105">
         <f>I40-L40</f>
-        <v>805275.79999999981</v>
+        <v>574860.79999999981</v>
       </c>
       <c r="M41" s="15"/>
     </row>
@@ -15357,7 +15357,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="144"/>
-      <c r="K36" s="187"/>
+      <c r="K36" s="85"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
     </row>
@@ -15537,17 +15537,17 @@
     <mergeCell ref="I41:J41"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A44:B44"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:H1"/>
@@ -15642,7 +15642,7 @@
       <c r="M1" s="186"/>
       <c r="N1" s="182" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>3 year, 0 months, 25 days</v>
+        <v>3 year, 1 months, 7 days</v>
       </c>
       <c r="O1" s="183"/>
       <c r="P1" s="183"/>
@@ -16055,7 +16055,7 @@
       </c>
       <c r="D13" s="96">
         <f t="shared" ref="D13" si="4">IF(F13="","",E13-F13)</f>
-        <v>640431</v>
+        <v>610376</v>
       </c>
       <c r="E13" s="89">
         <f>'Term-12'!$L$2</f>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="F13" s="89">
         <f>'Term-12'!$D$2</f>
-        <v>1548845</v>
+        <v>1578900</v>
       </c>
       <c r="G13" s="143">
         <f>MIN('Term-12'!G6:G14)</f>
@@ -16217,7 +16217,7 @@
       <c r="C25" s="181"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>4231648</v>
+        <v>4201593</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
-        <v>15378422</v>
+        <v>15408477</v>
       </c>
       <c r="G25" s="143"/>
       <c r="H25" s="89"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>170708.5</v>
+        <v>140653.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -16341,7 +16341,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>4231648</v>
+        <v>4201593</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F207E58-29D4-49DA-88C6-005388BF7F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E02090-342C-458B-9F17-C71C6D058B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="2" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Term-1" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="373">
   <si>
     <t>#</t>
   </si>
@@ -1163,6 +1163,24 @@
   </si>
   <si>
     <t>Cash-24-04-2026</t>
+  </si>
+  <si>
+    <t>8L from Tuni</t>
+  </si>
+  <si>
+    <t>Gas Drums</t>
+  </si>
+  <si>
+    <t>Term-13</t>
+  </si>
+  <si>
+    <t>May2026 - July2026</t>
+  </si>
+  <si>
+    <t>Salt</t>
+  </si>
+  <si>
+    <t>from Narsapuram</t>
   </si>
 </sst>
 </file>
@@ -1776,7 +1794,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -2214,9 +2232,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2224,64 +2239,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2302,6 +2259,12 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -2315,6 +2278,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2335,6 +2302,54 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -3784,7 +3799,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>4201593</c:v>
+                  <c:v>3916593</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4199,7 +4214,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>140653.5</c:v>
+                  <c:v>-144346.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8149,28 +8164,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="145" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="147"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="148">
         <v>45076</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="149"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="150">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="151"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -8179,8 +8194,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="153"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8192,10 +8207,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="154" t="s">
         <v>327</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="155"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8208,25 +8223,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="157"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="157"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="159"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8248,10 +8263,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="173" t="s">
+      <c r="H4" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="174"/>
+      <c r="I4" s="173"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -8519,11 +8534,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="163" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="164"/>
+      <c r="I12" s="165"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8584,10 +8599,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="154" t="s">
         <v>328</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="155"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8613,11 +8628,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="161"/>
+      <c r="I15" s="161"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -8644,10 +8659,10 @@
       <c r="G16" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="173" t="s">
+      <c r="H16" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="174"/>
+      <c r="I16" s="173"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -10946,34 +10961,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="145" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="147"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="148">
         <v>45918</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="149"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="150">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="151"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="152"/>
+      <c r="B2" s="153"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10985,10 +11000,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="154" t="s">
         <v>347</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="155"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -11001,25 +11016,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="157"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="161"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="157"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="159"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11382,11 +11397,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="163" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="164"/>
+      <c r="H14" s="165"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11406,10 +11421,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="148">
         <v>45918</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="149"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11429,10 +11444,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="154" t="s">
         <v>347</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="166"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11449,11 +11464,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="161"/>
+      <c r="H17" s="167"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11793,14 +11808,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="168" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="168"/>
+      <c r="K32" s="143" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="144"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11820,11 +11835,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="162">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="162"/>
       <c r="K33" s="85" t="s">
         <v>320</v>
       </c>
@@ -11850,11 +11865,11 @@
       <c r="H34" s="62">
         <v>300</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="162">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="162"/>
       <c r="K34" s="85" t="s">
         <v>143</v>
       </c>
@@ -11881,11 +11896,11 @@
       <c r="H35" s="62">
         <v>335</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="162">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="162"/>
       <c r="K35" s="85" t="s">
         <v>330</v>
       </c>
@@ -11913,11 +11928,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="162">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="162"/>
       <c r="K36" s="85" t="s">
         <v>331</v>
       </c>
@@ -11943,11 +11958,11 @@
       <c r="H37" s="62">
         <v>335</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="162">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="162"/>
       <c r="K37" s="85" t="s">
         <v>333</v>
       </c>
@@ -11973,11 +11988,11 @@
       <c r="H38" s="62">
         <v>290</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="162">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="162"/>
       <c r="K38" s="85" t="s">
         <v>320</v>
       </c>
@@ -11995,11 +12010,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="162"/>
       <c r="K39" s="85" t="s">
         <v>155</v>
       </c>
@@ -12022,11 +12037,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="169">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="169"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -12047,8 +12062,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="170"/>
+      <c r="J41" s="170"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -12064,10 +12079,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="171" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="171"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -12087,10 +12102,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="171" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="171"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -12128,15 +12143,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -12153,6 +12159,15 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
@@ -12202,34 +12217,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="145" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="147"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="148">
         <v>46016</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="149"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="150">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="151"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="152"/>
+      <c r="B2" s="153"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12241,10 +12256,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="154" t="s">
         <v>350</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="155"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12257,25 +12272,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="157"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="161"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="157"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="159"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12569,11 +12584,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="163" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="164"/>
+      <c r="H14" s="165"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12593,10 +12608,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="148">
         <v>46016</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="149"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12616,10 +12631,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="154" t="s">
         <v>351</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="166"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12636,11 +12651,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="161"/>
+      <c r="H17" s="167"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12962,14 +12977,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="168" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="168"/>
+      <c r="K32" s="143" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="144"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12989,11 +13004,11 @@
       <c r="H33" s="62">
         <v>65</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="162">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="162"/>
       <c r="K33" s="85" t="s">
         <v>143</v>
       </c>
@@ -13011,11 +13026,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="144">
+      <c r="I34" s="162">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="162"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -13030,11 +13045,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="144">
+      <c r="I35" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="162"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -13050,11 +13065,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="144">
+      <c r="I36" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="162"/>
       <c r="K36" s="2"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -13068,11 +13083,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="144">
+      <c r="I37" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="162"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -13086,11 +13101,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="162"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -13104,11 +13119,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="162"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -13127,11 +13142,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="169">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="169"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -13152,8 +13167,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="170"/>
+      <c r="J41" s="170"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -13169,10 +13184,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="171" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="171"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -13192,10 +13207,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="171" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="171"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -13233,15 +13248,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13253,11 +13264,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="16" priority="2" operator="greaterThan">
@@ -13307,34 +13322,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="145" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="147"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="148">
         <v>46068</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="149"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="150">
         <f>L2-D2</f>
         <v>610376</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="151"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="152"/>
+      <c r="B2" s="153"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -13346,10 +13361,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="154" t="s">
         <v>363</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="155"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13362,25 +13377,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="157"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="161"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="157"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="159"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13474,7 +13489,9 @@
       <c r="D6" s="5">
         <v>33000</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="23" t="s">
+        <v>368</v>
+      </c>
       <c r="F6" s="45">
         <v>46127</v>
       </c>
@@ -13737,11 +13754,11 @@
         <v>4000</v>
       </c>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="163" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="164"/>
+      <c r="H14" s="165"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13767,10 +13784,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="148">
         <v>46068</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="149"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13790,10 +13807,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="154" t="s">
         <v>363</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="166"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13810,11 +13827,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="161"/>
+      <c r="H17" s="167"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -14157,14 +14174,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="168" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="168"/>
+      <c r="K32" s="143" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="144"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -14184,11 +14201,11 @@
       <c r="H33" s="62">
         <v>234</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="162">
         <f>G33*H33</f>
         <v>456768</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="162"/>
       <c r="K33" s="85" t="s">
         <v>355</v>
       </c>
@@ -14214,11 +14231,11 @@
       <c r="H34" s="62">
         <v>254</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="162">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>1519732.8</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="162"/>
       <c r="K34" s="85" t="s">
         <v>356</v>
       </c>
@@ -14245,11 +14262,11 @@
       <c r="H35" s="62">
         <v>100</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="162">
         <f t="shared" si="3"/>
         <v>5000</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="162"/>
       <c r="K35" s="85" t="s">
         <v>366</v>
       </c>
@@ -14277,11 +14294,11 @@
       <c r="H36" s="62">
         <v>285</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="162">
         <f t="shared" si="3"/>
         <v>203775</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="162"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -14307,11 +14324,11 @@
       <c r="H37" s="62">
         <v>100</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="162">
         <f t="shared" si="3"/>
         <v>4000</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="162"/>
       <c r="K37" s="85" t="s">
         <v>215</v>
       </c>
@@ -14329,11 +14346,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="162"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -14347,11 +14364,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="162"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -14370,11 +14387,11 @@
         <v>8740.2000000000007</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="169">
         <f>SUM(I33:I39)</f>
         <v>2189275.7999999998</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="169"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -14395,8 +14412,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="170"/>
+      <c r="J41" s="170"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -14412,10 +14429,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="171" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="171"/>
       <c r="C43" s="59">
         <v>450000</v>
       </c>
@@ -14441,10 +14458,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="171" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="171"/>
       <c r="C44" s="59">
         <v>100000</v>
       </c>
@@ -14485,15 +14502,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14505,11 +14518,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
@@ -14562,48 +14579,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
-        <v>337</v>
-      </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="A1" s="145" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="147"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151"/>
-      <c r="H1" s="152"/>
+      <c r="G1" s="148">
+        <v>46154</v>
+      </c>
+      <c r="H1" s="149"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="150">
         <f>L2-D2</f>
-        <v>0</v>
-      </c>
-      <c r="K1" s="165"/>
+        <v>-285000</v>
+      </c>
+      <c r="K1" s="151"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="152"/>
+      <c r="B2" s="153"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>0</v>
+        <v>285000</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="str">
+      <c r="G2" s="154" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v/>
-      </c>
-      <c r="H2" s="168"/>
+        <v>1 days</v>
+      </c>
+      <c r="H2" s="155"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -14616,25 +14635,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="157"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="161"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="157"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="159"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -14681,10 +14700,18 @@
       <c r="A5" s="41">
         <v>1</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="23"/>
+      <c r="B5" s="7">
+        <v>46154</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="9">
+        <v>260000</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>367</v>
+      </c>
       <c r="F5" s="45"/>
       <c r="G5" s="46"/>
       <c r="H5" s="49" t="str">
@@ -14703,10 +14730,18 @@
       <c r="A6" s="41">
         <v>2</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="23"/>
+      <c r="B6" s="7">
+        <v>46154</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" s="5">
+        <v>15000</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>368</v>
+      </c>
       <c r="F6" s="45"/>
       <c r="G6" s="46"/>
       <c r="H6" s="49" t="str">
@@ -14725,10 +14760,18 @@
       <c r="A7" s="41">
         <v>3</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="23"/>
+      <c r="B7" s="7">
+        <v>46152</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D7" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>372</v>
+      </c>
       <c r="F7" s="45"/>
       <c r="G7" s="46"/>
       <c r="H7" s="49" t="str">
@@ -14883,11 +14926,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="9"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="163" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="164"/>
+      <c r="H14" s="165"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -14907,8 +14950,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151"/>
-      <c r="H15" s="152"/>
+      <c r="G15" s="148">
+        <v>46154</v>
+      </c>
+      <c r="H15" s="149"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -14928,11 +14973,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="str">
+      <c r="G16" s="154" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v/>
-      </c>
-      <c r="H16" s="154"/>
+        <v>1 days</v>
+      </c>
+      <c r="H16" s="166"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -14949,11 +14994,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="161"/>
+      <c r="H17" s="167"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -15276,14 +15321,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="168" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="168"/>
+      <c r="K32" s="143" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="160"/>
+      <c r="L32" s="144"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -15295,11 +15340,11 @@
       <c r="F33" s="59"/>
       <c r="G33" s="67"/>
       <c r="H33" s="62"/>
-      <c r="I33" s="144">
+      <c r="I33" s="162">
         <f>G33*H33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="162"/>
       <c r="K33" s="85"/>
       <c r="L33" s="136"/>
       <c r="M33" s="15"/>
@@ -15313,11 +15358,11 @@
       <c r="F34" s="59"/>
       <c r="G34" s="67"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="144">
+      <c r="I34" s="162">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="162"/>
       <c r="K34" s="85"/>
       <c r="L34" s="136"/>
       <c r="M34" s="15"/>
@@ -15332,11 +15377,11 @@
       <c r="F35" s="59"/>
       <c r="G35" s="67"/>
       <c r="H35" s="62"/>
-      <c r="I35" s="144">
+      <c r="I35" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="162"/>
       <c r="K35" s="85"/>
       <c r="L35" s="136"/>
       <c r="M35" s="15" t="s">
@@ -15352,11 +15397,11 @@
       <c r="F36" s="59"/>
       <c r="G36" s="67"/>
       <c r="H36" s="62"/>
-      <c r="I36" s="144">
+      <c r="I36" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="162"/>
       <c r="K36" s="85"/>
       <c r="L36" s="136"/>
       <c r="M36" s="15"/>
@@ -15370,11 +15415,11 @@
       <c r="F37" s="59"/>
       <c r="G37" s="67"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="144">
+      <c r="I37" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="162"/>
       <c r="K37" s="85"/>
       <c r="L37" s="136"/>
       <c r="M37" s="15"/>
@@ -15388,11 +15433,11 @@
       <c r="F38" s="59"/>
       <c r="G38" s="67"/>
       <c r="H38" s="62"/>
-      <c r="I38" s="144">
+      <c r="I38" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="162"/>
       <c r="K38" s="85"/>
       <c r="L38" s="136"/>
       <c r="M38" s="15"/>
@@ -15406,11 +15451,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="162"/>
       <c r="K39" s="85"/>
       <c r="L39" s="136"/>
       <c r="M39" s="15"/>
@@ -15429,11 +15474,11 @@
         <v>0</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="169">
         <f>SUM(I33:I39)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="169"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -15454,8 +15499,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="170"/>
+      <c r="J41" s="170"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -15471,10 +15516,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="171" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="171"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -15494,10 +15539,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="171" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="147"/>
+      <c r="B44" s="171"/>
       <c r="C44" s="59"/>
       <c r="D44" s="15"/>
       <c r="E44" s="131" t="e">
@@ -15532,11 +15577,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -15548,15 +15597,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
@@ -15630,24 +15675,24 @@
       <c r="G1" s="92" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="142" t="s">
+      <c r="H1" s="141" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="185" t="s">
+      <c r="I1" s="184" t="s">
         <v>206</v>
       </c>
-      <c r="J1" s="185"/>
-      <c r="K1" s="185"/>
-      <c r="L1" s="185"/>
-      <c r="M1" s="186"/>
-      <c r="N1" s="182" t="str">
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
+      <c r="M1" s="185"/>
+      <c r="N1" s="181" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>3 year, 1 months, 7 days</v>
-      </c>
-      <c r="O1" s="183"/>
-      <c r="P1" s="183"/>
-      <c r="Q1" s="183"/>
-      <c r="R1" s="184"/>
+        <v>3 year, 1 months, 11 days</v>
+      </c>
+      <c r="O1" s="182"/>
+      <c r="P1" s="182"/>
+      <c r="Q1" s="182"/>
+      <c r="R1" s="183"/>
       <c r="S1" s="8" t="s">
         <v>205</v>
       </c>
@@ -15680,11 +15725,11 @@
         <f>'Term-1'!$E$2</f>
         <v>2050924</v>
       </c>
-      <c r="G2" s="143">
+      <c r="G2" s="142">
         <f>MIN('Term-1'!H5:H11)</f>
         <v>80</v>
       </c>
-      <c r="H2" s="141" t="str" cm="1">
+      <c r="H2" s="140" t="str" cm="1">
         <f t="array" ref="H2:I2">'Term-1'!H2:I2</f>
         <v>75 days</v>
       </c>
@@ -15715,11 +15760,11 @@
         <f>'Term-2'!$E$2</f>
         <v>518110</v>
       </c>
-      <c r="G3" s="143">
+      <c r="G3" s="142">
         <f>MIN('Term-2'!H5:H11)</f>
         <v>325</v>
       </c>
-      <c r="H3" s="141" t="str" cm="1">
+      <c r="H3" s="140" t="str" cm="1">
         <f t="array" ref="H3:I3">'Term-2'!H2:I2</f>
         <v>27 days</v>
       </c>
@@ -15750,11 +15795,11 @@
         <f>'Term-3'!$E$2</f>
         <v>590000</v>
       </c>
-      <c r="G4" s="143">
+      <c r="G4" s="142">
         <f>MIN('Term-3'!H5:H11)</f>
         <v>325</v>
       </c>
-      <c r="H4" s="141" t="str" cm="1">
+      <c r="H4" s="140" t="str" cm="1">
         <f t="array" ref="H4:I4">'Term-3'!H2:I2</f>
         <v>37 days</v>
       </c>
@@ -15785,11 +15830,11 @@
         <f>'Term-4'!$E$2</f>
         <v>1601499</v>
       </c>
-      <c r="G5" s="143">
+      <c r="G5" s="142">
         <f>MIN('Term-4'!H5:H11)</f>
         <v>62</v>
       </c>
-      <c r="H5" s="141" t="str" cm="1">
+      <c r="H5" s="140" t="str" cm="1">
         <f t="array" ref="H5:I5">'Term-4'!H2:I2</f>
         <v>72 days</v>
       </c>
@@ -15820,11 +15865,11 @@
         <f>'Term-5'!$E$2</f>
         <v>1221202</v>
       </c>
-      <c r="G6" s="143">
+      <c r="G6" s="142">
         <f>MIN('Term-5'!H5:H11)</f>
         <v>110</v>
       </c>
-      <c r="H6" s="141" t="str" cm="1">
+      <c r="H6" s="140" t="str" cm="1">
         <f t="array" ref="H6:I6">'Term-5'!H2:I2</f>
         <v>58 days</v>
       </c>
@@ -15855,11 +15900,11 @@
         <f>'Term-6'!$E$2</f>
         <v>1412799</v>
       </c>
-      <c r="G7" s="143">
+      <c r="G7" s="142">
         <f>MIN('Term-6'!H5:H11)</f>
         <v>65</v>
       </c>
-      <c r="H7" s="141" t="str" cm="1">
+      <c r="H7" s="140" t="str" cm="1">
         <f t="array" ref="H7:I7">'Term-6'!H2:I2</f>
         <v>73 days</v>
       </c>
@@ -15890,11 +15935,11 @@
         <f>'Term-7'!$E$2</f>
         <v>1502849</v>
       </c>
-      <c r="G8" s="143">
+      <c r="G8" s="142">
         <f>MIN('Term-7'!H5:H11)</f>
         <v>97</v>
       </c>
-      <c r="H8" s="141" t="str" cm="1">
+      <c r="H8" s="140" t="str" cm="1">
         <f t="array" ref="H8:I8">'Term-7'!H2:I2</f>
         <v>79 days</v>
       </c>
@@ -15925,11 +15970,11 @@
         <f>'Term-8'!$E$2</f>
         <v>1386194</v>
       </c>
-      <c r="G9" s="143">
+      <c r="G9" s="142">
         <f>MIN('Term-8'!H5:H11)</f>
         <v>67</v>
       </c>
-      <c r="H9" s="141" t="str" cm="1">
+      <c r="H9" s="140" t="str" cm="1">
         <f t="array" ref="H9:I9">'Term-8'!H2:I2</f>
         <v>78 days</v>
       </c>
@@ -15960,11 +16005,11 @@
         <f>'Term-9'!$D$2</f>
         <v>1410000</v>
       </c>
-      <c r="G10" s="143">
+      <c r="G10" s="142">
         <f>MIN('Term-9'!G5:G13)</f>
         <v>78</v>
       </c>
-      <c r="H10" s="141" t="str" cm="1">
+      <c r="H10" s="140" t="str" cm="1">
         <f t="array" ref="H10:I10">'Term-9'!G2:H2</f>
         <v>62 days</v>
       </c>
@@ -15995,11 +16040,11 @@
         <f>'Term-10'!$D$2</f>
         <v>1551000</v>
       </c>
-      <c r="G11" s="143">
+      <c r="G11" s="142">
         <f>MIN('Term-10'!G5:G13)</f>
         <v>58</v>
       </c>
-      <c r="H11" s="141" t="str" cm="1">
+      <c r="H11" s="140" t="str" cm="1">
         <f t="array" ref="H11:I11">'Term-10'!G2:H2</f>
         <v>78 days</v>
       </c>
@@ -16030,11 +16075,11 @@
         <f>'Term-11'!$D$2</f>
         <v>585000</v>
       </c>
-      <c r="G12" s="143">
+      <c r="G12" s="142">
         <f>MIN('Term-11'!G5:G13)</f>
         <v>518</v>
       </c>
-      <c r="H12" s="141" t="str" cm="1">
+      <c r="H12" s="140" t="str" cm="1">
         <f t="array" ref="H12:I12">'Term-11'!G2:H2</f>
         <v>34 days</v>
       </c>
@@ -16047,8 +16092,8 @@
         <v>12</v>
       </c>
       <c r="B13" s="128" t="str">
-        <f>'Term-11'!$A$1</f>
-        <v>Dec2025 - Jan2026</v>
+        <f>'Term-12'!$A$1</f>
+        <v>Feb2026 - Apr2026</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>340</v>
@@ -16065,11 +16110,11 @@
         <f>'Term-12'!$D$2</f>
         <v>1578900</v>
       </c>
-      <c r="G13" s="143">
+      <c r="G13" s="142">
         <f>MIN('Term-12'!G6:G14)</f>
         <v>121</v>
       </c>
-      <c r="H13" s="141" t="str" cm="1">
+      <c r="H13" s="140" t="str" cm="1">
         <f t="array" ref="H13:I13">'Term-12'!G2:H2</f>
         <v>71 days</v>
       </c>
@@ -16081,13 +16126,36 @@
       <c r="A14" s="88">
         <v>13</v>
       </c>
-      <c r="B14" s="128"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="143"/>
-      <c r="H14" s="141"/>
+      <c r="B14" s="128" t="str">
+        <f>'Term-13'!$A$1</f>
+        <v>May2026 - July2026</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="D14" s="96">
+        <f t="shared" ref="D14" si="5">IF(F14="","",E14-F14)</f>
+        <v>-285000</v>
+      </c>
+      <c r="E14" s="89">
+        <f>'Term-13'!$L$2</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="89">
+        <f>'Term-13'!$D$2</f>
+        <v>285000</v>
+      </c>
+      <c r="G14" s="142">
+        <f>MIN('Term-13'!G6:G14)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="140" cm="1">
+        <f t="array" ref="H14:I14">'Term-13'!G3:H3</f>
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="88">
@@ -16098,8 +16166,8 @@
       <c r="D15" s="96"/>
       <c r="E15" s="89"/>
       <c r="F15" s="89"/>
-      <c r="G15" s="143"/>
-      <c r="H15" s="141"/>
+      <c r="G15" s="142"/>
+      <c r="H15" s="140"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="88">
@@ -16110,8 +16178,8 @@
       <c r="D16" s="96"/>
       <c r="E16" s="89"/>
       <c r="F16" s="89"/>
-      <c r="G16" s="143"/>
-      <c r="H16" s="141"/>
+      <c r="G16" s="142"/>
+      <c r="H16" s="140"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="88">
@@ -16122,8 +16190,8 @@
       <c r="D17" s="96"/>
       <c r="E17" s="89"/>
       <c r="F17" s="89"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="141"/>
+      <c r="G17" s="142"/>
+      <c r="H17" s="140"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="88">
@@ -16134,7 +16202,7 @@
       <c r="D18" s="96"/>
       <c r="E18" s="89"/>
       <c r="F18" s="108"/>
-      <c r="G18" s="143"/>
+      <c r="G18" s="142"/>
       <c r="H18" s="88"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -16146,8 +16214,8 @@
       <c r="D19" s="96"/>
       <c r="E19" s="89"/>
       <c r="F19" s="89"/>
-      <c r="G19" s="143"/>
-      <c r="H19" s="141"/>
+      <c r="G19" s="142"/>
+      <c r="H19" s="140"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="88">
@@ -16158,8 +16226,8 @@
       <c r="D20" s="96"/>
       <c r="E20" s="89"/>
       <c r="F20" s="89"/>
-      <c r="G20" s="143"/>
-      <c r="H20" s="141"/>
+      <c r="G20" s="142"/>
+      <c r="H20" s="140"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="88">
@@ -16170,8 +16238,8 @@
       <c r="D21" s="96"/>
       <c r="E21" s="89"/>
       <c r="F21" s="89"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="141"/>
+      <c r="G21" s="142"/>
+      <c r="H21" s="140"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="88">
@@ -16182,8 +16250,8 @@
       <c r="D22" s="96"/>
       <c r="E22" s="89"/>
       <c r="F22" s="89"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="141"/>
+      <c r="G22" s="142"/>
+      <c r="H22" s="140"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="88">
@@ -16194,8 +16262,8 @@
       <c r="D23" s="96"/>
       <c r="E23" s="89"/>
       <c r="F23" s="89"/>
-      <c r="G23" s="143"/>
-      <c r="H23" s="141"/>
+      <c r="G23" s="142"/>
+      <c r="H23" s="140"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="88">
@@ -16206,18 +16274,18 @@
       <c r="D24" s="96"/>
       <c r="E24" s="89"/>
       <c r="F24" s="89"/>
-      <c r="G24" s="143"/>
-      <c r="H24" s="141"/>
+      <c r="G24" s="142"/>
+      <c r="H24" s="140"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="179" t="s">
+      <c r="A25" s="178" t="s">
         <v>189</v>
       </c>
-      <c r="B25" s="180"/>
-      <c r="C25" s="181"/>
+      <c r="B25" s="179"/>
+      <c r="C25" s="180"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>4201593</v>
+        <v>3916593</v>
       </c>
       <c r="E25" s="89">
         <f>SUM(E2:E24)</f>
@@ -16225,9 +16293,9 @@
       </c>
       <c r="F25" s="89">
         <f>SUM(F2:F24)</f>
-        <v>15408477</v>
-      </c>
-      <c r="G25" s="143"/>
+        <v>15693477</v>
+      </c>
+      <c r="G25" s="142"/>
       <c r="H25" s="89"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -16273,8 +16341,8 @@
         <v>2024</v>
       </c>
       <c r="C30" s="108">
-        <f>COUNTIF(C4:C7, "*")</f>
-        <v>4</v>
+        <f>COUNTIF(C5:C7, "*")</f>
+        <v>3</v>
       </c>
       <c r="D30" s="89">
         <f>SUM(D5:D7)</f>
@@ -16289,8 +16357,8 @@
         <v>2025</v>
       </c>
       <c r="C31" s="108">
-        <f>COUNTIF(C8:C11, "*")</f>
-        <v>4</v>
+        <f>COUNTIF(C8:C12, "*")</f>
+        <v>5</v>
       </c>
       <c r="D31" s="89">
         <f>SUM(D8:D11)</f>
@@ -16305,12 +16373,12 @@
         <v>2026</v>
       </c>
       <c r="C32" s="108">
-        <f>COUNTIF(C12:C15, "*")</f>
+        <f>COUNTIF(C13:C16, "*")</f>
         <v>2</v>
       </c>
       <c r="D32" s="89">
         <f>SUM(D12:D15)</f>
-        <v>140653.5</v>
+        <v>-144346.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -16335,13 +16403,16 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="139"/>
-      <c r="B35" s="140"/>
-      <c r="C35" s="8" t="s">
+      <c r="B35" s="8" t="s">
         <v>144</v>
+      </c>
+      <c r="C35" s="8">
+        <f>SUM(C29:C34)</f>
+        <v>13</v>
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>4201593</v>
+        <v>3916593</v>
       </c>
     </row>
   </sheetData>
@@ -16590,28 +16661,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="145" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="147"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="148">
         <v>45163</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="149"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="150">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="151"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -16620,8 +16691,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="153"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -16633,10 +16704,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="154" t="s">
         <v>353</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="155"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -16649,25 +16720,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="157"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="157"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="159"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -16689,10 +16760,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="173" t="s">
+      <c r="H4" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="174"/>
+      <c r="I4" s="173"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -16914,11 +16985,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="163" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="164"/>
+      <c r="I12" s="165"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -16939,10 +17010,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="148">
         <v>45163</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="149"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -16963,10 +17034,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="154" t="s">
         <v>353</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="155"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -16984,11 +17055,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="161"/>
+      <c r="I15" s="161"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17009,10 +17080,10 @@
       <c r="G16" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="173" t="s">
+      <c r="H16" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="174"/>
+      <c r="I16" s="173"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -18752,12 +18823,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -18766,6 +18831,12 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
     <cfRule type="duplicateValues" dxfId="62" priority="6"/>
@@ -18822,28 +18893,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="145" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="147"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="148">
         <v>45163</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="149"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="150">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="151"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -18852,8 +18923,8 @@
         <f>SUM(A5:A104)</f>
         <v>430300</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="153"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -18865,10 +18936,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="154" t="s">
         <v>354</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="155"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -18881,25 +18952,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="157"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="157"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="159"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -18921,10 +18992,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="173" t="s">
+      <c r="H4" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="174"/>
+      <c r="I4" s="173"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -19142,11 +19213,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="163" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
+      <c r="H12" s="164"/>
+      <c r="I12" s="165"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -19167,10 +19238,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="151">
+      <c r="H13" s="148">
         <v>45163</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="149"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -19191,10 +19262,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="153" t="s">
+      <c r="H14" s="154" t="s">
         <v>354</v>
       </c>
-      <c r="I14" s="168"/>
+      <c r="I14" s="155"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -19212,11 +19283,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="155" t="s">
+      <c r="G15" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
+      <c r="H15" s="161"/>
+      <c r="I15" s="161"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -19237,10 +19308,10 @@
       <c r="G16" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="173" t="s">
+      <c r="H16" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="174"/>
+      <c r="I16" s="173"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -21050,28 +21121,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="145" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="147"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="148">
         <v>45345</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="149"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="150">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="151"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -21080,8 +21151,8 @@
         <f>SUM(A5:A26)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="153"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -21093,10 +21164,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="154" t="s">
         <v>342</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="155"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -21109,25 +21180,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="157"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="157"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="159"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -21149,10 +21220,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="173" t="s">
+      <c r="H4" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="174"/>
+      <c r="I4" s="173"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -21469,11 +21540,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="163" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="164"/>
+      <c r="I14" s="165"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21494,10 +21565,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="148">
         <v>45345</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="149"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21539,11 +21610,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="161"/>
+      <c r="I17" s="167"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21761,8 +21832,8 @@
       <c r="G27" s="61"/>
       <c r="H27" s="61"/>
       <c r="I27" s="61"/>
-      <c r="J27" s="175"/>
-      <c r="K27" s="175"/>
+      <c r="J27" s="174"/>
+      <c r="K27" s="174"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E28" s="61" t="s">
@@ -21780,10 +21851,10 @@
       <c r="I28" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="158" t="s">
+      <c r="J28" s="168" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="158"/>
+      <c r="K28" s="168"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="15" t="s">
@@ -21802,11 +21873,11 @@
       <c r="I29" s="62">
         <v>0</v>
       </c>
-      <c r="J29" s="144">
+      <c r="J29" s="162">
         <f>H29*I29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="144"/>
+      <c r="K29" s="162"/>
       <c r="L29" s="6" t="s">
         <v>138</v>
       </c>
@@ -21831,11 +21902,11 @@
       <c r="I30" s="62">
         <v>200</v>
       </c>
-      <c r="J30" s="144">
+      <c r="J30" s="162">
         <f t="shared" ref="J30:J33" si="1">H30*I30</f>
         <v>432360.00000000006</v>
       </c>
-      <c r="K30" s="144"/>
+      <c r="K30" s="162"/>
       <c r="L30" s="6" t="s">
         <v>143</v>
       </c>
@@ -21860,11 +21931,11 @@
       <c r="I31" s="62">
         <v>230</v>
       </c>
-      <c r="J31" s="144">
+      <c r="J31" s="162">
         <f t="shared" si="1"/>
         <v>454020</v>
       </c>
-      <c r="K31" s="144"/>
+      <c r="K31" s="162"/>
       <c r="L31" s="6" t="s">
         <v>153</v>
       </c>
@@ -21889,11 +21960,11 @@
       <c r="I32" s="62">
         <v>250</v>
       </c>
-      <c r="J32" s="144">
+      <c r="J32" s="162">
         <f t="shared" si="1"/>
         <v>541000</v>
       </c>
-      <c r="K32" s="144"/>
+      <c r="K32" s="162"/>
       <c r="L32" s="6" t="s">
         <v>154</v>
       </c>
@@ -21918,11 +21989,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="162">
         <f t="shared" si="1"/>
         <v>253179</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="162"/>
       <c r="L33" s="6" t="s">
         <v>143</v>
       </c>
@@ -21946,11 +22017,11 @@
       <c r="I34" s="62">
         <v>275</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="162">
         <f t="shared" ref="J34:J35" si="2">H34*I34</f>
         <v>1014090</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="162"/>
       <c r="L34" s="6" t="s">
         <v>155</v>
       </c>
@@ -21974,11 +22045,11 @@
       <c r="I35" s="62">
         <v>215</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="162">
         <f t="shared" si="2"/>
         <v>11395</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="162"/>
       <c r="L35" s="6" t="s">
         <v>155</v>
       </c>
@@ -22000,11 +22071,11 @@
         <v>11018.1</v>
       </c>
       <c r="I36" s="52"/>
-      <c r="J36" s="145">
+      <c r="J36" s="169">
         <f>SUM(J29:J35)</f>
         <v>2706044</v>
       </c>
-      <c r="K36" s="145"/>
+      <c r="K36" s="169"/>
       <c r="L36" s="6" t="s">
         <v>154</v>
       </c>
@@ -22023,8 +22094,8 @@
       <c r="G37" s="15"/>
       <c r="H37" s="58"/>
       <c r="I37" s="15"/>
-      <c r="J37" s="146"/>
-      <c r="K37" s="146"/>
+      <c r="J37" s="170"/>
+      <c r="K37" s="170"/>
       <c r="L37" s="6"/>
       <c r="M37" s="26">
         <f>SUM(M29:M36)</f>
@@ -22073,6 +22144,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J27:K27"/>
@@ -22082,20 +22167,6 @@
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="J35:K35"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G17:I17"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="48" priority="4" operator="greaterThan">
@@ -22143,35 +22214,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="145" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="147"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="148">
         <v>45477</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="149"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="150">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="151"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="153"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -22183,10 +22254,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="154" t="s">
         <v>343</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="155"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22199,25 +22270,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="157"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="157"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="159"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22239,10 +22310,10 @@
       <c r="G4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="173" t="s">
+      <c r="H4" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="174"/>
+      <c r="I4" s="173"/>
       <c r="J4" s="21" t="s">
         <v>0</v>
       </c>
@@ -22551,11 +22622,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="163" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="164"/>
+      <c r="I14" s="165"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22578,10 +22649,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="148">
         <v>45477</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="149"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22627,11 +22698,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="161"/>
+      <c r="I17" s="167"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22972,8 +23043,8 @@
       <c r="G31" s="61"/>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="175"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="174"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C32" s="6" t="s">
@@ -22997,14 +23068,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="168" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="168"/>
+      <c r="L32" s="143" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="143"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
@@ -23029,11 +23100,11 @@
       <c r="I33" s="62">
         <v>249</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="162">
         <f>H33*I33</f>
         <v>1327120.2</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="162"/>
       <c r="L33" s="85" t="s">
         <v>172</v>
       </c>
@@ -23061,11 +23132,11 @@
       <c r="I34" s="62">
         <v>124.5</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="162">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>7470</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="162"/>
       <c r="L34" s="85" t="s">
         <v>173</v>
       </c>
@@ -23097,11 +23168,11 @@
       <c r="I35" s="62">
         <v>250</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="162">
         <f t="shared" si="3"/>
         <v>267050</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="162"/>
       <c r="L35" s="85" t="s">
         <v>173</v>
       </c>
@@ -23122,11 +23193,11 @@
       <c r="I36" s="62">
         <v>10</v>
       </c>
-      <c r="J36" s="145">
+      <c r="J36" s="169">
         <f t="shared" si="3"/>
         <v>10682</v>
       </c>
-      <c r="K36" s="145"/>
+      <c r="K36" s="169"/>
       <c r="L36" s="85" t="s">
         <v>155</v>
       </c>
@@ -23143,11 +23214,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="162"/>
       <c r="L37" s="85" t="s">
         <v>179</v>
       </c>
@@ -23164,11 +23235,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="162"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -23185,11 +23256,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="162"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -23207,11 +23278,11 @@
         <v>7526.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="169">
         <f>SUM(J33:J39)</f>
         <v>1612322.2</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="169"/>
       <c r="L40" s="85"/>
       <c r="M40" s="62"/>
     </row>
@@ -23226,8 +23297,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="170"/>
+      <c r="K41" s="170"/>
       <c r="L41" s="52" t="s">
         <v>174</v>
       </c>
@@ -23257,16 +23328,16 @@
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="176" t="s">
+      <c r="A43" s="175" t="s">
         <v>163</v>
       </c>
-      <c r="B43" s="176"/>
-      <c r="C43" s="176"/>
-      <c r="F43" s="176" t="s">
+      <c r="B43" s="175"/>
+      <c r="C43" s="175"/>
+      <c r="F43" s="175" t="s">
         <v>164</v>
       </c>
-      <c r="G43" s="176"/>
-      <c r="H43" s="176"/>
+      <c r="G43" s="175"/>
+      <c r="H43" s="175"/>
       <c r="K43" s="14"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
@@ -23298,16 +23369,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -23324,6 +23385,16 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="44" priority="1" operator="greaterThan">
@@ -23372,35 +23443,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="145" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="147"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="148">
         <v>45548</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="149"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="150">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="151"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="153"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -23412,10 +23483,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="154" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="155"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -23428,25 +23499,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="157"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="157"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="159"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -23820,11 +23891,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="163" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="164"/>
+      <c r="I14" s="165"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -23851,10 +23922,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="148">
         <v>45561</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="149"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -23881,10 +23952,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="154" t="s">
         <v>291</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="166"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -23908,11 +23979,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="161"/>
+      <c r="I17" s="167"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -24256,8 +24327,8 @@
       <c r="G31" s="61"/>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="175"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="174"/>
       <c r="L31" s="100"/>
       <c r="M31" s="100"/>
     </row>
@@ -24277,14 +24348,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="168" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="168"/>
+      <c r="L32" s="143" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="143"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -24303,11 +24374,11 @@
       <c r="I33" s="62">
         <v>270</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="162">
         <f>H33*I33</f>
         <v>558927</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="162"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -24332,11 +24403,11 @@
       <c r="I34" s="62">
         <v>320</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="162">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1478368</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="162"/>
       <c r="L34" s="6" t="s">
         <v>153</v>
       </c>
@@ -24361,11 +24432,11 @@
       <c r="I35" s="62">
         <v>340</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="162">
         <f t="shared" si="3"/>
         <v>377808</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="162"/>
       <c r="L35" s="85" t="s">
         <v>155</v>
       </c>
@@ -24382,11 +24453,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="144">
+      <c r="J36" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="162"/>
       <c r="L36" s="85" t="s">
         <v>172</v>
       </c>
@@ -24403,11 +24474,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="162"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -24424,11 +24495,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="162"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -24448,11 +24519,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="162"/>
       <c r="L39" s="85" t="s">
         <v>131</v>
       </c>
@@ -24466,8 +24537,8 @@
       <c r="G40" s="59"/>
       <c r="H40" s="67"/>
       <c r="I40" s="62"/>
-      <c r="J40" s="177"/>
-      <c r="K40" s="178"/>
+      <c r="J40" s="176"/>
+      <c r="K40" s="177"/>
       <c r="L40" s="85" t="s">
         <v>155</v>
       </c>
@@ -24481,8 +24552,8 @@
       <c r="G41" s="59"/>
       <c r="H41" s="67"/>
       <c r="I41" s="62"/>
-      <c r="J41" s="177"/>
-      <c r="K41" s="178"/>
+      <c r="J41" s="176"/>
+      <c r="K41" s="177"/>
       <c r="L41" s="85" t="s">
         <v>155</v>
       </c>
@@ -24504,11 +24575,11 @@
         <v>7801.2</v>
       </c>
       <c r="I42" s="52"/>
-      <c r="J42" s="145">
+      <c r="J42" s="169">
         <f>SUM(J33:J39)</f>
         <v>2415103</v>
       </c>
-      <c r="K42" s="145"/>
+      <c r="K42" s="169"/>
       <c r="L42" s="52" t="s">
         <v>174</v>
       </c>
@@ -24528,8 +24599,8 @@
       <c r="G43" s="15"/>
       <c r="H43" s="58"/>
       <c r="I43" s="15"/>
-      <c r="J43" s="146"/>
-      <c r="K43" s="146"/>
+      <c r="J43" s="170"/>
+      <c r="K43" s="170"/>
       <c r="L43" s="83" t="s">
         <v>175</v>
       </c>
@@ -24544,11 +24615,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="147" t="s">
+      <c r="A45" s="171" t="s">
         <v>196</v>
       </c>
-      <c r="B45" s="147"/>
-      <c r="C45" s="147"/>
+      <c r="B45" s="171"/>
+      <c r="C45" s="171"/>
       <c r="D45" s="62"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -24665,19 +24736,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -24692,6 +24750,19 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="40" priority="1" operator="greaterThan">
@@ -24740,35 +24811,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="145" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="147"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="148">
         <v>45631</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="149"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="150">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="151"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="153"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -24780,10 +24851,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="154" t="s">
         <v>345</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="155"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -24796,25 +24867,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="157"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="157"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="159"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -25154,11 +25225,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="163" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="164"/>
+      <c r="I14" s="165"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -25179,10 +25250,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="148">
         <v>45653</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="149"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -25203,10 +25274,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="154" t="s">
         <v>346</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="166"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -25224,11 +25295,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="161"/>
+      <c r="I17" s="167"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -25553,8 +25624,8 @@
       <c r="G31" s="61"/>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="175"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="174"/>
       <c r="L31" s="100"/>
       <c r="M31" s="100"/>
     </row>
@@ -25574,14 +25645,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="168" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="168"/>
+      <c r="L32" s="143" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="143"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -25600,11 +25671,11 @@
       <c r="I33" s="62">
         <v>245</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="162">
         <f>H33*I33</f>
         <v>526627.5</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="162"/>
       <c r="L33" s="85" t="s">
         <v>215</v>
       </c>
@@ -25629,11 +25700,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="162">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>1357200</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="162"/>
       <c r="L34" s="85" t="s">
         <v>215</v>
       </c>
@@ -25658,11 +25729,11 @@
       <c r="I35" s="62">
         <v>200</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="162">
         <f t="shared" si="3"/>
         <v>148000</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="162"/>
       <c r="L35" s="85" t="s">
         <v>215</v>
       </c>
@@ -25679,11 +25750,11 @@
       <c r="G36" s="59"/>
       <c r="H36" s="67"/>
       <c r="I36" s="62"/>
-      <c r="J36" s="144">
+      <c r="J36" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="162"/>
       <c r="L36" s="85" t="s">
         <v>143</v>
       </c>
@@ -25700,11 +25771,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="162"/>
       <c r="L37" s="85" t="s">
         <v>64</v>
       </c>
@@ -25721,11 +25792,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="162"/>
       <c r="L38" s="85" t="s">
         <v>155</v>
       </c>
@@ -25742,11 +25813,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="162"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -25764,11 +25835,11 @@
         <v>8109.5</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="169">
         <f>SUM(J33:J39)</f>
         <v>2031827.5</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="169"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -25788,8 +25859,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="170"/>
+      <c r="K41" s="170"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -25804,11 +25875,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="171" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="147"/>
+      <c r="B43" s="171"/>
+      <c r="C43" s="171"/>
       <c r="D43" s="62"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -25956,6 +26027,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -25964,23 +26052,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
@@ -26032,35 +26103,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="145" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="147"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="151">
+      <c r="H1" s="148">
         <v>45714</v>
       </c>
-      <c r="I1" s="152"/>
+      <c r="I1" s="149"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="164">
+      <c r="K1" s="150">
         <f>M2-E2</f>
         <v>405496</v>
       </c>
-      <c r="L1" s="165"/>
+      <c r="L1" s="151"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="43"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="167"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="153"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -26072,10 +26143,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="153" t="s">
+      <c r="H2" s="154" t="s">
         <v>347</v>
       </c>
-      <c r="I2" s="168"/>
+      <c r="I2" s="155"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -26088,25 +26159,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="155" t="s">
+      <c r="C3" s="157"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="169" t="s">
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="K3" s="157"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="159"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -26448,11 +26519,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="69"/>
-      <c r="G14" s="148" t="s">
+      <c r="G14" s="163" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="149"/>
-      <c r="I14" s="150"/>
+      <c r="H14" s="164"/>
+      <c r="I14" s="165"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -26475,10 +26546,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="151">
+      <c r="H15" s="148">
         <v>45743</v>
       </c>
-      <c r="I15" s="152"/>
+      <c r="I15" s="149"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -26501,10 +26572,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="154" t="s">
         <v>348</v>
       </c>
-      <c r="I16" s="154"/>
+      <c r="I16" s="166"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -26524,11 +26595,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="H17" s="161"/>
+      <c r="I17" s="167"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -26847,8 +26918,8 @@
       <c r="G31" s="61"/>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="175"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="174"/>
       <c r="L31" s="100"/>
       <c r="M31" s="100"/>
     </row>
@@ -26868,14 +26939,14 @@
       <c r="I32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="158" t="s">
+      <c r="J32" s="168" t="s">
         <v>148</v>
       </c>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159" t="s">
+      <c r="K32" s="168"/>
+      <c r="L32" s="143" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="159"/>
+      <c r="M32" s="143"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E33" s="15" t="s">
@@ -26894,11 +26965,11 @@
       <c r="I33" s="62">
         <v>220</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="162">
         <f>H33*I33</f>
         <v>368280</v>
       </c>
-      <c r="K33" s="144"/>
+      <c r="K33" s="162"/>
       <c r="L33" s="85" t="s">
         <v>257</v>
       </c>
@@ -26923,11 +26994,11 @@
       <c r="I34" s="62">
         <v>260</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="162">
         <f t="shared" ref="J34:J39" si="3">H34*I34</f>
         <v>571064</v>
       </c>
-      <c r="K34" s="144"/>
+      <c r="K34" s="162"/>
       <c r="L34" s="85" t="s">
         <v>262</v>
       </c>
@@ -26953,11 +27024,11 @@
       <c r="I35" s="62">
         <v>280</v>
       </c>
-      <c r="J35" s="144">
+      <c r="J35" s="162">
         <f t="shared" si="3"/>
         <v>679140</v>
       </c>
-      <c r="K35" s="144"/>
+      <c r="K35" s="162"/>
       <c r="L35" s="85" t="s">
         <v>263</v>
       </c>
@@ -26982,11 +27053,11 @@
       <c r="I36" s="62">
         <v>220</v>
       </c>
-      <c r="J36" s="144">
+      <c r="J36" s="162">
         <f t="shared" si="3"/>
         <v>173206</v>
       </c>
-      <c r="K36" s="144"/>
+      <c r="K36" s="162"/>
       <c r="L36" s="85" t="s">
         <v>264</v>
       </c>
@@ -27002,11 +27073,11 @@
       <c r="G37" s="59"/>
       <c r="H37" s="67"/>
       <c r="I37" s="62"/>
-      <c r="J37" s="144">
+      <c r="J37" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="144"/>
+      <c r="K37" s="162"/>
       <c r="L37" s="85"/>
       <c r="M37" s="62"/>
     </row>
@@ -27019,11 +27090,11 @@
       <c r="G38" s="59"/>
       <c r="H38" s="67"/>
       <c r="I38" s="62"/>
-      <c r="J38" s="144">
+      <c r="J38" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="144"/>
+      <c r="K38" s="162"/>
       <c r="L38" s="85"/>
       <c r="M38" s="62"/>
     </row>
@@ -27036,11 +27107,11 @@
       <c r="G39" s="59"/>
       <c r="H39" s="67"/>
       <c r="I39" s="62"/>
-      <c r="J39" s="144">
+      <c r="J39" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="144"/>
+      <c r="K39" s="162"/>
       <c r="L39" s="85"/>
       <c r="M39" s="62"/>
     </row>
@@ -27058,11 +27129,11 @@
         <v>7083.2</v>
       </c>
       <c r="I40" s="52"/>
-      <c r="J40" s="145">
+      <c r="J40" s="169">
         <f>SUM(J33:J39)</f>
         <v>1791690</v>
       </c>
-      <c r="K40" s="145"/>
+      <c r="K40" s="169"/>
       <c r="L40" s="52" t="s">
         <v>174</v>
       </c>
@@ -27082,8 +27153,8 @@
       <c r="G41" s="15"/>
       <c r="H41" s="58"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
+      <c r="J41" s="170"/>
+      <c r="K41" s="170"/>
       <c r="L41" s="83" t="s">
         <v>175</v>
       </c>
@@ -27098,11 +27169,11 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="171" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="147"/>
-      <c r="C43" s="147"/>
+      <c r="B43" s="171"/>
+      <c r="C43" s="171"/>
       <c r="D43" s="59"/>
       <c r="E43" s="15"/>
       <c r="F43" s="3" t="e">
@@ -27134,23 +27205,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -27159,6 +27213,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="31" priority="2" operator="greaterThan">
@@ -27208,34 +27279,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="145" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="147"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="151">
+      <c r="G1" s="148">
         <v>45840</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="149"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="164">
+      <c r="J1" s="150">
         <f>L2-D2</f>
         <v>1125929.5</v>
       </c>
-      <c r="K1" s="165"/>
+      <c r="K1" s="151"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
+      <c r="A2" s="152"/>
+      <c r="B2" s="153"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -27247,10 +27318,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="153" t="s">
+      <c r="G2" s="154" t="s">
         <v>349</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="155"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -27263,25 +27334,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="155" t="s">
+      <c r="B3" s="157"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="169" t="s">
+      <c r="G3" s="161"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="170"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="172"/>
+      <c r="J3" s="157"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="159"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -27599,11 +27670,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="69"/>
-      <c r="F14" s="148" t="s">
+      <c r="F14" s="163" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="G14" s="164"/>
+      <c r="H14" s="165"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -27623,10 +27694,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="148">
         <v>45840</v>
       </c>
-      <c r="H15" s="152"/>
+      <c r="H15" s="149"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -27646,10 +27717,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="153" t="s">
+      <c r="G16" s="154" t="s">
         <v>291</v>
       </c>
-      <c r="H16" s="154"/>
+      <c r="H16" s="166"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -27666,11 +27737,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="157"/>
+      <c r="G17" s="161"/>
+      <c r="H17" s="167"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -28003,10 +28074,10 @@
       <c r="H31" s="61" t="s">
         <v>275</v>
       </c>
-      <c r="I31" s="175">
+      <c r="I31" s="174">
         <v>150000</v>
       </c>
-      <c r="J31" s="175"/>
+      <c r="J31" s="174"/>
       <c r="K31" s="100"/>
       <c r="L31" s="100"/>
     </row>
@@ -28026,14 +28097,14 @@
       <c r="H32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="158" t="s">
+      <c r="I32" s="168" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="158"/>
-      <c r="K32" s="159" t="s">
+      <c r="J32" s="168"/>
+      <c r="K32" s="143" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="159"/>
+      <c r="L32" s="143"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -28052,11 +28123,11 @@
       <c r="H33" s="62">
         <v>240</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="162">
         <f>G33*H33</f>
         <v>467304</v>
       </c>
-      <c r="J33" s="144"/>
+      <c r="J33" s="162"/>
       <c r="K33" s="85" t="s">
         <v>287</v>
       </c>
@@ -28081,11 +28152,11 @@
       <c r="H34" s="62">
         <v>240</v>
       </c>
-      <c r="I34" s="144">
+      <c r="I34" s="162">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>53736</v>
       </c>
-      <c r="J34" s="144"/>
+      <c r="J34" s="162"/>
       <c r="K34" s="85" t="s">
         <v>290</v>
       </c>
@@ -28111,11 +28182,11 @@
       <c r="H35" s="62">
         <v>265</v>
       </c>
-      <c r="I35" s="144">
+      <c r="I35" s="162">
         <f t="shared" si="3"/>
         <v>605260</v>
       </c>
-      <c r="J35" s="144"/>
+      <c r="J35" s="162"/>
       <c r="K35" s="85" t="s">
         <v>294</v>
       </c>
@@ -28140,11 +28211,11 @@
       <c r="H36" s="62">
         <v>265</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="162">
         <f t="shared" si="3"/>
         <v>151235.5</v>
       </c>
-      <c r="J36" s="144"/>
+      <c r="J36" s="162"/>
       <c r="K36" s="85" t="s">
         <v>143</v>
       </c>
@@ -28169,11 +28240,11 @@
       <c r="H37" s="62">
         <v>265</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="162">
         <f t="shared" si="3"/>
         <v>940405.5</v>
       </c>
-      <c r="J37" s="144"/>
+      <c r="J37" s="162"/>
       <c r="K37" s="85" t="s">
         <v>295</v>
       </c>
@@ -28198,11 +28269,11 @@
       <c r="H38" s="62">
         <v>330</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="162">
         <f t="shared" si="3"/>
         <v>317988</v>
       </c>
-      <c r="J38" s="144"/>
+      <c r="J38" s="162"/>
       <c r="K38" s="85" t="s">
         <v>297</v>
       </c>
@@ -28219,11 +28290,11 @@
       <c r="F39" s="59"/>
       <c r="G39" s="67"/>
       <c r="H39" s="62"/>
-      <c r="I39" s="144">
+      <c r="I39" s="162">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="144"/>
+      <c r="J39" s="162"/>
       <c r="K39" s="85"/>
       <c r="L39" s="62"/>
     </row>
@@ -28241,11 +28312,11 @@
         <v>9538</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="145">
+      <c r="I40" s="169">
         <f>SUM(I33:I39)</f>
         <v>2535929</v>
       </c>
-      <c r="J40" s="145"/>
+      <c r="J40" s="169"/>
       <c r="K40" s="52" t="s">
         <v>174</v>
       </c>
@@ -28265,8 +28336,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="58"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
+      <c r="I41" s="170"/>
+      <c r="J41" s="170"/>
       <c r="K41" s="83" t="s">
         <v>175</v>
       </c>
@@ -28281,10 +28352,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="147" t="s">
+      <c r="A43" s="171" t="s">
         <v>288</v>
       </c>
-      <c r="B43" s="147"/>
+      <c r="B43" s="171"/>
       <c r="C43" s="59"/>
       <c r="D43" s="15"/>
       <c r="E43" s="131" t="e">
@@ -28324,23 +28395,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -28349,6 +28403,23 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="26" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E02090-342C-458B-9F17-C71C6D058B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6428A353-7D2B-4F41-BC32-D90B5092A98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="2" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -12143,6 +12143,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -12159,15 +12168,6 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
@@ -13248,11 +13248,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13264,15 +13268,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="16" priority="2" operator="greaterThan">
@@ -14502,11 +14502,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14518,15 +14522,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
@@ -15292,13 +15292,13 @@
         <v>274</v>
       </c>
       <c r="G31" s="86">
-        <v>700000</v>
+        <v>800000</v>
       </c>
       <c r="H31" s="61" t="s">
         <v>275</v>
       </c>
       <c r="I31" s="86">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="J31" s="86"/>
       <c r="K31" s="100"/>
@@ -15577,15 +15577,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -15597,11 +15593,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
@@ -18823,6 +18823,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -18831,12 +18837,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D106">
     <cfRule type="duplicateValues" dxfId="62" priority="6"/>
@@ -22144,6 +22144,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="J29:K29"/>
@@ -22153,20 +22167,6 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="G17:I17"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="48" priority="4" operator="greaterThan">
@@ -23369,6 +23369,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J38:K38"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="B1:F1"/>
@@ -23385,16 +23395,6 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="44" priority="1" operator="greaterThan">
@@ -24736,6 +24736,19 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H16:I16"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J42:K42"/>
@@ -24750,19 +24763,6 @@
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="40" priority="1" operator="greaterThan">
@@ -26027,23 +26027,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -26052,6 +26035,23 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
@@ -27205,6 +27205,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -27213,23 +27230,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="31" priority="2" operator="greaterThan">
@@ -28395,6 +28395,23 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -28403,23 +28420,6 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="26" priority="2" operator="greaterThan">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED774933-52EF-47F5-837B-16C30A06C340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196243DC-DD23-4E5E-B793-D8665147A7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="706" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="372">
   <si>
     <t>#</t>
   </si>
@@ -1175,6 +1175,9 @@
   </si>
   <si>
     <t>from Narsapuram</t>
+  </si>
+  <si>
+    <t>Tractor charges</t>
   </si>
 </sst>
 </file>
@@ -2228,6 +2231,64 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2248,12 +2309,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -2267,10 +2322,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2291,54 +2342,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -3780,7 +3783,7 @@
                 <c:formatCode>"₹"\ #,##0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>3920593</c:v>
+                  <c:v>3902640</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4195,7 +4198,7 @@
                   <c:v>3039754.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-140346.5</c:v>
+                  <c:v>-158299.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8145,28 +8148,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="43"/>
-      <c r="B1" s="147" t="s">
+      <c r="B1" s="162" t="s">
         <v>263</v>
       </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="164"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="150">
+      <c r="H1" s="152">
         <v>45076</v>
       </c>
-      <c r="I1" s="151"/>
+      <c r="I1" s="153"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="152">
+      <c r="K1" s="165">
         <f>M2-E2</f>
         <v>-782674</v>
       </c>
-      <c r="L1" s="153"/>
+      <c r="L1" s="166"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -8175,8 +8178,8 @@
         <f>SUM(A5:A105)</f>
         <v>473100</v>
       </c>
-      <c r="B2" s="154"/>
-      <c r="C2" s="155"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="168"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -8188,10 +8191,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="156" t="s">
+      <c r="H2" s="154" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="157"/>
+      <c r="I2" s="169"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -8204,25 +8207,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="158" t="s">
+      <c r="B3" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="159"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="162" t="s">
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="158" t="s">
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="170" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="159"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="161"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="172"/>
+      <c r="M3" s="172"/>
+      <c r="N3" s="173"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -8515,11 +8518,11 @@
       <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="165" t="s">
+      <c r="G12" s="149" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="166"/>
-      <c r="I12" s="167"/>
+      <c r="H12" s="150"/>
+      <c r="I12" s="151"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -8580,10 +8583,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="156" t="s">
+      <c r="H14" s="154" t="s">
         <v>326</v>
       </c>
-      <c r="I14" s="157"/>
+      <c r="I14" s="169"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -8609,11 +8612,11 @@
       <c r="F15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="162" t="s">
+      <c r="G15" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="163"/>
-      <c r="I15" s="163"/>
+      <c r="H15" s="157"/>
+      <c r="I15" s="157"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -10936,34 +10939,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="162" t="s">
         <v>313</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="149"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="164"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="150">
+      <c r="G1" s="152">
         <v>45918</v>
       </c>
-      <c r="H1" s="151"/>
+      <c r="H1" s="153"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="152">
+      <c r="J1" s="165">
         <f>L2-D2</f>
         <v>979350</v>
       </c>
-      <c r="K1" s="153"/>
+      <c r="K1" s="166"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="154"/>
-      <c r="B2" s="155"/>
+      <c r="A2" s="167"/>
+      <c r="B2" s="168"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -10975,10 +10978,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="156" t="s">
+      <c r="G2" s="154" t="s">
         <v>345</v>
       </c>
-      <c r="H2" s="157"/>
+      <c r="H2" s="169"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -10991,25 +10994,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="158" t="s">
+      <c r="A3" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="159"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="162" t="s">
+      <c r="B3" s="171"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="173"/>
+      <c r="F3" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="158" t="s">
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="170" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="159"/>
-      <c r="K3" s="160"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="161"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="172"/>
+      <c r="L3" s="172"/>
+      <c r="M3" s="173"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -11372,11 +11375,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="68"/>
-      <c r="F14" s="165" t="s">
+      <c r="F14" s="149" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="166"/>
-      <c r="H14" s="167"/>
+      <c r="G14" s="150"/>
+      <c r="H14" s="151"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -11396,10 +11399,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="150">
+      <c r="G15" s="152">
         <v>45918</v>
       </c>
-      <c r="H15" s="151"/>
+      <c r="H15" s="153"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -11419,10 +11422,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="156" t="s">
+      <c r="G16" s="154" t="s">
         <v>345</v>
       </c>
-      <c r="H16" s="168"/>
+      <c r="H16" s="155"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -11439,11 +11442,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="162" t="s">
+      <c r="F17" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="163"/>
-      <c r="H17" s="169"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="158"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -11783,14 +11786,14 @@
       <c r="H32" s="92" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="170" t="s">
+      <c r="I32" s="159" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="170"/>
-      <c r="K32" s="145" t="s">
+      <c r="J32" s="159"/>
+      <c r="K32" s="160" t="s">
         <v>244</v>
       </c>
-      <c r="L32" s="146"/>
+      <c r="L32" s="161"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -11810,11 +11813,11 @@
       <c r="H33" s="61">
         <v>240</v>
       </c>
-      <c r="I33" s="164">
+      <c r="I33" s="145">
         <f>G33*H33</f>
         <v>496056</v>
       </c>
-      <c r="J33" s="164"/>
+      <c r="J33" s="145"/>
       <c r="K33" s="84" t="s">
         <v>318</v>
       </c>
@@ -11840,11 +11843,11 @@
       <c r="H34" s="61">
         <v>300</v>
       </c>
-      <c r="I34" s="164">
+      <c r="I34" s="145">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>644160</v>
       </c>
-      <c r="J34" s="164"/>
+      <c r="J34" s="145"/>
       <c r="K34" s="84" t="s">
         <v>143</v>
       </c>
@@ -11871,11 +11874,11 @@
       <c r="H35" s="61">
         <v>335</v>
       </c>
-      <c r="I35" s="164">
+      <c r="I35" s="145">
         <f t="shared" si="3"/>
         <v>1136588</v>
       </c>
-      <c r="J35" s="164"/>
+      <c r="J35" s="145"/>
       <c r="K35" s="84" t="s">
         <v>328</v>
       </c>
@@ -11903,11 +11906,11 @@
       <c r="H36" s="61">
         <v>285</v>
       </c>
-      <c r="I36" s="164">
+      <c r="I36" s="145">
         <f t="shared" si="3"/>
         <v>244273.5</v>
       </c>
-      <c r="J36" s="164"/>
+      <c r="J36" s="145"/>
       <c r="K36" s="84" t="s">
         <v>329</v>
       </c>
@@ -11933,11 +11936,11 @@
       <c r="H37" s="61">
         <v>335</v>
       </c>
-      <c r="I37" s="164">
+      <c r="I37" s="145">
         <f t="shared" si="3"/>
         <v>3182.5</v>
       </c>
-      <c r="J37" s="164"/>
+      <c r="J37" s="145"/>
       <c r="K37" s="84" t="s">
         <v>331</v>
       </c>
@@ -11963,11 +11966,11 @@
       <c r="H38" s="61">
         <v>290</v>
       </c>
-      <c r="I38" s="164">
+      <c r="I38" s="145">
         <f t="shared" si="3"/>
         <v>6090</v>
       </c>
-      <c r="J38" s="164"/>
+      <c r="J38" s="145"/>
       <c r="K38" s="84" t="s">
         <v>318</v>
       </c>
@@ -11985,11 +11988,11 @@
       <c r="F39" s="58"/>
       <c r="G39" s="66"/>
       <c r="H39" s="61"/>
-      <c r="I39" s="164">
+      <c r="I39" s="145">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="164"/>
+      <c r="J39" s="145"/>
       <c r="K39" s="84" t="s">
         <v>155</v>
       </c>
@@ -12012,11 +12015,11 @@
         <v>8494.5</v>
       </c>
       <c r="H40" s="51"/>
-      <c r="I40" s="171">
+      <c r="I40" s="146">
         <f>SUM(I33:I39)</f>
         <v>2530350</v>
       </c>
-      <c r="J40" s="171"/>
+      <c r="J40" s="146"/>
       <c r="K40" s="51" t="s">
         <v>174</v>
       </c>
@@ -12037,8 +12040,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="57"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="172"/>
-      <c r="J41" s="172"/>
+      <c r="I41" s="147"/>
+      <c r="J41" s="147"/>
       <c r="K41" s="82" t="s">
         <v>175</v>
       </c>
@@ -12054,10 +12057,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="173" t="s">
+      <c r="A43" s="148" t="s">
         <v>286</v>
       </c>
-      <c r="B43" s="173"/>
+      <c r="B43" s="148"/>
       <c r="C43" s="58"/>
       <c r="D43" s="15"/>
       <c r="E43" s="129" t="e">
@@ -12077,10 +12080,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="173" t="s">
+      <c r="A44" s="148" t="s">
         <v>286</v>
       </c>
-      <c r="B44" s="173"/>
+      <c r="B44" s="148"/>
       <c r="C44" s="58"/>
       <c r="D44" s="15"/>
       <c r="E44" s="129" t="e">
@@ -12118,15 +12121,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I38:J38"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
@@ -12143,6 +12137,15 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
@@ -12192,34 +12195,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="162" t="s">
         <v>334</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="149"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="164"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="150">
+      <c r="G1" s="152">
         <v>46016</v>
       </c>
-      <c r="H1" s="151"/>
+      <c r="H1" s="153"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="152">
+      <c r="J1" s="165">
         <f>L2-D2</f>
         <v>-469722.5</v>
       </c>
-      <c r="K1" s="153"/>
+      <c r="K1" s="166"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="154"/>
-      <c r="B2" s="155"/>
+      <c r="A2" s="167"/>
+      <c r="B2" s="168"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -12231,10 +12234,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="156" t="s">
+      <c r="G2" s="154" t="s">
         <v>348</v>
       </c>
-      <c r="H2" s="157"/>
+      <c r="H2" s="169"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -12247,25 +12250,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="158" t="s">
+      <c r="A3" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="159"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="162" t="s">
+      <c r="B3" s="171"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="173"/>
+      <c r="F3" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="158" t="s">
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="170" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="159"/>
-      <c r="K3" s="160"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="161"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="172"/>
+      <c r="L3" s="172"/>
+      <c r="M3" s="173"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -12559,11 +12562,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="5"/>
       <c r="E14" s="68"/>
-      <c r="F14" s="165" t="s">
+      <c r="F14" s="149" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="166"/>
-      <c r="H14" s="167"/>
+      <c r="G14" s="150"/>
+      <c r="H14" s="151"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -12583,10 +12586,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="150">
+      <c r="G15" s="152">
         <v>46016</v>
       </c>
-      <c r="H15" s="151"/>
+      <c r="H15" s="153"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -12606,10 +12609,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="156" t="s">
+      <c r="G16" s="154" t="s">
         <v>349</v>
       </c>
-      <c r="H16" s="168"/>
+      <c r="H16" s="155"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -12626,11 +12629,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="162" t="s">
+      <c r="F17" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="163"/>
-      <c r="H17" s="169"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="158"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -12952,14 +12955,14 @@
       <c r="H32" s="92" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="170" t="s">
+      <c r="I32" s="159" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="170"/>
-      <c r="K32" s="145" t="s">
+      <c r="J32" s="159"/>
+      <c r="K32" s="160" t="s">
         <v>244</v>
       </c>
-      <c r="L32" s="146"/>
+      <c r="L32" s="161"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -12979,11 +12982,11 @@
       <c r="H33" s="61">
         <v>65</v>
       </c>
-      <c r="I33" s="164">
+      <c r="I33" s="145">
         <f>G33*H33</f>
         <v>115277.5</v>
       </c>
-      <c r="J33" s="164"/>
+      <c r="J33" s="145"/>
       <c r="K33" s="84" t="s">
         <v>143</v>
       </c>
@@ -13001,11 +13004,11 @@
       <c r="F34" s="58"/>
       <c r="G34" s="66"/>
       <c r="H34" s="61"/>
-      <c r="I34" s="164">
+      <c r="I34" s="145">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="164"/>
+      <c r="J34" s="145"/>
       <c r="K34" s="84"/>
       <c r="L34" s="134"/>
       <c r="M34" s="15"/>
@@ -13020,11 +13023,11 @@
       <c r="F35" s="58"/>
       <c r="G35" s="66"/>
       <c r="H35" s="61"/>
-      <c r="I35" s="164">
+      <c r="I35" s="145">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="164"/>
+      <c r="J35" s="145"/>
       <c r="K35" s="84"/>
       <c r="L35" s="134"/>
       <c r="M35" s="15" t="s">
@@ -13040,11 +13043,11 @@
       <c r="F36" s="58"/>
       <c r="G36" s="66"/>
       <c r="H36" s="61"/>
-      <c r="I36" s="164">
+      <c r="I36" s="145">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="164"/>
+      <c r="J36" s="145"/>
       <c r="K36" s="2"/>
       <c r="L36" s="134"/>
       <c r="M36" s="15"/>
@@ -13058,11 +13061,11 @@
       <c r="F37" s="58"/>
       <c r="G37" s="66"/>
       <c r="H37" s="61"/>
-      <c r="I37" s="164">
+      <c r="I37" s="145">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="164"/>
+      <c r="J37" s="145"/>
       <c r="K37" s="84"/>
       <c r="L37" s="134"/>
       <c r="M37" s="15"/>
@@ -13076,11 +13079,11 @@
       <c r="F38" s="58"/>
       <c r="G38" s="66"/>
       <c r="H38" s="61"/>
-      <c r="I38" s="164">
+      <c r="I38" s="145">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="164"/>
+      <c r="J38" s="145"/>
       <c r="K38" s="84"/>
       <c r="L38" s="134"/>
       <c r="M38" s="15"/>
@@ -13094,11 +13097,11 @@
       <c r="F39" s="58"/>
       <c r="G39" s="66"/>
       <c r="H39" s="61"/>
-      <c r="I39" s="164">
+      <c r="I39" s="145">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="164"/>
+      <c r="J39" s="145"/>
       <c r="K39" s="84"/>
       <c r="L39" s="134"/>
       <c r="M39" s="15"/>
@@ -13117,11 +13120,11 @@
         <v>1773.5</v>
       </c>
       <c r="H40" s="51"/>
-      <c r="I40" s="171">
+      <c r="I40" s="146">
         <f>SUM(I33:I39)</f>
         <v>115277.5</v>
       </c>
-      <c r="J40" s="171"/>
+      <c r="J40" s="146"/>
       <c r="K40" s="51" t="s">
         <v>174</v>
       </c>
@@ -13142,8 +13145,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="57"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="172"/>
-      <c r="J41" s="172"/>
+      <c r="I41" s="147"/>
+      <c r="J41" s="147"/>
       <c r="K41" s="82" t="s">
         <v>175</v>
       </c>
@@ -13159,10 +13162,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="173" t="s">
+      <c r="A43" s="148" t="s">
         <v>286</v>
       </c>
-      <c r="B43" s="173"/>
+      <c r="B43" s="148"/>
       <c r="C43" s="58"/>
       <c r="D43" s="15"/>
       <c r="E43" s="129" t="e">
@@ -13182,10 +13185,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="173" t="s">
+      <c r="A44" s="148" t="s">
         <v>286</v>
       </c>
-      <c r="B44" s="173"/>
+      <c r="B44" s="148"/>
       <c r="C44" s="58"/>
       <c r="D44" s="15"/>
       <c r="E44" s="129" t="e">
@@ -13223,15 +13226,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -13243,11 +13242,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="16" priority="2" operator="greaterThan">
@@ -13297,34 +13300,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="162" t="s">
         <v>335</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="149"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="164"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="150">
+      <c r="G1" s="152">
         <v>46068</v>
       </c>
-      <c r="H1" s="151"/>
+      <c r="H1" s="153"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="152">
+      <c r="J1" s="165">
         <f>L2-D2</f>
         <v>610376</v>
       </c>
-      <c r="K1" s="153"/>
+      <c r="K1" s="166"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="154"/>
-      <c r="B2" s="155"/>
+      <c r="A2" s="167"/>
+      <c r="B2" s="168"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
@@ -13336,10 +13339,10 @@
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="156" t="s">
+      <c r="G2" s="154" t="s">
         <v>361</v>
       </c>
-      <c r="H2" s="157"/>
+      <c r="H2" s="169"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -13352,25 +13355,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="158" t="s">
+      <c r="A3" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="159"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="162" t="s">
+      <c r="B3" s="171"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="173"/>
+      <c r="F3" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="158" t="s">
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="170" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="159"/>
-      <c r="K3" s="160"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="161"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="172"/>
+      <c r="L3" s="172"/>
+      <c r="M3" s="173"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -13729,11 +13732,11 @@
         <v>4000</v>
       </c>
       <c r="E14" s="68"/>
-      <c r="F14" s="165" t="s">
+      <c r="F14" s="149" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="166"/>
-      <c r="H14" s="167"/>
+      <c r="G14" s="150"/>
+      <c r="H14" s="151"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -13759,10 +13762,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="150">
+      <c r="G15" s="152">
         <v>46068</v>
       </c>
-      <c r="H15" s="151"/>
+      <c r="H15" s="153"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -13782,10 +13785,10 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="156" t="s">
+      <c r="G16" s="154" t="s">
         <v>361</v>
       </c>
-      <c r="H16" s="168"/>
+      <c r="H16" s="155"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -13802,11 +13805,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="162" t="s">
+      <c r="F17" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="163"/>
-      <c r="H17" s="169"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="158"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -14149,14 +14152,14 @@
       <c r="H32" s="92" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="170" t="s">
+      <c r="I32" s="159" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="170"/>
-      <c r="K32" s="145" t="s">
+      <c r="J32" s="159"/>
+      <c r="K32" s="160" t="s">
         <v>244</v>
       </c>
-      <c r="L32" s="146"/>
+      <c r="L32" s="161"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -14176,11 +14179,11 @@
       <c r="H33" s="61">
         <v>234</v>
       </c>
-      <c r="I33" s="164">
+      <c r="I33" s="145">
         <f>G33*H33</f>
         <v>456768</v>
       </c>
-      <c r="J33" s="164"/>
+      <c r="J33" s="145"/>
       <c r="K33" s="84" t="s">
         <v>353</v>
       </c>
@@ -14206,11 +14209,11 @@
       <c r="H34" s="61">
         <v>254</v>
       </c>
-      <c r="I34" s="164">
+      <c r="I34" s="145">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>1519732.8</v>
       </c>
-      <c r="J34" s="164"/>
+      <c r="J34" s="145"/>
       <c r="K34" s="84" t="s">
         <v>354</v>
       </c>
@@ -14237,11 +14240,11 @@
       <c r="H35" s="61">
         <v>100</v>
       </c>
-      <c r="I35" s="164">
+      <c r="I35" s="145">
         <f t="shared" si="3"/>
         <v>5000</v>
       </c>
-      <c r="J35" s="164"/>
+      <c r="J35" s="145"/>
       <c r="K35" s="84" t="s">
         <v>364</v>
       </c>
@@ -14269,11 +14272,11 @@
       <c r="H36" s="61">
         <v>285</v>
       </c>
-      <c r="I36" s="164">
+      <c r="I36" s="145">
         <f t="shared" si="3"/>
         <v>203775</v>
       </c>
-      <c r="J36" s="164"/>
+      <c r="J36" s="145"/>
       <c r="K36" s="84" t="s">
         <v>143</v>
       </c>
@@ -14299,11 +14302,11 @@
       <c r="H37" s="61">
         <v>100</v>
       </c>
-      <c r="I37" s="164">
+      <c r="I37" s="145">
         <f t="shared" si="3"/>
         <v>4000</v>
       </c>
-      <c r="J37" s="164"/>
+      <c r="J37" s="145"/>
       <c r="K37" s="84" t="s">
         <v>213</v>
       </c>
@@ -14321,11 +14324,11 @@
       <c r="F38" s="58"/>
       <c r="G38" s="66"/>
       <c r="H38" s="61"/>
-      <c r="I38" s="164">
+      <c r="I38" s="145">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="164"/>
+      <c r="J38" s="145"/>
       <c r="K38" s="84"/>
       <c r="L38" s="134"/>
       <c r="M38" s="15"/>
@@ -14339,11 +14342,11 @@
       <c r="F39" s="58"/>
       <c r="G39" s="66"/>
       <c r="H39" s="61"/>
-      <c r="I39" s="164">
+      <c r="I39" s="145">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="164"/>
+      <c r="J39" s="145"/>
       <c r="K39" s="84"/>
       <c r="L39" s="134"/>
       <c r="M39" s="15"/>
@@ -14362,11 +14365,11 @@
         <v>8740.2000000000007</v>
       </c>
       <c r="H40" s="51"/>
-      <c r="I40" s="171">
+      <c r="I40" s="146">
         <f>SUM(I33:I39)</f>
         <v>2189275.7999999998</v>
       </c>
-      <c r="J40" s="171"/>
+      <c r="J40" s="146"/>
       <c r="K40" s="51" t="s">
         <v>174</v>
       </c>
@@ -14387,8 +14390,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="57"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="172"/>
-      <c r="J41" s="172"/>
+      <c r="I41" s="147"/>
+      <c r="J41" s="147"/>
       <c r="K41" s="82" t="s">
         <v>175</v>
       </c>
@@ -14404,10 +14407,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="173" t="s">
+      <c r="A43" s="148" t="s">
         <v>286</v>
       </c>
-      <c r="B43" s="173"/>
+      <c r="B43" s="148"/>
       <c r="C43" s="58">
         <v>450000</v>
       </c>
@@ -14433,10 +14436,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="173" t="s">
+      <c r="A44" s="148" t="s">
         <v>286</v>
       </c>
-      <c r="B44" s="173"/>
+      <c r="B44" s="148"/>
       <c r="C44" s="58">
         <v>100000</v>
       </c>
@@ -14477,15 +14480,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -14497,11 +14496,15 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
@@ -14539,7 +14542,7 @@
   <cols>
     <col min="1" max="1" width="3" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.88671875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -14554,50 +14557,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="162" t="s">
         <v>368</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="149"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="164"/>
       <c r="F1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="150">
+      <c r="G1" s="152">
         <v>46154</v>
       </c>
-      <c r="H1" s="151"/>
+      <c r="H1" s="153"/>
       <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="152">
+      <c r="J1" s="165">
         <f>L2-D2</f>
-        <v>-281000</v>
-      </c>
-      <c r="K1" s="153"/>
+        <v>-298953</v>
+      </c>
+      <c r="K1" s="166"/>
       <c r="L1" s="18"/>
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="154"/>
-      <c r="B2" s="155"/>
+      <c r="A2" s="167"/>
+      <c r="B2" s="168"/>
       <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="12">
         <f>SUM(D5:D30)</f>
-        <v>281000</v>
+        <v>298953</v>
       </c>
       <c r="E2" s="20"/>
       <c r="F2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="156" t="str">
+      <c r="G2" s="154" t="str">
         <f ca="1">IF(ISBLANK(G1),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>7 days</v>
-      </c>
-      <c r="H2" s="157"/>
+        <v>17 days</v>
+      </c>
+      <c r="H2" s="169"/>
       <c r="I2" s="38"/>
       <c r="J2" s="10"/>
       <c r="K2" s="11" t="s">
@@ -14610,25 +14613,25 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="158" t="s">
+      <c r="A3" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="159"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="162" t="s">
+      <c r="B3" s="171"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="173"/>
+      <c r="F3" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="158" t="s">
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="170" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="159"/>
-      <c r="K3" s="160"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="161"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="172"/>
+      <c r="L3" s="172"/>
+      <c r="M3" s="173"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
@@ -14765,9 +14768,15 @@
       <c r="A8" s="41">
         <v>4</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="5"/>
+      <c r="B8" s="7">
+        <v>46161</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="5">
+        <v>14953</v>
+      </c>
       <c r="E8" s="22"/>
       <c r="F8" s="44"/>
       <c r="G8" s="45"/>
@@ -14787,10 +14796,18 @@
       <c r="A9" s="41">
         <v>5</v>
       </c>
-      <c r="B9" s="130"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="22"/>
+      <c r="B9" s="130">
+        <v>46167</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D9" s="9">
+        <v>3000</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>140</v>
+      </c>
       <c r="F9" s="47"/>
       <c r="G9" s="45"/>
       <c r="H9" s="48" t="str">
@@ -14901,11 +14918,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="9"/>
       <c r="E14" s="68"/>
-      <c r="F14" s="165" t="s">
+      <c r="F14" s="149" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="166"/>
-      <c r="H14" s="167"/>
+      <c r="G14" s="150"/>
+      <c r="H14" s="151"/>
       <c r="I14" s="21">
         <v>10</v>
       </c>
@@ -14925,10 +14942,10 @@
       <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="150">
+      <c r="G15" s="152">
         <v>46154</v>
       </c>
-      <c r="H15" s="151"/>
+      <c r="H15" s="153"/>
       <c r="I15" s="21">
         <v>11</v>
       </c>
@@ -14948,11 +14965,11 @@
       <c r="F16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="156" t="str">
+      <c r="G16" s="154" t="str">
         <f ca="1">IF(ISBLANK(G15),"",CONCATENATE(_xlfn.DAYS(TODAY(), G1-1)," days"))</f>
-        <v>7 days</v>
-      </c>
-      <c r="H16" s="168"/>
+        <v>17 days</v>
+      </c>
+      <c r="H16" s="155"/>
       <c r="I16" s="21">
         <v>12</v>
       </c>
@@ -14969,11 +14986,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="162" t="s">
+      <c r="F17" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="163"/>
-      <c r="H17" s="169"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="158"/>
       <c r="I17" s="21">
         <v>13</v>
       </c>
@@ -15296,14 +15313,14 @@
       <c r="H32" s="92" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="170" t="s">
+      <c r="I32" s="159" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="170"/>
-      <c r="K32" s="145" t="s">
+      <c r="J32" s="159"/>
+      <c r="K32" s="160" t="s">
         <v>244</v>
       </c>
-      <c r="L32" s="146"/>
+      <c r="L32" s="161"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -15315,11 +15332,11 @@
       <c r="F33" s="58"/>
       <c r="G33" s="66"/>
       <c r="H33" s="61"/>
-      <c r="I33" s="164">
+      <c r="I33" s="145">
         <f>G33*H33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="164"/>
+      <c r="J33" s="145"/>
       <c r="K33" s="84"/>
       <c r="L33" s="134"/>
       <c r="M33" s="15"/>
@@ -15333,11 +15350,11 @@
       <c r="F34" s="58"/>
       <c r="G34" s="66"/>
       <c r="H34" s="61"/>
-      <c r="I34" s="164">
+      <c r="I34" s="145">
         <f t="shared" ref="I34:I39" si="3">G34*H34</f>
         <v>0</v>
       </c>
-      <c r="J34" s="164"/>
+      <c r="J34" s="145"/>
       <c r="K34" s="84"/>
       <c r="L34" s="134"/>
       <c r="M34" s="15"/>
@@ -15352,11 +15369,11 @@
       <c r="F35" s="58"/>
       <c r="G35" s="66"/>
       <c r="H35" s="61"/>
-      <c r="I35" s="164">
+      <c r="I35" s="145">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="164"/>
+      <c r="J35" s="145"/>
       <c r="K35" s="84"/>
       <c r="L35" s="134"/>
       <c r="M35" s="15" t="s">
@@ -15372,11 +15389,11 @@
       <c r="F36" s="58"/>
       <c r="G36" s="66"/>
       <c r="H36" s="61"/>
-      <c r="I36" s="164">
+      <c r="I36" s="145">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="164"/>
+      <c r="J36" s="145"/>
       <c r="K36" s="84"/>
       <c r="L36" s="134"/>
       <c r="M36" s="15"/>
@@ -15390,11 +15407,11 @@
       <c r="F37" s="58"/>
       <c r="G37" s="66"/>
       <c r="H37" s="61"/>
-      <c r="I37" s="164">
+      <c r="I37" s="145">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="164"/>
+      <c r="J37" s="145"/>
       <c r="K37" s="84"/>
       <c r="L37" s="134"/>
       <c r="M37" s="15"/>
@@ -15408,11 +15425,11 @@
       <c r="F38" s="58"/>
       <c r="G38" s="66"/>
       <c r="H38" s="61"/>
-      <c r="I38" s="164">
+      <c r="I38" s="145">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="164"/>
+      <c r="J38" s="145"/>
       <c r="K38" s="84"/>
       <c r="L38" s="134"/>
       <c r="M38" s="15"/>
@@ -15426,11 +15443,11 @@
       <c r="F39" s="58"/>
       <c r="G39" s="66"/>
       <c r="H39" s="61"/>
-      <c r="I39" s="164">
+      <c r="I39" s="145">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="164"/>
+      <c r="J39" s="145"/>
       <c r="K39" s="84"/>
       <c r="L39" s="134"/>
       <c r="M39" s="15"/>
@@ -15449,11 +15466,11 @@
         <v>0</v>
       </c>
       <c r="H40" s="51"/>
-      <c r="I40" s="171">
+      <c r="I40" s="146">
         <f>SUM(I33:I39)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="171"/>
+      <c r="J40" s="146"/>
       <c r="K40" s="51" t="s">
         <v>174</v>
       </c>
@@ -15474,8 +15491,8 @@
       <c r="F41" s="15"/>
       <c r="G41" s="57"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="172"/>
-      <c r="J41" s="172"/>
+      <c r="I41" s="147"/>
+      <c r="J41" s="147"/>
       <c r="K41" s="82" t="s">
         <v>175</v>
       </c>
@@ -15491,10 +15508,10 @@
       <c r="L42" s="40"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="173" t="s">
+      <c r="A43" s="148" t="s">
         <v>286</v>
       </c>
-      <c r="B43" s="173"/>
+      <c r="B43" s="148"/>
       <c r="C43" s="58"/>
       <c r="D43" s="15"/>
       <c r="E43" s="129" t="e">
@@ -15514,10 +15531,10 @@
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="173" t="s">
+      <c r="A44" s="148" t="s">
         <v>286</v>
       </c>
-      <c r="B44" s="173"/>
+      <c r="B44" s="148"/>
       <c r="C44" s="58"/>
       <c r="D44" s="15"/>
       <c r="E44" s="129" t="e">
@@ -15552,11 +15569,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="G15:H15"/>
@@ -15568,15 +15589,11 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <conditionalFormatting sqref="J1:K1">
     <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
@@ -15662,7 +15679,7 @@
       <c r="M1" s="185"/>
       <c r="N1" s="181" t="str">
         <f ca="1">DATEDIF(T1,TODAY(),"y")&amp;" year, "&amp;DATEDIF(T1,TODAY(),"ym")&amp;" months, "&amp;TODAY()-DATE(YEAR(TODAY()),MONTH(TODAY()),1)&amp;" days"</f>
-        <v>3 year, 1 months, 17 days</v>
+        <v>3 year, 1 months, 27 days</v>
       </c>
       <c r="O1" s="182"/>
       <c r="P1" s="182"/>
@@ -16110,7 +16127,7 @@
       </c>
       <c r="D14" s="95">
         <f t="shared" ref="D14" si="5">IF(F14="","",E14-F14)</f>
-        <v>-281000</v>
+        <v>-298953</v>
       </c>
       <c r="E14" s="88">
         <f>'Term-13'!$L$2</f>
@@ -16118,7 +16135,7 @@
       </c>
       <c r="F14" s="88">
         <f>'Term-13'!$D$2</f>
-        <v>281000</v>
+        <v>298953</v>
       </c>
       <c r="G14" s="140">
         <f>MIN('Term-13'!G6:G14)</f>
@@ -16260,7 +16277,7 @@
       <c r="C25" s="180"/>
       <c r="D25" s="9">
         <f>SUM(D2:D24)</f>
-        <v>3920593</v>
+        <v>3902640</v>
       </c>
       <c r="E25" s="88">
         <f>SUM(E2:E24)</f>
@@ -16268,7 +16285,7 @@
       </c>
       <c r="F25" s="88">
         <f>SUM(F2:F24)</f>
-        <v>15689477</v>
+        <v>15707430</v>
       </c>
       <c r="G25" s="140"/>
       <c r="H25" s="88"/>
@@ -16353,7 +16370,7 @@
       </c>
       <c r="D32" s="88">
         <f>SUM(D12:D15)</f>
-        <v>-140346.5</v>
+        <v>-158299.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -16387,7 +16404,7 @@
       </c>
       <c r="D35" s="9">
         <f>SUM(D29:D34)</f>
-        <v>3920593</v>
+        <v>3902640</v>
       </c>
     </row>
   </sheetData>
@@ -16636,28 +16653,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="43"/>
-      <c r="B1" s="147" t="s">
+      <c r="B1" s="162" t="s">
         <v>264</v>
       </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="164"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="150">
+      <c r="H1" s="152">
         <v>45163</v>
       </c>
-      <c r="I1" s="151"/>
+      <c r="I1" s="153"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="152">
+      <c r="K1" s="165">
         <f>M2-E2</f>
         <v>-218110</v>
       </c>
-      <c r="L1" s="153"/>
+      <c r="L1" s="166"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -16666,8 +16683,8 @@
         <f>SUM(A5:A30)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="154"/>
-      <c r="C2" s="155"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="168"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -16679,10 +16696,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="156" t="s">
+      <c r="H2" s="154" t="s">
         <v>351</v>
       </c>
-      <c r="I2" s="157"/>
+      <c r="I2" s="169"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -16695,25 +16712,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="158" t="s">
+      <c r="B3" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="159"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="162" t="s">
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="158" t="s">
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="170" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="159"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="161"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="172"/>
+      <c r="M3" s="172"/>
+      <c r="N3" s="173"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -16960,11 +16977,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="165" t="s">
+      <c r="G12" s="149" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="166"/>
-      <c r="I12" s="167"/>
+      <c r="H12" s="150"/>
+      <c r="I12" s="151"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -16985,10 +17002,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="150">
+      <c r="H13" s="152">
         <v>45163</v>
       </c>
-      <c r="I13" s="151"/>
+      <c r="I13" s="153"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17009,10 +17026,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="156" t="s">
+      <c r="H14" s="154" t="s">
         <v>351</v>
       </c>
-      <c r="I14" s="157"/>
+      <c r="I14" s="169"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17030,11 +17047,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="162" t="s">
+      <c r="G15" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="163"/>
-      <c r="I15" s="163"/>
+      <c r="H15" s="157"/>
+      <c r="I15" s="157"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -17395,12 +17412,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -17409,6 +17420,12 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D32">
     <cfRule type="duplicateValues" dxfId="62" priority="28"/>
@@ -17465,28 +17482,28 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="43"/>
-      <c r="B1" s="147" t="s">
+      <c r="B1" s="162" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="164"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="150">
+      <c r="H1" s="152">
         <v>45163</v>
       </c>
-      <c r="I1" s="151"/>
+      <c r="I1" s="153"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="152">
+      <c r="K1" s="165">
         <f>M2-E2</f>
         <v>-470000</v>
       </c>
-      <c r="L1" s="153"/>
+      <c r="L1" s="166"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
@@ -17495,8 +17512,8 @@
         <f>SUM(A5:A30)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="154"/>
-      <c r="C2" s="155"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="168"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -17508,10 +17525,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="156" t="s">
+      <c r="H2" s="154" t="s">
         <v>352</v>
       </c>
-      <c r="I2" s="157"/>
+      <c r="I2" s="169"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -17524,25 +17541,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="158" t="s">
+      <c r="B3" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="159"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="162" t="s">
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="158" t="s">
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="170" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="159"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="161"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="172"/>
+      <c r="M3" s="172"/>
+      <c r="N3" s="173"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -17785,11 +17802,11 @@
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
       <c r="F12" s="22"/>
-      <c r="G12" s="165" t="s">
+      <c r="G12" s="149" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="166"/>
-      <c r="I12" s="167"/>
+      <c r="H12" s="150"/>
+      <c r="I12" s="151"/>
       <c r="J12" s="21">
         <v>8</v>
       </c>
@@ -17810,10 +17827,10 @@
       <c r="G13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="150">
+      <c r="H13" s="152">
         <v>45163</v>
       </c>
-      <c r="I13" s="151"/>
+      <c r="I13" s="153"/>
       <c r="J13" s="21">
         <v>9</v>
       </c>
@@ -17834,10 +17851,10 @@
       <c r="G14" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="156" t="s">
+      <c r="H14" s="154" t="s">
         <v>352</v>
       </c>
-      <c r="I14" s="157"/>
+      <c r="I14" s="169"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -17855,11 +17872,11 @@
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="162" t="s">
+      <c r="G15" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="163"/>
-      <c r="I15" s="163"/>
+      <c r="H15" s="157"/>
+      <c r="I15" s="157"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -18290,35 +18307,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="43"/>
-      <c r="B1" s="147" t="s">
+      <c r="B1" s="162" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="164"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="150">
+      <c r="H1" s="152">
         <v>45345</v>
       </c>
-      <c r="I1" s="151"/>
+      <c r="I1" s="153"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="152">
+      <c r="K1" s="165">
         <f>M2-E2</f>
         <v>1098545</v>
       </c>
-      <c r="L1" s="153"/>
+      <c r="L1" s="166"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="42"/>
-      <c r="B2" s="154"/>
-      <c r="C2" s="155"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="168"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -18330,10 +18347,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="156" t="s">
+      <c r="H2" s="154" t="s">
         <v>340</v>
       </c>
-      <c r="I2" s="157"/>
+      <c r="I2" s="169"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -18346,25 +18363,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="158" t="s">
+      <c r="B3" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="159"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="162" t="s">
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="158" t="s">
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="170" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="159"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="161"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="172"/>
+      <c r="M3" s="172"/>
+      <c r="N3" s="173"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -18706,11 +18723,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="68"/>
-      <c r="G14" s="165" t="s">
+      <c r="G14" s="149" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="166"/>
-      <c r="I14" s="167"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="151"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -18731,10 +18748,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="150">
+      <c r="H15" s="152">
         <v>45345</v>
       </c>
-      <c r="I15" s="151"/>
+      <c r="I15" s="153"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -18776,11 +18793,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="162" t="s">
+      <c r="G17" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="163"/>
-      <c r="I17" s="169"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="158"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -19379,11 +19396,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="B3:F3"/>
@@ -19391,6 +19403,11 @@
     <mergeCell ref="J3:N3"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="G14:I14"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="48" priority="4" operator="greaterThan">
@@ -19438,35 +19455,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="43"/>
-      <c r="B1" s="147" t="s">
+      <c r="B1" s="162" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="164"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="150">
+      <c r="H1" s="152">
         <v>45477</v>
       </c>
-      <c r="I1" s="151"/>
+      <c r="I1" s="153"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="152">
+      <c r="K1" s="165">
         <f>M2-E2</f>
         <v>391120</v>
       </c>
-      <c r="L1" s="153"/>
+      <c r="L1" s="166"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="42"/>
-      <c r="B2" s="154"/>
-      <c r="C2" s="155"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="168"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -19478,10 +19495,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="156" t="s">
+      <c r="H2" s="154" t="s">
         <v>341</v>
       </c>
-      <c r="I2" s="157"/>
+      <c r="I2" s="169"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -19494,25 +19511,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="158" t="s">
+      <c r="B3" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="159"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="162" t="s">
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="158" t="s">
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="170" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="159"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="161"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="172"/>
+      <c r="M3" s="172"/>
+      <c r="N3" s="173"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -19846,11 +19863,11 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="68"/>
-      <c r="G14" s="165" t="s">
+      <c r="G14" s="149" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="166"/>
-      <c r="I14" s="167"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="151"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -19873,10 +19890,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="150">
+      <c r="H15" s="152">
         <v>45477</v>
       </c>
-      <c r="I15" s="151"/>
+      <c r="I15" s="153"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -19922,11 +19939,11 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="162" t="s">
+      <c r="G17" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="163"/>
-      <c r="I17" s="169"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="158"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -20627,35 +20644,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="43"/>
-      <c r="B1" s="147" t="s">
+      <c r="B1" s="162" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="164"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="150">
+      <c r="H1" s="152">
         <v>45548</v>
       </c>
-      <c r="I1" s="151"/>
+      <c r="I1" s="153"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="152">
+      <c r="K1" s="165">
         <f>M2-E2</f>
         <v>1002304</v>
       </c>
-      <c r="L1" s="153"/>
+      <c r="L1" s="166"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="42"/>
-      <c r="B2" s="154"/>
-      <c r="C2" s="155"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="168"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -20667,10 +20684,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="156" t="s">
+      <c r="H2" s="154" t="s">
         <v>289</v>
       </c>
-      <c r="I2" s="157"/>
+      <c r="I2" s="169"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -20683,25 +20700,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="158" t="s">
+      <c r="B3" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="159"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="162" t="s">
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="158" t="s">
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="170" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="159"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="161"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="172"/>
+      <c r="M3" s="172"/>
+      <c r="N3" s="173"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -21075,11 +21092,11 @@
         <v>17400</v>
       </c>
       <c r="F14" s="68"/>
-      <c r="G14" s="165" t="s">
+      <c r="G14" s="149" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="166"/>
-      <c r="I14" s="167"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="151"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -21106,10 +21123,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="150">
+      <c r="H15" s="152">
         <v>45561</v>
       </c>
-      <c r="I15" s="151"/>
+      <c r="I15" s="153"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -21136,10 +21153,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="156" t="s">
+      <c r="H16" s="154" t="s">
         <v>289</v>
       </c>
-      <c r="I16" s="168"/>
+      <c r="I16" s="155"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -21163,11 +21180,11 @@
         <v>45000</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="162" t="s">
+      <c r="G17" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="163"/>
-      <c r="I17" s="169"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="158"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -21798,11 +21815,11 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="173" t="s">
+      <c r="A45" s="148" t="s">
         <v>194</v>
       </c>
-      <c r="B45" s="173"/>
-      <c r="C45" s="173"/>
+      <c r="B45" s="148"/>
+      <c r="C45" s="148"/>
       <c r="D45" s="61"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -21919,6 +21936,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A45:C45"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:N3"/>
@@ -21927,11 +21949,6 @@
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="A45:C45"/>
   </mergeCells>
   <conditionalFormatting sqref="K1:L1">
     <cfRule type="cellIs" dxfId="40" priority="1" operator="greaterThan">
@@ -21980,35 +21997,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="43"/>
-      <c r="B1" s="147" t="s">
+      <c r="B1" s="162" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="164"/>
       <c r="G1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="150">
+      <c r="H1" s="152">
         <v>45631</v>
       </c>
-      <c r="I1" s="151"/>
+      <c r="I1" s="153"/>
       <c r="J1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="152">
+      <c r="K1" s="165">
         <f>M2-E2</f>
         <v>528979</v>
       </c>
-      <c r="L1" s="153"/>
+      <c r="L1" s="166"/>
       <c r="M1" s="18"/>
       <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="42"/>
-      <c r="B2" s="154"/>
-      <c r="C2" s="155"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="168"/>
       <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
@@ -22020,10 +22037,10 @@
       <c r="G2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="156" t="s">
+      <c r="H2" s="154" t="s">
         <v>343</v>
       </c>
-      <c r="I2" s="157"/>
+      <c r="I2" s="169"/>
       <c r="J2" s="38"/>
       <c r="K2" s="10"/>
       <c r="L2" s="11" t="s">
@@ -22036,25 +22053,25 @@
       <c r="N2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="158" t="s">
+      <c r="B3" s="170" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="159"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="162" t="s">
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="158" t="s">
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="170" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="159"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="161"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="172"/>
+      <c r="M3" s="172"/>
+      <c r="N3" s="173"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -22394,11 +22411,11 @@
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
       <c r="F14" s="68"/>
-      <c r="G14" s="165" t="s">
+      <c r="G14" s="149" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="166"/>
-      <c r="I14" s="167"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="151"/>
       <c r="J14" s="21">
         <v>10</v>
       </c>
@@ -22419,10 +22436,10 @@
       <c r="G15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="150">
+      <c r="H15" s="152">
         <v>45653</v>
       </c>
-      <c r="I15" s="151"/>
+      <c r="I15" s="153"/>
       <c r="J15" s="21">
         <v>11</v>
       </c>
@@ -22443,10 +22460,10 @@
       <c r="G16" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="156" t="s">
+      <c r="H16" s="154" t="s">
         <v>344</v>
       </c>
-      <c r="I16" s="168"/>
+      <c r="I16" s="155"/>
       <c r="J16" s="21">
         <v>12</v>
       </c>
@@ -22464,11 +22481,11 @@
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
       <c r="F17" s="22"/>
-      <c r="G17" s="162" t="s">
+      <c r="G17" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="163"/>
-      <c r="I17" s="169"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="158"/>
       <c r="J17" s="21">
         <v>13</v>
       </c>
@@ -22814,14 +22831,14 @@
       <c r="H32" s="92" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="170" t="s">
+      <c r="I32" s="159" t="s">
         <v>148</v>
       </c>
-      <c r="J32" s="170"/>
-      <c r="K32" s="145" t="s">
+      <c r="J32" s="159"/>
+      <c r="K32" s="160" t="s">
         <v>244</v>
       </c>
-      <c r="L32" s="145"/>
+      <c r="L32" s="160"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D33" s="15" t="s">
@@ -22840,11 +22857,11 @@
       <c r="H33" s="61">
         <v>245</v>
       </c>
-      <c r="I33" s="164">
+      <c r="I33" s="145">
         <f>G33*H33</f>
         <v